--- a/testdata/DirectGrn.xlsx
+++ b/testdata/DirectGrn.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8400" tabRatio="703" firstSheet="9" activeTab="9"/>
+    <workbookView windowWidth="21600" windowHeight="9600" tabRatio="703" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="DGSUomWI" sheetId="6" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2766" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2784" uniqueCount="235">
   <si>
     <t>Purchase Order &amp; GRN</t>
   </si>
@@ -695,6 +695,60 @@
   </si>
   <si>
     <t>GWL_Item_FP_Pl_Dissimilar_03</t>
+  </si>
+  <si>
+    <t>662</t>
+  </si>
+  <si>
+    <t>3764.23791</t>
+  </si>
+  <si>
+    <t>274</t>
+  </si>
+  <si>
+    <t>2881.34244</t>
+  </si>
+  <si>
+    <t>730</t>
+  </si>
+  <si>
+    <t>1539.19605</t>
+  </si>
+  <si>
+    <t>667</t>
+  </si>
+  <si>
+    <t>3815.37799</t>
+  </si>
+  <si>
+    <t>278</t>
+  </si>
+  <si>
+    <t>2940.31881</t>
+  </si>
+  <si>
+    <t>750</t>
+  </si>
+  <si>
+    <t>1596.29749</t>
+  </si>
+  <si>
+    <t>672</t>
+  </si>
+  <si>
+    <t>3865.75706</t>
+  </si>
+  <si>
+    <t>282</t>
+  </si>
+  <si>
+    <t>2997.62209</t>
+  </si>
+  <si>
+    <t>770</t>
+  </si>
+  <si>
+    <t>1650.43262</t>
   </si>
 </sst>
 </file>
@@ -1517,7 +1571,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2164,13 +2218,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ20"/>
-  <sheetFormatPr defaultColWidth="8.85185185185185" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.84761904761905" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="13" max="13" width="9.13888888888889" customWidth="1"/>
-    <col min="14" max="14" width="13.8518518518519" customWidth="1"/>
-    <col min="64" max="64" width="11" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="28.0"/>
+    <col min="3" max="3" customWidth="true" width="23.0"/>
+    <col min="13" max="13" customWidth="true" width="9.14285714285714"/>
+    <col min="14" max="14" customWidth="true" width="13.847619047619"/>
+    <col min="29" max="29" width="9.28571428571429"/>
+    <col min="35" max="35" width="11.4285714285714"/>
+    <col min="52" max="52" width="13.2857142857143"/>
+    <col min="64" max="64" customWidth="true" width="11.0"/>
+    <col min="67" max="67" width="12.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -2246,7 +2304,7 @@
       <c r="BP1" s="40"/>
       <c r="BQ1" s="40"/>
     </row>
-    <row r="2" ht="15.15" spans="1:69">
+    <row r="2" ht="15.75" spans="1:69">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -2341,7 +2399,7 @@
       <c r="BP2" s="40"/>
       <c r="BQ2" s="40"/>
     </row>
-    <row r="3" ht="59.1" spans="1:69">
+    <row r="3" ht="61.5" spans="1:69">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
@@ -2550,7 +2608,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.15" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="7">
         <v>1</v>
       </c>
@@ -2569,14 +2627,14 @@
       <c r="F4" s="8">
         <v>5</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" t="s" s="0">
         <v>78</v>
       </c>
       <c r="H4" s="8">
         <f>F4*G4</f>
         <v>750</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" t="s" s="0">
         <v>79</v>
       </c>
       <c r="J4" s="8">
@@ -2714,11 +2772,11 @@
       <c r="AT4" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU4" t="s">
-        <v>81</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>82</v>
+      <c r="AU4" t="s" s="0">
+        <v>229</v>
+      </c>
+      <c r="AV4" t="s" s="0">
+        <v>230</v>
       </c>
       <c r="AW4" s="39">
         <f>AM4</f>
@@ -2732,9 +2790,9 @@
         <f>AU4+AW4</f>
         <v>15</v>
       </c>
-      <c r="AZ4" s="43">
-        <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),3)</f>
-        <v>3578.592</v>
+      <c r="AZ4" s="39">
+        <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),5)</f>
+        <v>3670.79889</v>
       </c>
       <c r="BA4" s="44"/>
       <c r="BB4" s="44" t="s">
@@ -2758,15 +2816,15 @@
       <c r="BL4" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>89</v>
       </c>
       <c r="BO4" s="39">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
-        <v>327.72424</v>
+        <v>333.14817</v>
       </c>
       <c r="BP4" s="48">
         <f>ROUND(BN4+AW4,3)</f>
@@ -2776,7 +2834,7 @@
         <v>123562</v>
       </c>
     </row>
-    <row r="5" ht="15.15" spans="1:69">
+    <row r="5" ht="15.75" spans="1:69">
       <c r="A5" s="7">
         <v>1</v>
       </c>
@@ -2795,14 +2853,14 @@
       <c r="F5" s="8">
         <v>4</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" t="s" s="0">
         <v>92</v>
       </c>
       <c r="H5" s="8">
         <f>F5*G5</f>
         <v>400</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" t="s" s="0">
         <v>93</v>
       </c>
       <c r="J5" s="8">
@@ -2850,26 +2908,26 @@
         <v>18</v>
       </c>
       <c r="V5" s="8">
-        <f>IF(OR(DGSUomWI!$C$2=1,DGSUomWI!$C$2=4),ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF(OR($C$2=1,$C$2=4),ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="W5" s="8">
-        <f>IF(DGSUomWI!$C$2=1,ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF($C$2=1,ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="X5" s="8">
-        <f>IF(DGSUomWI!$C$2=2,ROUND(((S5*U5)/100),2),0)</f>
+        <f>IF($C$2=2,ROUND(((S5*U5)/100),2),0)</f>
         <v>0</v>
       </c>
       <c r="Y5" s="8">
-        <f>IF(DGSUomWI!$C$2=4,ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF($C$2=4,ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="Z5" s="8">
         <v>0</v>
       </c>
       <c r="AA5" s="8">
-        <f>IF(DGSUomWI!$C3=3,0,(S5*Z5)/100)</f>
+        <f>IF($C3=3,0,(S5*Z5)/100)</f>
         <v>0</v>
       </c>
       <c r="AB5" s="8">
@@ -2877,35 +2935,35 @@
         <v>0</v>
       </c>
       <c r="AC5" s="8">
-        <f>IF(DGSUomWI!$V3=1,S5+AB5,S5)</f>
+        <f>IF($V3=1,S5+AB5,S5)</f>
         <v>328.47</v>
       </c>
       <c r="AD5" s="26">
         <v>120</v>
       </c>
       <c r="AE5" s="26">
-        <f>IF(DGSUomWI!$P$2=1,(S5/DGSUomWI!$S$7)*DGSUomWI!$E$18,AD5/DGSUomWI!$AD$7*DGSUomWI!$E$18)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$18,AD5/$AD$7*$E$18)</f>
         <v>0</v>
       </c>
       <c r="AF5" s="26"/>
       <c r="AG5" s="26">
-        <f>IF(DGSUomWI!$P$2=1,(S5/DGSUomWI!$S$7)*DGSUomWI!$E$20,AD5/DGSUomWI!$AD$7*DGSUomWI!$E$20)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$20,AD5/$AD$7*$E$20)</f>
         <v>0</v>
       </c>
       <c r="AH5" s="26">
-        <f>IF(DGSUomWI!$P$2=1,(S5/DGSUomWI!$S$7)*DGSUomWI!$E$21,AD5/DGSUomWI!$AD$7*DGSUomWI!$E$21)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$21,AD5/$AD$7*$E$21)</f>
         <v>0</v>
       </c>
       <c r="AI5" s="26">
-        <f>S5*DGSUomWI!$M$2</f>
+        <f>S5*$M$2</f>
         <v>27919.95</v>
       </c>
       <c r="AJ5" s="26">
-        <f>IF(DGSUomWI!$C$2=3,0,AG5+AH5)</f>
+        <f>IF($C$2=3,0,AG5+AH5)</f>
         <v>0</v>
       </c>
       <c r="AK5" s="26">
-        <f>IF(DGSUomWI!$C$2=3,AE5+AG5+AH5,0)</f>
+        <f>IF($C$2=3,AE5+AG5+AH5,0)</f>
         <v>0</v>
       </c>
       <c r="AL5" s="34">
@@ -2940,11 +2998,11 @@
       <c r="AT5" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU5" t="s">
-        <v>94</v>
-      </c>
-      <c r="AV5" t="s">
-        <v>95</v>
+      <c r="AU5" t="s" s="0">
+        <v>231</v>
+      </c>
+      <c r="AV5" t="s" s="0">
+        <v>232</v>
       </c>
       <c r="AW5" s="39">
         <f>AM5</f>
@@ -2958,9 +3016,9 @@
         <f>AU5+AW5</f>
         <v>12</v>
       </c>
-      <c r="AZ5" s="42">
-        <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),2)</f>
-        <v>1972.62</v>
+      <c r="AZ5" s="39">
+        <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),5)</f>
+        <v>2076.94724</v>
       </c>
       <c r="BA5" s="44"/>
       <c r="BB5" s="44" t="s">
@@ -2984,15 +3042,15 @@
       <c r="BL5" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BM5" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BN5" t="s" s="0">
         <v>97</v>
       </c>
       <c r="BO5" s="39">
         <f>ROUND((((AW5*AZ5)+(BN5*BM5))/(AW5+BN5)),5)</f>
-        <v>200.27625</v>
+        <v>206.7967</v>
       </c>
       <c r="BP5" s="48">
         <f>ROUND(BN5+AW5,3)</f>
@@ -3002,7 +3060,7 @@
         <v>123562</v>
       </c>
     </row>
-    <row r="6" ht="15.15" spans="1:69">
+    <row r="6" ht="15.75" spans="1:69">
       <c r="A6" s="7">
         <v>1</v>
       </c>
@@ -3021,14 +3079,14 @@
       <c r="F6" s="8">
         <v>20</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H6" s="8">
         <f>F6*G6</f>
         <v>1000</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" t="s" s="0">
         <v>101</v>
       </c>
       <c r="J6" s="8">
@@ -3076,26 +3134,26 @@
         <v>18</v>
       </c>
       <c r="V6" s="8">
-        <f>IF(OR(DGSUomWI!$C$2=1,DGSUomWI!$C$2=4),ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF(OR($C$2=1,$C$2=4),ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="W6" s="8">
-        <f>IF(DGSUomWI!$C$2=1,ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF($C$2=1,ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="X6" s="8">
-        <f>IF(DGSUomWI!$C$2=2,ROUND(((S6*U6)/100),2),0)</f>
+        <f>IF($C$2=2,ROUND(((S6*U6)/100),2),0)</f>
         <v>0</v>
       </c>
       <c r="Y6" s="8">
-        <f>IF(DGSUomWI!$C$2=4,ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF($C$2=4,ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="Z6" s="8">
         <v>0</v>
       </c>
       <c r="AA6" s="8">
-        <f>IF(DGSUomWI!$C4=3,0,(S6*Z6)/100)</f>
+        <f>IF($C4=3,0,(S6*Z6)/100)</f>
         <v>0</v>
       </c>
       <c r="AB6" s="8">
@@ -3103,35 +3161,35 @@
         <v>0</v>
       </c>
       <c r="AC6" s="8">
-        <f>IF(DGSUomWI!$V4=1,S6+AB6,S6)</f>
+        <f>IF($V4=1,S6+AB6,S6)</f>
         <v>866.02</v>
       </c>
       <c r="AD6" s="26">
         <v>120</v>
       </c>
       <c r="AE6" s="26">
-        <f>IF(DGSUomWI!$P$2=1,(S6/DGSUomWI!$S$7)*DGSUomWI!$E$18,AD6/DGSUomWI!$AD$7*DGSUomWI!$E$18)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$18,AD6/$AD$7*$E$18)</f>
         <v>0</v>
       </c>
       <c r="AF6" s="26"/>
       <c r="AG6" s="26">
-        <f>IF(DGSUomWI!$P$2=1,(S6/DGSUomWI!$S$7)*DGSUomWI!$E$20,AD6/DGSUomWI!$AD$7*DGSUomWI!$E$20)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$20,AD6/$AD$7*$E$20)</f>
         <v>0</v>
       </c>
       <c r="AH6" s="26">
-        <f>IF(DGSUomWI!$P$2=1,(S6/DGSUomWI!$S$7)*DGSUomWI!$E$21,AD6/DGSUomWI!$AD$7*DGSUomWI!$E$21)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$21,AD6/$AD$7*$E$21)</f>
         <v>0</v>
       </c>
       <c r="AI6" s="26">
-        <f>S6*DGSUomWI!$M$2</f>
+        <f>S6*$M$2</f>
         <v>73611.7</v>
       </c>
       <c r="AJ6" s="26">
-        <f>IF(DGSUomWI!$C$2=3,0,AG6+AH6)</f>
+        <f>IF($C$2=3,0,AG6+AH6)</f>
         <v>0</v>
       </c>
       <c r="AK6" s="26">
-        <f>IF(DGSUomWI!$C$2=3,AE6+AG6+AH6,0)</f>
+        <f>IF($C$2=3,AE6+AG6+AH6,0)</f>
         <v>0</v>
       </c>
       <c r="AL6" s="34">
@@ -3166,11 +3224,11 @@
       <c r="AT6" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU6" t="s">
-        <v>102</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>103</v>
+      <c r="AU6" t="s" s="0">
+        <v>233</v>
+      </c>
+      <c r="AV6" t="s" s="0">
+        <v>234</v>
       </c>
       <c r="AW6" s="39">
         <f>AM6</f>
@@ -3185,8 +3243,8 @@
         <v>50</v>
       </c>
       <c r="AZ6" s="39">
-        <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),1)</f>
-        <v>1095.1</v>
+        <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),5)</f>
+        <v>1198.5474</v>
       </c>
       <c r="BA6" s="44"/>
       <c r="BB6" s="44" t="s">
@@ -3210,15 +3268,15 @@
       <c r="BL6" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM6" t="s">
+      <c r="BM6" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="BN6" t="s">
+      <c r="BN6" t="s" s="0">
         <v>105</v>
       </c>
       <c r="BO6" s="39">
         <f>ROUND((((AW6*AZ6)+(BN6*BM6))/(AW6+BN6)),5)</f>
-        <v>109.0375</v>
+        <v>115.50296</v>
       </c>
       <c r="BP6" s="48">
         <f>ROUND(BN6+AW6,3)</f>
@@ -3228,7 +3286,7 @@
         <v>123562</v>
       </c>
     </row>
-    <row r="7" ht="15.15" spans="1:69">
+    <row r="7" ht="15.75" spans="1:69">
       <c r="A7" s="9"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -3346,7 +3404,7 @@
       <c r="BP7" s="40"/>
       <c r="BQ7" s="40"/>
     </row>
-    <row r="8" ht="15.15" spans="1:69">
+    <row r="8" ht="15.75" spans="1:69">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -3417,7 +3475,7 @@
       <c r="BP8" s="40"/>
       <c r="BQ8" s="40"/>
     </row>
-    <row r="9" ht="15.15" spans="1:69">
+    <row r="9" ht="15.75" spans="1:69">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -3499,7 +3557,7 @@
       <c r="BP9" s="40"/>
       <c r="BQ9" s="40"/>
     </row>
-    <row r="10" ht="15.15" spans="1:69">
+    <row r="10" ht="15.75" spans="1:69">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -3587,7 +3645,7 @@
       <c r="BP10" s="40"/>
       <c r="BQ10" s="40"/>
     </row>
-    <row r="11" ht="15.15" spans="1:69">
+    <row r="11" ht="15.75" spans="1:69">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -3671,7 +3729,7 @@
       <c r="BP11" s="40"/>
       <c r="BQ11" s="40"/>
     </row>
-    <row r="12" ht="15.15" spans="1:69">
+    <row r="12" ht="15.75" spans="1:69">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -3755,7 +3813,7 @@
       <c r="BP12" s="40"/>
       <c r="BQ12" s="40"/>
     </row>
-    <row r="13" ht="15.15" spans="1:69">
+    <row r="13" ht="15.75" spans="1:69">
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -4393,13 +4451,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ20"/>
-  <sheetFormatPr defaultColWidth="8.85185185185185" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.84761904761905" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="27.1388888888889" customWidth="1"/>
-    <col min="13" max="13" width="9.13888888888889" customWidth="1"/>
-    <col min="14" max="14" width="13.8518518518519" customWidth="1"/>
-    <col min="64" max="64" width="11" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="28.0"/>
+    <col min="3" max="3" customWidth="true" width="27.1428571428571"/>
+    <col min="13" max="13" customWidth="true" width="9.14285714285714"/>
+    <col min="14" max="14" customWidth="true" width="13.847619047619"/>
+    <col min="64" max="64" customWidth="true" width="11.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -4475,7 +4533,7 @@
       <c r="BP1" s="40"/>
       <c r="BQ1" s="40"/>
     </row>
-    <row r="2" ht="15.15" spans="1:69">
+    <row r="2" ht="15.75" spans="1:69">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -4570,7 +4628,7 @@
       <c r="BP2" s="40"/>
       <c r="BQ2" s="40"/>
     </row>
-    <row r="3" ht="59.1" spans="1:69">
+    <row r="3" ht="61.5" spans="1:69">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
@@ -4779,7 +4837,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.15" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="7">
         <v>1</v>
       </c>
@@ -4798,14 +4856,14 @@
       <c r="F4" s="8">
         <v>5</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="0">
         <v>150</v>
       </c>
       <c r="H4" s="8">
         <f t="shared" ref="H4:H6" si="0">F4*G4</f>
         <v>750</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="0">
         <v>5</v>
       </c>
       <c r="J4" s="8">
@@ -4943,10 +5001,10 @@
       <c r="AT4" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AU4" t="s" s="0">
         <v>81</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AV4" t="s" s="0">
         <v>82</v>
       </c>
       <c r="AW4" s="39">
@@ -4987,10 +5045,10 @@
       <c r="BL4" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>89</v>
       </c>
       <c r="BO4" s="39">
@@ -5005,7 +5063,7 @@
         <v>123562</v>
       </c>
     </row>
-    <row r="5" spans="1:69">
+    <row r="5" ht="15.75" spans="1:69">
       <c r="A5" s="7">
         <v>1</v>
       </c>
@@ -5024,14 +5082,14 @@
       <c r="F5" s="8">
         <v>4</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" t="s" s="0">
         <v>92</v>
       </c>
       <c r="H5" s="8">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" t="s" s="0">
         <v>93</v>
       </c>
       <c r="J5" s="8">
@@ -5169,10 +5227,10 @@
       <c r="AT5" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AU5" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AV5" t="s" s="0">
         <v>95</v>
       </c>
       <c r="AW5" s="39">
@@ -5213,10 +5271,10 @@
       <c r="BL5" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BM5" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BN5" t="s" s="0">
         <v>97</v>
       </c>
       <c r="BO5" s="39">
@@ -5231,7 +5289,7 @@
         <v>123562</v>
       </c>
     </row>
-    <row r="6" spans="1:69">
+    <row r="6" ht="15.75" spans="1:69">
       <c r="A6" s="7">
         <v>1</v>
       </c>
@@ -5250,14 +5308,14 @@
       <c r="F6" s="8">
         <v>20</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H6" s="8">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" t="s" s="0">
         <v>101</v>
       </c>
       <c r="J6" s="8">
@@ -5395,10 +5453,10 @@
       <c r="AT6" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AU6" t="s" s="0">
         <v>102</v>
       </c>
-      <c r="AV6" t="s">
+      <c r="AV6" t="s" s="0">
         <v>103</v>
       </c>
       <c r="AW6" s="39">
@@ -5439,10 +5497,10 @@
       <c r="BL6" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM6" t="s">
+      <c r="BM6" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="BN6" t="s">
+      <c r="BN6" t="s" s="0">
         <v>105</v>
       </c>
       <c r="BO6" s="39">
@@ -5457,7 +5515,7 @@
         <v>123562</v>
       </c>
     </row>
-    <row r="7" ht="15.15" spans="1:69">
+    <row r="7" ht="15.75" spans="1:69">
       <c r="A7" s="9"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -5575,7 +5633,7 @@
       <c r="BP7" s="40"/>
       <c r="BQ7" s="40"/>
     </row>
-    <row r="8" ht="15.15" spans="1:69">
+    <row r="8" ht="15.75" spans="1:69">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -5646,7 +5704,7 @@
       <c r="BP8" s="40"/>
       <c r="BQ8" s="40"/>
     </row>
-    <row r="9" ht="15.15" spans="1:69">
+    <row r="9" ht="15.75" spans="1:69">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -5728,7 +5786,7 @@
       <c r="BP9" s="40"/>
       <c r="BQ9" s="40"/>
     </row>
-    <row r="10" ht="15.15" spans="1:69">
+    <row r="10" ht="15.75" spans="1:69">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -5816,7 +5874,7 @@
       <c r="BP10" s="40"/>
       <c r="BQ10" s="40"/>
     </row>
-    <row r="11" ht="15.15" spans="1:69">
+    <row r="11" ht="15.75" spans="1:69">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -5900,7 +5958,7 @@
       <c r="BP11" s="40"/>
       <c r="BQ11" s="40"/>
     </row>
-    <row r="12" ht="15.15" spans="1:69">
+    <row r="12" ht="15.75" spans="1:69">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -5984,7 +6042,7 @@
       <c r="BP12" s="40"/>
       <c r="BQ12" s="40"/>
     </row>
-    <row r="13" ht="15.15" spans="1:69">
+    <row r="13" ht="15.75" spans="1:69">
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -6622,13 +6680,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ20"/>
-  <sheetFormatPr defaultColWidth="8.85185185185185" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.84761904761905" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="13" max="13" width="9.13888888888889" customWidth="1"/>
-    <col min="14" max="14" width="13.8518518518519" customWidth="1"/>
-    <col min="64" max="64" width="11" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="28.0"/>
+    <col min="3" max="3" customWidth="true" width="23.0"/>
+    <col min="13" max="13" customWidth="true" width="9.14285714285714"/>
+    <col min="14" max="14" customWidth="true" width="13.847619047619"/>
+    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
+    <col min="52" max="52" width="13.2857142857143"/>
+    <col min="64" max="64" customWidth="true" width="11.0"/>
+    <col min="67" max="67" width="12.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -6704,7 +6765,7 @@
       <c r="BP1" s="40"/>
       <c r="BQ1" s="40"/>
     </row>
-    <row r="2" ht="15.15" spans="1:69">
+    <row r="2" ht="15.75" spans="1:69">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -6799,7 +6860,7 @@
       <c r="BP2" s="40"/>
       <c r="BQ2" s="40"/>
     </row>
-    <row r="3" ht="59.1" spans="1:69">
+    <row r="3" ht="61.5" spans="1:69">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
@@ -7008,7 +7069,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.15" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="7">
         <v>1</v>
       </c>
@@ -7025,16 +7086,16 @@
         <v>77</v>
       </c>
       <c r="F4" s="8">
-        <v>5</v>
-      </c>
-      <c r="G4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H4" s="8">
         <f t="shared" ref="H4:H6" si="0">F4*G4</f>
-        <v>250</v>
-      </c>
-      <c r="I4" t="s">
+        <v>150</v>
+      </c>
+      <c r="I4" t="s" s="0">
         <v>79</v>
       </c>
       <c r="J4" s="8">
@@ -7045,35 +7106,35 @@
       </c>
       <c r="L4" s="8">
         <f t="shared" ref="L4:L6" si="1">IF(OR(I4=0,I4="0"),0,H4)</f>
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="M4" s="8">
         <f>ROUND(L4*I4%,3)</f>
-        <v>12.5</v>
+        <v>7.5</v>
       </c>
       <c r="N4" s="8">
         <f t="shared" ref="N4:N6" si="2">H4-M4</f>
-        <v>237.5</v>
+        <v>142.5</v>
       </c>
       <c r="O4" s="8">
         <f>ROUND(N4*J4%,3)</f>
-        <v>19</v>
+        <v>11.4</v>
       </c>
       <c r="P4" s="8">
         <f t="shared" ref="P4:P6" si="3">ROUND(N4-O4,2)</f>
-        <v>218.5</v>
+        <v>131.1</v>
       </c>
       <c r="Q4" s="8">
         <f t="shared" ref="Q4:Q6" si="4">ROUND(P4*K4%,2)</f>
-        <v>10.93</v>
+        <v>6.56</v>
       </c>
       <c r="R4" s="26">
         <f>ROUND(M4+O4+Q4,3)</f>
-        <v>42.43</v>
+        <v>25.46</v>
       </c>
       <c r="S4" s="26">
         <f t="shared" ref="S4:S6" si="5">(H4-R4)</f>
-        <v>207.57</v>
+        <v>124.54</v>
       </c>
       <c r="T4" s="8">
         <v>88363222</v>
@@ -7110,7 +7171,7 @@
       </c>
       <c r="AC4" s="31">
         <f>IF($V2=1,S4+AB4,S4)</f>
-        <v>207.57</v>
+        <v>124.54</v>
       </c>
       <c r="AD4" s="26">
         <v>120</v>
@@ -7130,7 +7191,7 @@
       </c>
       <c r="AI4" s="26">
         <f>S4*$M2</f>
-        <v>17643.45</v>
+        <v>10585.9</v>
       </c>
       <c r="AJ4" s="26">
         <f>IF($C$2=3,0,AG4+AH4)</f>
@@ -7145,11 +7206,11 @@
       </c>
       <c r="AM4" s="26">
         <f t="shared" ref="AM4:AM6" si="7">F4/AL4</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AN4" s="26">
         <f t="shared" ref="AN4:AN6" si="8">ROUND(AI4/AM4,5)</f>
-        <v>3528.69</v>
+        <v>3528.63333</v>
       </c>
       <c r="AO4" s="26">
         <f t="shared" ref="AO4:AO6" si="9">AJ4/AM4</f>
@@ -7164,7 +7225,7 @@
       </c>
       <c r="AR4" s="26">
         <f t="shared" ref="AR4:AR6" si="11">ROUND(AN4+AO4+AP4,5)</f>
-        <v>3528.69</v>
+        <v>3528.63333</v>
       </c>
       <c r="AS4" s="38" t="s">
         <v>80</v>
@@ -7172,27 +7233,27 @@
       <c r="AT4" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AU4" t="s" s="0">
         <v>168</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AV4" t="s" s="0">
         <v>169</v>
       </c>
       <c r="AW4" s="39">
         <f t="shared" ref="AW4:AW6" si="12">AM4</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AX4" s="42">
         <f t="shared" ref="AX4:AX6" si="13">AR4</f>
-        <v>3528.69</v>
+        <v>3528.63333</v>
       </c>
       <c r="AY4" s="39">
         <f t="shared" ref="AY4:AY6" si="14">AU4+AW4</f>
-        <v>380</v>
-      </c>
-      <c r="AZ4" s="43">
-        <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),3)</f>
-        <v>3577.936</v>
+        <v>158</v>
+      </c>
+      <c r="AZ4" s="39">
+        <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),5)</f>
+        <v>851.84345</v>
       </c>
       <c r="BA4" s="44"/>
       <c r="BB4" s="44" t="s">
@@ -7216,25 +7277,25 @@
       <c r="BL4" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>89</v>
       </c>
       <c r="BO4" s="39">
         <f t="shared" ref="BO4:BO6" si="15">ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
-        <v>327.68565</v>
+        <v>150.8329</v>
       </c>
       <c r="BP4" s="48">
         <f t="shared" ref="BP4:BP6" si="16">ROUND(BN4+AW4,3)</f>
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="BQ4" s="49">
         <v>123562</v>
       </c>
     </row>
-    <row r="5" ht="15.15" spans="1:69">
+    <row r="5" ht="15.75" spans="1:69">
       <c r="A5" s="7">
         <v>1</v>
       </c>
@@ -7251,16 +7312,16 @@
         <v>77</v>
       </c>
       <c r="F5" s="8">
-        <v>4</v>
-      </c>
-      <c r="G5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" t="s" s="0">
         <v>92</v>
       </c>
       <c r="H5" s="8">
         <f t="shared" si="0"/>
-        <v>400</v>
-      </c>
-      <c r="I5" t="s">
+        <v>600</v>
+      </c>
+      <c r="I5" t="s" s="0">
         <v>171</v>
       </c>
       <c r="J5" s="8">
@@ -7271,35 +7332,35 @@
       </c>
       <c r="L5" s="8">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="M5" s="8">
         <f>ROUND(L5*I5%,2)</f>
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="N5" s="8">
         <f t="shared" si="2"/>
-        <v>376</v>
+        <v>564</v>
       </c>
       <c r="O5" s="8">
         <f>ROUND(N5*J5%,2)</f>
-        <v>33.84</v>
+        <v>50.76</v>
       </c>
       <c r="P5" s="8">
         <f t="shared" si="3"/>
-        <v>342.16</v>
+        <v>513.24</v>
       </c>
       <c r="Q5" s="8">
         <f t="shared" si="4"/>
-        <v>20.53</v>
+        <v>30.79</v>
       </c>
       <c r="R5" s="8">
         <f>M5+O5+Q5</f>
-        <v>78.37</v>
+        <v>117.55</v>
       </c>
       <c r="S5" s="8">
         <f t="shared" si="5"/>
-        <v>321.63</v>
+        <v>482.45</v>
       </c>
       <c r="T5" s="8">
         <v>88363222</v>
@@ -7336,7 +7397,7 @@
       </c>
       <c r="AC5" s="8">
         <f>IF(DGSUomWIRcImp!$V3=1,S5+AB5,S5)</f>
-        <v>321.63</v>
+        <v>482.45</v>
       </c>
       <c r="AD5" s="26">
         <v>120</v>
@@ -7356,7 +7417,7 @@
       </c>
       <c r="AI5" s="26">
         <f>S5*DGSUomWIRcImp!$M$2</f>
-        <v>27338.55</v>
+        <v>41008.25</v>
       </c>
       <c r="AJ5" s="26">
         <f>IF(DGSUomWIRcImp!$C$2=3,0,AG5+AH5)</f>
@@ -7371,11 +7432,11 @@
       </c>
       <c r="AM5" s="26">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AN5" s="26">
         <f t="shared" si="8"/>
-        <v>6834.6375</v>
+        <v>6834.70833</v>
       </c>
       <c r="AO5" s="26">
         <f t="shared" si="9"/>
@@ -7390,7 +7451,7 @@
       </c>
       <c r="AR5" s="26">
         <f t="shared" si="11"/>
-        <v>6834.6375</v>
+        <v>6834.70833</v>
       </c>
       <c r="AS5" s="38" t="s">
         <v>80</v>
@@ -7398,27 +7459,27 @@
       <c r="AT5" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AU5" t="s" s="0">
         <v>172</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AV5" t="s" s="0">
         <v>173</v>
       </c>
       <c r="AW5" s="39">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX5" s="42">
         <f t="shared" si="13"/>
-        <v>6834.6375</v>
+        <v>6834.70833</v>
       </c>
       <c r="AY5" s="39">
         <f t="shared" si="14"/>
-        <v>192</v>
-      </c>
-      <c r="AZ5" s="42">
-        <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),2)</f>
-        <v>2073.92</v>
+        <v>130</v>
+      </c>
+      <c r="AZ5" s="39">
+        <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),5)</f>
+        <v>1789.94569</v>
       </c>
       <c r="BA5" s="44"/>
       <c r="BB5" s="44" t="s">
@@ -7442,25 +7503,25 @@
       <c r="BL5" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BM5" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BN5" t="s" s="0">
         <v>97</v>
       </c>
       <c r="BO5" s="39">
         <f t="shared" si="15"/>
-        <v>206.6075</v>
+        <v>237.37688</v>
       </c>
       <c r="BP5" s="48">
         <f t="shared" si="16"/>
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="BQ5" s="49">
         <v>123562</v>
       </c>
     </row>
-    <row r="6" ht="15.15" spans="1:69">
+    <row r="6" ht="15.75" spans="1:69">
       <c r="A6" s="7">
         <v>1</v>
       </c>
@@ -7477,16 +7538,16 @@
         <v>77</v>
       </c>
       <c r="F6" s="8">
-        <v>20</v>
-      </c>
-      <c r="G6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s" s="0">
         <v>78</v>
       </c>
       <c r="H6" s="8">
         <f t="shared" si="0"/>
-        <v>3000</v>
-      </c>
-      <c r="I6" t="s">
+        <v>1800</v>
+      </c>
+      <c r="I6" t="s" s="0">
         <v>175</v>
       </c>
       <c r="J6" s="8">
@@ -7497,35 +7558,35 @@
       </c>
       <c r="L6" s="8">
         <f t="shared" si="1"/>
-        <v>3000</v>
+        <v>1800</v>
       </c>
       <c r="M6" s="8">
         <f>ROUND(L6*I6%,2)</f>
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="N6" s="8">
         <f t="shared" si="2"/>
-        <v>2910</v>
+        <v>1674</v>
       </c>
       <c r="O6" s="8">
         <f>ROUND(N6*J6%,2)</f>
-        <v>203.7</v>
+        <v>117.18</v>
       </c>
       <c r="P6" s="8">
         <f t="shared" si="3"/>
-        <v>2706.3</v>
+        <v>1556.82</v>
       </c>
       <c r="Q6" s="8">
         <f t="shared" si="4"/>
-        <v>108.25</v>
+        <v>62.27</v>
       </c>
       <c r="R6" s="8">
         <f>M6+O6+Q6</f>
-        <v>401.95</v>
+        <v>305.45</v>
       </c>
       <c r="S6" s="8">
         <f t="shared" si="5"/>
-        <v>2598.05</v>
+        <v>1494.55</v>
       </c>
       <c r="T6" s="8">
         <v>88363222</v>
@@ -7562,7 +7623,7 @@
       </c>
       <c r="AC6" s="8">
         <f>IF(DGSUomWIRcImp!$V4=1,S6+AB6,S6)</f>
-        <v>2598.05</v>
+        <v>1494.55</v>
       </c>
       <c r="AD6" s="26">
         <v>120</v>
@@ -7582,7 +7643,7 @@
       </c>
       <c r="AI6" s="26">
         <f>S6*DGSUomWIRcImp!$M$2</f>
-        <v>220834.25</v>
+        <v>127036.75</v>
       </c>
       <c r="AJ6" s="26">
         <f>IF(DGSUomWIRcImp!$C$2=3,0,AG6+AH6)</f>
@@ -7597,11 +7658,11 @@
       </c>
       <c r="AM6" s="26">
         <f t="shared" si="7"/>
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AN6" s="26">
         <f t="shared" si="8"/>
-        <v>11041.7125</v>
+        <v>10586.39583</v>
       </c>
       <c r="AO6" s="26">
         <f t="shared" si="9"/>
@@ -7616,7 +7677,7 @@
       </c>
       <c r="AR6" s="26">
         <f t="shared" si="11"/>
-        <v>11041.7125</v>
+        <v>10586.39583</v>
       </c>
       <c r="AS6" s="38" t="s">
         <v>80</v>
@@ -7624,27 +7685,27 @@
       <c r="AT6" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AU6" t="s" s="0">
         <v>176</v>
       </c>
-      <c r="AV6" t="s">
+      <c r="AV6" t="s" s="0">
         <v>177</v>
       </c>
       <c r="AW6" s="39">
         <f t="shared" si="12"/>
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AX6" s="39">
         <f t="shared" si="13"/>
-        <v>11041.7125</v>
+        <v>10586.39583</v>
       </c>
       <c r="AY6" s="39">
         <f t="shared" si="14"/>
-        <v>500</v>
+        <v>332</v>
       </c>
       <c r="AZ6" s="39">
-        <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),1)</f>
-        <v>1493</v>
+        <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),5)</f>
+        <v>2939.56468</v>
       </c>
       <c r="BA6" s="44"/>
       <c r="BB6" s="44" t="s">
@@ -7668,25 +7729,25 @@
       <c r="BL6" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM6" t="s">
+      <c r="BM6" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="BN6" t="s">
+      <c r="BN6" t="s" s="0">
         <v>105</v>
       </c>
       <c r="BO6" s="39">
         <f t="shared" si="15"/>
-        <v>133.90625</v>
+        <v>154.6948</v>
       </c>
       <c r="BP6" s="48">
         <f t="shared" si="16"/>
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="BQ6" s="49">
         <v>123562</v>
       </c>
     </row>
-    <row r="7" ht="15.15" spans="1:69">
+    <row r="7" ht="15.75" spans="1:69">
       <c r="A7" s="9"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -7698,7 +7759,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="13">
         <f>SUM(H4:H4)</f>
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
@@ -7711,11 +7772,11 @@
       <c r="Q7" s="7"/>
       <c r="R7" s="27">
         <f t="shared" ref="R7:X7" si="17">SUM(R4:R4)</f>
-        <v>42.43</v>
+        <v>25.46</v>
       </c>
       <c r="S7" s="13">
         <f t="shared" si="17"/>
-        <v>207.57</v>
+        <v>124.54</v>
       </c>
       <c r="T7" s="27"/>
       <c r="U7" s="27"/>
@@ -7740,7 +7801,7 @@
       </c>
       <c r="AC7" s="32">
         <f t="shared" si="18"/>
-        <v>207.57</v>
+        <v>124.54</v>
       </c>
       <c r="AD7" s="33">
         <f t="shared" si="18"/>
@@ -7761,7 +7822,7 @@
       </c>
       <c r="AI7" s="33">
         <f t="shared" si="19"/>
-        <v>17643.45</v>
+        <v>10585.9</v>
       </c>
       <c r="AJ7" s="33">
         <f t="shared" si="19"/>
@@ -7804,7 +7865,7 @@
       <c r="BP7" s="40"/>
       <c r="BQ7" s="40"/>
     </row>
-    <row r="8" ht="15.15" spans="1:69">
+    <row r="8" ht="15.75" spans="1:69">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -7875,7 +7936,7 @@
       <c r="BP8" s="40"/>
       <c r="BQ8" s="40"/>
     </row>
-    <row r="9" ht="15.15" spans="1:69">
+    <row r="9" ht="15.75" spans="1:69">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -7888,7 +7949,7 @@
       <c r="H9" s="15"/>
       <c r="I9" s="19">
         <f>H7</f>
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="J9" s="19"/>
       <c r="K9" s="9"/>
@@ -7957,7 +8018,7 @@
       <c r="BP9" s="40"/>
       <c r="BQ9" s="40"/>
     </row>
-    <row r="10" ht="15.15" spans="1:69">
+    <row r="10" ht="15.75" spans="1:69">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -7970,7 +8031,7 @@
       <c r="H10" s="15"/>
       <c r="I10" s="19">
         <f>R7</f>
-        <v>42.43</v>
+        <v>25.46</v>
       </c>
       <c r="J10" s="19"/>
       <c r="K10" s="9"/>
@@ -8045,7 +8106,7 @@
       <c r="BP10" s="40"/>
       <c r="BQ10" s="40"/>
     </row>
-    <row r="11" ht="15.15" spans="1:69">
+    <row r="11" ht="15.75" spans="1:69">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -8058,7 +8119,7 @@
       <c r="H11" s="15"/>
       <c r="I11" s="19">
         <f>S7</f>
-        <v>207.57</v>
+        <v>124.54</v>
       </c>
       <c r="J11" s="19"/>
       <c r="K11" s="9"/>
@@ -8129,7 +8190,7 @@
       <c r="BP11" s="40"/>
       <c r="BQ11" s="40"/>
     </row>
-    <row r="12" ht="15.15" spans="1:69">
+    <row r="12" ht="15.75" spans="1:69">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -8213,7 +8274,7 @@
       <c r="BP12" s="40"/>
       <c r="BQ12" s="40"/>
     </row>
-    <row r="13" ht="15.15" spans="1:69">
+    <row r="13" ht="15.75" spans="1:69">
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -8226,7 +8287,7 @@
       <c r="H13" s="15"/>
       <c r="I13" s="24">
         <f>I11+I12</f>
-        <v>207.57</v>
+        <v>124.54</v>
       </c>
       <c r="J13" s="24"/>
       <c r="K13" s="9"/>
@@ -8851,14 +8912,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ20"/>
-  <sheetFormatPr defaultColWidth="8.85185185185185" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.84761904761905" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="12" max="12" width="14.287037037037" customWidth="1"/>
-    <col min="13" max="13" width="9.42592592592593" customWidth="1"/>
-    <col min="14" max="14" width="13.8518518518519" customWidth="1"/>
-    <col min="64" max="64" width="11" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="28.0"/>
+    <col min="3" max="3" customWidth="true" width="23.0"/>
+    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
+    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
+    <col min="14" max="14" customWidth="true" width="13.847619047619"/>
+    <col min="64" max="64" customWidth="true" width="11.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -8934,7 +8995,7 @@
       <c r="BP1" s="40"/>
       <c r="BQ1" s="40"/>
     </row>
-    <row r="2" ht="15.15" spans="1:69">
+    <row r="2" ht="15.75" spans="1:69">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -9029,7 +9090,7 @@
       <c r="BP2" s="40"/>
       <c r="BQ2" s="40"/>
     </row>
-    <row r="3" ht="59.1" spans="1:69">
+    <row r="3" ht="61.5" spans="1:69">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
@@ -9238,7 +9299,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.15" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="7">
         <v>1</v>
       </c>
@@ -9257,14 +9318,14 @@
       <c r="F4" s="8">
         <v>5</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H4" s="8">
         <f t="shared" ref="H4:H6" si="0">F4*G4</f>
         <v>250</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J4" s="8">
@@ -9402,10 +9463,10 @@
       <c r="AT4" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AU4" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AV4" t="s" s="0">
         <v>179</v>
       </c>
       <c r="AW4" s="39">
@@ -9446,10 +9507,10 @@
       <c r="BL4" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>89</v>
       </c>
       <c r="BO4" s="39">
@@ -9464,7 +9525,7 @@
         <v>123562</v>
       </c>
     </row>
-    <row r="5" ht="15.15" spans="1:69">
+    <row r="5" ht="15.75" spans="1:69">
       <c r="A5" s="7">
         <v>1</v>
       </c>
@@ -9483,14 +9544,14 @@
       <c r="F5" s="8">
         <v>4</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" t="s" s="0">
         <v>92</v>
       </c>
       <c r="H5" s="8">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" t="s" s="0">
         <v>93</v>
       </c>
       <c r="J5" s="8">
@@ -9628,10 +9689,10 @@
       <c r="AT5" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AU5" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AV5" t="s" s="0">
         <v>130</v>
       </c>
       <c r="AW5" s="39">
@@ -9672,10 +9733,10 @@
       <c r="BL5" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BM5" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BN5" t="s" s="0">
         <v>97</v>
       </c>
       <c r="BO5" s="39">
@@ -9690,7 +9751,7 @@
         <v>123562</v>
       </c>
     </row>
-    <row r="6" ht="15.15" spans="1:69">
+    <row r="6" ht="15.75" spans="1:69">
       <c r="A6" s="7">
         <v>1</v>
       </c>
@@ -9709,14 +9770,14 @@
       <c r="F6" s="8">
         <v>20</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H6" s="8">
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" t="s" s="0">
         <v>101</v>
       </c>
       <c r="J6" s="8">
@@ -9854,10 +9915,10 @@
       <c r="AT6" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AU6" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="AV6" t="s">
+      <c r="AV6" t="s" s="0">
         <v>132</v>
       </c>
       <c r="AW6" s="39">
@@ -9898,10 +9959,10 @@
       <c r="BL6" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM6" t="s">
+      <c r="BM6" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="BN6" t="s">
+      <c r="BN6" t="s" s="0">
         <v>105</v>
       </c>
       <c r="BO6" s="39">
@@ -9916,7 +9977,7 @@
         <v>123562</v>
       </c>
     </row>
-    <row r="7" ht="15.15" spans="1:69">
+    <row r="7" ht="15.75" spans="1:69">
       <c r="A7" s="9"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -10034,7 +10095,7 @@
       <c r="BP7" s="40"/>
       <c r="BQ7" s="40"/>
     </row>
-    <row r="8" ht="15.15" spans="1:69">
+    <row r="8" ht="15.75" spans="1:69">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -10105,7 +10166,7 @@
       <c r="BP8" s="40"/>
       <c r="BQ8" s="40"/>
     </row>
-    <row r="9" ht="15.15" spans="1:69">
+    <row r="9" ht="15.75" spans="1:69">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -10187,7 +10248,7 @@
       <c r="BP9" s="40"/>
       <c r="BQ9" s="40"/>
     </row>
-    <row r="10" ht="15.15" spans="1:69">
+    <row r="10" ht="15.75" spans="1:69">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -10275,7 +10336,7 @@
       <c r="BP10" s="40"/>
       <c r="BQ10" s="40"/>
     </row>
-    <row r="11" ht="15.15" spans="1:69">
+    <row r="11" ht="15.75" spans="1:69">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -10359,7 +10420,7 @@
       <c r="BP11" s="40"/>
       <c r="BQ11" s="40"/>
     </row>
-    <row r="12" ht="15.15" spans="1:69">
+    <row r="12" ht="15.75" spans="1:69">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -10443,7 +10504,7 @@
       <c r="BP12" s="40"/>
       <c r="BQ12" s="40"/>
     </row>
-    <row r="13" ht="15.15" spans="1:69">
+    <row r="13" ht="15.75" spans="1:69">
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -11081,13 +11142,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ20"/>
-  <sheetFormatPr defaultColWidth="8.85185185185185" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.84761904761905" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="13" max="13" width="9.13888888888889" customWidth="1"/>
-    <col min="14" max="14" width="13.8518518518519" customWidth="1"/>
-    <col min="64" max="64" width="11" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="28.0"/>
+    <col min="3" max="3" customWidth="true" width="23.0"/>
+    <col min="13" max="13" customWidth="true" width="9.14285714285714"/>
+    <col min="14" max="14" customWidth="true" width="13.847619047619"/>
+    <col min="29" max="29" width="9.28571428571429"/>
+    <col min="35" max="35" width="11.4285714285714"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="64" max="64" customWidth="true" width="11.0"/>
+    <col min="67" max="67" width="12.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -11163,7 +11228,7 @@
       <c r="BP1" s="40"/>
       <c r="BQ1" s="40"/>
     </row>
-    <row r="2" ht="15.15" spans="1:69">
+    <row r="2" ht="15.75" spans="1:69">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -11258,7 +11323,7 @@
       <c r="BP2" s="40"/>
       <c r="BQ2" s="40"/>
     </row>
-    <row r="3" ht="59.1" spans="1:69">
+    <row r="3" ht="61.5" spans="1:69">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
@@ -11467,7 +11532,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.15" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="7">
         <v>1</v>
       </c>
@@ -11484,16 +11549,16 @@
         <v>77</v>
       </c>
       <c r="F4" s="8">
-        <v>5</v>
-      </c>
-      <c r="G4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" t="s" s="0">
         <v>78</v>
       </c>
       <c r="H4" s="8">
         <f t="shared" ref="H4:H6" si="0">F4*G4</f>
-        <v>250</v>
-      </c>
-      <c r="I4" t="s">
+        <v>450</v>
+      </c>
+      <c r="I4" t="s" s="0">
         <v>79</v>
       </c>
       <c r="J4" s="8">
@@ -11504,35 +11569,35 @@
       </c>
       <c r="L4" s="8">
         <f t="shared" ref="L4:L6" si="1">IF(OR(I4=0,I4="0"),0,H4)</f>
-        <v>250</v>
+        <v>450</v>
       </c>
       <c r="M4" s="8">
         <f>ROUND(L4*I4%,3)</f>
-        <v>12.5</v>
+        <v>22.5</v>
       </c>
       <c r="N4" s="8">
         <f t="shared" ref="N4:N6" si="2">H4-M4</f>
-        <v>237.5</v>
+        <v>427.5</v>
       </c>
       <c r="O4" s="8">
         <f>ROUND(N4*J4%,3)</f>
-        <v>19</v>
+        <v>34.2</v>
       </c>
       <c r="P4" s="8">
         <f t="shared" ref="P4:P6" si="3">ROUND(N4-O4,2)</f>
-        <v>218.5</v>
+        <v>393.3</v>
       </c>
       <c r="Q4" s="8">
         <f t="shared" ref="Q4:Q6" si="4">ROUND(P4*K4%,2)</f>
-        <v>10.93</v>
+        <v>19.67</v>
       </c>
       <c r="R4" s="26">
         <f>ROUND(M4+O4+Q4,3)</f>
-        <v>42.43</v>
+        <v>76.37</v>
       </c>
       <c r="S4" s="26">
         <f t="shared" ref="S4:S6" si="5">(H4-R4)</f>
-        <v>207.57</v>
+        <v>373.63</v>
       </c>
       <c r="T4" s="8">
         <v>88363222</v>
@@ -11569,7 +11634,7 @@
       </c>
       <c r="AC4" s="31">
         <f>IF($V2=1,S4+AB4,S4)</f>
-        <v>207.57</v>
+        <v>373.63</v>
       </c>
       <c r="AD4" s="26">
         <v>120</v>
@@ -11589,7 +11654,7 @@
       </c>
       <c r="AI4" s="26">
         <f>S4*$M2</f>
-        <v>17643.45</v>
+        <v>31758.55</v>
       </c>
       <c r="AJ4" s="26">
         <f>IF($C$2=3,0,AG4+AH4)</f>
@@ -11604,11 +11669,11 @@
       </c>
       <c r="AM4" s="26">
         <f t="shared" ref="AM4:AM6" si="7">F4/AL4</f>
-        <v>1.66666666666667</v>
+        <v>1</v>
       </c>
       <c r="AN4" s="26">
         <f t="shared" ref="AN4:AN6" si="8">ROUND(AI4/AM4,5)</f>
-        <v>10586.07</v>
+        <v>31758.55</v>
       </c>
       <c r="AO4" s="26">
         <f t="shared" ref="AO4:AO6" si="9">AJ4/AM4</f>
@@ -11623,7 +11688,7 @@
       </c>
       <c r="AR4" s="26">
         <f t="shared" ref="AR4:AR6" si="11">ROUND(AN4+AO4+AP4,5)</f>
-        <v>10586.07</v>
+        <v>31758.55</v>
       </c>
       <c r="AS4" s="38" t="s">
         <v>80</v>
@@ -11631,27 +11696,27 @@
       <c r="AT4" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AU4" t="s" s="0">
         <v>183</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AV4" t="s" s="0">
         <v>184</v>
       </c>
       <c r="AW4" s="39">
         <f t="shared" ref="AW4:AW6" si="12">AM4</f>
-        <v>1.66666666666667</v>
+        <v>1</v>
       </c>
       <c r="AX4" s="42">
         <f t="shared" ref="AX4:AX6" si="13">AR4</f>
-        <v>10586.07</v>
+        <v>31758.55</v>
       </c>
       <c r="AY4" s="39">
         <f t="shared" ref="AY4:AY6" si="14">AU4+AW4</f>
-        <v>156.666666666667</v>
-      </c>
-      <c r="AZ4" s="43">
-        <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),3)</f>
-        <v>904.141</v>
+        <v>59.328</v>
+      </c>
+      <c r="AZ4" s="39">
+        <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),5)</f>
+        <v>12363.72915</v>
       </c>
       <c r="BA4" s="44"/>
       <c r="BB4" s="44" t="s">
@@ -11675,25 +11740,25 @@
       <c r="BL4" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>89</v>
       </c>
       <c r="BO4" s="39">
         <f t="shared" ref="BO4:BO6" si="15">ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
-        <v>140.45512</v>
+        <v>275.64604</v>
       </c>
       <c r="BP4" s="48">
         <f t="shared" ref="BP4:BP6" si="16">ROUND(BN4+AW4,3)</f>
-        <v>81.667</v>
+        <v>81</v>
       </c>
       <c r="BQ4" s="49">
         <v>123562</v>
       </c>
     </row>
-    <row r="5" ht="15.15" spans="1:69">
+    <row r="5" ht="15.75" spans="1:69">
       <c r="A5" s="7">
         <v>1</v>
       </c>
@@ -11710,16 +11775,16 @@
         <v>77</v>
       </c>
       <c r="F5" s="8">
-        <v>4</v>
-      </c>
-      <c r="G5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s" s="0">
         <v>92</v>
       </c>
       <c r="H5" s="8">
         <f t="shared" si="0"/>
-        <v>400</v>
-      </c>
-      <c r="I5" t="s">
+        <v>1200</v>
+      </c>
+      <c r="I5" t="s" s="0">
         <v>93</v>
       </c>
       <c r="J5" s="8">
@@ -11730,35 +11795,35 @@
       </c>
       <c r="L5" s="8">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="M5" s="8">
         <f>ROUND(L5*I5%,2)</f>
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="N5" s="8">
         <f t="shared" si="2"/>
-        <v>376</v>
+        <v>1152</v>
       </c>
       <c r="O5" s="8">
         <f>ROUND(N5*J5%,2)</f>
-        <v>33.84</v>
+        <v>103.68</v>
       </c>
       <c r="P5" s="8">
         <f t="shared" si="3"/>
-        <v>342.16</v>
+        <v>1048.32</v>
       </c>
       <c r="Q5" s="8">
         <f t="shared" si="4"/>
-        <v>20.53</v>
+        <v>62.9</v>
       </c>
       <c r="R5" s="8">
         <f>M5+O5+Q5</f>
-        <v>78.37</v>
+        <v>214.58</v>
       </c>
       <c r="S5" s="8">
         <f t="shared" si="5"/>
-        <v>321.63</v>
+        <v>985.42</v>
       </c>
       <c r="T5" s="8">
         <v>88363222</v>
@@ -11767,26 +11832,26 @@
         <v>18</v>
       </c>
       <c r="V5" s="8">
-        <f>IF(OR(DGDUomWIRcImp!$C$2=1,DGDUomWIRcImp!$C$2=4),ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF(OR($C$2=1,$C$2=4),ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="W5" s="8">
-        <f>IF(DGDUomWIRcImp!$C$2=1,ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF($C$2=1,ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="X5" s="8">
-        <f>IF(DGDUomWIRcImp!$C$2=2,ROUND(((S5*U5)/100),2),0)</f>
+        <f>IF($C$2=2,ROUND(((S5*U5)/100),2),0)</f>
         <v>0</v>
       </c>
       <c r="Y5" s="8">
-        <f>IF(DGDUomWIRcImp!$C$2=4,ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF($C$2=4,ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="Z5" s="8">
         <v>0</v>
       </c>
       <c r="AA5" s="8">
-        <f>IF(DGDUomWIRcImp!$C3=3,0,(S5*Z5)/100)</f>
+        <f>IF($C3=3,0,(S5*Z5)/100)</f>
         <v>0</v>
       </c>
       <c r="AB5" s="8">
@@ -11794,35 +11859,35 @@
         <v>0</v>
       </c>
       <c r="AC5" s="8">
-        <f>IF(DGDUomWIRcImp!$V3=1,S5+AB5,S5)</f>
-        <v>321.63</v>
+        <f>IF($V3=1,S5+AB5,S5)</f>
+        <v>985.42</v>
       </c>
       <c r="AD5" s="26">
         <v>120</v>
       </c>
       <c r="AE5" s="26">
-        <f>IF(DGDUomWIRcImp!$P$2=1,(S5/DGDUomWIRcImp!$S$7)*DGDUomWIRcImp!$E$18,AD5/DGDUomWIRcImp!$AD$7*DGDUomWIRcImp!$E$18)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$18,AD5/$AD$7*$E$18)</f>
         <v>0</v>
       </c>
       <c r="AF5" s="26"/>
       <c r="AG5" s="26">
-        <f>IF(DGDUomWIRcImp!$P$2=1,(S5/DGDUomWIRcImp!$S$7)*DGDUomWIRcImp!$E$20,AD5/DGDUomWIRcImp!$AD$7*DGDUomWIRcImp!$E$20)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$20,AD5/$AD$7*$E$20)</f>
         <v>0</v>
       </c>
       <c r="AH5" s="26">
-        <f>IF(DGDUomWIRcImp!$P$2=1,(S5/DGDUomWIRcImp!$S$7)*DGDUomWIRcImp!$E$21,AD5/DGDUomWIRcImp!$AD$7*DGDUomWIRcImp!$E$21)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$21,AD5/$AD$7*$E$21)</f>
         <v>0</v>
       </c>
       <c r="AI5" s="26">
-        <f>S5*DGDUomWIRcImp!$M$2</f>
-        <v>27338.55</v>
+        <f>S5*$M$2</f>
+        <v>83760.7</v>
       </c>
       <c r="AJ5" s="26">
-        <f>IF(DGDUomWIRcImp!$C$2=3,0,AG5+AH5)</f>
+        <f>IF($C$2=3,0,AG5+AH5)</f>
         <v>0</v>
       </c>
       <c r="AK5" s="26">
-        <f>IF(DGDUomWIRcImp!$C$2=3,AE5+AG5+AH5,0)</f>
+        <f>IF($C$2=3,AE5+AG5+AH5,0)</f>
         <v>0</v>
       </c>
       <c r="AL5" s="34">
@@ -11830,11 +11895,11 @@
       </c>
       <c r="AM5" s="26">
         <f t="shared" si="7"/>
-        <v>1.33333333333333</v>
+        <v>4</v>
       </c>
       <c r="AN5" s="26">
         <f t="shared" si="8"/>
-        <v>20503.9125</v>
+        <v>20940.175</v>
       </c>
       <c r="AO5" s="26">
         <f t="shared" si="9"/>
@@ -11849,7 +11914,7 @@
       </c>
       <c r="AR5" s="26">
         <f t="shared" si="11"/>
-        <v>20503.9125</v>
+        <v>20940.175</v>
       </c>
       <c r="AS5" s="38" t="s">
         <v>80</v>
@@ -11857,27 +11922,27 @@
       <c r="AT5" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AU5" t="s" s="0">
         <v>186</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AV5" t="s" s="0">
         <v>187</v>
       </c>
       <c r="AW5" s="39">
         <f t="shared" si="12"/>
-        <v>1.33333333333333</v>
+        <v>4</v>
       </c>
       <c r="AX5" s="42">
         <f t="shared" si="13"/>
-        <v>20503.9125</v>
+        <v>20940.175</v>
       </c>
       <c r="AY5" s="39">
         <f t="shared" si="14"/>
-        <v>125.333333333333</v>
-      </c>
-      <c r="AZ5" s="42">
-        <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),2)</f>
-        <v>1747.53</v>
+        <v>63.327</v>
+      </c>
+      <c r="AZ5" s="39">
+        <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),5)</f>
+        <v>8524.09451</v>
       </c>
       <c r="BA5" s="44"/>
       <c r="BB5" s="44" t="s">
@@ -11901,25 +11966,25 @@
       <c r="BL5" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BM5" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BN5" t="s" s="0">
         <v>97</v>
       </c>
       <c r="BO5" s="39">
         <f t="shared" si="15"/>
-        <v>118.32457</v>
+        <v>609.74341</v>
       </c>
       <c r="BP5" s="48">
         <f t="shared" si="16"/>
-        <v>61.333</v>
+        <v>64</v>
       </c>
       <c r="BQ5" s="49">
         <v>123562</v>
       </c>
     </row>
-    <row r="6" ht="15.15" spans="1:69">
+    <row r="6" ht="15.75" spans="1:69">
       <c r="A6" s="7">
         <v>1</v>
       </c>
@@ -11936,16 +12001,16 @@
         <v>77</v>
       </c>
       <c r="F6" s="8">
-        <v>20</v>
-      </c>
-      <c r="G6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H6" s="8">
         <f t="shared" si="0"/>
-        <v>3000</v>
-      </c>
-      <c r="I6" t="s">
+        <v>450</v>
+      </c>
+      <c r="I6" t="s" s="0">
         <v>101</v>
       </c>
       <c r="J6" s="8">
@@ -11956,35 +12021,35 @@
       </c>
       <c r="L6" s="8">
         <f t="shared" si="1"/>
-        <v>3000</v>
+        <v>450</v>
       </c>
       <c r="M6" s="8">
         <f>ROUND(L6*I6%,2)</f>
-        <v>210</v>
+        <v>13.5</v>
       </c>
       <c r="N6" s="8">
         <f t="shared" si="2"/>
-        <v>2790</v>
+        <v>436.5</v>
       </c>
       <c r="O6" s="8">
         <f>ROUND(N6*J6%,2)</f>
-        <v>195.3</v>
+        <v>30.56</v>
       </c>
       <c r="P6" s="8">
         <f t="shared" si="3"/>
-        <v>2594.7</v>
+        <v>405.94</v>
       </c>
       <c r="Q6" s="8">
         <f t="shared" si="4"/>
-        <v>103.79</v>
+        <v>16.24</v>
       </c>
       <c r="R6" s="8">
         <f>M6+O6+Q6</f>
-        <v>509.09</v>
+        <v>60.3</v>
       </c>
       <c r="S6" s="8">
         <f t="shared" si="5"/>
-        <v>2490.91</v>
+        <v>389.7</v>
       </c>
       <c r="T6" s="8">
         <v>88363222</v>
@@ -11993,26 +12058,26 @@
         <v>18</v>
       </c>
       <c r="V6" s="8">
-        <f>IF(OR(DGDUomWIRcImp!$C$2=1,DGDUomWIRcImp!$C$2=4),ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF(OR($C$2=1,$C$2=4),ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="W6" s="8">
-        <f>IF(DGDUomWIRcImp!$C$2=1,ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF($C$2=1,ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="X6" s="8">
-        <f>IF(DGDUomWIRcImp!$C$2=2,ROUND(((S6*U6)/100),2),0)</f>
+        <f>IF($C$2=2,ROUND(((S6*U6)/100),2),0)</f>
         <v>0</v>
       </c>
       <c r="Y6" s="8">
-        <f>IF(DGDUomWIRcImp!$C$2=4,ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF($C$2=4,ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="Z6" s="8">
         <v>0</v>
       </c>
       <c r="AA6" s="8">
-        <f>IF(DGDUomWIRcImp!$C4=3,0,(S6*Z6)/100)</f>
+        <f>IF($C4=3,0,(S6*Z6)/100)</f>
         <v>0</v>
       </c>
       <c r="AB6" s="8">
@@ -12020,35 +12085,35 @@
         <v>0</v>
       </c>
       <c r="AC6" s="8">
-        <f>IF(DGDUomWIRcImp!$V4=1,S6+AB6,S6)</f>
-        <v>2490.91</v>
+        <f>IF($V4=1,S6+AB6,S6)</f>
+        <v>389.7</v>
       </c>
       <c r="AD6" s="26">
         <v>120</v>
       </c>
       <c r="AE6" s="26">
-        <f>IF(DGDUomWIRcImp!$P$2=1,(S6/DGDUomWIRcImp!$S$7)*DGDUomWIRcImp!$E$18,AD6/DGDUomWIRcImp!$AD$7*DGDUomWIRcImp!$E$18)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$18,AD6/$AD$7*$E$18)</f>
         <v>0</v>
       </c>
       <c r="AF6" s="26"/>
       <c r="AG6" s="26">
-        <f>IF(DGDUomWIRcImp!$P$2=1,(S6/DGDUomWIRcImp!$S$7)*DGDUomWIRcImp!$E$20,AD6/DGDUomWIRcImp!$AD$7*DGDUomWIRcImp!$E$20)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$20,AD6/$AD$7*$E$20)</f>
         <v>0</v>
       </c>
       <c r="AH6" s="26">
-        <f>IF(DGDUomWIRcImp!$P$2=1,(S6/DGDUomWIRcImp!$S$7)*DGDUomWIRcImp!$E$21,AD6/DGDUomWIRcImp!$AD$7*DGDUomWIRcImp!$E$21)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$21,AD6/$AD$7*$E$21)</f>
         <v>0</v>
       </c>
       <c r="AI6" s="26">
-        <f>S6*DGDUomWIRcImp!$M$2</f>
-        <v>211727.35</v>
+        <f>S6*$M$2</f>
+        <v>33124.5</v>
       </c>
       <c r="AJ6" s="26">
-        <f>IF(DGDUomWIRcImp!$C$2=3,0,AG6+AH6)</f>
+        <f>IF($C$2=3,0,AG6+AH6)</f>
         <v>0</v>
       </c>
       <c r="AK6" s="26">
-        <f>IF(DGDUomWIRcImp!$C$2=3,AE6+AG6+AH6,0)</f>
+        <f>IF($C$2=3,AE6+AG6+AH6,0)</f>
         <v>0</v>
       </c>
       <c r="AL6" s="34">
@@ -12056,11 +12121,11 @@
       </c>
       <c r="AM6" s="26">
         <f t="shared" si="7"/>
-        <v>6.66666666666667</v>
+        <v>3</v>
       </c>
       <c r="AN6" s="26">
         <f t="shared" si="8"/>
-        <v>31759.1025</v>
+        <v>11041.5</v>
       </c>
       <c r="AO6" s="26">
         <f t="shared" si="9"/>
@@ -12075,7 +12140,7 @@
       </c>
       <c r="AR6" s="26">
         <f t="shared" si="11"/>
-        <v>31759.1025</v>
+        <v>11041.5</v>
       </c>
       <c r="AS6" s="38" t="s">
         <v>80</v>
@@ -12083,27 +12148,27 @@
       <c r="AT6" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AU6" t="s" s="0">
         <v>189</v>
       </c>
-      <c r="AV6" t="s">
+      <c r="AV6" t="s" s="0">
         <v>190</v>
       </c>
       <c r="AW6" s="39">
         <f t="shared" si="12"/>
-        <v>6.66666666666667</v>
+        <v>3</v>
       </c>
       <c r="AX6" s="39">
         <f t="shared" si="13"/>
-        <v>31759.1025</v>
+        <v>11041.5</v>
       </c>
       <c r="AY6" s="39">
         <f t="shared" si="14"/>
-        <v>326.666666666667</v>
+        <v>69.661</v>
       </c>
       <c r="AZ6" s="39">
-        <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),1)</f>
-        <v>3246.8</v>
+        <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),5)</f>
+        <v>4776.58342</v>
       </c>
       <c r="BA6" s="44"/>
       <c r="BB6" s="44" t="s">
@@ -12127,25 +12192,25 @@
       <c r="BL6" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM6" t="s">
+      <c r="BM6" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="BN6" t="s">
+      <c r="BN6" t="s" s="0">
         <v>105</v>
       </c>
       <c r="BO6" s="39">
         <f t="shared" si="15"/>
-        <v>112.9413</v>
+        <v>90.16419</v>
       </c>
       <c r="BP6" s="48">
         <f t="shared" si="16"/>
-        <v>306.667</v>
+        <v>303</v>
       </c>
       <c r="BQ6" s="49">
         <v>123562</v>
       </c>
     </row>
-    <row r="7" ht="15.15" spans="1:69">
+    <row r="7" ht="15.75" spans="1:69">
       <c r="A7" s="9"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -12157,7 +12222,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="13">
         <f>SUM(H4:H4)</f>
-        <v>250</v>
+        <v>450</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
@@ -12170,11 +12235,11 @@
       <c r="Q7" s="7"/>
       <c r="R7" s="27">
         <f t="shared" ref="R7:X7" si="17">SUM(R4:R4)</f>
-        <v>42.43</v>
+        <v>76.37</v>
       </c>
       <c r="S7" s="13">
         <f t="shared" si="17"/>
-        <v>207.57</v>
+        <v>373.63</v>
       </c>
       <c r="T7" s="27"/>
       <c r="U7" s="27"/>
@@ -12199,7 +12264,7 @@
       </c>
       <c r="AC7" s="32">
         <f t="shared" si="18"/>
-        <v>207.57</v>
+        <v>373.63</v>
       </c>
       <c r="AD7" s="33">
         <f t="shared" si="18"/>
@@ -12220,7 +12285,7 @@
       </c>
       <c r="AI7" s="33">
         <f t="shared" si="19"/>
-        <v>17643.45</v>
+        <v>31758.55</v>
       </c>
       <c r="AJ7" s="33">
         <f t="shared" si="19"/>
@@ -12263,7 +12328,7 @@
       <c r="BP7" s="40"/>
       <c r="BQ7" s="40"/>
     </row>
-    <row r="8" ht="15.15" spans="1:69">
+    <row r="8" ht="15.75" spans="1:69">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -12334,7 +12399,7 @@
       <c r="BP8" s="40"/>
       <c r="BQ8" s="40"/>
     </row>
-    <row r="9" ht="15.15" spans="1:69">
+    <row r="9" ht="15.75" spans="1:69">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -12347,7 +12412,7 @@
       <c r="H9" s="15"/>
       <c r="I9" s="19">
         <f>H7</f>
-        <v>250</v>
+        <v>450</v>
       </c>
       <c r="J9" s="19"/>
       <c r="K9" s="9"/>
@@ -12416,7 +12481,7 @@
       <c r="BP9" s="40"/>
       <c r="BQ9" s="40"/>
     </row>
-    <row r="10" ht="15.15" spans="1:69">
+    <row r="10" ht="15.75" spans="1:69">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -12429,7 +12494,7 @@
       <c r="H10" s="15"/>
       <c r="I10" s="19">
         <f>R7</f>
-        <v>42.43</v>
+        <v>76.37</v>
       </c>
       <c r="J10" s="19"/>
       <c r="K10" s="9"/>
@@ -12504,7 +12569,7 @@
       <c r="BP10" s="40"/>
       <c r="BQ10" s="40"/>
     </row>
-    <row r="11" ht="15.15" spans="1:69">
+    <row r="11" ht="15.75" spans="1:69">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -12517,7 +12582,7 @@
       <c r="H11" s="15"/>
       <c r="I11" s="19">
         <f>S7</f>
-        <v>207.57</v>
+        <v>373.63</v>
       </c>
       <c r="J11" s="19"/>
       <c r="K11" s="9"/>
@@ -12588,7 +12653,7 @@
       <c r="BP11" s="40"/>
       <c r="BQ11" s="40"/>
     </row>
-    <row r="12" ht="15.15" spans="1:69">
+    <row r="12" ht="15.75" spans="1:69">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -12672,7 +12737,7 @@
       <c r="BP12" s="40"/>
       <c r="BQ12" s="40"/>
     </row>
-    <row r="13" ht="15.15" spans="1:69">
+    <row r="13" ht="15.75" spans="1:69">
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -12685,7 +12750,7 @@
       <c r="H13" s="15"/>
       <c r="I13" s="24">
         <f>I11+I12</f>
-        <v>207.57</v>
+        <v>373.63</v>
       </c>
       <c r="J13" s="24"/>
       <c r="K13" s="9"/>
@@ -13310,13 +13375,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ20"/>
-  <sheetFormatPr defaultColWidth="8.85185185185185" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.84761904761905" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="13" max="13" width="9.13888888888889" customWidth="1"/>
-    <col min="14" max="14" width="13.8518518518519" customWidth="1"/>
-    <col min="64" max="64" width="11" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="28.0"/>
+    <col min="3" max="3" customWidth="true" width="30.0"/>
+    <col min="13" max="13" customWidth="true" width="9.14285714285714"/>
+    <col min="14" max="14" customWidth="true" width="13.847619047619"/>
+    <col min="64" max="64" customWidth="true" width="11.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -13392,7 +13457,7 @@
       <c r="BP1" s="40"/>
       <c r="BQ1" s="40"/>
     </row>
-    <row r="2" ht="15.15" spans="1:69">
+    <row r="2" ht="15.75" spans="1:69">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -13487,7 +13552,7 @@
       <c r="BP2" s="40"/>
       <c r="BQ2" s="40"/>
     </row>
-    <row r="3" ht="59.1" spans="1:69">
+    <row r="3" ht="61.5" spans="1:69">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
@@ -13696,7 +13761,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.15" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="7">
         <v>1</v>
       </c>
@@ -13715,14 +13780,14 @@
       <c r="F4" s="8">
         <v>5</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="0">
         <v>50</v>
       </c>
       <c r="H4" s="8">
         <f t="shared" ref="H4:H6" si="0">F4*G4</f>
         <v>250</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="0">
         <v>0</v>
       </c>
       <c r="J4" s="8">
@@ -13860,10 +13925,10 @@
       <c r="AT4" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AU4" t="s" s="0">
         <v>183</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AV4" t="s" s="0">
         <v>184</v>
       </c>
       <c r="AW4" s="39">
@@ -13904,10 +13969,10 @@
       <c r="BL4" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>89</v>
       </c>
       <c r="BO4" s="39">
@@ -13922,7 +13987,7 @@
         <v>123562</v>
       </c>
     </row>
-    <row r="5" ht="15.15" spans="1:69">
+    <row r="5" ht="15.75" spans="1:69">
       <c r="A5" s="7">
         <v>1</v>
       </c>
@@ -13941,14 +14006,14 @@
       <c r="F5" s="8">
         <v>4</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" t="s" s="0">
         <v>92</v>
       </c>
       <c r="H5" s="8">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" t="s" s="0">
         <v>93</v>
       </c>
       <c r="J5" s="8">
@@ -14086,10 +14151,10 @@
       <c r="AT5" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AU5" t="s" s="0">
         <v>186</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AV5" t="s" s="0">
         <v>187</v>
       </c>
       <c r="AW5" s="39">
@@ -14130,10 +14195,10 @@
       <c r="BL5" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BM5" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BN5" t="s" s="0">
         <v>97</v>
       </c>
       <c r="BO5" s="39">
@@ -14148,7 +14213,7 @@
         <v>123562</v>
       </c>
     </row>
-    <row r="6" ht="15.15" spans="1:69">
+    <row r="6" ht="15.75" spans="1:69">
       <c r="A6" s="7">
         <v>1</v>
       </c>
@@ -14167,14 +14232,14 @@
       <c r="F6" s="8">
         <v>20</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H6" s="8">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" t="s" s="0">
         <v>101</v>
       </c>
       <c r="J6" s="8">
@@ -14312,10 +14377,10 @@
       <c r="AT6" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AU6" t="s" s="0">
         <v>189</v>
       </c>
-      <c r="AV6" t="s">
+      <c r="AV6" t="s" s="0">
         <v>190</v>
       </c>
       <c r="AW6" s="39">
@@ -14356,10 +14421,10 @@
       <c r="BL6" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM6" t="s">
+      <c r="BM6" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="BN6" t="s">
+      <c r="BN6" t="s" s="0">
         <v>105</v>
       </c>
       <c r="BO6" s="39">
@@ -14374,7 +14439,7 @@
         <v>123562</v>
       </c>
     </row>
-    <row r="7" ht="15.15" spans="1:69">
+    <row r="7" ht="15.75" spans="1:69">
       <c r="A7" s="9"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -14492,7 +14557,7 @@
       <c r="BP7" s="40"/>
       <c r="BQ7" s="40"/>
     </row>
-    <row r="8" ht="15.15" spans="1:69">
+    <row r="8" ht="15.75" spans="1:69">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -14563,7 +14628,7 @@
       <c r="BP8" s="40"/>
       <c r="BQ8" s="40"/>
     </row>
-    <row r="9" ht="15.15" spans="1:69">
+    <row r="9" ht="15.75" spans="1:69">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -14645,7 +14710,7 @@
       <c r="BP9" s="40"/>
       <c r="BQ9" s="40"/>
     </row>
-    <row r="10" ht="15.15" spans="1:69">
+    <row r="10" ht="15.75" spans="1:69">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -14733,7 +14798,7 @@
       <c r="BP10" s="40"/>
       <c r="BQ10" s="40"/>
     </row>
-    <row r="11" ht="15.15" spans="1:69">
+    <row r="11" ht="15.75" spans="1:69">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -14817,7 +14882,7 @@
       <c r="BP11" s="40"/>
       <c r="BQ11" s="40"/>
     </row>
-    <row r="12" ht="15.15" spans="1:69">
+    <row r="12" ht="15.75" spans="1:69">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -14901,7 +14966,7 @@
       <c r="BP12" s="40"/>
       <c r="BQ12" s="40"/>
     </row>
-    <row r="13" ht="15.15" spans="1:69">
+    <row r="13" ht="15.75" spans="1:69">
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -15539,13 +15604,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ20"/>
-  <sheetFormatPr defaultColWidth="8.85185185185185" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.84761904761905" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="13" max="13" width="9.13888888888889" customWidth="1"/>
-    <col min="14" max="14" width="13.8518518518519" customWidth="1"/>
-    <col min="64" max="64" width="11" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="28.0"/>
+    <col min="3" max="3" customWidth="true" width="23.0"/>
+    <col min="13" max="13" customWidth="true" width="9.14285714285714"/>
+    <col min="14" max="14" customWidth="true" width="13.847619047619"/>
+    <col min="29" max="29" width="9.28571428571429"/>
+    <col min="35" max="35" width="11.4285714285714"/>
+    <col min="52" max="52" width="13.2857142857143"/>
+    <col min="64" max="64" customWidth="true" width="11.0"/>
+    <col min="67" max="67" width="12.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -15621,7 +15690,7 @@
       <c r="BP1" s="40"/>
       <c r="BQ1" s="40"/>
     </row>
-    <row r="2" ht="15.15" spans="1:69">
+    <row r="2" ht="15.75" spans="1:69">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -15716,7 +15785,7 @@
       <c r="BP2" s="40"/>
       <c r="BQ2" s="40"/>
     </row>
-    <row r="3" ht="59.1" spans="1:69">
+    <row r="3" ht="61.5" spans="1:69">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
@@ -15925,7 +15994,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.15" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="7">
         <v>1</v>
       </c>
@@ -15942,16 +16011,16 @@
         <v>77</v>
       </c>
       <c r="F4" s="8">
-        <v>5</v>
-      </c>
-      <c r="G4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" t="s" s="0">
         <v>78</v>
       </c>
       <c r="H4" s="8">
         <f t="shared" ref="H4:H6" si="0">F4*G4</f>
-        <v>750</v>
-      </c>
-      <c r="I4" t="s">
+        <v>450</v>
+      </c>
+      <c r="I4" t="s" s="0">
         <v>79</v>
       </c>
       <c r="J4" s="8">
@@ -15962,35 +16031,35 @@
       </c>
       <c r="L4" s="8">
         <f t="shared" ref="L4:L6" si="1">IF(OR(I4=0,I4="0"),0,H4)</f>
-        <v>750</v>
+        <v>450</v>
       </c>
       <c r="M4" s="8">
         <f>ROUND(L4*I4%,3)</f>
-        <v>37.5</v>
+        <v>22.5</v>
       </c>
       <c r="N4" s="8">
         <f t="shared" ref="N4:N6" si="2">H4-M4</f>
-        <v>712.5</v>
+        <v>427.5</v>
       </c>
       <c r="O4" s="8">
         <f>ROUND(N4*J4%,3)</f>
-        <v>57</v>
+        <v>34.2</v>
       </c>
       <c r="P4" s="8">
         <f t="shared" ref="P4:P6" si="3">ROUND(N4-O4,2)</f>
-        <v>655.5</v>
+        <v>393.3</v>
       </c>
       <c r="Q4" s="8">
         <f t="shared" ref="Q4:Q6" si="4">ROUND(P4*K4%,2)</f>
-        <v>32.78</v>
+        <v>19.67</v>
       </c>
       <c r="R4" s="26">
         <f>ROUND(M4+O4+Q4,3)</f>
-        <v>127.28</v>
+        <v>76.37</v>
       </c>
       <c r="S4" s="26">
         <f t="shared" ref="S4:S6" si="5">(H4-R4)</f>
-        <v>622.72</v>
+        <v>373.63</v>
       </c>
       <c r="T4" s="8">
         <v>88363222</v>
@@ -16027,7 +16096,7 @@
       </c>
       <c r="AC4" s="31">
         <f>IF($V2=1,S4+AB4,S4)</f>
-        <v>622.72</v>
+        <v>373.63</v>
       </c>
       <c r="AD4" s="26">
         <v>120</v>
@@ -16047,7 +16116,7 @@
       </c>
       <c r="AI4" s="26">
         <f>S4*$M2</f>
-        <v>52931.2</v>
+        <v>31758.55</v>
       </c>
       <c r="AJ4" s="26">
         <f>IF($C$2=3,0,AG4+AH4)</f>
@@ -16062,11 +16131,11 @@
       </c>
       <c r="AM4" s="26">
         <f t="shared" ref="AM4:AM6" si="7">F4/AL4</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AN4" s="26">
         <f t="shared" ref="AN4:AN6" si="8">ROUND(AI4/AM4,5)</f>
-        <v>10586.24</v>
+        <v>10586.18333</v>
       </c>
       <c r="AO4" s="26">
         <f t="shared" ref="AO4:AO6" si="9">AJ4/AM4</f>
@@ -16081,7 +16150,7 @@
       </c>
       <c r="AR4" s="26">
         <f t="shared" ref="AR4:AR6" si="11">ROUND(AN4+AO4+AP4,5)</f>
-        <v>10586.24</v>
+        <v>10586.18333</v>
       </c>
       <c r="AS4" s="38" t="s">
         <v>80</v>
@@ -16089,27 +16158,27 @@
       <c r="AT4" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AU4" t="s" s="0">
         <v>89</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AV4" t="s" s="0">
         <v>195</v>
       </c>
       <c r="AW4" s="39">
         <f t="shared" ref="AW4:AW6" si="12">AM4</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AX4" s="42">
         <f t="shared" ref="AX4:AX6" si="13">AR4</f>
-        <v>10586.24</v>
+        <v>10586.18333</v>
       </c>
       <c r="AY4" s="39">
         <f t="shared" ref="AY4:AY6" si="14">AU4+AW4</f>
-        <v>160</v>
-      </c>
-      <c r="AZ4" s="43">
-        <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),3)</f>
-        <v>4047.707</v>
+        <v>83</v>
+      </c>
+      <c r="AZ4" s="39">
+        <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),5)</f>
+        <v>4284.04277</v>
       </c>
       <c r="BA4" s="44"/>
       <c r="BB4" s="44" t="s">
@@ -16133,25 +16202,25 @@
       <c r="BL4" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>89</v>
       </c>
       <c r="BO4" s="39">
         <f t="shared" ref="BO4:BO6" si="15">ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
-        <v>355.31924</v>
+        <v>274.88829</v>
       </c>
       <c r="BP4" s="48">
         <f t="shared" ref="BP4:BP6" si="16">ROUND(BN4+AW4,3)</f>
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="BQ4" s="49">
         <v>123562</v>
       </c>
     </row>
-    <row r="5" ht="15.15" spans="1:69">
+    <row r="5" ht="15.75" spans="1:69">
       <c r="A5" s="7">
         <v>1</v>
       </c>
@@ -16168,16 +16237,16 @@
         <v>77</v>
       </c>
       <c r="F5" s="8">
-        <v>4</v>
-      </c>
-      <c r="G5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" t="s" s="0">
         <v>92</v>
       </c>
       <c r="H5" s="8">
         <f t="shared" si="0"/>
-        <v>400</v>
-      </c>
-      <c r="I5" t="s">
+        <v>600</v>
+      </c>
+      <c r="I5" t="s" s="0">
         <v>93</v>
       </c>
       <c r="J5" s="8">
@@ -16188,7 +16257,7 @@
       </c>
       <c r="L5" s="8">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="M5" s="8">
         <f>ROUND(L5*I5%,2)</f>
@@ -16196,27 +16265,27 @@
       </c>
       <c r="N5" s="8">
         <f t="shared" si="2"/>
-        <v>376</v>
+        <v>576</v>
       </c>
       <c r="O5" s="8">
         <f>ROUND(N5*J5%,2)</f>
-        <v>33.84</v>
+        <v>51.84</v>
       </c>
       <c r="P5" s="8">
         <f t="shared" si="3"/>
-        <v>342.16</v>
+        <v>524.16</v>
       </c>
       <c r="Q5" s="8">
         <f t="shared" si="4"/>
-        <v>20.53</v>
+        <v>31.45</v>
       </c>
       <c r="R5" s="8">
         <f>M5+O5+Q5</f>
-        <v>78.37</v>
+        <v>107.29</v>
       </c>
       <c r="S5" s="8">
         <f t="shared" si="5"/>
-        <v>321.63</v>
+        <v>492.71</v>
       </c>
       <c r="T5" s="8">
         <v>88363222</v>
@@ -16225,26 +16294,26 @@
         <v>18</v>
       </c>
       <c r="V5" s="8">
-        <f>IF(OR(DGSUomWIPlImp!$C$2=1,DGSUomWIPlImp!$C$2=4),ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF(OR($C$2=1,$C$2=4),ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="W5" s="8">
-        <f>IF(DGSUomWIPlImp!$C$2=1,ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF($C$2=1,ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="X5" s="8">
-        <f>IF(DGSUomWIPlImp!$C$2=2,ROUND(((S5*U5)/100),2),0)</f>
+        <f>IF($C$2=2,ROUND(((S5*U5)/100),2),0)</f>
         <v>0</v>
       </c>
       <c r="Y5" s="8">
-        <f>IF(DGSUomWIPlImp!$C$2=4,ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF($C$2=4,ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="Z5" s="8">
         <v>0</v>
       </c>
       <c r="AA5" s="8">
-        <f>IF(DGSUomWIPlImp!$C3=3,0,(S5*Z5)/100)</f>
+        <f>IF($C3=3,0,(S5*Z5)/100)</f>
         <v>0</v>
       </c>
       <c r="AB5" s="8">
@@ -16252,35 +16321,35 @@
         <v>0</v>
       </c>
       <c r="AC5" s="8">
-        <f>IF(DGSUomWIPlImp!$V3=1,S5+AB5,S5)</f>
-        <v>321.63</v>
+        <f>IF($V3=1,S5+AB5,S5)</f>
+        <v>492.71</v>
       </c>
       <c r="AD5" s="26">
         <v>120</v>
       </c>
       <c r="AE5" s="26">
-        <f>IF(DGSUomWIPlImp!$P$2=1,(S5/DGSUomWIPlImp!$S$7)*DGSUomWIPlImp!$E$18,AD5/DGSUomWIPlImp!$AD$7*DGSUomWIPlImp!$E$18)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$18,AD5/$AD$7*$E$18)</f>
         <v>0</v>
       </c>
       <c r="AF5" s="26"/>
       <c r="AG5" s="26">
-        <f>IF(DGSUomWIPlImp!$P$2=1,(S5/DGSUomWIPlImp!$S$7)*DGSUomWIPlImp!$E$20,AD5/DGSUomWIPlImp!$AD$7*DGSUomWIPlImp!$E$20)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$20,AD5/$AD$7*$E$20)</f>
         <v>0</v>
       </c>
       <c r="AH5" s="26">
-        <f>IF(DGSUomWIPlImp!$P$2=1,(S5/DGSUomWIPlImp!$S$7)*DGSUomWIPlImp!$E$21,AD5/DGSUomWIPlImp!$AD$7*DGSUomWIPlImp!$E$21)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$21,AD5/$AD$7*$E$21)</f>
         <v>0</v>
       </c>
       <c r="AI5" s="26">
-        <f>S5*DGSUomWIPlImp!$M$2</f>
-        <v>27338.55</v>
+        <f>S5*$M$2</f>
+        <v>41880.35</v>
       </c>
       <c r="AJ5" s="26">
-        <f>IF(DGSUomWIPlImp!$C$2=3,0,AG5+AH5)</f>
+        <f>IF($C$2=3,0,AG5+AH5)</f>
         <v>0</v>
       </c>
       <c r="AK5" s="26">
-        <f>IF(DGSUomWIPlImp!$C$2=3,AE5+AG5+AH5,0)</f>
+        <f>IF($C$2=3,AE5+AG5+AH5,0)</f>
         <v>0</v>
       </c>
       <c r="AL5" s="34">
@@ -16288,11 +16357,11 @@
       </c>
       <c r="AM5" s="26">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AN5" s="26">
         <f t="shared" si="8"/>
-        <v>6834.6375</v>
+        <v>6980.05833</v>
       </c>
       <c r="AO5" s="26">
         <f t="shared" si="9"/>
@@ -16307,7 +16376,7 @@
       </c>
       <c r="AR5" s="26">
         <f t="shared" si="11"/>
-        <v>6834.6375</v>
+        <v>6980.05833</v>
       </c>
       <c r="AS5" s="38" t="s">
         <v>80</v>
@@ -16315,27 +16384,27 @@
       <c r="AT5" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AU5" t="s" s="0">
         <v>197</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AV5" t="s" s="0">
         <v>198</v>
       </c>
       <c r="AW5" s="39">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX5" s="42">
         <f t="shared" si="13"/>
-        <v>6834.6375</v>
+        <v>6980.05833</v>
       </c>
       <c r="AY5" s="39">
         <f t="shared" si="14"/>
-        <v>128</v>
-      </c>
-      <c r="AZ5" s="42">
-        <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),2)</f>
-        <v>2508.17</v>
+        <v>74</v>
+      </c>
+      <c r="AZ5" s="39">
+        <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),5)</f>
+        <v>2878.62743</v>
       </c>
       <c r="BA5" s="44"/>
       <c r="BB5" s="44" t="s">
@@ -16359,25 +16428,25 @@
       <c r="BL5" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BM5" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BN5" t="s" s="0">
         <v>97</v>
       </c>
       <c r="BO5" s="39">
         <f t="shared" si="15"/>
-        <v>233.74813</v>
+        <v>336.34795</v>
       </c>
       <c r="BP5" s="48">
         <f t="shared" si="16"/>
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="BQ5" s="49">
         <v>123562</v>
       </c>
     </row>
-    <row r="6" ht="15.15" spans="1:69">
+    <row r="6" ht="15.75" spans="1:69">
       <c r="A6" s="7">
         <v>1</v>
       </c>
@@ -16394,16 +16463,16 @@
         <v>77</v>
       </c>
       <c r="F6" s="8">
-        <v>20</v>
-      </c>
-      <c r="G6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H6" s="8">
         <f t="shared" si="0"/>
-        <v>3000</v>
-      </c>
-      <c r="I6" t="s">
+        <v>600</v>
+      </c>
+      <c r="I6" t="s" s="0">
         <v>101</v>
       </c>
       <c r="J6" s="8">
@@ -16414,35 +16483,35 @@
       </c>
       <c r="L6" s="8">
         <f t="shared" si="1"/>
-        <v>3000</v>
+        <v>600</v>
       </c>
       <c r="M6" s="8">
         <f>ROUND(L6*I6%,2)</f>
-        <v>210</v>
+        <v>18</v>
       </c>
       <c r="N6" s="8">
         <f t="shared" si="2"/>
-        <v>2790</v>
+        <v>582</v>
       </c>
       <c r="O6" s="8">
         <f>ROUND(N6*J6%,2)</f>
-        <v>195.3</v>
+        <v>40.74</v>
       </c>
       <c r="P6" s="8">
         <f t="shared" si="3"/>
-        <v>2594.7</v>
+        <v>541.26</v>
       </c>
       <c r="Q6" s="8">
         <f t="shared" si="4"/>
-        <v>103.79</v>
+        <v>21.65</v>
       </c>
       <c r="R6" s="8">
         <f>M6+O6+Q6</f>
-        <v>509.09</v>
+        <v>80.39</v>
       </c>
       <c r="S6" s="8">
         <f t="shared" si="5"/>
-        <v>2490.91</v>
+        <v>519.61</v>
       </c>
       <c r="T6" s="8">
         <v>88363222</v>
@@ -16451,26 +16520,26 @@
         <v>18</v>
       </c>
       <c r="V6" s="8">
-        <f>IF(OR(DGSUomWIPlImp!$C$2=1,DGSUomWIPlImp!$C$2=4),ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF(OR($C$2=1,$C$2=4),ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="W6" s="8">
-        <f>IF(DGSUomWIPlImp!$C$2=1,ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF($C$2=1,ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="X6" s="8">
-        <f>IF(DGSUomWIPlImp!$C$2=2,ROUND(((S6*U6)/100),2),0)</f>
+        <f>IF($C$2=2,ROUND(((S6*U6)/100),2),0)</f>
         <v>0</v>
       </c>
       <c r="Y6" s="8">
-        <f>IF(DGSUomWIPlImp!$C$2=4,ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF($C$2=4,ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="Z6" s="8">
         <v>0</v>
       </c>
       <c r="AA6" s="8">
-        <f>IF(DGSUomWIPlImp!$C4=3,0,(S6*Z6)/100)</f>
+        <f>IF($C4=3,0,(S6*Z6)/100)</f>
         <v>0</v>
       </c>
       <c r="AB6" s="8">
@@ -16478,35 +16547,35 @@
         <v>0</v>
       </c>
       <c r="AC6" s="8">
-        <f>IF(DGSUomWIPlImp!$V4=1,S6+AB6,S6)</f>
-        <v>2490.91</v>
+        <f>IF($V4=1,S6+AB6,S6)</f>
+        <v>519.61</v>
       </c>
       <c r="AD6" s="26">
         <v>120</v>
       </c>
       <c r="AE6" s="26">
-        <f>IF(DGSUomWIPlImp!$P$2=1,(S6/DGSUomWIPlImp!$S$7)*DGSUomWIPlImp!$E$18,AD6/DGSUomWIPlImp!$AD$7*DGSUomWIPlImp!$E$18)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$18,AD6/$AD$7*$E$18)</f>
         <v>0</v>
       </c>
       <c r="AF6" s="26"/>
       <c r="AG6" s="26">
-        <f>IF(DGSUomWIPlImp!$P$2=1,(S6/DGSUomWIPlImp!$S$7)*DGSUomWIPlImp!$E$20,AD6/DGSUomWIPlImp!$AD$7*DGSUomWIPlImp!$E$20)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$20,AD6/$AD$7*$E$20)</f>
         <v>0</v>
       </c>
       <c r="AH6" s="26">
-        <f>IF(DGSUomWIPlImp!$P$2=1,(S6/DGSUomWIPlImp!$S$7)*DGSUomWIPlImp!$E$21,AD6/DGSUomWIPlImp!$AD$7*DGSUomWIPlImp!$E$21)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$21,AD6/$AD$7*$E$21)</f>
         <v>0</v>
       </c>
       <c r="AI6" s="26">
-        <f>S6*DGSUomWIPlImp!$M$2</f>
-        <v>211727.35</v>
+        <f>S6*$M$2</f>
+        <v>44166.85</v>
       </c>
       <c r="AJ6" s="26">
-        <f>IF(DGSUomWIPlImp!$C$2=3,0,AG6+AH6)</f>
+        <f>IF($C$2=3,0,AG6+AH6)</f>
         <v>0</v>
       </c>
       <c r="AK6" s="26">
-        <f>IF(DGSUomWIPlImp!$C$2=3,AE6+AG6+AH6,0)</f>
+        <f>IF($C$2=3,AE6+AG6+AH6,0)</f>
         <v>0</v>
       </c>
       <c r="AL6" s="34">
@@ -16514,11 +16583,11 @@
       </c>
       <c r="AM6" s="26">
         <f t="shared" si="7"/>
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AN6" s="26">
         <f t="shared" si="8"/>
-        <v>10586.3675</v>
+        <v>3680.57083</v>
       </c>
       <c r="AO6" s="26">
         <f t="shared" si="9"/>
@@ -16533,7 +16602,7 @@
       </c>
       <c r="AR6" s="26">
         <f t="shared" si="11"/>
-        <v>10586.3675</v>
+        <v>3680.57083</v>
       </c>
       <c r="AS6" s="38" t="s">
         <v>80</v>
@@ -16541,27 +16610,27 @@
       <c r="AT6" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AU6" t="s" s="0">
         <v>200</v>
       </c>
-      <c r="AV6" t="s">
+      <c r="AV6" t="s" s="0">
         <v>201</v>
       </c>
       <c r="AW6" s="39">
         <f t="shared" si="12"/>
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AX6" s="39">
         <f t="shared" si="13"/>
-        <v>10586.3675</v>
+        <v>3680.57083</v>
       </c>
       <c r="AY6" s="39">
         <f t="shared" si="14"/>
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AZ6" s="39">
-        <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),1)</f>
-        <v>1784.5</v>
+        <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),5)</f>
+        <v>1447.13407</v>
       </c>
       <c r="BA6" s="44"/>
       <c r="BB6" s="44" t="s">
@@ -16585,25 +16654,25 @@
       <c r="BL6" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM6" t="s">
+      <c r="BM6" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="BN6" t="s">
+      <c r="BN6" t="s" s="0">
         <v>105</v>
       </c>
       <c r="BO6" s="39">
         <f t="shared" si="15"/>
-        <v>152.125</v>
+        <v>97.29362</v>
       </c>
       <c r="BP6" s="48">
         <f t="shared" si="16"/>
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="BQ6" s="49">
         <v>123562</v>
       </c>
     </row>
-    <row r="7" ht="15.15" spans="1:69">
+    <row r="7" ht="15.75" spans="1:69">
       <c r="A7" s="9"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -16615,7 +16684,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="13">
         <f>SUM(H4:H4)</f>
-        <v>750</v>
+        <v>450</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
@@ -16628,11 +16697,11 @@
       <c r="Q7" s="7"/>
       <c r="R7" s="27">
         <f t="shared" ref="R7:X7" si="17">SUM(R4:R4)</f>
-        <v>127.28</v>
+        <v>76.37</v>
       </c>
       <c r="S7" s="13">
         <f t="shared" si="17"/>
-        <v>622.72</v>
+        <v>373.63</v>
       </c>
       <c r="T7" s="27"/>
       <c r="U7" s="27"/>
@@ -16657,7 +16726,7 @@
       </c>
       <c r="AC7" s="32">
         <f t="shared" si="18"/>
-        <v>622.72</v>
+        <v>373.63</v>
       </c>
       <c r="AD7" s="33">
         <f t="shared" si="18"/>
@@ -16678,7 +16747,7 @@
       </c>
       <c r="AI7" s="33">
         <f t="shared" si="19"/>
-        <v>52931.2</v>
+        <v>31758.55</v>
       </c>
       <c r="AJ7" s="33">
         <f t="shared" si="19"/>
@@ -16721,7 +16790,7 @@
       <c r="BP7" s="40"/>
       <c r="BQ7" s="40"/>
     </row>
-    <row r="8" ht="15.15" spans="1:69">
+    <row r="8" ht="15.75" spans="1:69">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -16792,7 +16861,7 @@
       <c r="BP8" s="40"/>
       <c r="BQ8" s="40"/>
     </row>
-    <row r="9" ht="15.15" spans="1:69">
+    <row r="9" ht="15.75" spans="1:69">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -16805,7 +16874,7 @@
       <c r="H9" s="15"/>
       <c r="I9" s="19">
         <f>H7</f>
-        <v>750</v>
+        <v>450</v>
       </c>
       <c r="J9" s="19"/>
       <c r="K9" s="9"/>
@@ -16874,7 +16943,7 @@
       <c r="BP9" s="40"/>
       <c r="BQ9" s="40"/>
     </row>
-    <row r="10" ht="15.15" spans="1:69">
+    <row r="10" ht="15.75" spans="1:69">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -16887,7 +16956,7 @@
       <c r="H10" s="15"/>
       <c r="I10" s="19">
         <f>R7</f>
-        <v>127.28</v>
+        <v>76.37</v>
       </c>
       <c r="J10" s="19"/>
       <c r="K10" s="9"/>
@@ -16962,7 +17031,7 @@
       <c r="BP10" s="40"/>
       <c r="BQ10" s="40"/>
     </row>
-    <row r="11" ht="15.15" spans="1:69">
+    <row r="11" ht="15.75" spans="1:69">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -16975,7 +17044,7 @@
       <c r="H11" s="15"/>
       <c r="I11" s="19">
         <f>S7</f>
-        <v>622.72</v>
+        <v>373.63</v>
       </c>
       <c r="J11" s="19"/>
       <c r="K11" s="9"/>
@@ -17046,7 +17115,7 @@
       <c r="BP11" s="40"/>
       <c r="BQ11" s="40"/>
     </row>
-    <row r="12" ht="15.15" spans="1:69">
+    <row r="12" ht="15.75" spans="1:69">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -17130,7 +17199,7 @@
       <c r="BP12" s="40"/>
       <c r="BQ12" s="40"/>
     </row>
-    <row r="13" ht="15.15" spans="1:69">
+    <row r="13" ht="15.75" spans="1:69">
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -17143,7 +17212,7 @@
       <c r="H13" s="15"/>
       <c r="I13" s="24">
         <f>I11+I12</f>
-        <v>622.72</v>
+        <v>373.63</v>
       </c>
       <c r="J13" s="24"/>
       <c r="K13" s="9"/>
@@ -17768,13 +17837,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ20"/>
-  <sheetFormatPr defaultColWidth="8.85185185185185" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.84761904761905" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="13" max="13" width="9.13888888888889" customWidth="1"/>
-    <col min="14" max="14" width="13.8518518518519" customWidth="1"/>
-    <col min="64" max="64" width="11" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="28.0"/>
+    <col min="3" max="3" customWidth="true" width="23.0"/>
+    <col min="13" max="13" customWidth="true" width="9.14285714285714"/>
+    <col min="14" max="14" customWidth="true" width="13.847619047619"/>
+    <col min="64" max="64" customWidth="true" width="11.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -17850,7 +17919,7 @@
       <c r="BP1" s="40"/>
       <c r="BQ1" s="40"/>
     </row>
-    <row r="2" ht="15.15" spans="1:69">
+    <row r="2" ht="15.75" spans="1:69">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -17945,7 +18014,7 @@
       <c r="BP2" s="40"/>
       <c r="BQ2" s="40"/>
     </row>
-    <row r="3" ht="59.1" spans="1:69">
+    <row r="3" ht="61.5" spans="1:69">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
@@ -18154,7 +18223,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.15" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="7">
         <v>1</v>
       </c>
@@ -18173,14 +18242,14 @@
       <c r="F4" s="8">
         <v>5</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H4" s="8">
         <f t="shared" ref="H4:H6" si="0">F4*G4</f>
         <v>250</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J4" s="8">
@@ -18318,10 +18387,10 @@
       <c r="AT4" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AU4" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AV4" t="s" s="0">
         <v>179</v>
       </c>
       <c r="AW4" s="39">
@@ -18362,10 +18431,10 @@
       <c r="BL4" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>89</v>
       </c>
       <c r="BO4" s="39">
@@ -18380,7 +18449,7 @@
         <v>123562</v>
       </c>
     </row>
-    <row r="5" ht="15.15" spans="1:69">
+    <row r="5" ht="15.75" spans="1:69">
       <c r="A5" s="7">
         <v>1</v>
       </c>
@@ -18399,14 +18468,14 @@
       <c r="F5" s="8">
         <v>4</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" t="s" s="0">
         <v>92</v>
       </c>
       <c r="H5" s="8">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" t="s" s="0">
         <v>93</v>
       </c>
       <c r="J5" s="8">
@@ -18544,10 +18613,10 @@
       <c r="AT5" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AU5" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AV5" t="s" s="0">
         <v>130</v>
       </c>
       <c r="AW5" s="39">
@@ -18588,10 +18657,10 @@
       <c r="BL5" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BM5" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BN5" t="s" s="0">
         <v>97</v>
       </c>
       <c r="BO5" s="39">
@@ -18606,7 +18675,7 @@
         <v>123562</v>
       </c>
     </row>
-    <row r="6" ht="15.15" spans="1:69">
+    <row r="6" ht="15.75" spans="1:69">
       <c r="A6" s="7">
         <v>1</v>
       </c>
@@ -18625,14 +18694,14 @@
       <c r="F6" s="8">
         <v>20</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H6" s="8">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" t="s" s="0">
         <v>101</v>
       </c>
       <c r="J6" s="8">
@@ -18770,10 +18839,10 @@
       <c r="AT6" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AU6" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="AV6" t="s">
+      <c r="AV6" t="s" s="0">
         <v>132</v>
       </c>
       <c r="AW6" s="39">
@@ -18814,10 +18883,10 @@
       <c r="BL6" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM6" t="s">
+      <c r="BM6" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="BN6" t="s">
+      <c r="BN6" t="s" s="0">
         <v>105</v>
       </c>
       <c r="BO6" s="39">
@@ -18832,7 +18901,7 @@
         <v>123562</v>
       </c>
     </row>
-    <row r="7" ht="15.15" spans="1:69">
+    <row r="7" ht="15.75" spans="1:69">
       <c r="A7" s="9"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -18950,7 +19019,7 @@
       <c r="BP7" s="40"/>
       <c r="BQ7" s="40"/>
     </row>
-    <row r="8" ht="15.15" spans="1:69">
+    <row r="8" ht="15.75" spans="1:69">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -19021,7 +19090,7 @@
       <c r="BP8" s="40"/>
       <c r="BQ8" s="40"/>
     </row>
-    <row r="9" ht="15.15" spans="1:69">
+    <row r="9" ht="15.75" spans="1:69">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -19103,7 +19172,7 @@
       <c r="BP9" s="40"/>
       <c r="BQ9" s="40"/>
     </row>
-    <row r="10" ht="15.15" spans="1:69">
+    <row r="10" ht="15.75" spans="1:69">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -19191,7 +19260,7 @@
       <c r="BP10" s="40"/>
       <c r="BQ10" s="40"/>
     </row>
-    <row r="11" ht="15.15" spans="1:69">
+    <row r="11" ht="15.75" spans="1:69">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -19275,7 +19344,7 @@
       <c r="BP11" s="40"/>
       <c r="BQ11" s="40"/>
     </row>
-    <row r="12" ht="15.15" spans="1:69">
+    <row r="12" ht="15.75" spans="1:69">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -19359,7 +19428,7 @@
       <c r="BP12" s="40"/>
       <c r="BQ12" s="40"/>
     </row>
-    <row r="13" ht="15.15" spans="1:69">
+    <row r="13" ht="15.75" spans="1:69">
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -19997,13 +20066,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ20"/>
-  <sheetFormatPr defaultColWidth="8.85185185185185" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.84761904761905" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="13" max="13" width="9.13888888888889" customWidth="1"/>
-    <col min="14" max="14" width="13.8518518518519" customWidth="1"/>
-    <col min="64" max="64" width="11" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="28.0"/>
+    <col min="3" max="3" customWidth="true" width="23.0"/>
+    <col min="13" max="13" customWidth="true" width="9.14285714285714"/>
+    <col min="14" max="14" customWidth="true" width="13.847619047619"/>
+    <col min="29" max="29" width="9.28571428571429"/>
+    <col min="35" max="35" width="11.4285714285714"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="64" max="64" customWidth="true" width="11.0"/>
+    <col min="67" max="67" width="12.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -20079,7 +20152,7 @@
       <c r="BP1" s="40"/>
       <c r="BQ1" s="40"/>
     </row>
-    <row r="2" ht="15.15" spans="1:69">
+    <row r="2" ht="15.75" spans="1:69">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -20174,7 +20247,7 @@
       <c r="BP2" s="40"/>
       <c r="BQ2" s="40"/>
     </row>
-    <row r="3" ht="59.1" spans="1:69">
+    <row r="3" ht="61.5" spans="1:69">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
@@ -20383,7 +20456,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.15" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="7">
         <v>1</v>
       </c>
@@ -20400,16 +20473,16 @@
         <v>77</v>
       </c>
       <c r="F4" s="8">
-        <v>5</v>
-      </c>
-      <c r="G4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" t="s" s="0">
         <v>78</v>
       </c>
       <c r="H4" s="8">
         <f t="shared" ref="H4:H6" si="0">F4*G4</f>
-        <v>750</v>
-      </c>
-      <c r="I4" t="s">
+        <v>450</v>
+      </c>
+      <c r="I4" t="s" s="0">
         <v>79</v>
       </c>
       <c r="J4" s="8">
@@ -20420,35 +20493,35 @@
       </c>
       <c r="L4" s="8">
         <f t="shared" ref="L4:L6" si="1">IF(OR(I4=0,I4="0"),0,H4)</f>
-        <v>750</v>
+        <v>450</v>
       </c>
       <c r="M4" s="8">
         <f>ROUND(L4*I4%,3)</f>
-        <v>37.5</v>
+        <v>22.5</v>
       </c>
       <c r="N4" s="8">
         <f t="shared" ref="N4:N6" si="2">H4-M4</f>
-        <v>712.5</v>
+        <v>427.5</v>
       </c>
       <c r="O4" s="8">
         <f>ROUND(N4*J4%,3)</f>
-        <v>57</v>
+        <v>34.2</v>
       </c>
       <c r="P4" s="8">
         <f t="shared" ref="P4:P6" si="3">ROUND(N4-O4,2)</f>
-        <v>655.5</v>
+        <v>393.3</v>
       </c>
       <c r="Q4" s="8">
         <f t="shared" ref="Q4:Q6" si="4">ROUND(P4*K4%,2)</f>
-        <v>32.78</v>
+        <v>19.67</v>
       </c>
       <c r="R4" s="26">
         <f>ROUND(M4+O4+Q4,3)</f>
-        <v>127.28</v>
+        <v>76.37</v>
       </c>
       <c r="S4" s="26">
         <f t="shared" ref="S4:S6" si="5">(H4-R4)</f>
-        <v>622.72</v>
+        <v>373.63</v>
       </c>
       <c r="T4" s="8">
         <v>88363222</v>
@@ -20485,7 +20558,7 @@
       </c>
       <c r="AC4" s="31">
         <f>IF($V2=1,S4+AB4,S4)</f>
-        <v>622.72</v>
+        <v>373.63</v>
       </c>
       <c r="AD4" s="26">
         <v>120</v>
@@ -20505,7 +20578,7 @@
       </c>
       <c r="AI4" s="26">
         <f>S4*$M2</f>
-        <v>52931.2</v>
+        <v>31758.55</v>
       </c>
       <c r="AJ4" s="26">
         <f>IF($C$2=3,0,AG4+AH4)</f>
@@ -20520,11 +20593,11 @@
       </c>
       <c r="AM4" s="26">
         <f t="shared" ref="AM4:AM6" si="7">F4/AL4</f>
-        <v>1.66666666666667</v>
+        <v>1</v>
       </c>
       <c r="AN4" s="26">
         <f t="shared" ref="AN4:AN6" si="8">ROUND(AI4/AM4,5)</f>
-        <v>31758.72</v>
+        <v>31758.55</v>
       </c>
       <c r="AO4" s="26">
         <f t="shared" ref="AO4:AO6" si="9">AJ4/AM4</f>
@@ -20539,7 +20612,7 @@
       </c>
       <c r="AR4" s="26">
         <f t="shared" ref="AR4:AR6" si="11">ROUND(AN4+AO4+AP4,5)</f>
-        <v>31758.72</v>
+        <v>31758.55</v>
       </c>
       <c r="AS4" s="38" t="s">
         <v>80</v>
@@ -20547,27 +20620,27 @@
       <c r="AT4" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AU4" t="s" s="0">
         <v>206</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AV4" t="s" s="0">
         <v>207</v>
       </c>
       <c r="AW4" s="39">
         <f t="shared" ref="AW4:AW6" si="12">AM4</f>
-        <v>1.66666666666667</v>
+        <v>1</v>
       </c>
       <c r="AX4" s="42">
         <f t="shared" ref="AX4:AX6" si="13">AR4</f>
-        <v>31758.72</v>
+        <v>31758.55</v>
       </c>
       <c r="AY4" s="39">
         <f t="shared" ref="AY4:AY6" si="14">AU4+AW4</f>
-        <v>63.3276666666667</v>
-      </c>
-      <c r="AZ4" s="43">
-        <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),3)</f>
-        <v>11936.857</v>
+        <v>64.328</v>
+      </c>
+      <c r="AZ4" s="39">
+        <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),5)</f>
+        <v>12245.10105</v>
       </c>
       <c r="BA4" s="44"/>
       <c r="BB4" s="44" t="s">
@@ -20591,25 +20664,25 @@
       <c r="BL4" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>89</v>
       </c>
       <c r="BO4" s="39">
         <f t="shared" ref="BO4:BO6" si="15">ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
-        <v>365.61259</v>
+        <v>274.18149</v>
       </c>
       <c r="BP4" s="48">
         <f t="shared" ref="BP4:BP6" si="16">ROUND(BN4+AW4,3)</f>
-        <v>81.667</v>
+        <v>81</v>
       </c>
       <c r="BQ4" s="49">
         <v>123562</v>
       </c>
     </row>
-    <row r="5" ht="15.15" spans="1:69">
+    <row r="5" ht="15.75" spans="1:69">
       <c r="A5" s="7">
         <v>1</v>
       </c>
@@ -20626,16 +20699,16 @@
         <v>77</v>
       </c>
       <c r="F5" s="8">
-        <v>4</v>
-      </c>
-      <c r="G5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" t="s" s="0">
         <v>92</v>
       </c>
       <c r="H5" s="8">
         <f t="shared" si="0"/>
-        <v>400</v>
-      </c>
-      <c r="I5" t="s">
+        <v>900</v>
+      </c>
+      <c r="I5" t="s" s="0">
         <v>93</v>
       </c>
       <c r="J5" s="8">
@@ -20646,35 +20719,35 @@
       </c>
       <c r="L5" s="8">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="M5" s="8">
         <f>ROUND(L5*I5%,2)</f>
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="N5" s="8">
         <f t="shared" si="2"/>
-        <v>384</v>
+        <v>864</v>
       </c>
       <c r="O5" s="8">
         <f>ROUND(N5*J5%,2)</f>
-        <v>34.56</v>
+        <v>77.76</v>
       </c>
       <c r="P5" s="8">
         <f t="shared" si="3"/>
-        <v>349.44</v>
+        <v>786.24</v>
       </c>
       <c r="Q5" s="8">
         <f t="shared" si="4"/>
-        <v>20.97</v>
+        <v>47.17</v>
       </c>
       <c r="R5" s="8">
         <f>M5+O5+Q5</f>
-        <v>71.53</v>
+        <v>160.93</v>
       </c>
       <c r="S5" s="8">
         <f t="shared" si="5"/>
-        <v>328.47</v>
+        <v>739.07</v>
       </c>
       <c r="T5" s="8">
         <v>88363222</v>
@@ -20683,26 +20756,26 @@
         <v>18</v>
       </c>
       <c r="V5" s="8">
-        <f>IF(OR(DGDUomWIPlImp!$C$2=1,DGDUomWIPlImp!$C$2=4),ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF(OR($C$2=1,$C$2=4),ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="W5" s="8">
-        <f>IF(DGDUomWIPlImp!$C$2=1,ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF($C$2=1,ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="X5" s="8">
-        <f>IF(DGDUomWIPlImp!$C$2=2,ROUND(((S5*U5)/100),2),0)</f>
+        <f>IF($C$2=2,ROUND(((S5*U5)/100),2),0)</f>
         <v>0</v>
       </c>
       <c r="Y5" s="8">
-        <f>IF(DGDUomWIPlImp!$C$2=4,ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF($C$2=4,ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="Z5" s="8">
         <v>0</v>
       </c>
       <c r="AA5" s="8">
-        <f>IF(DGDUomWIPlImp!$C3=3,0,(S5*Z5)/100)</f>
+        <f>IF($C3=3,0,(S5*Z5)/100)</f>
         <v>0</v>
       </c>
       <c r="AB5" s="8">
@@ -20710,35 +20783,35 @@
         <v>0</v>
       </c>
       <c r="AC5" s="8">
-        <f>IF(DGDUomWIPlImp!$V3=1,S5+AB5,S5)</f>
-        <v>328.47</v>
+        <f>IF($V3=1,S5+AB5,S5)</f>
+        <v>739.07</v>
       </c>
       <c r="AD5" s="26">
         <v>120</v>
       </c>
       <c r="AE5" s="26">
-        <f>IF(DGDUomWIPlImp!$P$2=1,(S5/DGDUomWIPlImp!$S$7)*DGDUomWIPlImp!$E$18,AD5/DGDUomWIPlImp!$AD$7*DGDUomWIPlImp!$E$18)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$18,AD5/$AD$7*$E$18)</f>
         <v>0</v>
       </c>
       <c r="AF5" s="26"/>
       <c r="AG5" s="26">
-        <f>IF(DGDUomWIPlImp!$P$2=1,(S5/DGDUomWIPlImp!$S$7)*DGDUomWIPlImp!$E$20,AD5/DGDUomWIPlImp!$AD$7*DGDUomWIPlImp!$E$20)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$20,AD5/$AD$7*$E$20)</f>
         <v>0</v>
       </c>
       <c r="AH5" s="26">
-        <f>IF(DGDUomWIPlImp!$P$2=1,(S5/DGDUomWIPlImp!$S$7)*DGDUomWIPlImp!$E$21,AD5/DGDUomWIPlImp!$AD$7*DGDUomWIPlImp!$E$21)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$21,AD5/$AD$7*$E$21)</f>
         <v>0</v>
       </c>
       <c r="AI5" s="26">
-        <f>S5*DGDUomWIPlImp!$M$2</f>
-        <v>27919.95</v>
+        <f>S5*$M$2</f>
+        <v>62820.95</v>
       </c>
       <c r="AJ5" s="26">
-        <f>IF(DGDUomWIPlImp!$C$2=3,0,AG5+AH5)</f>
+        <f>IF($C$2=3,0,AG5+AH5)</f>
         <v>0</v>
       </c>
       <c r="AK5" s="26">
-        <f>IF(DGDUomWIPlImp!$C$2=3,AE5+AG5+AH5,0)</f>
+        <f>IF($C$2=3,AE5+AG5+AH5,0)</f>
         <v>0</v>
       </c>
       <c r="AL5" s="34">
@@ -20746,11 +20819,11 @@
       </c>
       <c r="AM5" s="26">
         <f t="shared" si="7"/>
-        <v>1.33333333333333</v>
+        <v>3</v>
       </c>
       <c r="AN5" s="26">
         <f t="shared" si="8"/>
-        <v>20939.9625</v>
+        <v>20940.31667</v>
       </c>
       <c r="AO5" s="26">
         <f t="shared" si="9"/>
@@ -20765,7 +20838,7 @@
       </c>
       <c r="AR5" s="26">
         <f t="shared" si="11"/>
-        <v>20939.9625</v>
+        <v>20940.31667</v>
       </c>
       <c r="AS5" s="38" t="s">
         <v>80</v>
@@ -20773,27 +20846,27 @@
       <c r="AT5" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AU5" t="s" s="0">
         <v>209</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AV5" t="s" s="0">
         <v>210</v>
       </c>
       <c r="AW5" s="39">
         <f t="shared" si="12"/>
-        <v>1.33333333333333</v>
+        <v>3</v>
       </c>
       <c r="AX5" s="42">
         <f t="shared" si="13"/>
-        <v>20939.9625</v>
+        <v>20940.31667</v>
       </c>
       <c r="AY5" s="39">
         <f t="shared" si="14"/>
-        <v>100.999333333333</v>
-      </c>
-      <c r="AZ5" s="42">
-        <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),2)</f>
-        <v>6939.51</v>
+        <v>103.999</v>
+      </c>
+      <c r="AZ5" s="39">
+        <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),5)</f>
+        <v>7343.35048</v>
       </c>
       <c r="BA5" s="44"/>
       <c r="BB5" s="44" t="s">
@@ -20817,25 +20890,25 @@
       <c r="BL5" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BM5" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BN5" t="s" s="0">
         <v>97</v>
       </c>
       <c r="BO5" s="39">
         <f t="shared" si="15"/>
-        <v>231.1937</v>
+        <v>427.89288</v>
       </c>
       <c r="BP5" s="48">
         <f t="shared" si="16"/>
-        <v>61.333</v>
+        <v>63</v>
       </c>
       <c r="BQ5" s="49">
         <v>123562</v>
       </c>
     </row>
-    <row r="6" ht="15.15" spans="1:69">
+    <row r="6" ht="15.75" spans="1:69">
       <c r="A6" s="7">
         <v>1</v>
       </c>
@@ -20852,16 +20925,16 @@
         <v>77</v>
       </c>
       <c r="F6" s="8">
-        <v>20</v>
-      </c>
-      <c r="G6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H6" s="8">
         <f t="shared" si="0"/>
-        <v>1000</v>
-      </c>
-      <c r="I6" t="s">
+        <v>600</v>
+      </c>
+      <c r="I6" t="s" s="0">
         <v>101</v>
       </c>
       <c r="J6" s="8">
@@ -20872,35 +20945,35 @@
       </c>
       <c r="L6" s="8">
         <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="M6" s="8">
         <f>ROUND(L6*I6%,2)</f>
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="N6" s="8">
         <f t="shared" si="2"/>
-        <v>970</v>
+        <v>582</v>
       </c>
       <c r="O6" s="8">
         <f>ROUND(N6*J6%,2)</f>
-        <v>67.9</v>
+        <v>40.74</v>
       </c>
       <c r="P6" s="8">
         <f t="shared" si="3"/>
-        <v>902.1</v>
+        <v>541.26</v>
       </c>
       <c r="Q6" s="8">
         <f t="shared" si="4"/>
-        <v>36.08</v>
+        <v>21.65</v>
       </c>
       <c r="R6" s="8">
         <f>M6+O6+Q6</f>
-        <v>133.98</v>
+        <v>80.39</v>
       </c>
       <c r="S6" s="8">
         <f t="shared" si="5"/>
-        <v>866.02</v>
+        <v>519.61</v>
       </c>
       <c r="T6" s="8">
         <v>88363222</v>
@@ -20909,26 +20982,26 @@
         <v>18</v>
       </c>
       <c r="V6" s="8">
-        <f>IF(OR(DGDUomWIPlImp!$C$2=1,DGDUomWIPlImp!$C$2=4),ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF(OR($C$2=1,$C$2=4),ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="W6" s="8">
-        <f>IF(DGDUomWIPlImp!$C$2=1,ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF($C$2=1,ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="X6" s="8">
-        <f>IF(DGDUomWIPlImp!$C$2=2,ROUND(((S6*U6)/100),2),0)</f>
+        <f>IF($C$2=2,ROUND(((S6*U6)/100),2),0)</f>
         <v>0</v>
       </c>
       <c r="Y6" s="8">
-        <f>IF(DGDUomWIPlImp!$C$2=4,ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF($C$2=4,ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="Z6" s="8">
         <v>0</v>
       </c>
       <c r="AA6" s="8">
-        <f>IF(DGDUomWIPlImp!$C4=3,0,(S6*Z6)/100)</f>
+        <f>IF($C4=3,0,(S6*Z6)/100)</f>
         <v>0</v>
       </c>
       <c r="AB6" s="8">
@@ -20936,35 +21009,35 @@
         <v>0</v>
       </c>
       <c r="AC6" s="8">
-        <f>IF(DGDUomWIPlImp!$V4=1,S6+AB6,S6)</f>
-        <v>866.02</v>
+        <f>IF($V4=1,S6+AB6,S6)</f>
+        <v>519.61</v>
       </c>
       <c r="AD6" s="26">
         <v>120</v>
       </c>
       <c r="AE6" s="26">
-        <f>IF(DGDUomWIPlImp!$P$2=1,(S6/DGDUomWIPlImp!$S$7)*DGDUomWIPlImp!$E$18,AD6/DGDUomWIPlImp!$AD$7*DGDUomWIPlImp!$E$18)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$18,AD6/$AD$7*$E$18)</f>
         <v>0</v>
       </c>
       <c r="AF6" s="26"/>
       <c r="AG6" s="26">
-        <f>IF(DGDUomWIPlImp!$P$2=1,(S6/DGDUomWIPlImp!$S$7)*DGDUomWIPlImp!$E$20,AD6/DGDUomWIPlImp!$AD$7*DGDUomWIPlImp!$E$20)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$20,AD6/$AD$7*$E$20)</f>
         <v>0</v>
       </c>
       <c r="AH6" s="26">
-        <f>IF(DGDUomWIPlImp!$P$2=1,(S6/DGDUomWIPlImp!$S$7)*DGDUomWIPlImp!$E$21,AD6/DGDUomWIPlImp!$AD$7*DGDUomWIPlImp!$E$21)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$21,AD6/$AD$7*$E$21)</f>
         <v>0</v>
       </c>
       <c r="AI6" s="26">
-        <f>S6*DGDUomWIPlImp!$M$2</f>
-        <v>73611.7</v>
+        <f>S6*$M$2</f>
+        <v>44166.85</v>
       </c>
       <c r="AJ6" s="26">
-        <f>IF(DGDUomWIPlImp!$C$2=3,0,AG6+AH6)</f>
+        <f>IF($C$2=3,0,AG6+AH6)</f>
         <v>0</v>
       </c>
       <c r="AK6" s="26">
-        <f>IF(DGDUomWIPlImp!$C$2=3,AE6+AG6+AH6,0)</f>
+        <f>IF($C$2=3,AE6+AG6+AH6,0)</f>
         <v>0</v>
       </c>
       <c r="AL6" s="34">
@@ -20972,11 +21045,11 @@
       </c>
       <c r="AM6" s="26">
         <f t="shared" si="7"/>
-        <v>6.66666666666667</v>
+        <v>4</v>
       </c>
       <c r="AN6" s="26">
         <f t="shared" si="8"/>
-        <v>11041.755</v>
+        <v>11041.7125</v>
       </c>
       <c r="AO6" s="26">
         <f t="shared" si="9"/>
@@ -20991,7 +21064,7 @@
       </c>
       <c r="AR6" s="26">
         <f t="shared" si="11"/>
-        <v>11041.755</v>
+        <v>11041.7125</v>
       </c>
       <c r="AS6" s="38" t="s">
         <v>80</v>
@@ -20999,27 +21072,27 @@
       <c r="AT6" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AU6" t="s" s="0">
         <v>212</v>
       </c>
-      <c r="AV6" t="s">
+      <c r="AV6" t="s" s="0">
         <v>213</v>
       </c>
       <c r="AW6" s="39">
         <f t="shared" si="12"/>
-        <v>6.66666666666667</v>
+        <v>4</v>
       </c>
       <c r="AX6" s="39">
         <f t="shared" si="13"/>
-        <v>11041.755</v>
+        <v>11041.7125</v>
       </c>
       <c r="AY6" s="39">
         <f t="shared" si="14"/>
-        <v>79.9936666666667</v>
+        <v>83.994</v>
       </c>
       <c r="AZ6" s="39">
-        <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),1)</f>
-        <v>4676.6</v>
+        <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),5)</f>
+        <v>4979.68333</v>
       </c>
       <c r="BA6" s="44"/>
       <c r="BB6" s="44" t="s">
@@ -21043,25 +21116,25 @@
       <c r="BL6" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM6" t="s">
+      <c r="BM6" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="BN6" t="s">
+      <c r="BN6" t="s" s="0">
         <v>105</v>
       </c>
       <c r="BO6" s="39">
         <f t="shared" si="15"/>
-        <v>144.02391</v>
+        <v>108.25241</v>
       </c>
       <c r="BP6" s="48">
         <f t="shared" si="16"/>
-        <v>306.667</v>
+        <v>304</v>
       </c>
       <c r="BQ6" s="49">
         <v>123562</v>
       </c>
     </row>
-    <row r="7" ht="15.15" spans="1:69">
+    <row r="7" ht="15.75" spans="1:69">
       <c r="A7" s="9"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -21073,7 +21146,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="13">
         <f>SUM(H4:H4)</f>
-        <v>750</v>
+        <v>450</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
@@ -21086,11 +21159,11 @@
       <c r="Q7" s="7"/>
       <c r="R7" s="27">
         <f t="shared" ref="R7:X7" si="17">SUM(R4:R4)</f>
-        <v>127.28</v>
+        <v>76.37</v>
       </c>
       <c r="S7" s="13">
         <f t="shared" si="17"/>
-        <v>622.72</v>
+        <v>373.63</v>
       </c>
       <c r="T7" s="27"/>
       <c r="U7" s="27"/>
@@ -21115,7 +21188,7 @@
       </c>
       <c r="AC7" s="32">
         <f t="shared" si="18"/>
-        <v>622.72</v>
+        <v>373.63</v>
       </c>
       <c r="AD7" s="33">
         <f t="shared" si="18"/>
@@ -21136,7 +21209,7 @@
       </c>
       <c r="AI7" s="33">
         <f t="shared" si="19"/>
-        <v>52931.2</v>
+        <v>31758.55</v>
       </c>
       <c r="AJ7" s="33">
         <f t="shared" si="19"/>
@@ -21179,7 +21252,7 @@
       <c r="BP7" s="40"/>
       <c r="BQ7" s="40"/>
     </row>
-    <row r="8" ht="15.15" spans="1:69">
+    <row r="8" ht="15.75" spans="1:69">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -21250,7 +21323,7 @@
       <c r="BP8" s="40"/>
       <c r="BQ8" s="40"/>
     </row>
-    <row r="9" ht="15.15" spans="1:69">
+    <row r="9" ht="15.75" spans="1:69">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -21263,7 +21336,7 @@
       <c r="H9" s="15"/>
       <c r="I9" s="19">
         <f>H7</f>
-        <v>750</v>
+        <v>450</v>
       </c>
       <c r="J9" s="19"/>
       <c r="K9" s="9"/>
@@ -21332,7 +21405,7 @@
       <c r="BP9" s="40"/>
       <c r="BQ9" s="40"/>
     </row>
-    <row r="10" ht="15.15" spans="1:69">
+    <row r="10" ht="15.75" spans="1:69">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -21345,7 +21418,7 @@
       <c r="H10" s="15"/>
       <c r="I10" s="19">
         <f>R7</f>
-        <v>127.28</v>
+        <v>76.37</v>
       </c>
       <c r="J10" s="19"/>
       <c r="K10" s="9"/>
@@ -21420,7 +21493,7 @@
       <c r="BP10" s="40"/>
       <c r="BQ10" s="40"/>
     </row>
-    <row r="11" ht="15.15" spans="1:69">
+    <row r="11" ht="15.75" spans="1:69">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -21433,7 +21506,7 @@
       <c r="H11" s="15"/>
       <c r="I11" s="19">
         <f>S7</f>
-        <v>622.72</v>
+        <v>373.63</v>
       </c>
       <c r="J11" s="19"/>
       <c r="K11" s="9"/>
@@ -21504,7 +21577,7 @@
       <c r="BP11" s="40"/>
       <c r="BQ11" s="40"/>
     </row>
-    <row r="12" ht="15.15" spans="1:69">
+    <row r="12" ht="15.75" spans="1:69">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -21588,7 +21661,7 @@
       <c r="BP12" s="40"/>
       <c r="BQ12" s="40"/>
     </row>
-    <row r="13" ht="15.15" spans="1:69">
+    <row r="13" ht="15.75" spans="1:69">
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -21601,7 +21674,7 @@
       <c r="H13" s="15"/>
       <c r="I13" s="24">
         <f>I11+I12</f>
-        <v>622.72</v>
+        <v>373.63</v>
       </c>
       <c r="J13" s="24"/>
       <c r="K13" s="9"/>
@@ -22226,13 +22299,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ20"/>
-  <sheetFormatPr defaultColWidth="8.85185185185185" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.84761904761905" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="29.4444444444444" customWidth="1"/>
-    <col min="13" max="13" width="9.13888888888889" customWidth="1"/>
-    <col min="14" max="14" width="13.8518518518519" customWidth="1"/>
-    <col min="64" max="64" width="11" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="28.0"/>
+    <col min="3" max="3" customWidth="true" width="29.447619047619"/>
+    <col min="13" max="13" customWidth="true" width="9.14285714285714"/>
+    <col min="14" max="14" customWidth="true" width="13.847619047619"/>
+    <col min="64" max="64" customWidth="true" width="11.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -22308,7 +22381,7 @@
       <c r="BP1" s="40"/>
       <c r="BQ1" s="40"/>
     </row>
-    <row r="2" ht="15.15" spans="1:69">
+    <row r="2" ht="15.75" spans="1:69">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -22403,7 +22476,7 @@
       <c r="BP2" s="40"/>
       <c r="BQ2" s="40"/>
     </row>
-    <row r="3" ht="59.1" spans="1:69">
+    <row r="3" ht="61.5" spans="1:69">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
@@ -22612,7 +22685,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.15" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="7">
         <v>1</v>
       </c>
@@ -22631,14 +22704,14 @@
       <c r="F4" s="8">
         <v>5</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="0">
         <v>50</v>
       </c>
       <c r="H4" s="8">
         <f t="shared" ref="H4:H6" si="0">F4*G4</f>
         <v>250</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="0">
         <v>0</v>
       </c>
       <c r="J4" s="8">
@@ -22776,10 +22849,10 @@
       <c r="AT4" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AU4" t="s" s="0">
         <v>206</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AV4" t="s" s="0">
         <v>207</v>
       </c>
       <c r="AW4" s="39">
@@ -22820,10 +22893,10 @@
       <c r="BL4" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>89</v>
       </c>
       <c r="BO4" s="39">
@@ -22838,7 +22911,7 @@
         <v>123562</v>
       </c>
     </row>
-    <row r="5" ht="15.15" spans="1:69">
+    <row r="5" ht="15.75" spans="1:69">
       <c r="A5" s="7">
         <v>1</v>
       </c>
@@ -22857,14 +22930,14 @@
       <c r="F5" s="8">
         <v>4</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" t="s" s="0">
         <v>92</v>
       </c>
       <c r="H5" s="8">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" t="s" s="0">
         <v>93</v>
       </c>
       <c r="J5" s="8">
@@ -23002,10 +23075,10 @@
       <c r="AT5" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AU5" t="s" s="0">
         <v>209</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AV5" t="s" s="0">
         <v>210</v>
       </c>
       <c r="AW5" s="39">
@@ -23046,10 +23119,10 @@
       <c r="BL5" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BM5" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BN5" t="s" s="0">
         <v>97</v>
       </c>
       <c r="BO5" s="39">
@@ -23064,7 +23137,7 @@
         <v>123562</v>
       </c>
     </row>
-    <row r="6" ht="15.15" spans="1:69">
+    <row r="6" ht="15.75" spans="1:69">
       <c r="A6" s="7">
         <v>1</v>
       </c>
@@ -23083,14 +23156,14 @@
       <c r="F6" s="8">
         <v>20</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H6" s="8">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" t="s" s="0">
         <v>101</v>
       </c>
       <c r="J6" s="8">
@@ -23228,10 +23301,10 @@
       <c r="AT6" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AU6" t="s" s="0">
         <v>212</v>
       </c>
-      <c r="AV6" t="s">
+      <c r="AV6" t="s" s="0">
         <v>213</v>
       </c>
       <c r="AW6" s="39">
@@ -23272,10 +23345,10 @@
       <c r="BL6" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM6" t="s">
+      <c r="BM6" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="BN6" t="s">
+      <c r="BN6" t="s" s="0">
         <v>105</v>
       </c>
       <c r="BO6" s="39">
@@ -23290,7 +23363,7 @@
         <v>123562</v>
       </c>
     </row>
-    <row r="7" ht="15.15" spans="1:69">
+    <row r="7" ht="15.75" spans="1:69">
       <c r="A7" s="9"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -23408,7 +23481,7 @@
       <c r="BP7" s="40"/>
       <c r="BQ7" s="40"/>
     </row>
-    <row r="8" ht="15.15" spans="1:69">
+    <row r="8" ht="15.75" spans="1:69">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -23479,7 +23552,7 @@
       <c r="BP8" s="40"/>
       <c r="BQ8" s="40"/>
     </row>
-    <row r="9" ht="15.15" spans="1:69">
+    <row r="9" ht="15.75" spans="1:69">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -23561,7 +23634,7 @@
       <c r="BP9" s="40"/>
       <c r="BQ9" s="40"/>
     </row>
-    <row r="10" ht="15.15" spans="1:69">
+    <row r="10" ht="15.75" spans="1:69">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -23649,7 +23722,7 @@
       <c r="BP10" s="40"/>
       <c r="BQ10" s="40"/>
     </row>
-    <row r="11" ht="15.15" spans="1:69">
+    <row r="11" ht="15.75" spans="1:69">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -23733,7 +23806,7 @@
       <c r="BP11" s="40"/>
       <c r="BQ11" s="40"/>
     </row>
-    <row r="12" ht="15.15" spans="1:69">
+    <row r="12" ht="15.75" spans="1:69">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -23817,7 +23890,7 @@
       <c r="BP12" s="40"/>
       <c r="BQ12" s="40"/>
     </row>
-    <row r="13" ht="15.15" spans="1:69">
+    <row r="13" ht="15.75" spans="1:69">
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -24455,15 +24528,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ20"/>
-  <sheetFormatPr defaultColWidth="8.85185185185185" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.84761904761905" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="3" width="32.1388888888889" customWidth="1"/>
-    <col min="13" max="13" width="9.13888888888889" customWidth="1"/>
-    <col min="14" max="14" width="13.8518518518519" customWidth="1"/>
-    <col min="35" max="35" width="14.712962962963" customWidth="1"/>
-    <col min="51" max="51" width="14.5740740740741" customWidth="1"/>
-    <col min="52" max="52" width="19.4259259259259" customWidth="1"/>
-    <col min="64" max="64" width="11" customWidth="1"/>
+    <col min="2" max="3" customWidth="true" width="32.1428571428571"/>
+    <col min="13" max="13" customWidth="true" width="9.14285714285714"/>
+    <col min="14" max="14" customWidth="true" width="13.847619047619"/>
+    <col min="29" max="29" width="9.28571428571429"/>
+    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
+    <col min="51" max="51" customWidth="true" width="14.5714285714286"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="64" max="64" customWidth="true" width="11.0"/>
+    <col min="67" max="67" width="12.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -24539,7 +24614,7 @@
       <c r="BP1" s="40"/>
       <c r="BQ1" s="40"/>
     </row>
-    <row r="2" ht="15.15" spans="1:69">
+    <row r="2" ht="15.75" spans="1:69">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -24634,7 +24709,7 @@
       <c r="BP2" s="40"/>
       <c r="BQ2" s="40"/>
     </row>
-    <row r="3" ht="59.1" spans="1:69">
+    <row r="3" ht="61.5" spans="1:69">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
@@ -24843,7 +24918,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.15" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="7">
         <v>1</v>
       </c>
@@ -24860,16 +24935,16 @@
         <v>77</v>
       </c>
       <c r="F4" s="8">
-        <v>5</v>
-      </c>
-      <c r="G4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" t="s" s="0">
         <v>78</v>
       </c>
       <c r="H4" s="8">
         <f t="shared" ref="H4:H6" si="0">F4*G4</f>
-        <v>750</v>
-      </c>
-      <c r="I4" t="s">
+        <v>450</v>
+      </c>
+      <c r="I4" t="s" s="0">
         <v>79</v>
       </c>
       <c r="J4" s="8">
@@ -24880,35 +24955,35 @@
       </c>
       <c r="L4" s="8">
         <f t="shared" ref="L4:L6" si="1">IF(OR(I4=0,I4="0"),0,H4)</f>
-        <v>750</v>
+        <v>450</v>
       </c>
       <c r="M4" s="8">
         <f>ROUND(L4*I4%,3)</f>
-        <v>37.5</v>
+        <v>22.5</v>
       </c>
       <c r="N4" s="8">
         <f t="shared" ref="N4:N6" si="2">H4-M4</f>
-        <v>712.5</v>
+        <v>427.5</v>
       </c>
       <c r="O4" s="8">
         <f>ROUND(N4*J4%,3)</f>
-        <v>57</v>
+        <v>34.2</v>
       </c>
       <c r="P4" s="8">
         <f t="shared" ref="P4:P6" si="3">ROUND(N4-O4,2)</f>
-        <v>655.5</v>
+        <v>393.3</v>
       </c>
       <c r="Q4" s="8">
         <f t="shared" ref="Q4:Q6" si="4">ROUND(P4*K4%,2)</f>
-        <v>32.78</v>
+        <v>19.67</v>
       </c>
       <c r="R4" s="26">
         <f>ROUND(M4+O4+Q4,3)</f>
-        <v>127.28</v>
+        <v>76.37</v>
       </c>
       <c r="S4" s="26">
         <f t="shared" ref="S4:S6" si="5">(H4-R4)</f>
-        <v>622.72</v>
+        <v>373.63</v>
       </c>
       <c r="T4" s="8">
         <v>88363222</v>
@@ -24945,7 +25020,7 @@
       </c>
       <c r="AC4" s="31">
         <f>IF($V2=1,S4+AB4,S4)</f>
-        <v>622.72</v>
+        <v>373.63</v>
       </c>
       <c r="AD4" s="26">
         <v>120</v>
@@ -24965,7 +25040,7 @@
       </c>
       <c r="AI4" s="26">
         <f>S4*$M2</f>
-        <v>52931.2</v>
+        <v>31758.55</v>
       </c>
       <c r="AJ4" s="26">
         <f>IF($C$2=3,0,AG4+AH4)</f>
@@ -24980,11 +25055,11 @@
       </c>
       <c r="AM4" s="26">
         <f t="shared" ref="AM4:AM6" si="7">F4/AL4</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AN4" s="26">
         <f t="shared" ref="AN4:AN6" si="8">ROUND(AI4/AM4,5)</f>
-        <v>10586.24</v>
+        <v>10586.18333</v>
       </c>
       <c r="AO4" s="26">
         <f t="shared" ref="AO4:AO6" si="9">AJ4/AM4</f>
@@ -24999,7 +25074,7 @@
       </c>
       <c r="AR4" s="26">
         <f t="shared" ref="AR4:AR6" si="11">ROUND(AN4+AO4+AP4,5)</f>
-        <v>10586.24</v>
+        <v>10586.18333</v>
       </c>
       <c r="AS4" s="38" t="s">
         <v>80</v>
@@ -25007,27 +25082,27 @@
       <c r="AT4" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AU4" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AV4" t="s" s="0">
         <v>128</v>
       </c>
       <c r="AW4" s="39">
         <f t="shared" ref="AW4:AW6" si="12">AM4</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AX4" s="42">
         <f t="shared" ref="AX4:AX6" si="13">AR4</f>
-        <v>10586.24</v>
+        <v>10586.18333</v>
       </c>
       <c r="AY4" s="39">
         <f t="shared" ref="AY4:AY6" si="14">AU4+AW4</f>
-        <v>5</v>
-      </c>
-      <c r="AZ4" s="43">
-        <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),3)</f>
-        <v>10586.24</v>
+        <v>3</v>
+      </c>
+      <c r="AZ4" s="39">
+        <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),5)</f>
+        <v>10586.18333</v>
       </c>
       <c r="BA4" s="44"/>
       <c r="BB4" s="44" t="s">
@@ -25051,25 +25126,25 @@
       <c r="BL4" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>89</v>
       </c>
       <c r="BO4" s="39">
         <f t="shared" ref="BO4:BO6" si="15">ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
-        <v>739.93882</v>
+        <v>502.67651</v>
       </c>
       <c r="BP4" s="48">
         <f t="shared" ref="BP4:BP6" si="16">ROUND(BN4+AW4,3)</f>
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="BQ4" s="49">
         <v>123562</v>
       </c>
     </row>
-    <row r="5" ht="15.15" spans="1:69">
+    <row r="5" ht="15.75" spans="1:69">
       <c r="A5" s="7">
         <v>1</v>
       </c>
@@ -25086,16 +25161,16 @@
         <v>77</v>
       </c>
       <c r="F5" s="8">
-        <v>4</v>
-      </c>
-      <c r="G5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" t="s" s="0">
         <v>92</v>
       </c>
       <c r="H5" s="8">
         <f t="shared" si="0"/>
-        <v>400</v>
-      </c>
-      <c r="I5" t="s">
+        <v>900</v>
+      </c>
+      <c r="I5" t="s" s="0">
         <v>93</v>
       </c>
       <c r="J5" s="8">
@@ -25106,35 +25181,35 @@
       </c>
       <c r="L5" s="8">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="M5" s="8">
         <f>ROUND(L5*I5%,2)</f>
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="N5" s="8">
         <f t="shared" si="2"/>
-        <v>384</v>
+        <v>864</v>
       </c>
       <c r="O5" s="8">
         <f>ROUND(N5*J5%,2)</f>
-        <v>34.56</v>
+        <v>77.76</v>
       </c>
       <c r="P5" s="8">
         <f t="shared" si="3"/>
-        <v>349.44</v>
+        <v>786.24</v>
       </c>
       <c r="Q5" s="8">
         <f t="shared" si="4"/>
-        <v>20.97</v>
+        <v>47.17</v>
       </c>
       <c r="R5" s="8">
         <f>M5+O5+Q5</f>
-        <v>71.53</v>
+        <v>160.93</v>
       </c>
       <c r="S5" s="8">
         <f t="shared" si="5"/>
-        <v>328.47</v>
+        <v>739.07</v>
       </c>
       <c r="T5" s="8">
         <v>88363222</v>
@@ -25143,26 +25218,26 @@
         <v>18</v>
       </c>
       <c r="V5" s="8">
-        <f>IF(OR(DGSUomWoQWI!$C$2=1,DGSUomWoQWI!$C$2=4),ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF(OR($C$2=1,$C$2=4),ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="W5" s="8">
-        <f>IF(DGSUomWoQWI!$C$2=1,ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF($C$2=1,ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="X5" s="8">
-        <f>IF(DGSUomWoQWI!$C$2=2,ROUND(((S5*U5)/100),2),0)</f>
+        <f>IF($C$2=2,ROUND(((S5*U5)/100),2),0)</f>
         <v>0</v>
       </c>
       <c r="Y5" s="8">
-        <f>IF(DGSUomWoQWI!$C$2=4,ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF($C$2=4,ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="Z5" s="8">
         <v>0</v>
       </c>
       <c r="AA5" s="8">
-        <f>IF(DGSUomWoQWI!$C3=3,0,(S5*Z5)/100)</f>
+        <f>IF($C3=3,0,(S5*Z5)/100)</f>
         <v>0</v>
       </c>
       <c r="AB5" s="8">
@@ -25170,35 +25245,35 @@
         <v>0</v>
       </c>
       <c r="AC5" s="8">
-        <f>IF(DGSUomWoQWI!$V3=1,S5+AB5,S5)</f>
-        <v>328.47</v>
+        <f>IF($V3=1,S5+AB5,S5)</f>
+        <v>739.07</v>
       </c>
       <c r="AD5" s="26">
         <v>120</v>
       </c>
       <c r="AE5" s="26">
-        <f>IF(DGSUomWoQWI!$P$2=1,(S5/DGSUomWoQWI!$S$7)*DGSUomWoQWI!$E$18,AD5/DGSUomWoQWI!$AD$7*DGSUomWoQWI!$E$18)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$18,AD5/$AD$7*$E$18)</f>
         <v>0</v>
       </c>
       <c r="AF5" s="26"/>
       <c r="AG5" s="26">
-        <f>IF(DGSUomWoQWI!$P$2=1,(S5/DGSUomWoQWI!$S$7)*DGSUomWoQWI!$E$20,AD5/DGSUomWoQWI!$AD$7*DGSUomWoQWI!$E$20)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$20,AD5/$AD$7*$E$20)</f>
         <v>0</v>
       </c>
       <c r="AH5" s="26">
-        <f>IF(DGSUomWoQWI!$P$2=1,(S5/DGSUomWoQWI!$S$7)*DGSUomWoQWI!$E$21,AD5/DGSUomWoQWI!$AD$7*DGSUomWoQWI!$E$21)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$21,AD5/$AD$7*$E$21)</f>
         <v>0</v>
       </c>
       <c r="AI5" s="26">
-        <f>S5*DGSUomWoQWI!$M$2</f>
-        <v>27919.95</v>
+        <f>S5*$M$2</f>
+        <v>62820.95</v>
       </c>
       <c r="AJ5" s="26">
-        <f>IF(DGSUomWoQWI!$C$2=3,0,AG5+AH5)</f>
+        <f>IF($C$2=3,0,AG5+AH5)</f>
         <v>0</v>
       </c>
       <c r="AK5" s="26">
-        <f>IF(DGSUomWoQWI!$C$2=3,AE5+AG5+AH5,0)</f>
+        <f>IF($C$2=3,AE5+AG5+AH5,0)</f>
         <v>0</v>
       </c>
       <c r="AL5" s="34">
@@ -25206,11 +25281,11 @@
       </c>
       <c r="AM5" s="26">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AN5" s="26">
         <f t="shared" si="8"/>
-        <v>6979.9875</v>
+        <v>6980.10556</v>
       </c>
       <c r="AO5" s="26">
         <f t="shared" si="9"/>
@@ -25225,7 +25300,7 @@
       </c>
       <c r="AR5" s="26">
         <f t="shared" si="11"/>
-        <v>6979.9875</v>
+        <v>6980.10556</v>
       </c>
       <c r="AS5" s="38" t="s">
         <v>80</v>
@@ -25233,27 +25308,27 @@
       <c r="AT5" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AU5" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AV5" t="s" s="0">
         <v>130</v>
       </c>
       <c r="AW5" s="39">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AX5" s="42">
         <f t="shared" si="13"/>
-        <v>6979.9875</v>
+        <v>6980.10556</v>
       </c>
       <c r="AY5" s="39">
         <f t="shared" si="14"/>
-        <v>4</v>
-      </c>
-      <c r="AZ5" s="42">
-        <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),2)</f>
-        <v>6979.99</v>
+        <v>9</v>
+      </c>
+      <c r="AZ5" s="39">
+        <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),5)</f>
+        <v>6980.10556</v>
       </c>
       <c r="BA5" s="44"/>
       <c r="BB5" s="44" t="s">
@@ -25277,25 +25352,25 @@
       <c r="BL5" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BM5" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BN5" t="s" s="0">
         <v>97</v>
       </c>
       <c r="BO5" s="39">
         <f t="shared" si="15"/>
-        <v>513.23688</v>
+        <v>981.85725</v>
       </c>
       <c r="BP5" s="48">
         <f t="shared" si="16"/>
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="BQ5" s="49">
         <v>123562</v>
       </c>
     </row>
-    <row r="6" ht="15.15" spans="1:69">
+    <row r="6" ht="15.75" spans="1:69">
       <c r="A6" s="7">
         <v>1</v>
       </c>
@@ -25312,16 +25387,16 @@
         <v>77</v>
       </c>
       <c r="F6" s="8">
-        <v>20</v>
-      </c>
-      <c r="G6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H6" s="8">
         <f t="shared" si="0"/>
-        <v>1000</v>
-      </c>
-      <c r="I6" t="s">
+        <v>600</v>
+      </c>
+      <c r="I6" t="s" s="0">
         <v>101</v>
       </c>
       <c r="J6" s="8">
@@ -25332,35 +25407,35 @@
       </c>
       <c r="L6" s="8">
         <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="M6" s="8">
         <f>ROUND(L6*I6%,2)</f>
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="N6" s="8">
         <f t="shared" si="2"/>
-        <v>970</v>
+        <v>582</v>
       </c>
       <c r="O6" s="8">
         <f>ROUND(N6*J6%,2)</f>
-        <v>67.9</v>
+        <v>40.74</v>
       </c>
       <c r="P6" s="8">
         <f t="shared" si="3"/>
-        <v>902.1</v>
+        <v>541.26</v>
       </c>
       <c r="Q6" s="8">
         <f t="shared" si="4"/>
-        <v>36.08</v>
+        <v>21.65</v>
       </c>
       <c r="R6" s="8">
         <f>M6+O6+Q6</f>
-        <v>133.98</v>
+        <v>80.39</v>
       </c>
       <c r="S6" s="8">
         <f t="shared" si="5"/>
-        <v>866.02</v>
+        <v>519.61</v>
       </c>
       <c r="T6" s="8">
         <v>88363222</v>
@@ -25369,26 +25444,26 @@
         <v>18</v>
       </c>
       <c r="V6" s="8">
-        <f>IF(OR(DGSUomWoQWI!$C$2=1,DGSUomWoQWI!$C$2=4),ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF(OR($C$2=1,$C$2=4),ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="W6" s="8">
-        <f>IF(DGSUomWoQWI!$C$2=1,ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF($C$2=1,ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="X6" s="8">
-        <f>IF(DGSUomWoQWI!$C$2=2,ROUND(((S6*U6)/100),2),0)</f>
+        <f>IF($C$2=2,ROUND(((S6*U6)/100),2),0)</f>
         <v>0</v>
       </c>
       <c r="Y6" s="8">
-        <f>IF(DGSUomWoQWI!$C$2=4,ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF($C$2=4,ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="Z6" s="8">
         <v>0</v>
       </c>
       <c r="AA6" s="8">
-        <f>IF(DGSUomWoQWI!$C4=3,0,(S6*Z6)/100)</f>
+        <f>IF($C4=3,0,(S6*Z6)/100)</f>
         <v>0</v>
       </c>
       <c r="AB6" s="8">
@@ -25396,35 +25471,35 @@
         <v>0</v>
       </c>
       <c r="AC6" s="8">
-        <f>IF(DGSUomWoQWI!$V4=1,S6+AB6,S6)</f>
-        <v>866.02</v>
+        <f>IF($V4=1,S6+AB6,S6)</f>
+        <v>519.61</v>
       </c>
       <c r="AD6" s="26">
         <v>120</v>
       </c>
       <c r="AE6" s="26">
-        <f>IF(DGSUomWoQWI!$P$2=1,(S6/DGSUomWoQWI!$S$7)*DGSUomWoQWI!$E$18,AD6/DGSUomWoQWI!$AD$7*DGSUomWoQWI!$E$18)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$18,AD6/$AD$7*$E$18)</f>
         <v>0</v>
       </c>
       <c r="AF6" s="26"/>
       <c r="AG6" s="26">
-        <f>IF(DGSUomWoQWI!$P$2=1,(S6/DGSUomWoQWI!$S$7)*DGSUomWoQWI!$E$20,AD6/DGSUomWoQWI!$AD$7*DGSUomWoQWI!$E$20)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$20,AD6/$AD$7*$E$20)</f>
         <v>0</v>
       </c>
       <c r="AH6" s="26">
-        <f>IF(DGSUomWoQWI!$P$2=1,(S6/DGSUomWoQWI!$S$7)*DGSUomWoQWI!$E$21,AD6/DGSUomWoQWI!$AD$7*DGSUomWoQWI!$E$21)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$21,AD6/$AD$7*$E$21)</f>
         <v>0</v>
       </c>
       <c r="AI6" s="26">
-        <f>S6*DGSUomWoQWI!$M$2</f>
-        <v>73611.7</v>
+        <f>S6*$M$2</f>
+        <v>44166.85</v>
       </c>
       <c r="AJ6" s="26">
-        <f>IF(DGSUomWoQWI!$C$2=3,0,AG6+AH6)</f>
+        <f>IF($C$2=3,0,AG6+AH6)</f>
         <v>0</v>
       </c>
       <c r="AK6" s="26">
-        <f>IF(DGSUomWoQWI!$C$2=3,AE6+AG6+AH6,0)</f>
+        <f>IF($C$2=3,AE6+AG6+AH6,0)</f>
         <v>0</v>
       </c>
       <c r="AL6" s="34">
@@ -25432,11 +25507,11 @@
       </c>
       <c r="AM6" s="26">
         <f t="shared" si="7"/>
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AN6" s="26">
         <f t="shared" si="8"/>
-        <v>3680.585</v>
+        <v>3680.57083</v>
       </c>
       <c r="AO6" s="26">
         <f t="shared" si="9"/>
@@ -25451,7 +25526,7 @@
       </c>
       <c r="AR6" s="26">
         <f t="shared" si="11"/>
-        <v>3680.585</v>
+        <v>3680.57083</v>
       </c>
       <c r="AS6" s="38" t="s">
         <v>80</v>
@@ -25459,27 +25534,27 @@
       <c r="AT6" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AU6" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="AV6" t="s">
+      <c r="AV6" t="s" s="0">
         <v>132</v>
       </c>
       <c r="AW6" s="39">
         <f t="shared" si="12"/>
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AX6" s="39">
         <f t="shared" si="13"/>
-        <v>3680.585</v>
+        <v>3680.57083</v>
       </c>
       <c r="AY6" s="39">
         <f t="shared" si="14"/>
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AZ6" s="39">
-        <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),1)</f>
-        <v>3680.6</v>
+        <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),5)</f>
+        <v>3680.57083</v>
       </c>
       <c r="BA6" s="44"/>
       <c r="BB6" s="44" t="s">
@@ -25503,25 +25578,25 @@
       <c r="BL6" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM6" t="s">
+      <c r="BM6" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="BN6" t="s">
+      <c r="BN6" t="s" s="0">
         <v>105</v>
       </c>
       <c r="BO6" s="39">
         <f t="shared" si="15"/>
-        <v>270.63125</v>
+        <v>183.19503</v>
       </c>
       <c r="BP6" s="48">
         <f t="shared" si="16"/>
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="BQ6" s="49">
         <v>123562</v>
       </c>
     </row>
-    <row r="7" ht="15.15" spans="1:69">
+    <row r="7" ht="15.75" spans="1:69">
       <c r="A7" s="9"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -25533,7 +25608,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="13">
         <f>SUM(H4:H4)</f>
-        <v>750</v>
+        <v>450</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
@@ -25546,11 +25621,11 @@
       <c r="Q7" s="7"/>
       <c r="R7" s="27">
         <f t="shared" ref="R7:X7" si="17">SUM(R4:R4)</f>
-        <v>127.28</v>
+        <v>76.37</v>
       </c>
       <c r="S7" s="13">
         <f t="shared" si="17"/>
-        <v>622.72</v>
+        <v>373.63</v>
       </c>
       <c r="T7" s="27"/>
       <c r="U7" s="27"/>
@@ -25575,7 +25650,7 @@
       </c>
       <c r="AC7" s="32">
         <f t="shared" si="18"/>
-        <v>622.72</v>
+        <v>373.63</v>
       </c>
       <c r="AD7" s="33">
         <f t="shared" si="18"/>
@@ -25596,7 +25671,7 @@
       </c>
       <c r="AI7" s="33">
         <f t="shared" si="19"/>
-        <v>52931.2</v>
+        <v>31758.55</v>
       </c>
       <c r="AJ7" s="33">
         <f t="shared" si="19"/>
@@ -25639,7 +25714,7 @@
       <c r="BP7" s="40"/>
       <c r="BQ7" s="40"/>
     </row>
-    <row r="8" ht="15.15" spans="1:69">
+    <row r="8" ht="15.75" spans="1:69">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -25710,7 +25785,7 @@
       <c r="BP8" s="40"/>
       <c r="BQ8" s="40"/>
     </row>
-    <row r="9" ht="15.15" spans="1:69">
+    <row r="9" ht="15.75" spans="1:69">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -25723,7 +25798,7 @@
       <c r="H9" s="15"/>
       <c r="I9" s="19">
         <f>H7</f>
-        <v>750</v>
+        <v>450</v>
       </c>
       <c r="J9" s="19"/>
       <c r="K9" s="9"/>
@@ -25792,7 +25867,7 @@
       <c r="BP9" s="40"/>
       <c r="BQ9" s="40"/>
     </row>
-    <row r="10" ht="15.15" spans="1:69">
+    <row r="10" ht="15.75" spans="1:69">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -25805,7 +25880,7 @@
       <c r="H10" s="15"/>
       <c r="I10" s="19">
         <f>R7</f>
-        <v>127.28</v>
+        <v>76.37</v>
       </c>
       <c r="J10" s="19"/>
       <c r="K10" s="9"/>
@@ -25880,7 +25955,7 @@
       <c r="BP10" s="40"/>
       <c r="BQ10" s="40"/>
     </row>
-    <row r="11" ht="15.15" spans="1:69">
+    <row r="11" ht="15.75" spans="1:69">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -25893,7 +25968,7 @@
       <c r="H11" s="15"/>
       <c r="I11" s="19">
         <f>S7</f>
-        <v>622.72</v>
+        <v>373.63</v>
       </c>
       <c r="J11" s="19"/>
       <c r="K11" s="9"/>
@@ -25964,7 +26039,7 @@
       <c r="BP11" s="40"/>
       <c r="BQ11" s="40"/>
     </row>
-    <row r="12" ht="15.15" spans="1:69">
+    <row r="12" ht="15.75" spans="1:69">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -26048,7 +26123,7 @@
       <c r="BP12" s="40"/>
       <c r="BQ12" s="40"/>
     </row>
-    <row r="13" ht="15.15" spans="1:69">
+    <row r="13" ht="15.75" spans="1:69">
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -26061,7 +26136,7 @@
       <c r="H13" s="15"/>
       <c r="I13" s="24">
         <f>I11+I12</f>
-        <v>622.72</v>
+        <v>373.63</v>
       </c>
       <c r="J13" s="24"/>
       <c r="K13" s="9"/>
@@ -26686,13 +26761,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ20"/>
-  <sheetFormatPr defaultColWidth="8.85185185185185" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.84761904761905" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="13" max="13" width="9.13888888888889" customWidth="1"/>
-    <col min="14" max="14" width="13.8518518518519" customWidth="1"/>
-    <col min="64" max="64" width="11" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="28.0"/>
+    <col min="3" max="3" customWidth="true" width="23.0"/>
+    <col min="13" max="13" customWidth="true" width="9.14285714285714"/>
+    <col min="14" max="14" customWidth="true" width="13.847619047619"/>
+    <col min="29" max="29" width="10.5714285714286"/>
+    <col min="35" max="35" width="12.8571428571429"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="64" max="64" customWidth="true" width="11.0"/>
+    <col min="67" max="67" width="12.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -26768,7 +26847,7 @@
       <c r="BP1" s="40"/>
       <c r="BQ1" s="40"/>
     </row>
-    <row r="2" ht="15.15" spans="1:69">
+    <row r="2" ht="15.75" spans="1:69">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -26863,7 +26942,7 @@
       <c r="BP2" s="40"/>
       <c r="BQ2" s="40"/>
     </row>
-    <row r="3" ht="59.1" spans="1:69">
+    <row r="3" ht="61.5" spans="1:69">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
@@ -27072,7 +27151,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.15" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="7">
         <v>1</v>
       </c>
@@ -27089,16 +27168,16 @@
         <v>77</v>
       </c>
       <c r="F4" s="8">
-        <v>5</v>
-      </c>
-      <c r="G4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" t="s" s="0">
         <v>78</v>
       </c>
       <c r="H4" s="8">
         <f t="shared" ref="H4:H6" si="0">F4*G4</f>
-        <v>750</v>
-      </c>
-      <c r="I4" t="s">
+        <v>1800</v>
+      </c>
+      <c r="I4" t="s" s="0">
         <v>79</v>
       </c>
       <c r="J4" s="8">
@@ -27109,35 +27188,35 @@
       </c>
       <c r="L4" s="8">
         <f t="shared" ref="L4:L6" si="1">IF(OR(I4=0,I4="0"),0,H4)</f>
-        <v>750</v>
+        <v>1800</v>
       </c>
       <c r="M4" s="8">
         <f>ROUND(L4*I4%,3)</f>
-        <v>37.5</v>
+        <v>90</v>
       </c>
       <c r="N4" s="8">
         <f t="shared" ref="N4:N6" si="2">H4-M4</f>
-        <v>712.5</v>
+        <v>1710</v>
       </c>
       <c r="O4" s="8">
         <f>ROUND(N4*J4%,3)</f>
-        <v>57</v>
+        <v>136.8</v>
       </c>
       <c r="P4" s="8">
         <f t="shared" ref="P4:P6" si="3">ROUND(N4-O4,2)</f>
-        <v>655.5</v>
+        <v>1573.2</v>
       </c>
       <c r="Q4" s="8">
         <f t="shared" ref="Q4:Q6" si="4">ROUND(P4*K4%,2)</f>
-        <v>32.78</v>
+        <v>78.66</v>
       </c>
       <c r="R4" s="26">
         <f>ROUND(M4+O4+Q4,3)</f>
-        <v>127.28</v>
+        <v>305.46</v>
       </c>
       <c r="S4" s="26">
         <f t="shared" ref="S4:S6" si="5">(H4-R4)</f>
-        <v>622.72</v>
+        <v>1494.54</v>
       </c>
       <c r="T4" s="8">
         <v>88363222</v>
@@ -27174,7 +27253,7 @@
       </c>
       <c r="AC4" s="31">
         <f>IF($V2=1,S4+AB4,S4)</f>
-        <v>622.72</v>
+        <v>1494.54</v>
       </c>
       <c r="AD4" s="26">
         <v>120</v>
@@ -27194,7 +27273,7 @@
       </c>
       <c r="AI4" s="26">
         <f>S4*$M2</f>
-        <v>52931.2</v>
+        <v>127035.9</v>
       </c>
       <c r="AJ4" s="26">
         <f>IF($C$2=3,0,AG4+AH4)</f>
@@ -27209,11 +27288,11 @@
       </c>
       <c r="AM4" s="26">
         <f t="shared" ref="AM4:AM6" si="7">F4/AL4</f>
-        <v>1.66666666666667</v>
+        <v>4</v>
       </c>
       <c r="AN4" s="26">
         <f t="shared" ref="AN4:AN6" si="8">ROUND(AI4/AM4,5)</f>
-        <v>31758.72</v>
+        <v>31758.975</v>
       </c>
       <c r="AO4" s="26">
         <f t="shared" ref="AO4:AO6" si="9">AJ4/AM4</f>
@@ -27228,7 +27307,7 @@
       </c>
       <c r="AR4" s="26">
         <f t="shared" ref="AR4:AR6" si="11">ROUND(AN4+AO4+AP4,5)</f>
-        <v>31758.72</v>
+        <v>31758.975</v>
       </c>
       <c r="AS4" s="38" t="s">
         <v>80</v>
@@ -27236,27 +27315,27 @@
       <c r="AT4" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AU4" t="s" s="0">
         <v>134</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AV4" t="s" s="0">
         <v>135</v>
       </c>
       <c r="AW4" s="39">
         <f t="shared" ref="AW4:AW6" si="12">AM4</f>
-        <v>1.66666666666667</v>
+        <v>4</v>
       </c>
       <c r="AX4" s="42">
         <f t="shared" ref="AX4:AX6" si="13">AR4</f>
-        <v>31758.72</v>
+        <v>31758.975</v>
       </c>
       <c r="AY4" s="39">
         <f t="shared" ref="AY4:AY6" si="14">AU4+AW4</f>
-        <v>376.666666666667</v>
-      </c>
-      <c r="AZ4" s="43">
-        <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),3)</f>
-        <v>3703.284</v>
+        <v>52.329</v>
+      </c>
+      <c r="AZ4" s="39">
+        <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),5)</f>
+        <v>13767.68826</v>
       </c>
       <c r="BA4" s="44"/>
       <c r="BB4" s="44" t="s">
@@ -27280,25 +27359,25 @@
       <c r="BL4" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>89</v>
       </c>
       <c r="BO4" s="39">
         <f t="shared" ref="BO4:BO6" si="15">ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
-        <v>197.58049</v>
+        <v>774.21849</v>
       </c>
       <c r="BP4" s="48">
         <f t="shared" ref="BP4:BP6" si="16">ROUND(BN4+AW4,3)</f>
-        <v>81.667</v>
+        <v>84</v>
       </c>
       <c r="BQ4" s="49">
         <v>123562</v>
       </c>
     </row>
-    <row r="5" ht="15.15" spans="1:69">
+    <row r="5" ht="15.75" spans="1:69">
       <c r="A5" s="7">
         <v>1</v>
       </c>
@@ -27315,16 +27394,16 @@
         <v>77</v>
       </c>
       <c r="F5" s="8">
-        <v>4</v>
-      </c>
-      <c r="G5" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5" t="s" s="0">
         <v>92</v>
       </c>
       <c r="H5" s="8">
         <f t="shared" si="0"/>
-        <v>400</v>
-      </c>
-      <c r="I5" t="s">
+        <v>300</v>
+      </c>
+      <c r="I5" t="s" s="0">
         <v>93</v>
       </c>
       <c r="J5" s="8">
@@ -27335,35 +27414,35 @@
       </c>
       <c r="L5" s="8">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="M5" s="8">
         <f>ROUND(L5*I5%,2)</f>
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="N5" s="8">
         <f t="shared" si="2"/>
-        <v>384</v>
+        <v>288</v>
       </c>
       <c r="O5" s="8">
         <f>ROUND(N5*J5%,2)</f>
-        <v>34.56</v>
+        <v>25.92</v>
       </c>
       <c r="P5" s="8">
         <f t="shared" si="3"/>
-        <v>349.44</v>
+        <v>262.08</v>
       </c>
       <c r="Q5" s="8">
         <f t="shared" si="4"/>
-        <v>20.97</v>
+        <v>15.72</v>
       </c>
       <c r="R5" s="8">
         <f>M5+O5+Q5</f>
-        <v>71.53</v>
+        <v>53.64</v>
       </c>
       <c r="S5" s="8">
         <f t="shared" si="5"/>
-        <v>328.47</v>
+        <v>246.36</v>
       </c>
       <c r="T5" s="8">
         <v>88363222</v>
@@ -27372,26 +27451,26 @@
         <v>18</v>
       </c>
       <c r="V5" s="8">
-        <f>IF(OR(DGDUomWI!$C$2=1,DGDUomWI!$C$2=4),ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF(OR($C$2=1,$C$2=4),ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="W5" s="8">
-        <f>IF(DGDUomWI!$C$2=1,ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF($C$2=1,ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="X5" s="8">
-        <f>IF(DGDUomWI!$C$2=2,ROUND(((S5*U5)/100),2),0)</f>
+        <f>IF($C$2=2,ROUND(((S5*U5)/100),2),0)</f>
         <v>0</v>
       </c>
       <c r="Y5" s="8">
-        <f>IF(DGDUomWI!$C$2=4,ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF($C$2=4,ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="Z5" s="8">
         <v>0</v>
       </c>
       <c r="AA5" s="8">
-        <f>IF(DGDUomWI!$C3=3,0,(S5*Z5)/100)</f>
+        <f>IF($C3=3,0,(S5*Z5)/100)</f>
         <v>0</v>
       </c>
       <c r="AB5" s="8">
@@ -27399,35 +27478,35 @@
         <v>0</v>
       </c>
       <c r="AC5" s="8">
-        <f>IF(DGDUomWI!$V3=1,S5+AB5,S5)</f>
-        <v>328.47</v>
+        <f>IF($V3=1,S5+AB5,S5)</f>
+        <v>246.36</v>
       </c>
       <c r="AD5" s="26">
         <v>120</v>
       </c>
       <c r="AE5" s="26">
-        <f>IF(DGDUomWI!$P$2=1,(S5/DGDUomWI!$S$7)*DGDUomWI!$E$18,AD5/DGDUomWI!$AD$7*DGDUomWI!$E$18)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$18,AD5/$AD$7*$E$18)</f>
         <v>0</v>
       </c>
       <c r="AF5" s="26"/>
       <c r="AG5" s="26">
-        <f>IF(DGDUomWI!$P$2=1,(S5/DGDUomWI!$S$7)*DGDUomWI!$E$20,AD5/DGDUomWI!$AD$7*DGDUomWI!$E$20)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$20,AD5/$AD$7*$E$20)</f>
         <v>0</v>
       </c>
       <c r="AH5" s="26">
-        <f>IF(DGDUomWI!$P$2=1,(S5/DGDUomWI!$S$7)*DGDUomWI!$E$21,AD5/DGDUomWI!$AD$7*DGDUomWI!$E$21)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$21,AD5/$AD$7*$E$21)</f>
         <v>0</v>
       </c>
       <c r="AI5" s="26">
-        <f>S5*DGDUomWI!$M$2</f>
-        <v>27919.95</v>
+        <f>S5*$M$2</f>
+        <v>20940.6</v>
       </c>
       <c r="AJ5" s="26">
-        <f>IF(DGDUomWI!$C$2=3,0,AG5+AH5)</f>
+        <f>IF($C$2=3,0,AG5+AH5)</f>
         <v>0</v>
       </c>
       <c r="AK5" s="26">
-        <f>IF(DGDUomWI!$C$2=3,AE5+AG5+AH5,0)</f>
+        <f>IF($C$2=3,AE5+AG5+AH5,0)</f>
         <v>0</v>
       </c>
       <c r="AL5" s="34">
@@ -27435,11 +27514,11 @@
       </c>
       <c r="AM5" s="26">
         <f t="shared" si="7"/>
-        <v>1.33333333333333</v>
+        <v>1</v>
       </c>
       <c r="AN5" s="26">
         <f t="shared" si="8"/>
-        <v>20939.9625</v>
+        <v>20940.6</v>
       </c>
       <c r="AO5" s="26">
         <f t="shared" si="9"/>
@@ -27454,7 +27533,7 @@
       </c>
       <c r="AR5" s="26">
         <f t="shared" si="11"/>
-        <v>20939.9625</v>
+        <v>20940.6</v>
       </c>
       <c r="AS5" s="38" t="s">
         <v>80</v>
@@ -27462,27 +27541,27 @@
       <c r="AT5" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AU5" t="s" s="0">
         <v>137</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AV5" t="s" s="0">
         <v>138</v>
       </c>
       <c r="AW5" s="39">
         <f t="shared" si="12"/>
-        <v>1.33333333333333</v>
+        <v>1</v>
       </c>
       <c r="AX5" s="42">
         <f t="shared" si="13"/>
-        <v>20939.9625</v>
+        <v>20940.6</v>
       </c>
       <c r="AY5" s="39">
         <f t="shared" si="14"/>
-        <v>189.333333333333</v>
-      </c>
-      <c r="AZ5" s="42">
-        <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),2)</f>
-        <v>2106.2</v>
+        <v>23.661</v>
+      </c>
+      <c r="AZ5" s="39">
+        <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),5)</f>
+        <v>8116.13607</v>
       </c>
       <c r="BA5" s="44"/>
       <c r="BB5" s="44" t="s">
@@ -27506,25 +27585,25 @@
       <c r="BL5" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BM5" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BN5" t="s" s="0">
         <v>97</v>
       </c>
       <c r="BO5" s="39">
         <f t="shared" si="15"/>
-        <v>126.12174</v>
+        <v>213.82518</v>
       </c>
       <c r="BP5" s="48">
         <f t="shared" si="16"/>
-        <v>61.333</v>
+        <v>61</v>
       </c>
       <c r="BQ5" s="49">
         <v>123562</v>
       </c>
     </row>
-    <row r="6" ht="15.15" spans="1:69">
+    <row r="6" ht="15.75" spans="1:69">
       <c r="A6" s="7">
         <v>1</v>
       </c>
@@ -27541,16 +27620,16 @@
         <v>77</v>
       </c>
       <c r="F6" s="8">
-        <v>20</v>
-      </c>
-      <c r="G6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H6" s="8">
         <f t="shared" si="0"/>
-        <v>1000</v>
-      </c>
-      <c r="I6" t="s">
+        <v>450</v>
+      </c>
+      <c r="I6" t="s" s="0">
         <v>101</v>
       </c>
       <c r="J6" s="8">
@@ -27561,35 +27640,35 @@
       </c>
       <c r="L6" s="8">
         <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="M6" s="8">
         <f>ROUND(L6*I6%,2)</f>
-        <v>30</v>
+        <v>13.5</v>
       </c>
       <c r="N6" s="8">
         <f t="shared" si="2"/>
-        <v>970</v>
+        <v>436.5</v>
       </c>
       <c r="O6" s="8">
         <f>ROUND(N6*J6%,2)</f>
-        <v>67.9</v>
+        <v>30.56</v>
       </c>
       <c r="P6" s="8">
         <f t="shared" si="3"/>
-        <v>902.1</v>
+        <v>405.94</v>
       </c>
       <c r="Q6" s="8">
         <f t="shared" si="4"/>
-        <v>36.08</v>
+        <v>16.24</v>
       </c>
       <c r="R6" s="8">
         <f>M6+O6+Q6</f>
-        <v>133.98</v>
+        <v>60.3</v>
       </c>
       <c r="S6" s="8">
         <f t="shared" si="5"/>
-        <v>866.02</v>
+        <v>389.7</v>
       </c>
       <c r="T6" s="8">
         <v>88363222</v>
@@ -27598,26 +27677,26 @@
         <v>18</v>
       </c>
       <c r="V6" s="8">
-        <f>IF(OR(DGDUomWI!$C$2=1,DGDUomWI!$C$2=4),ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF(OR($C$2=1,$C$2=4),ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="W6" s="8">
-        <f>IF(DGDUomWI!$C$2=1,ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF($C$2=1,ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="X6" s="8">
-        <f>IF(DGDUomWI!$C$2=2,ROUND(((S6*U6)/100),2),0)</f>
+        <f>IF($C$2=2,ROUND(((S6*U6)/100),2),0)</f>
         <v>0</v>
       </c>
       <c r="Y6" s="8">
-        <f>IF(DGDUomWI!$C$2=4,ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF($C$2=4,ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="Z6" s="8">
         <v>0</v>
       </c>
       <c r="AA6" s="8">
-        <f>IF(DGDUomWI!$C4=3,0,(S6*Z6)/100)</f>
+        <f>IF($C4=3,0,(S6*Z6)/100)</f>
         <v>0</v>
       </c>
       <c r="AB6" s="8">
@@ -27625,35 +27704,35 @@
         <v>0</v>
       </c>
       <c r="AC6" s="8">
-        <f>IF(DGDUomWI!$V4=1,S6+AB6,S6)</f>
-        <v>866.02</v>
+        <f>IF($V4=1,S6+AB6,S6)</f>
+        <v>389.7</v>
       </c>
       <c r="AD6" s="26">
         <v>120</v>
       </c>
       <c r="AE6" s="26">
-        <f>IF(DGDUomWI!$P$2=1,(S6/DGDUomWI!$S$7)*DGDUomWI!$E$18,AD6/DGDUomWI!$AD$7*DGDUomWI!$E$18)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$18,AD6/$AD$7*$E$18)</f>
         <v>0</v>
       </c>
       <c r="AF6" s="26"/>
       <c r="AG6" s="26">
-        <f>IF(DGDUomWI!$P$2=1,(S6/DGDUomWI!$S$7)*DGDUomWI!$E$20,AD6/DGDUomWI!$AD$7*DGDUomWI!$E$20)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$20,AD6/$AD$7*$E$20)</f>
         <v>0</v>
       </c>
       <c r="AH6" s="26">
-        <f>IF(DGDUomWI!$P$2=1,(S6/DGDUomWI!$S$7)*DGDUomWI!$E$21,AD6/DGDUomWI!$AD$7*DGDUomWI!$E$21)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$21,AD6/$AD$7*$E$21)</f>
         <v>0</v>
       </c>
       <c r="AI6" s="26">
-        <f>S6*DGDUomWI!$M$2</f>
-        <v>73611.7</v>
+        <f>S6*$M$2</f>
+        <v>33124.5</v>
       </c>
       <c r="AJ6" s="26">
-        <f>IF(DGDUomWI!$C$2=3,0,AG6+AH6)</f>
+        <f>IF($C$2=3,0,AG6+AH6)</f>
         <v>0</v>
       </c>
       <c r="AK6" s="26">
-        <f>IF(DGDUomWI!$C$2=3,AE6+AG6+AH6,0)</f>
+        <f>IF($C$2=3,AE6+AG6+AH6,0)</f>
         <v>0</v>
       </c>
       <c r="AL6" s="34">
@@ -27661,11 +27740,11 @@
       </c>
       <c r="AM6" s="26">
         <f t="shared" si="7"/>
-        <v>6.66666666666667</v>
+        <v>3</v>
       </c>
       <c r="AN6" s="26">
         <f t="shared" si="8"/>
-        <v>11041.755</v>
+        <v>11041.5</v>
       </c>
       <c r="AO6" s="26">
         <f t="shared" si="9"/>
@@ -27680,7 +27759,7 @@
       </c>
       <c r="AR6" s="26">
         <f t="shared" si="11"/>
-        <v>11041.755</v>
+        <v>11041.5</v>
       </c>
       <c r="AS6" s="38" t="s">
         <v>80</v>
@@ -27688,27 +27767,27 @@
       <c r="AT6" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AU6" t="s" s="0">
         <v>140</v>
       </c>
-      <c r="AV6" t="s">
+      <c r="AV6" t="s" s="0">
         <v>141</v>
       </c>
       <c r="AW6" s="39">
         <f t="shared" si="12"/>
-        <v>6.66666666666667</v>
+        <v>3</v>
       </c>
       <c r="AX6" s="39">
         <f t="shared" si="13"/>
-        <v>11041.755</v>
+        <v>11041.5</v>
       </c>
       <c r="AY6" s="39">
         <f t="shared" si="14"/>
-        <v>486.666666666667</v>
+        <v>62.995</v>
       </c>
       <c r="AZ6" s="39">
-        <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),1)</f>
-        <v>1231.4</v>
+        <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),5)</f>
+        <v>4690.96439</v>
       </c>
       <c r="BA6" s="44"/>
       <c r="BB6" s="44" t="s">
@@ -27732,25 +27811,25 @@
       <c r="BL6" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM6" t="s">
+      <c r="BM6" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="BN6" t="s">
+      <c r="BN6" t="s" s="0">
         <v>105</v>
       </c>
       <c r="BO6" s="39">
         <f t="shared" si="15"/>
-        <v>69.12826</v>
+        <v>89.31648</v>
       </c>
       <c r="BP6" s="48">
         <f t="shared" si="16"/>
-        <v>306.667</v>
+        <v>303</v>
       </c>
       <c r="BQ6" s="49">
         <v>123562</v>
       </c>
     </row>
-    <row r="7" ht="15.15" spans="1:69">
+    <row r="7" ht="15.75" spans="1:69">
       <c r="A7" s="9"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -27762,7 +27841,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="13">
         <f>SUM(H4:H4)</f>
-        <v>750</v>
+        <v>1800</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
@@ -27775,11 +27854,11 @@
       <c r="Q7" s="7"/>
       <c r="R7" s="27">
         <f t="shared" ref="R7:X7" si="17">SUM(R4:R4)</f>
-        <v>127.28</v>
+        <v>305.46</v>
       </c>
       <c r="S7" s="13">
         <f t="shared" si="17"/>
-        <v>622.72</v>
+        <v>1494.54</v>
       </c>
       <c r="T7" s="27"/>
       <c r="U7" s="27"/>
@@ -27804,7 +27883,7 @@
       </c>
       <c r="AC7" s="32">
         <f t="shared" si="18"/>
-        <v>622.72</v>
+        <v>1494.54</v>
       </c>
       <c r="AD7" s="33">
         <f t="shared" si="18"/>
@@ -27825,7 +27904,7 @@
       </c>
       <c r="AI7" s="33">
         <f t="shared" si="19"/>
-        <v>52931.2</v>
+        <v>127035.9</v>
       </c>
       <c r="AJ7" s="33">
         <f t="shared" si="19"/>
@@ -27868,7 +27947,7 @@
       <c r="BP7" s="40"/>
       <c r="BQ7" s="40"/>
     </row>
-    <row r="8" ht="15.15" spans="1:69">
+    <row r="8" ht="15.75" spans="1:69">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -27939,7 +28018,7 @@
       <c r="BP8" s="40"/>
       <c r="BQ8" s="40"/>
     </row>
-    <row r="9" ht="15.15" spans="1:69">
+    <row r="9" ht="15.75" spans="1:69">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -27952,7 +28031,7 @@
       <c r="H9" s="15"/>
       <c r="I9" s="19">
         <f>H7</f>
-        <v>750</v>
+        <v>1800</v>
       </c>
       <c r="J9" s="19"/>
       <c r="K9" s="9"/>
@@ -28021,7 +28100,7 @@
       <c r="BP9" s="40"/>
       <c r="BQ9" s="40"/>
     </row>
-    <row r="10" ht="15.15" spans="1:69">
+    <row r="10" ht="15.75" spans="1:69">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -28034,7 +28113,7 @@
       <c r="H10" s="15"/>
       <c r="I10" s="19">
         <f>R7</f>
-        <v>127.28</v>
+        <v>305.46</v>
       </c>
       <c r="J10" s="19"/>
       <c r="K10" s="9"/>
@@ -28109,7 +28188,7 @@
       <c r="BP10" s="40"/>
       <c r="BQ10" s="40"/>
     </row>
-    <row r="11" ht="15.15" spans="1:69">
+    <row r="11" ht="15.75" spans="1:69">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -28122,7 +28201,7 @@
       <c r="H11" s="15"/>
       <c r="I11" s="19">
         <f>S7</f>
-        <v>622.72</v>
+        <v>1494.54</v>
       </c>
       <c r="J11" s="19"/>
       <c r="K11" s="9"/>
@@ -28193,7 +28272,7 @@
       <c r="BP11" s="40"/>
       <c r="BQ11" s="40"/>
     </row>
-    <row r="12" ht="15.15" spans="1:69">
+    <row r="12" ht="15.75" spans="1:69">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -28277,7 +28356,7 @@
       <c r="BP12" s="40"/>
       <c r="BQ12" s="40"/>
     </row>
-    <row r="13" ht="15.15" spans="1:69">
+    <row r="13" ht="15.75" spans="1:69">
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -28290,7 +28369,7 @@
       <c r="H13" s="15"/>
       <c r="I13" s="24">
         <f>I11+I12</f>
-        <v>622.72</v>
+        <v>1494.54</v>
       </c>
       <c r="J13" s="24"/>
       <c r="K13" s="9"/>
@@ -28915,24 +28994,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ19"/>
-  <sheetFormatPr defaultColWidth="8.85185185185185" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.84761904761905" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="13" max="13" width="9.13888888888889" customWidth="1"/>
-    <col min="14" max="14" width="13.8518518518519" customWidth="1"/>
-    <col min="18" max="19" width="9.28703703703704"/>
-    <col min="20" max="20" width="10.712962962963"/>
-    <col min="29" max="29" width="9.28703703703704"/>
-    <col min="35" max="35" width="11.4259259259259"/>
-    <col min="40" max="40" width="10.1388888888889"/>
-    <col min="44" max="44" width="10.1388888888889"/>
-    <col min="49" max="49" width="14.5740740740741"/>
-    <col min="50" max="50" width="10.1388888888889"/>
-    <col min="51" max="51" width="14.5740740740741"/>
-    <col min="52" max="52" width="19.4259259259259" customWidth="1"/>
-    <col min="64" max="64" width="11" customWidth="1"/>
-    <col min="67" max="67" width="12"/>
+    <col min="2" max="2" customWidth="true" width="28.0"/>
+    <col min="3" max="3" customWidth="true" width="23.0"/>
+    <col min="13" max="13" customWidth="true" width="9.14285714285714"/>
+    <col min="14" max="14" customWidth="true" width="13.847619047619"/>
+    <col min="18" max="19" width="9.28571428571429"/>
+    <col min="20" max="20" width="10.7142857142857"/>
+    <col min="29" max="29" width="9.28571428571429"/>
+    <col min="35" max="35" width="11.4285714285714"/>
+    <col min="40" max="40" width="10.1428571428571"/>
+    <col min="44" max="44" width="10.1428571428571"/>
+    <col min="49" max="49" width="14.5714285714286"/>
+    <col min="50" max="50" width="10.1428571428571"/>
+    <col min="51" max="51" width="14.5714285714286"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="64" max="64" customWidth="true" width="11.0"/>
+    <col min="67" max="67" width="12.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -29008,7 +29087,7 @@
       <c r="BP1" s="40"/>
       <c r="BQ1" s="40"/>
     </row>
-    <row r="2" ht="15.15" spans="1:69">
+    <row r="2" ht="15.75" spans="1:69">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -29103,7 +29182,7 @@
       <c r="BP2" s="40"/>
       <c r="BQ2" s="40"/>
     </row>
-    <row r="3" ht="44.7" spans="1:69">
+    <row r="3" ht="46.5" spans="1:69">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
@@ -29312,7 +29391,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.15" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="7">
         <v>1</v>
       </c>
@@ -29331,14 +29410,14 @@
       <c r="F4" s="8">
         <v>5</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" t="s" s="0">
         <v>78</v>
       </c>
       <c r="H4" s="8">
         <f>F4*G4</f>
         <v>750</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" t="s" s="0">
         <v>79</v>
       </c>
       <c r="J4" s="8">
@@ -29476,10 +29555,10 @@
       <c r="AT4" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AU4" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AV4" t="s" s="0">
         <v>143</v>
       </c>
       <c r="AW4" s="39">
@@ -29520,10 +29599,10 @@
       <c r="BL4" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>89</v>
       </c>
       <c r="BO4" s="39">
@@ -29538,7 +29617,7 @@
         <v>123562</v>
       </c>
     </row>
-    <row r="5" ht="15.15" spans="1:69">
+    <row r="5" ht="15.75" spans="1:69">
       <c r="A5" s="7">
         <v>1</v>
       </c>
@@ -29557,14 +29636,14 @@
       <c r="F5" s="8">
         <v>4</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" t="s" s="0">
         <v>92</v>
       </c>
       <c r="H5" s="8">
         <f>F5*G5</f>
         <v>400</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" t="s" s="0">
         <v>93</v>
       </c>
       <c r="J5" s="8">
@@ -29702,10 +29781,10 @@
       <c r="AT5" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AU5" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AV5" t="s" s="0">
         <v>145</v>
       </c>
       <c r="AW5" s="39">
@@ -29746,10 +29825,10 @@
       <c r="BL5" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BM5" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BN5" t="s" s="0">
         <v>97</v>
       </c>
       <c r="BO5" s="39">
@@ -29764,7 +29843,7 @@
         <v>123562</v>
       </c>
     </row>
-    <row r="6" ht="15.15" spans="1:69">
+    <row r="6" ht="15.75" spans="1:69">
       <c r="A6" s="9"/>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
@@ -29882,7 +29961,7 @@
       <c r="BP6" s="40"/>
       <c r="BQ6" s="40"/>
     </row>
-    <row r="7" ht="15.15" spans="1:69">
+    <row r="7" ht="15.75" spans="1:69">
       <c r="A7" s="9"/>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
@@ -29953,7 +30032,7 @@
       <c r="BP7" s="40"/>
       <c r="BQ7" s="40"/>
     </row>
-    <row r="8" ht="15.15" spans="1:69">
+    <row r="8" ht="15.75" spans="1:69">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -30035,7 +30114,7 @@
       <c r="BP8" s="40"/>
       <c r="BQ8" s="40"/>
     </row>
-    <row r="9" ht="15.15" spans="1:69">
+    <row r="9" ht="15.75" spans="1:69">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -30123,7 +30202,7 @@
       <c r="BP9" s="40"/>
       <c r="BQ9" s="40"/>
     </row>
-    <row r="10" ht="15.15" spans="1:69">
+    <row r="10" ht="15.75" spans="1:69">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -30207,7 +30286,7 @@
       <c r="BP10" s="40"/>
       <c r="BQ10" s="40"/>
     </row>
-    <row r="11" ht="15.15" spans="1:69">
+    <row r="11" ht="15.75" spans="1:69">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -30291,7 +30370,7 @@
       <c r="BP11" s="40"/>
       <c r="BQ11" s="40"/>
     </row>
-    <row r="12" ht="15.15" spans="1:69">
+    <row r="12" ht="15.75" spans="1:69">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -30928,13 +31007,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ20"/>
-  <sheetFormatPr defaultColWidth="8.85185185185185" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.84761904761905" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="13" max="13" width="9.13888888888889" customWidth="1"/>
-    <col min="14" max="14" width="13.8518518518519" customWidth="1"/>
-    <col min="64" max="64" width="11" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="28.0"/>
+    <col min="3" max="3" customWidth="true" width="23.0"/>
+    <col min="13" max="13" customWidth="true" width="9.14285714285714"/>
+    <col min="14" max="14" customWidth="true" width="13.847619047619"/>
+    <col min="29" max="29" width="9.28571428571429"/>
+    <col min="35" max="35" width="11.4285714285714"/>
+    <col min="52" max="52" width="13.2857142857143"/>
+    <col min="64" max="64" customWidth="true" width="11.0"/>
+    <col min="67" max="67" width="12.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -31010,7 +31093,7 @@
       <c r="BP1" s="40"/>
       <c r="BQ1" s="40"/>
     </row>
-    <row r="2" ht="15.15" spans="1:69">
+    <row r="2" ht="15.75" spans="1:69">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -31105,7 +31188,7 @@
       <c r="BP2" s="40"/>
       <c r="BQ2" s="40"/>
     </row>
-    <row r="3" ht="59.1" spans="1:69">
+    <row r="3" ht="61.5" spans="1:69">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
@@ -31314,7 +31397,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.15" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="7">
         <v>1</v>
       </c>
@@ -31331,16 +31414,16 @@
         <v>77</v>
       </c>
       <c r="F4" s="8">
-        <v>5</v>
-      </c>
-      <c r="G4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" t="s" s="0">
         <v>78</v>
       </c>
       <c r="H4" s="8">
         <f t="shared" ref="H4:H6" si="0">F4*G4</f>
-        <v>750</v>
-      </c>
-      <c r="I4" t="s">
+        <v>450</v>
+      </c>
+      <c r="I4" t="s" s="0">
         <v>79</v>
       </c>
       <c r="J4" s="8">
@@ -31351,35 +31434,35 @@
       </c>
       <c r="L4" s="8">
         <f t="shared" ref="L4:L6" si="1">IF(OR(I4=0,I4="0"),0,H4)</f>
-        <v>750</v>
+        <v>450</v>
       </c>
       <c r="M4" s="8">
         <f>ROUND(L4*I4%,3)</f>
-        <v>37.5</v>
+        <v>22.5</v>
       </c>
       <c r="N4" s="8">
         <f t="shared" ref="N4:N6" si="2">H4-M4</f>
-        <v>712.5</v>
+        <v>427.5</v>
       </c>
       <c r="O4" s="8">
         <f>ROUND(N4*J4%,3)</f>
-        <v>57</v>
+        <v>34.2</v>
       </c>
       <c r="P4" s="8">
         <f t="shared" ref="P4:P6" si="3">ROUND(N4-O4,2)</f>
-        <v>655.5</v>
+        <v>393.3</v>
       </c>
       <c r="Q4" s="8">
         <f t="shared" ref="Q4:Q6" si="4">ROUND(P4*K4%,2)</f>
-        <v>32.78</v>
+        <v>19.67</v>
       </c>
       <c r="R4" s="26">
         <f>ROUND(M4+O4+Q4,3)</f>
-        <v>127.28</v>
+        <v>76.37</v>
       </c>
       <c r="S4" s="26">
         <f t="shared" ref="S4:S6" si="5">(H4-R4)</f>
-        <v>622.72</v>
+        <v>373.63</v>
       </c>
       <c r="T4" s="8">
         <v>88363222</v>
@@ -31416,7 +31499,7 @@
       </c>
       <c r="AC4" s="31">
         <f>IF($V2=1,S4+AB4,S4)</f>
-        <v>622.72</v>
+        <v>373.63</v>
       </c>
       <c r="AD4" s="26">
         <v>120</v>
@@ -31436,7 +31519,7 @@
       </c>
       <c r="AI4" s="26">
         <f>S4*$M2</f>
-        <v>52931.2</v>
+        <v>31758.55</v>
       </c>
       <c r="AJ4" s="26">
         <f>IF($C$2=3,0,AG4+AH4)</f>
@@ -31451,11 +31534,11 @@
       </c>
       <c r="AM4" s="26">
         <f t="shared" ref="AM4:AM6" si="7">F4/AL4</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AN4" s="26">
         <f t="shared" ref="AN4:AN6" si="8">ROUND(AI4/AM4,5)</f>
-        <v>10586.24</v>
+        <v>10586.18333</v>
       </c>
       <c r="AO4" s="26">
         <f t="shared" ref="AO4:AO6" si="9">AJ4/AM4</f>
@@ -31470,7 +31553,7 @@
       </c>
       <c r="AR4" s="26">
         <f t="shared" ref="AR4:AR6" si="11">ROUND(AN4+AO4+AP4,5)</f>
-        <v>10586.24</v>
+        <v>10586.18333</v>
       </c>
       <c r="AS4" s="38" t="s">
         <v>80</v>
@@ -31478,27 +31561,27 @@
       <c r="AT4" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AU4" t="s" s="0">
         <v>81</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AV4" t="s" s="0">
         <v>82</v>
       </c>
       <c r="AW4" s="39">
         <f t="shared" ref="AW4:AW6" si="12">AM4</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AX4" s="42">
         <f t="shared" ref="AX4:AX6" si="13">AR4</f>
-        <v>10586.24</v>
+        <v>10586.18333</v>
       </c>
       <c r="AY4" s="39">
         <f t="shared" ref="AY4:AY6" si="14">AU4+AW4</f>
-        <v>380</v>
-      </c>
-      <c r="AZ4" s="43">
-        <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),3)</f>
-        <v>3670.799</v>
+        <v>378</v>
+      </c>
+      <c r="AZ4" s="39">
+        <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),5)</f>
+        <v>3634.20881</v>
       </c>
       <c r="BA4" s="44"/>
       <c r="BB4" s="44" t="s">
@@ -31522,25 +31605,25 @@
       <c r="BL4" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>89</v>
       </c>
       <c r="BO4" s="39">
         <f t="shared" ref="BO4:BO6" si="15">ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
-        <v>333.14818</v>
+        <v>251.40032</v>
       </c>
       <c r="BP4" s="48">
         <f t="shared" ref="BP4:BP6" si="16">ROUND(BN4+AW4,3)</f>
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="BQ4" s="49">
         <v>123562</v>
       </c>
     </row>
-    <row r="5" ht="15.15" spans="1:69">
+    <row r="5" ht="15.75" spans="1:69">
       <c r="A5" s="7">
         <v>1</v>
       </c>
@@ -31557,16 +31640,16 @@
         <v>77</v>
       </c>
       <c r="F5" s="8">
-        <v>4</v>
-      </c>
-      <c r="G5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" t="s" s="0">
         <v>92</v>
       </c>
       <c r="H5" s="8">
         <f t="shared" si="0"/>
-        <v>400</v>
-      </c>
-      <c r="I5" t="s">
+        <v>600</v>
+      </c>
+      <c r="I5" t="s" s="0">
         <v>93</v>
       </c>
       <c r="J5" s="8">
@@ -31577,35 +31660,35 @@
       </c>
       <c r="L5" s="8">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="M5" s="8">
         <f>ROUND(L5*I5%,2)</f>
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="N5" s="8">
         <f t="shared" si="2"/>
-        <v>384</v>
+        <v>576</v>
       </c>
       <c r="O5" s="8">
         <f>ROUND(N5*J5%,2)</f>
-        <v>34.56</v>
+        <v>51.84</v>
       </c>
       <c r="P5" s="8">
         <f t="shared" si="3"/>
-        <v>349.44</v>
+        <v>524.16</v>
       </c>
       <c r="Q5" s="8">
         <f t="shared" si="4"/>
-        <v>20.97</v>
+        <v>31.45</v>
       </c>
       <c r="R5" s="8">
         <f>M5+O5+Q5</f>
-        <v>71.53</v>
+        <v>107.29</v>
       </c>
       <c r="S5" s="8">
         <f t="shared" si="5"/>
-        <v>328.47</v>
+        <v>492.71</v>
       </c>
       <c r="T5" s="8">
         <v>88363222</v>
@@ -31614,26 +31697,26 @@
         <v>18</v>
       </c>
       <c r="V5" s="8">
-        <f>IF(OR(DGSUomWISer!$C$2=1,DGSUomWISer!$C$2=4),ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF(OR($C$2=1,$C$2=4),ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="W5" s="8">
-        <f>IF(DGSUomWISer!$C$2=1,ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF($C$2=1,ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="X5" s="8">
-        <f>IF(DGSUomWISer!$C$2=2,ROUND(((S5*U5)/100),2),0)</f>
+        <f>IF($C$2=2,ROUND(((S5*U5)/100),2),0)</f>
         <v>0</v>
       </c>
       <c r="Y5" s="8">
-        <f>IF(DGSUomWISer!$C$2=4,ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF($C$2=4,ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="Z5" s="8">
         <v>0</v>
       </c>
       <c r="AA5" s="8">
-        <f>IF(DGSUomWISer!$C3=3,0,(S5*Z5)/100)</f>
+        <f>IF($C3=3,0,(S5*Z5)/100)</f>
         <v>0</v>
       </c>
       <c r="AB5" s="8">
@@ -31641,35 +31724,35 @@
         <v>0</v>
       </c>
       <c r="AC5" s="8">
-        <f>IF(DGSUomWISer!$V3=1,S5+AB5,S5)</f>
-        <v>328.47</v>
+        <f>IF($V3=1,S5+AB5,S5)</f>
+        <v>492.71</v>
       </c>
       <c r="AD5" s="26">
         <v>120</v>
       </c>
       <c r="AE5" s="26">
-        <f>IF(DGSUomWISer!$P$2=1,(S5/DGSUomWISer!$S$7)*DGSUomWISer!$E$18,AD5/DGSUomWISer!$AD$7*DGSUomWISer!$E$18)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$18,AD5/$AD$7*$E$18)</f>
         <v>0</v>
       </c>
       <c r="AF5" s="26"/>
       <c r="AG5" s="26">
-        <f>IF(DGSUomWISer!$P$2=1,(S5/DGSUomWISer!$S$7)*DGSUomWISer!$E$20,AD5/DGSUomWISer!$AD$7*DGSUomWISer!$E$20)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$20,AD5/$AD$7*$E$20)</f>
         <v>0</v>
       </c>
       <c r="AH5" s="26">
-        <f>IF(DGSUomWISer!$P$2=1,(S5/DGSUomWISer!$S$7)*DGSUomWISer!$E$21,AD5/DGSUomWISer!$AD$7*DGSUomWISer!$E$21)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$21,AD5/$AD$7*$E$21)</f>
         <v>0</v>
       </c>
       <c r="AI5" s="26">
-        <f>S5*DGSUomWISer!$M$2</f>
-        <v>27919.95</v>
+        <f>S5*$M$2</f>
+        <v>41880.35</v>
       </c>
       <c r="AJ5" s="26">
-        <f>IF(DGSUomWISer!$C$2=3,0,AG5+AH5)</f>
+        <f>IF($C$2=3,0,AG5+AH5)</f>
         <v>0</v>
       </c>
       <c r="AK5" s="26">
-        <f>IF(DGSUomWISer!$C$2=3,AE5+AG5+AH5,0)</f>
+        <f>IF($C$2=3,AE5+AG5+AH5,0)</f>
         <v>0</v>
       </c>
       <c r="AL5" s="34">
@@ -31677,11 +31760,11 @@
       </c>
       <c r="AM5" s="26">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AN5" s="26">
         <f t="shared" si="8"/>
-        <v>6979.9875</v>
+        <v>6980.05833</v>
       </c>
       <c r="AO5" s="26">
         <f t="shared" si="9"/>
@@ -31696,7 +31779,7 @@
       </c>
       <c r="AR5" s="26">
         <f t="shared" si="11"/>
-        <v>6979.9875</v>
+        <v>6980.05833</v>
       </c>
       <c r="AS5" s="38" t="s">
         <v>80</v>
@@ -31704,27 +31787,27 @@
       <c r="AT5" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AU5" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AV5" t="s" s="0">
         <v>95</v>
       </c>
       <c r="AW5" s="39">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX5" s="42">
         <f t="shared" si="13"/>
-        <v>6979.9875</v>
+        <v>6980.05833</v>
       </c>
       <c r="AY5" s="39">
         <f t="shared" si="14"/>
-        <v>192</v>
-      </c>
-      <c r="AZ5" s="42">
-        <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),2)</f>
-        <v>2076.95</v>
+        <v>194</v>
+      </c>
+      <c r="AZ5" s="39">
+        <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),5)</f>
+        <v>2127.49623</v>
       </c>
       <c r="BA5" s="44"/>
       <c r="BB5" s="44" t="s">
@@ -31748,25 +31831,25 @@
       <c r="BL5" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BM5" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BN5" t="s" s="0">
         <v>97</v>
       </c>
       <c r="BO5" s="39">
         <f t="shared" si="15"/>
-        <v>206.79688</v>
+        <v>268.06329</v>
       </c>
       <c r="BP5" s="48">
         <f t="shared" si="16"/>
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="BQ5" s="49">
         <v>123562</v>
       </c>
     </row>
-    <row r="6" ht="15.15" spans="1:69">
+    <row r="6" ht="15.75" spans="1:69">
       <c r="A6" s="7">
         <v>1</v>
       </c>
@@ -31783,16 +31866,16 @@
         <v>77</v>
       </c>
       <c r="F6" s="8">
-        <v>20</v>
-      </c>
-      <c r="G6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H6" s="8">
         <f t="shared" si="0"/>
-        <v>1000</v>
-      </c>
-      <c r="I6" t="s">
+        <v>600</v>
+      </c>
+      <c r="I6" t="s" s="0">
         <v>101</v>
       </c>
       <c r="J6" s="8">
@@ -31803,35 +31886,35 @@
       </c>
       <c r="L6" s="8">
         <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="M6" s="8">
         <f>ROUND(L6*I6%,2)</f>
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="N6" s="8">
         <f t="shared" si="2"/>
-        <v>970</v>
+        <v>582</v>
       </c>
       <c r="O6" s="8">
         <f>ROUND(N6*J6%,2)</f>
-        <v>67.9</v>
+        <v>40.74</v>
       </c>
       <c r="P6" s="8">
         <f t="shared" si="3"/>
-        <v>902.1</v>
+        <v>541.26</v>
       </c>
       <c r="Q6" s="8">
         <f t="shared" si="4"/>
-        <v>36.08</v>
+        <v>21.65</v>
       </c>
       <c r="R6" s="8">
         <f>M6+O6+Q6</f>
-        <v>133.98</v>
+        <v>80.39</v>
       </c>
       <c r="S6" s="8">
         <f t="shared" si="5"/>
-        <v>866.02</v>
+        <v>519.61</v>
       </c>
       <c r="T6" s="8">
         <v>88363222</v>
@@ -31840,26 +31923,26 @@
         <v>18</v>
       </c>
       <c r="V6" s="8">
-        <f>IF(OR(DGSUomWISer!$C$2=1,DGSUomWISer!$C$2=4),ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF(OR($C$2=1,$C$2=4),ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="W6" s="8">
-        <f>IF(DGSUomWISer!$C$2=1,ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF($C$2=1,ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="X6" s="8">
-        <f>IF(DGSUomWISer!$C$2=2,ROUND(((S6*U6)/100),2),0)</f>
+        <f>IF($C$2=2,ROUND(((S6*U6)/100),2),0)</f>
         <v>0</v>
       </c>
       <c r="Y6" s="8">
-        <f>IF(DGSUomWISer!$C$2=4,ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF($C$2=4,ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="Z6" s="8">
         <v>0</v>
       </c>
       <c r="AA6" s="8">
-        <f>IF(DGSUomWISer!$C4=3,0,(S6*Z6)/100)</f>
+        <f>IF($C4=3,0,(S6*Z6)/100)</f>
         <v>0</v>
       </c>
       <c r="AB6" s="8">
@@ -31867,35 +31950,35 @@
         <v>0</v>
       </c>
       <c r="AC6" s="8">
-        <f>IF(DGSUomWISer!$V4=1,S6+AB6,S6)</f>
-        <v>866.02</v>
+        <f>IF($V4=1,S6+AB6,S6)</f>
+        <v>519.61</v>
       </c>
       <c r="AD6" s="26">
         <v>120</v>
       </c>
       <c r="AE6" s="26">
-        <f>IF(DGSUomWISer!$P$2=1,(S6/DGSUomWISer!$S$7)*DGSUomWISer!$E$18,AD6/DGSUomWISer!$AD$7*DGSUomWISer!$E$18)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$18,AD6/$AD$7*$E$18)</f>
         <v>0</v>
       </c>
       <c r="AF6" s="26"/>
       <c r="AG6" s="26">
-        <f>IF(DGSUomWISer!$P$2=1,(S6/DGSUomWISer!$S$7)*DGSUomWISer!$E$20,AD6/DGSUomWISer!$AD$7*DGSUomWISer!$E$20)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$20,AD6/$AD$7*$E$20)</f>
         <v>0</v>
       </c>
       <c r="AH6" s="26">
-        <f>IF(DGSUomWISer!$P$2=1,(S6/DGSUomWISer!$S$7)*DGSUomWISer!$E$21,AD6/DGSUomWISer!$AD$7*DGSUomWISer!$E$21)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$21,AD6/$AD$7*$E$21)</f>
         <v>0</v>
       </c>
       <c r="AI6" s="26">
-        <f>S6*DGSUomWISer!$M$2</f>
-        <v>73611.7</v>
+        <f>S6*$M$2</f>
+        <v>44166.85</v>
       </c>
       <c r="AJ6" s="26">
-        <f>IF(DGSUomWISer!$C$2=3,0,AG6+AH6)</f>
+        <f>IF($C$2=3,0,AG6+AH6)</f>
         <v>0</v>
       </c>
       <c r="AK6" s="26">
-        <f>IF(DGSUomWISer!$C$2=3,AE6+AG6+AH6,0)</f>
+        <f>IF($C$2=3,AE6+AG6+AH6,0)</f>
         <v>0</v>
       </c>
       <c r="AL6" s="34">
@@ -31903,11 +31986,11 @@
       </c>
       <c r="AM6" s="26">
         <f t="shared" si="7"/>
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AN6" s="26">
         <f t="shared" si="8"/>
-        <v>3680.585</v>
+        <v>3680.57083</v>
       </c>
       <c r="AO6" s="26">
         <f t="shared" si="9"/>
@@ -31922,7 +32005,7 @@
       </c>
       <c r="AR6" s="26">
         <f t="shared" si="11"/>
-        <v>3680.585</v>
+        <v>3680.57083</v>
       </c>
       <c r="AS6" s="38" t="s">
         <v>80</v>
@@ -31930,27 +32013,27 @@
       <c r="AT6" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AU6" t="s" s="0">
         <v>102</v>
       </c>
-      <c r="AV6" t="s">
+      <c r="AV6" t="s" s="0">
         <v>103</v>
       </c>
       <c r="AW6" s="39">
         <f t="shared" si="12"/>
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AX6" s="39">
         <f t="shared" si="13"/>
-        <v>3680.585</v>
+        <v>3680.57083</v>
       </c>
       <c r="AY6" s="39">
         <f t="shared" si="14"/>
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="AZ6" s="39">
-        <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),1)</f>
-        <v>1198.5</v>
+        <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),5)</f>
+        <v>1158.18872</v>
       </c>
       <c r="BA6" s="44"/>
       <c r="BB6" s="44" t="s">
@@ -31974,25 +32057,25 @@
       <c r="BL6" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM6" t="s">
+      <c r="BM6" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="BN6" t="s">
+      <c r="BN6" t="s" s="0">
         <v>105</v>
       </c>
       <c r="BO6" s="39">
         <f t="shared" si="15"/>
-        <v>115.5</v>
+        <v>86.18034</v>
       </c>
       <c r="BP6" s="48">
         <f t="shared" si="16"/>
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="BQ6" s="49">
         <v>123562</v>
       </c>
     </row>
-    <row r="7" ht="15.15" spans="1:69">
+    <row r="7" ht="15.75" spans="1:69">
       <c r="A7" s="9"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -32004,7 +32087,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="13">
         <f>SUM(H4:H4)</f>
-        <v>750</v>
+        <v>450</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
@@ -32017,11 +32100,11 @@
       <c r="Q7" s="7"/>
       <c r="R7" s="27">
         <f t="shared" ref="R7:X7" si="17">SUM(R4:R4)</f>
-        <v>127.28</v>
+        <v>76.37</v>
       </c>
       <c r="S7" s="13">
         <f t="shared" si="17"/>
-        <v>622.72</v>
+        <v>373.63</v>
       </c>
       <c r="T7" s="27"/>
       <c r="U7" s="27"/>
@@ -32046,7 +32129,7 @@
       </c>
       <c r="AC7" s="32">
         <f t="shared" si="18"/>
-        <v>622.72</v>
+        <v>373.63</v>
       </c>
       <c r="AD7" s="33">
         <f t="shared" si="18"/>
@@ -32067,7 +32150,7 @@
       </c>
       <c r="AI7" s="33">
         <f t="shared" si="19"/>
-        <v>52931.2</v>
+        <v>31758.55</v>
       </c>
       <c r="AJ7" s="33">
         <f t="shared" si="19"/>
@@ -32110,7 +32193,7 @@
       <c r="BP7" s="40"/>
       <c r="BQ7" s="40"/>
     </row>
-    <row r="8" ht="15.15" spans="1:69">
+    <row r="8" ht="15.75" spans="1:69">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -32181,7 +32264,7 @@
       <c r="BP8" s="40"/>
       <c r="BQ8" s="40"/>
     </row>
-    <row r="9" ht="15.15" spans="1:69">
+    <row r="9" ht="15.75" spans="1:69">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -32194,7 +32277,7 @@
       <c r="H9" s="15"/>
       <c r="I9" s="19">
         <f>H7</f>
-        <v>750</v>
+        <v>450</v>
       </c>
       <c r="J9" s="19"/>
       <c r="K9" s="9"/>
@@ -32263,7 +32346,7 @@
       <c r="BP9" s="40"/>
       <c r="BQ9" s="40"/>
     </row>
-    <row r="10" ht="15.15" spans="1:69">
+    <row r="10" ht="15.75" spans="1:69">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -32276,7 +32359,7 @@
       <c r="H10" s="15"/>
       <c r="I10" s="19">
         <f>R7</f>
-        <v>127.28</v>
+        <v>76.37</v>
       </c>
       <c r="J10" s="19"/>
       <c r="K10" s="9"/>
@@ -32351,7 +32434,7 @@
       <c r="BP10" s="40"/>
       <c r="BQ10" s="40"/>
     </row>
-    <row r="11" ht="15.15" spans="1:69">
+    <row r="11" ht="15.75" spans="1:69">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -32364,7 +32447,7 @@
       <c r="H11" s="15"/>
       <c r="I11" s="19">
         <f>S7</f>
-        <v>622.72</v>
+        <v>373.63</v>
       </c>
       <c r="J11" s="19"/>
       <c r="K11" s="9"/>
@@ -32435,7 +32518,7 @@
       <c r="BP11" s="40"/>
       <c r="BQ11" s="40"/>
     </row>
-    <row r="12" ht="15.15" spans="1:69">
+    <row r="12" ht="15.75" spans="1:69">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -32519,7 +32602,7 @@
       <c r="BP12" s="40"/>
       <c r="BQ12" s="40"/>
     </row>
-    <row r="13" ht="15.15" spans="1:69">
+    <row r="13" ht="15.75" spans="1:69">
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -32532,7 +32615,7 @@
       <c r="H13" s="15"/>
       <c r="I13" s="24">
         <f>I11+I12</f>
-        <v>622.72</v>
+        <v>373.63</v>
       </c>
       <c r="J13" s="24"/>
       <c r="K13" s="9"/>
@@ -33157,13 +33240,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ20"/>
-  <sheetFormatPr defaultColWidth="8.85185185185185" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.84761904761905" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="13" max="13" width="9.13888888888889" customWidth="1"/>
-    <col min="14" max="14" width="13.8518518518519" customWidth="1"/>
-    <col min="64" max="64" width="11" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="28.0"/>
+    <col min="3" max="3" customWidth="true" width="23.0"/>
+    <col min="13" max="13" customWidth="true" width="9.14285714285714"/>
+    <col min="14" max="14" customWidth="true" width="13.847619047619"/>
+    <col min="64" max="64" customWidth="true" width="11.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -33239,7 +33322,7 @@
       <c r="BP1" s="40"/>
       <c r="BQ1" s="40"/>
     </row>
-    <row r="2" ht="15.15" spans="1:69">
+    <row r="2" ht="15.75" spans="1:69">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -33334,7 +33417,7 @@
       <c r="BP2" s="40"/>
       <c r="BQ2" s="40"/>
     </row>
-    <row r="3" ht="59.1" spans="1:69">
+    <row r="3" ht="61.5" spans="1:69">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
@@ -33543,7 +33626,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.15" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="7">
         <v>1</v>
       </c>
@@ -33562,14 +33645,14 @@
       <c r="F4" s="8">
         <v>5</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" t="s" s="0">
         <v>78</v>
       </c>
       <c r="H4" s="8">
         <f t="shared" ref="H4:H6" si="0">F4*G4</f>
         <v>750</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" t="s" s="0">
         <v>79</v>
       </c>
       <c r="J4" s="8">
@@ -33707,10 +33790,10 @@
       <c r="AT4" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AU4" t="s" s="0">
         <v>81</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AV4" t="s" s="0">
         <v>82</v>
       </c>
       <c r="AW4" s="39">
@@ -33751,10 +33834,10 @@
       <c r="BL4" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>89</v>
       </c>
       <c r="BO4" s="39">
@@ -33769,7 +33852,7 @@
         <v>123562</v>
       </c>
     </row>
-    <row r="5" ht="15.15" spans="1:69">
+    <row r="5" ht="15.75" spans="1:69">
       <c r="A5" s="7">
         <v>1</v>
       </c>
@@ -33788,14 +33871,14 @@
       <c r="F5" s="8">
         <v>4</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" t="s" s="0">
         <v>92</v>
       </c>
       <c r="H5" s="8">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" t="s" s="0">
         <v>93</v>
       </c>
       <c r="J5" s="8">
@@ -33933,10 +34016,10 @@
       <c r="AT5" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AU5" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AV5" t="s" s="0">
         <v>95</v>
       </c>
       <c r="AW5" s="39">
@@ -33977,10 +34060,10 @@
       <c r="BL5" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BM5" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BN5" t="s" s="0">
         <v>97</v>
       </c>
       <c r="BO5" s="39">
@@ -33995,7 +34078,7 @@
         <v>123562</v>
       </c>
     </row>
-    <row r="6" ht="15.15" spans="1:69">
+    <row r="6" ht="15.75" spans="1:69">
       <c r="A6" s="7">
         <v>1</v>
       </c>
@@ -34014,14 +34097,14 @@
       <c r="F6" s="8">
         <v>20</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H6" s="8">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" t="s" s="0">
         <v>101</v>
       </c>
       <c r="J6" s="8">
@@ -34159,10 +34242,10 @@
       <c r="AT6" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AU6" t="s" s="0">
         <v>102</v>
       </c>
-      <c r="AV6" t="s">
+      <c r="AV6" t="s" s="0">
         <v>103</v>
       </c>
       <c r="AW6" s="39">
@@ -34203,10 +34286,10 @@
       <c r="BL6" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM6" t="s">
+      <c r="BM6" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="BN6" t="s">
+      <c r="BN6" t="s" s="0">
         <v>105</v>
       </c>
       <c r="BO6" s="39">
@@ -34221,7 +34304,7 @@
         <v>123562</v>
       </c>
     </row>
-    <row r="7" ht="15.15" spans="1:69">
+    <row r="7" ht="15.75" spans="1:69">
       <c r="A7" s="9"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -34339,7 +34422,7 @@
       <c r="BP7" s="40"/>
       <c r="BQ7" s="40"/>
     </row>
-    <row r="8" ht="15.15" spans="1:69">
+    <row r="8" ht="15.75" spans="1:69">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -34410,7 +34493,7 @@
       <c r="BP8" s="40"/>
       <c r="BQ8" s="40"/>
     </row>
-    <row r="9" ht="15.15" spans="1:69">
+    <row r="9" ht="15.75" spans="1:69">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -34492,7 +34575,7 @@
       <c r="BP9" s="40"/>
       <c r="BQ9" s="40"/>
     </row>
-    <row r="10" ht="15.15" spans="1:69">
+    <row r="10" ht="15.75" spans="1:69">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -34580,7 +34663,7 @@
       <c r="BP10" s="40"/>
       <c r="BQ10" s="40"/>
     </row>
-    <row r="11" ht="15.15" spans="1:69">
+    <row r="11" ht="15.75" spans="1:69">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -34664,7 +34747,7 @@
       <c r="BP11" s="40"/>
       <c r="BQ11" s="40"/>
     </row>
-    <row r="12" ht="15.15" spans="1:69">
+    <row r="12" ht="15.75" spans="1:69">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -34748,7 +34831,7 @@
       <c r="BP12" s="40"/>
       <c r="BQ12" s="40"/>
     </row>
-    <row r="13" ht="15.15" spans="1:69">
+    <row r="13" ht="15.75" spans="1:69">
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -35386,13 +35469,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ20"/>
-  <sheetFormatPr defaultColWidth="8.85185185185185" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.84761904761905" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="29.1388888888889" customWidth="1"/>
-    <col min="13" max="13" width="9.13888888888889" customWidth="1"/>
-    <col min="14" max="14" width="13.8518518518519" customWidth="1"/>
-    <col min="64" max="64" width="11" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="28.0"/>
+    <col min="3" max="3" customWidth="true" width="29.1428571428571"/>
+    <col min="13" max="13" customWidth="true" width="9.14285714285714"/>
+    <col min="14" max="14" customWidth="true" width="13.847619047619"/>
+    <col min="64" max="64" customWidth="true" width="11.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -35468,7 +35551,7 @@
       <c r="BP1" s="40"/>
       <c r="BQ1" s="40"/>
     </row>
-    <row r="2" ht="15.15" spans="1:69">
+    <row r="2" ht="15.75" spans="1:69">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -35563,7 +35646,7 @@
       <c r="BP2" s="40"/>
       <c r="BQ2" s="40"/>
     </row>
-    <row r="3" ht="59.1" spans="1:69">
+    <row r="3" ht="61.5" spans="1:69">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
@@ -35772,7 +35855,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.15" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="7">
         <v>1</v>
       </c>
@@ -35791,14 +35874,14 @@
       <c r="F4" s="8">
         <v>5</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H4" s="8">
         <f t="shared" ref="H4:H6" si="0">F4*G4</f>
         <v>250</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J4" s="8">
@@ -35936,10 +36019,10 @@
       <c r="AT4" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AU4" t="s" s="0">
         <v>81</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AV4" t="s" s="0">
         <v>82</v>
       </c>
       <c r="AW4" s="39">
@@ -35980,10 +36063,10 @@
       <c r="BL4" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>89</v>
       </c>
       <c r="BO4" s="39">
@@ -35998,7 +36081,7 @@
         <v>123562</v>
       </c>
     </row>
-    <row r="5" ht="15.15" spans="1:69">
+    <row r="5" ht="15.75" spans="1:69">
       <c r="A5" s="7">
         <v>1</v>
       </c>
@@ -36017,14 +36100,14 @@
       <c r="F5" s="8">
         <v>4</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" t="s" s="0">
         <v>92</v>
       </c>
       <c r="H5" s="8">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" t="s" s="0">
         <v>93</v>
       </c>
       <c r="J5" s="8">
@@ -36162,10 +36245,10 @@
       <c r="AT5" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AU5" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AV5" t="s" s="0">
         <v>95</v>
       </c>
       <c r="AW5" s="39">
@@ -36206,10 +36289,10 @@
       <c r="BL5" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BM5" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BN5" t="s" s="0">
         <v>97</v>
       </c>
       <c r="BO5" s="39">
@@ -36224,7 +36307,7 @@
         <v>123562</v>
       </c>
     </row>
-    <row r="6" ht="15.15" spans="1:69">
+    <row r="6" ht="15.75" spans="1:69">
       <c r="A6" s="7">
         <v>1</v>
       </c>
@@ -36243,14 +36326,14 @@
       <c r="F6" s="8">
         <v>20</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H6" s="8">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" t="s" s="0">
         <v>101</v>
       </c>
       <c r="J6" s="8">
@@ -36388,10 +36471,10 @@
       <c r="AT6" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AU6" t="s" s="0">
         <v>102</v>
       </c>
-      <c r="AV6" t="s">
+      <c r="AV6" t="s" s="0">
         <v>103</v>
       </c>
       <c r="AW6" s="39">
@@ -36432,10 +36515,10 @@
       <c r="BL6" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM6" t="s">
+      <c r="BM6" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="BN6" t="s">
+      <c r="BN6" t="s" s="0">
         <v>105</v>
       </c>
       <c r="BO6" s="39">
@@ -36450,7 +36533,7 @@
         <v>123562</v>
       </c>
     </row>
-    <row r="7" ht="15.15" spans="1:69">
+    <row r="7" ht="15.75" spans="1:69">
       <c r="A7" s="9"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -36568,7 +36651,7 @@
       <c r="BP7" s="40"/>
       <c r="BQ7" s="40"/>
     </row>
-    <row r="8" ht="15.15" spans="1:69">
+    <row r="8" ht="15.75" spans="1:69">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -36639,7 +36722,7 @@
       <c r="BP8" s="40"/>
       <c r="BQ8" s="40"/>
     </row>
-    <row r="9" ht="15.15" spans="1:69">
+    <row r="9" ht="15.75" spans="1:69">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -36721,7 +36804,7 @@
       <c r="BP9" s="40"/>
       <c r="BQ9" s="40"/>
     </row>
-    <row r="10" ht="15.15" spans="1:69">
+    <row r="10" ht="15.75" spans="1:69">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -36809,7 +36892,7 @@
       <c r="BP10" s="40"/>
       <c r="BQ10" s="40"/>
     </row>
-    <row r="11" ht="15.15" spans="1:69">
+    <row r="11" ht="15.75" spans="1:69">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -36893,7 +36976,7 @@
       <c r="BP11" s="40"/>
       <c r="BQ11" s="40"/>
     </row>
-    <row r="12" ht="15.15" spans="1:69">
+    <row r="12" ht="15.75" spans="1:69">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -36977,7 +37060,7 @@
       <c r="BP12" s="40"/>
       <c r="BQ12" s="40"/>
     </row>
-    <row r="13" ht="15.15" spans="1:69">
+    <row r="13" ht="15.75" spans="1:69">
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -37615,13 +37698,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ20"/>
-  <sheetFormatPr defaultColWidth="8.85185185185185" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.84761904761905" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="13" max="13" width="9.13888888888889" customWidth="1"/>
-    <col min="14" max="14" width="13.8518518518519" customWidth="1"/>
-    <col min="64" max="64" width="11" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="28.0"/>
+    <col min="3" max="3" customWidth="true" width="23.0"/>
+    <col min="13" max="13" customWidth="true" width="9.14285714285714"/>
+    <col min="14" max="14" customWidth="true" width="13.847619047619"/>
+    <col min="29" max="29" width="9.28571428571429"/>
+    <col min="35" max="35" width="11.4285714285714"/>
+    <col min="52" max="52" width="13.2857142857143"/>
+    <col min="64" max="64" customWidth="true" width="11.0"/>
+    <col min="67" max="67" width="12.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -37697,7 +37784,7 @@
       <c r="BP1" s="40"/>
       <c r="BQ1" s="40"/>
     </row>
-    <row r="2" ht="15.15" spans="1:69">
+    <row r="2" ht="15.75" spans="1:69">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -37792,7 +37879,7 @@
       <c r="BP2" s="40"/>
       <c r="BQ2" s="40"/>
     </row>
-    <row r="3" ht="59.1" spans="1:69">
+    <row r="3" ht="61.5" spans="1:69">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
@@ -38001,7 +38088,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.15" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="7">
         <v>1</v>
       </c>
@@ -38018,16 +38105,16 @@
         <v>77</v>
       </c>
       <c r="F4" s="8">
-        <v>5</v>
-      </c>
-      <c r="G4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" t="s" s="0">
         <v>78</v>
       </c>
       <c r="H4" s="8">
         <f t="shared" ref="H4:H6" si="0">F4*G4</f>
-        <v>750</v>
-      </c>
-      <c r="I4" t="s">
+        <v>450</v>
+      </c>
+      <c r="I4" t="s" s="0">
         <v>79</v>
       </c>
       <c r="J4" s="8">
@@ -38038,35 +38125,35 @@
       </c>
       <c r="L4" s="8">
         <f t="shared" ref="L4:L6" si="1">IF(OR(I4=0,I4="0"),0,H4)</f>
-        <v>750</v>
+        <v>450</v>
       </c>
       <c r="M4" s="8">
         <f>ROUND(L4*I4%,3)</f>
-        <v>37.5</v>
+        <v>22.5</v>
       </c>
       <c r="N4" s="8">
         <f t="shared" ref="N4:N6" si="2">H4-M4</f>
-        <v>712.5</v>
+        <v>427.5</v>
       </c>
       <c r="O4" s="8">
         <f>ROUND(N4*J4%,3)</f>
-        <v>57</v>
+        <v>34.2</v>
       </c>
       <c r="P4" s="8">
         <f t="shared" ref="P4:P6" si="3">ROUND(N4-O4,2)</f>
-        <v>655.5</v>
+        <v>393.3</v>
       </c>
       <c r="Q4" s="8">
         <f t="shared" ref="Q4:Q6" si="4">ROUND(P4*K4%,2)</f>
-        <v>32.78</v>
+        <v>19.67</v>
       </c>
       <c r="R4" s="26">
         <f>ROUND(M4+O4+Q4,3)</f>
-        <v>127.28</v>
+        <v>76.37</v>
       </c>
       <c r="S4" s="26">
         <f t="shared" ref="S4:S6" si="5">(H4-R4)</f>
-        <v>622.72</v>
+        <v>373.63</v>
       </c>
       <c r="T4" s="8">
         <v>88363222</v>
@@ -38103,7 +38190,7 @@
       </c>
       <c r="AC4" s="31">
         <f>IF($V2=1,S4+AB4,S4)</f>
-        <v>622.72</v>
+        <v>373.63</v>
       </c>
       <c r="AD4" s="26">
         <v>120</v>
@@ -38123,7 +38210,7 @@
       </c>
       <c r="AI4" s="26">
         <f>S4*$M2</f>
-        <v>52931.2</v>
+        <v>31758.55</v>
       </c>
       <c r="AJ4" s="26">
         <f>IF($C$2=3,0,AG4+AH4)</f>
@@ -38138,11 +38225,11 @@
       </c>
       <c r="AM4" s="26">
         <f t="shared" ref="AM4:AM6" si="7">F4/AL4</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AN4" s="26">
         <f t="shared" ref="AN4:AN6" si="8">ROUND(AI4/AM4,5)</f>
-        <v>10586.24</v>
+        <v>10586.18333</v>
       </c>
       <c r="AO4" s="26">
         <f t="shared" ref="AO4:AO6" si="9">AJ4/AM4</f>
@@ -38157,7 +38244,7 @@
       </c>
       <c r="AR4" s="26">
         <f t="shared" ref="AR4:AR6" si="11">ROUND(AN4+AO4+AP4,5)</f>
-        <v>10586.24</v>
+        <v>10586.18333</v>
       </c>
       <c r="AS4" s="38" t="s">
         <v>80</v>
@@ -38165,27 +38252,27 @@
       <c r="AT4" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AU4" t="s" s="0">
         <v>81</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AV4" t="s" s="0">
         <v>82</v>
       </c>
       <c r="AW4" s="39">
         <f t="shared" ref="AW4:AW6" si="12">AM4</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AX4" s="42">
         <f t="shared" ref="AX4:AX6" si="13">AR4</f>
-        <v>10586.24</v>
+        <v>10586.18333</v>
       </c>
       <c r="AY4" s="39">
         <f t="shared" ref="AY4:AY6" si="14">AU4+AW4</f>
-        <v>380</v>
-      </c>
-      <c r="AZ4" s="43">
-        <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),3)</f>
-        <v>3670.799</v>
+        <v>378</v>
+      </c>
+      <c r="AZ4" s="39">
+        <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),5)</f>
+        <v>3634.20881</v>
       </c>
       <c r="BA4" s="44"/>
       <c r="BB4" s="44" t="s">
@@ -38209,25 +38296,25 @@
       <c r="BL4" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>89</v>
       </c>
       <c r="BO4" s="39">
         <f t="shared" ref="BO4:BO6" si="15">ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
-        <v>333.14818</v>
+        <v>251.40032</v>
       </c>
       <c r="BP4" s="48">
         <f t="shared" ref="BP4:BP6" si="16">ROUND(BN4+AW4,3)</f>
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="BQ4" s="49">
         <v>123562</v>
       </c>
     </row>
-    <row r="5" ht="15.15" spans="1:69">
+    <row r="5" ht="15.75" spans="1:69">
       <c r="A5" s="7">
         <v>1</v>
       </c>
@@ -38244,16 +38331,16 @@
         <v>77</v>
       </c>
       <c r="F5" s="8">
-        <v>4</v>
-      </c>
-      <c r="G5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" t="s" s="0">
         <v>92</v>
       </c>
       <c r="H5" s="8">
         <f t="shared" si="0"/>
-        <v>400</v>
-      </c>
-      <c r="I5" t="s">
+        <v>600</v>
+      </c>
+      <c r="I5" t="s" s="0">
         <v>93</v>
       </c>
       <c r="J5" s="8">
@@ -38264,35 +38351,35 @@
       </c>
       <c r="L5" s="8">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="M5" s="8">
         <f>ROUND(L5*I5%,2)</f>
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="N5" s="8">
         <f t="shared" si="2"/>
-        <v>384</v>
+        <v>576</v>
       </c>
       <c r="O5" s="8">
         <f>ROUND(N5*J5%,2)</f>
-        <v>34.56</v>
+        <v>51.84</v>
       </c>
       <c r="P5" s="8">
         <f t="shared" si="3"/>
-        <v>349.44</v>
+        <v>524.16</v>
       </c>
       <c r="Q5" s="8">
         <f t="shared" si="4"/>
-        <v>20.97</v>
+        <v>31.45</v>
       </c>
       <c r="R5" s="8">
         <f>M5+O5+Q5</f>
-        <v>71.53</v>
+        <v>107.29</v>
       </c>
       <c r="S5" s="8">
         <f t="shared" si="5"/>
-        <v>328.47</v>
+        <v>492.71</v>
       </c>
       <c r="T5" s="8">
         <v>88363222</v>
@@ -38301,26 +38388,26 @@
         <v>18</v>
       </c>
       <c r="V5" s="8">
-        <f>IF(OR(DGSUomWIRcSer!$C$2=1,DGSUomWIRcSer!$C$2=4),ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF(OR($C$2=1,$C$2=4),ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="W5" s="8">
-        <f>IF(DGSUomWIRcSer!$C$2=1,ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF($C$2=1,ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="X5" s="8">
-        <f>IF(DGSUomWIRcSer!$C$2=2,ROUND(((S5*U5)/100),2),0)</f>
+        <f>IF($C$2=2,ROUND(((S5*U5)/100),2),0)</f>
         <v>0</v>
       </c>
       <c r="Y5" s="8">
-        <f>IF(DGSUomWIRcSer!$C$2=4,ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF($C$2=4,ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="Z5" s="8">
         <v>0</v>
       </c>
       <c r="AA5" s="8">
-        <f>IF(DGSUomWIRcSer!$C3=3,0,(S5*Z5)/100)</f>
+        <f>IF($C3=3,0,(S5*Z5)/100)</f>
         <v>0</v>
       </c>
       <c r="AB5" s="8">
@@ -38328,35 +38415,35 @@
         <v>0</v>
       </c>
       <c r="AC5" s="8">
-        <f>IF(DGSUomWIRcSer!$V3=1,S5+AB5,S5)</f>
-        <v>328.47</v>
+        <f>IF($V3=1,S5+AB5,S5)</f>
+        <v>492.71</v>
       </c>
       <c r="AD5" s="26">
         <v>120</v>
       </c>
       <c r="AE5" s="26">
-        <f>IF(DGSUomWIRcSer!$P$2=1,(S5/DGSUomWIRcSer!$S$7)*DGSUomWIRcSer!$E$18,AD5/DGSUomWIRcSer!$AD$7*DGSUomWIRcSer!$E$18)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$18,AD5/$AD$7*$E$18)</f>
         <v>0</v>
       </c>
       <c r="AF5" s="26"/>
       <c r="AG5" s="26">
-        <f>IF(DGSUomWIRcSer!$P$2=1,(S5/DGSUomWIRcSer!$S$7)*DGSUomWIRcSer!$E$20,AD5/DGSUomWIRcSer!$AD$7*DGSUomWIRcSer!$E$20)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$20,AD5/$AD$7*$E$20)</f>
         <v>0</v>
       </c>
       <c r="AH5" s="26">
-        <f>IF(DGSUomWIRcSer!$P$2=1,(S5/DGSUomWIRcSer!$S$7)*DGSUomWIRcSer!$E$21,AD5/DGSUomWIRcSer!$AD$7*DGSUomWIRcSer!$E$21)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$21,AD5/$AD$7*$E$21)</f>
         <v>0</v>
       </c>
       <c r="AI5" s="26">
-        <f>S5*DGSUomWIRcSer!$M$2</f>
-        <v>27919.95</v>
+        <f>S5*$M$2</f>
+        <v>41880.35</v>
       </c>
       <c r="AJ5" s="26">
-        <f>IF(DGSUomWIRcSer!$C$2=3,0,AG5+AH5)</f>
+        <f>IF($C$2=3,0,AG5+AH5)</f>
         <v>0</v>
       </c>
       <c r="AK5" s="26">
-        <f>IF(DGSUomWIRcSer!$C$2=3,AE5+AG5+AH5,0)</f>
+        <f>IF($C$2=3,AE5+AG5+AH5,0)</f>
         <v>0</v>
       </c>
       <c r="AL5" s="34">
@@ -38364,11 +38451,11 @@
       </c>
       <c r="AM5" s="26">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AN5" s="26">
         <f t="shared" si="8"/>
-        <v>6979.9875</v>
+        <v>6980.05833</v>
       </c>
       <c r="AO5" s="26">
         <f t="shared" si="9"/>
@@ -38383,7 +38470,7 @@
       </c>
       <c r="AR5" s="26">
         <f t="shared" si="11"/>
-        <v>6979.9875</v>
+        <v>6980.05833</v>
       </c>
       <c r="AS5" s="38" t="s">
         <v>80</v>
@@ -38391,27 +38478,27 @@
       <c r="AT5" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AU5" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AV5" t="s" s="0">
         <v>95</v>
       </c>
       <c r="AW5" s="39">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX5" s="42">
         <f t="shared" si="13"/>
-        <v>6979.9875</v>
+        <v>6980.05833</v>
       </c>
       <c r="AY5" s="39">
         <f t="shared" si="14"/>
-        <v>192</v>
-      </c>
-      <c r="AZ5" s="42">
-        <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),2)</f>
-        <v>2076.95</v>
+        <v>194</v>
+      </c>
+      <c r="AZ5" s="39">
+        <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),5)</f>
+        <v>2127.49623</v>
       </c>
       <c r="BA5" s="44"/>
       <c r="BB5" s="44" t="s">
@@ -38435,25 +38522,25 @@
       <c r="BL5" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BM5" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BN5" t="s" s="0">
         <v>97</v>
       </c>
       <c r="BO5" s="39">
         <f t="shared" si="15"/>
-        <v>206.79688</v>
+        <v>268.06329</v>
       </c>
       <c r="BP5" s="48">
         <f t="shared" si="16"/>
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="BQ5" s="49">
         <v>123562</v>
       </c>
     </row>
-    <row r="6" ht="15.15" spans="1:69">
+    <row r="6" ht="15.75" spans="1:69">
       <c r="A6" s="7">
         <v>1</v>
       </c>
@@ -38470,16 +38557,16 @@
         <v>77</v>
       </c>
       <c r="F6" s="8">
-        <v>20</v>
-      </c>
-      <c r="G6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H6" s="8">
         <f t="shared" si="0"/>
-        <v>1000</v>
-      </c>
-      <c r="I6" t="s">
+        <v>450</v>
+      </c>
+      <c r="I6" t="s" s="0">
         <v>101</v>
       </c>
       <c r="J6" s="8">
@@ -38490,35 +38577,35 @@
       </c>
       <c r="L6" s="8">
         <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="M6" s="8">
         <f>ROUND(L6*I6%,2)</f>
-        <v>30</v>
+        <v>13.5</v>
       </c>
       <c r="N6" s="8">
         <f t="shared" si="2"/>
-        <v>970</v>
+        <v>436.5</v>
       </c>
       <c r="O6" s="8">
         <f>ROUND(N6*J6%,2)</f>
-        <v>67.9</v>
+        <v>30.56</v>
       </c>
       <c r="P6" s="8">
         <f t="shared" si="3"/>
-        <v>902.1</v>
+        <v>405.94</v>
       </c>
       <c r="Q6" s="8">
         <f t="shared" si="4"/>
-        <v>36.08</v>
+        <v>16.24</v>
       </c>
       <c r="R6" s="8">
         <f>M6+O6+Q6</f>
-        <v>133.98</v>
+        <v>60.3</v>
       </c>
       <c r="S6" s="8">
         <f t="shared" si="5"/>
-        <v>866.02</v>
+        <v>389.7</v>
       </c>
       <c r="T6" s="8">
         <v>88363222</v>
@@ -38527,26 +38614,26 @@
         <v>18</v>
       </c>
       <c r="V6" s="8">
-        <f>IF(OR(DGSUomWIRcSer!$C$2=1,DGSUomWIRcSer!$C$2=4),ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF(OR($C$2=1,$C$2=4),ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="W6" s="8">
-        <f>IF(DGSUomWIRcSer!$C$2=1,ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF($C$2=1,ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="X6" s="8">
-        <f>IF(DGSUomWIRcSer!$C$2=2,ROUND(((S6*U6)/100),2),0)</f>
+        <f>IF($C$2=2,ROUND(((S6*U6)/100),2),0)</f>
         <v>0</v>
       </c>
       <c r="Y6" s="8">
-        <f>IF(DGSUomWIRcSer!$C$2=4,ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF($C$2=4,ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="Z6" s="8">
         <v>0</v>
       </c>
       <c r="AA6" s="8">
-        <f>IF(DGSUomWIRcSer!$C4=3,0,(S6*Z6)/100)</f>
+        <f>IF($C4=3,0,(S6*Z6)/100)</f>
         <v>0</v>
       </c>
       <c r="AB6" s="8">
@@ -38554,35 +38641,35 @@
         <v>0</v>
       </c>
       <c r="AC6" s="8">
-        <f>IF(DGSUomWIRcSer!$V4=1,S6+AB6,S6)</f>
-        <v>866.02</v>
+        <f>IF($V4=1,S6+AB6,S6)</f>
+        <v>389.7</v>
       </c>
       <c r="AD6" s="26">
         <v>120</v>
       </c>
       <c r="AE6" s="26">
-        <f>IF(DGSUomWIRcSer!$P$2=1,(S6/DGSUomWIRcSer!$S$7)*DGSUomWIRcSer!$E$18,AD6/DGSUomWIRcSer!$AD$7*DGSUomWIRcSer!$E$18)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$18,AD6/$AD$7*$E$18)</f>
         <v>0</v>
       </c>
       <c r="AF6" s="26"/>
       <c r="AG6" s="26">
-        <f>IF(DGSUomWIRcSer!$P$2=1,(S6/DGSUomWIRcSer!$S$7)*DGSUomWIRcSer!$E$20,AD6/DGSUomWIRcSer!$AD$7*DGSUomWIRcSer!$E$20)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$20,AD6/$AD$7*$E$20)</f>
         <v>0</v>
       </c>
       <c r="AH6" s="26">
-        <f>IF(DGSUomWIRcSer!$P$2=1,(S6/DGSUomWIRcSer!$S$7)*DGSUomWIRcSer!$E$21,AD6/DGSUomWIRcSer!$AD$7*DGSUomWIRcSer!$E$21)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$21,AD6/$AD$7*$E$21)</f>
         <v>0</v>
       </c>
       <c r="AI6" s="26">
-        <f>S6*DGSUomWIRcSer!$M$2</f>
-        <v>73611.7</v>
+        <f>S6*$M$2</f>
+        <v>33124.5</v>
       </c>
       <c r="AJ6" s="26">
-        <f>IF(DGSUomWIRcSer!$C$2=3,0,AG6+AH6)</f>
+        <f>IF($C$2=3,0,AG6+AH6)</f>
         <v>0</v>
       </c>
       <c r="AK6" s="26">
-        <f>IF(DGSUomWIRcSer!$C$2=3,AE6+AG6+AH6,0)</f>
+        <f>IF($C$2=3,AE6+AG6+AH6,0)</f>
         <v>0</v>
       </c>
       <c r="AL6" s="34">
@@ -38590,11 +38677,11 @@
       </c>
       <c r="AM6" s="26">
         <f t="shared" si="7"/>
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="AN6" s="26">
         <f t="shared" si="8"/>
-        <v>3680.585</v>
+        <v>3680.5</v>
       </c>
       <c r="AO6" s="26">
         <f t="shared" si="9"/>
@@ -38609,7 +38696,7 @@
       </c>
       <c r="AR6" s="26">
         <f t="shared" si="11"/>
-        <v>3680.585</v>
+        <v>3680.5</v>
       </c>
       <c r="AS6" s="38" t="s">
         <v>80</v>
@@ -38617,27 +38704,27 @@
       <c r="AT6" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AU6" t="s" s="0">
         <v>102</v>
       </c>
-      <c r="AV6" t="s">
+      <c r="AV6" t="s" s="0">
         <v>103</v>
       </c>
       <c r="AW6" s="39">
         <f t="shared" si="12"/>
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="AX6" s="39">
         <f t="shared" si="13"/>
-        <v>3680.585</v>
+        <v>3680.5</v>
       </c>
       <c r="AY6" s="39">
         <f t="shared" si="14"/>
-        <v>500</v>
+        <v>489</v>
       </c>
       <c r="AZ6" s="39">
-        <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),1)</f>
-        <v>1198.5</v>
+        <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),5)</f>
+        <v>1142.71268</v>
       </c>
       <c r="BA6" s="44"/>
       <c r="BB6" s="44" t="s">
@@ -38661,25 +38748,25 @@
       <c r="BL6" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM6" t="s">
+      <c r="BM6" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="BN6" t="s">
+      <c r="BN6" t="s" s="0">
         <v>105</v>
       </c>
       <c r="BO6" s="39">
         <f t="shared" si="15"/>
-        <v>115.5</v>
+        <v>75.32173</v>
       </c>
       <c r="BP6" s="48">
         <f t="shared" si="16"/>
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="BQ6" s="49">
         <v>123562</v>
       </c>
     </row>
-    <row r="7" ht="15.15" spans="1:69">
+    <row r="7" ht="15.75" spans="1:69">
       <c r="A7" s="9"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -38691,7 +38778,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="13">
         <f>SUM(H4:H4)</f>
-        <v>750</v>
+        <v>450</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
@@ -38704,11 +38791,11 @@
       <c r="Q7" s="7"/>
       <c r="R7" s="27">
         <f t="shared" ref="R7:X7" si="17">SUM(R4:R4)</f>
-        <v>127.28</v>
+        <v>76.37</v>
       </c>
       <c r="S7" s="13">
         <f t="shared" si="17"/>
-        <v>622.72</v>
+        <v>373.63</v>
       </c>
       <c r="T7" s="27"/>
       <c r="U7" s="27"/>
@@ -38733,7 +38820,7 @@
       </c>
       <c r="AC7" s="32">
         <f t="shared" si="18"/>
-        <v>622.72</v>
+        <v>373.63</v>
       </c>
       <c r="AD7" s="33">
         <f t="shared" si="18"/>
@@ -38754,7 +38841,7 @@
       </c>
       <c r="AI7" s="33">
         <f t="shared" si="19"/>
-        <v>52931.2</v>
+        <v>31758.55</v>
       </c>
       <c r="AJ7" s="33">
         <f t="shared" si="19"/>
@@ -38797,7 +38884,7 @@
       <c r="BP7" s="40"/>
       <c r="BQ7" s="40"/>
     </row>
-    <row r="8" ht="15.15" spans="1:69">
+    <row r="8" ht="15.75" spans="1:69">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -38868,7 +38955,7 @@
       <c r="BP8" s="40"/>
       <c r="BQ8" s="40"/>
     </row>
-    <row r="9" ht="15.15" spans="1:69">
+    <row r="9" ht="15.75" spans="1:69">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -38881,7 +38968,7 @@
       <c r="H9" s="15"/>
       <c r="I9" s="19">
         <f>H7</f>
-        <v>750</v>
+        <v>450</v>
       </c>
       <c r="J9" s="19"/>
       <c r="K9" s="9"/>
@@ -38950,7 +39037,7 @@
       <c r="BP9" s="40"/>
       <c r="BQ9" s="40"/>
     </row>
-    <row r="10" ht="15.15" spans="1:69">
+    <row r="10" ht="15.75" spans="1:69">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -38963,7 +39050,7 @@
       <c r="H10" s="15"/>
       <c r="I10" s="19">
         <f>R7</f>
-        <v>127.28</v>
+        <v>76.37</v>
       </c>
       <c r="J10" s="19"/>
       <c r="K10" s="9"/>
@@ -39038,7 +39125,7 @@
       <c r="BP10" s="40"/>
       <c r="BQ10" s="40"/>
     </row>
-    <row r="11" ht="15.15" spans="1:69">
+    <row r="11" ht="15.75" spans="1:69">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -39051,7 +39138,7 @@
       <c r="H11" s="15"/>
       <c r="I11" s="19">
         <f>S7</f>
-        <v>622.72</v>
+        <v>373.63</v>
       </c>
       <c r="J11" s="19"/>
       <c r="K11" s="9"/>
@@ -39122,7 +39209,7 @@
       <c r="BP11" s="40"/>
       <c r="BQ11" s="40"/>
     </row>
-    <row r="12" ht="15.15" spans="1:69">
+    <row r="12" ht="15.75" spans="1:69">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -39206,7 +39293,7 @@
       <c r="BP12" s="40"/>
       <c r="BQ12" s="40"/>
     </row>
-    <row r="13" ht="15.15" spans="1:69">
+    <row r="13" ht="15.75" spans="1:69">
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -39219,7 +39306,7 @@
       <c r="H13" s="15"/>
       <c r="I13" s="24">
         <f>I11+I12</f>
-        <v>622.72</v>
+        <v>373.63</v>
       </c>
       <c r="J13" s="24"/>
       <c r="K13" s="9"/>
@@ -39844,13 +39931,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ20"/>
-  <sheetFormatPr defaultColWidth="8.85185185185185" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.84761904761905" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="13" max="13" width="9.13888888888889" customWidth="1"/>
-    <col min="14" max="14" width="13.8518518518519" customWidth="1"/>
-    <col min="64" max="64" width="11" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="28.0"/>
+    <col min="3" max="3" customWidth="true" width="23.0"/>
+    <col min="13" max="13" customWidth="true" width="9.14285714285714"/>
+    <col min="14" max="14" customWidth="true" width="13.847619047619"/>
+    <col min="35" max="35" width="11.4285714285714"/>
+    <col min="52" max="52" width="13.2857142857143"/>
+    <col min="64" max="64" customWidth="true" width="11.0"/>
+    <col min="67" max="67" width="12.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -39926,7 +40016,7 @@
       <c r="BP1" s="40"/>
       <c r="BQ1" s="40"/>
     </row>
-    <row r="2" ht="15.15" spans="1:69">
+    <row r="2" ht="15.75" spans="1:69">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -40021,7 +40111,7 @@
       <c r="BP2" s="40"/>
       <c r="BQ2" s="40"/>
     </row>
-    <row r="3" ht="59.1" spans="1:69">
+    <row r="3" ht="61.5" spans="1:69">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
@@ -40230,7 +40320,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.15" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="7">
         <v>1</v>
       </c>
@@ -40247,16 +40337,16 @@
         <v>77</v>
       </c>
       <c r="F4" s="8">
-        <v>5</v>
-      </c>
-      <c r="G4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H4" s="8">
         <f t="shared" ref="H4:H6" si="0">F4*G4</f>
-        <v>250</v>
-      </c>
-      <c r="I4" t="s">
+        <v>150</v>
+      </c>
+      <c r="I4" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J4" s="8">
@@ -40275,27 +40365,27 @@
       </c>
       <c r="N4" s="8">
         <f t="shared" ref="N4:N6" si="2">H4-M4</f>
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="O4" s="8">
         <f>ROUND(N4*J4%,3)</f>
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="P4" s="8">
         <f t="shared" ref="P4:P6" si="3">ROUND(N4-O4,2)</f>
-        <v>230</v>
+        <v>138</v>
       </c>
       <c r="Q4" s="8">
         <f t="shared" ref="Q4:Q6" si="4">ROUND(P4*K4%,2)</f>
-        <v>11.5</v>
+        <v>6.9</v>
       </c>
       <c r="R4" s="26">
         <f>ROUND(M4+O4+Q4,3)</f>
-        <v>31.5</v>
+        <v>18.9</v>
       </c>
       <c r="S4" s="8">
         <f>(H4-R4)</f>
-        <v>218.5</v>
+        <v>131.1</v>
       </c>
       <c r="T4" s="8">
         <v>88363222</v>
@@ -40332,7 +40422,7 @@
       </c>
       <c r="AC4" s="31">
         <f>IF($V2=1,S4+AB4,S4)</f>
-        <v>218.5</v>
+        <v>131.1</v>
       </c>
       <c r="AD4" s="26">
         <v>120</v>
@@ -40352,7 +40442,7 @@
       </c>
       <c r="AI4" s="26">
         <f>S4*$M2</f>
-        <v>18572.5</v>
+        <v>11143.5</v>
       </c>
       <c r="AJ4" s="26">
         <f>IF($C$2=3,0,AG4+AH4)</f>
@@ -40367,7 +40457,7 @@
       </c>
       <c r="AM4" s="26">
         <f t="shared" ref="AM4:AM6" si="6">F4/AL4</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AN4" s="26">
         <f t="shared" ref="AN4:AN6" si="7">ROUND(AI4/AM4,5)</f>
@@ -40394,15 +40484,15 @@
       <c r="AT4" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AU4" t="s" s="0">
         <v>81</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AV4" t="s" s="0">
         <v>82</v>
       </c>
       <c r="AW4" s="39">
         <f t="shared" ref="AW4:AW6" si="11">AM4</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AX4" s="42">
         <f t="shared" ref="AX4:AX6" si="12">AR4</f>
@@ -40410,11 +40500,11 @@
       </c>
       <c r="AY4" s="39">
         <f t="shared" ref="AY4:AY6" si="13">AU4+AW4</f>
-        <v>380</v>
-      </c>
-      <c r="AZ4" s="43">
-        <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),3)</f>
-        <v>3580.381</v>
+        <v>378</v>
+      </c>
+      <c r="AZ4" s="39">
+        <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),5)</f>
+        <v>3579.67164</v>
       </c>
       <c r="BA4" s="44"/>
       <c r="BB4" s="44" t="s">
@@ -40438,25 +40528,25 @@
       <c r="BL4" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>89</v>
       </c>
       <c r="BO4" s="39">
         <f t="shared" ref="BO4:BO6" si="14">ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
-        <v>327.82947</v>
+        <v>249.4291</v>
       </c>
       <c r="BP4" s="48">
         <f t="shared" ref="BP4:BP6" si="15">ROUND(BN4+AW4,3)</f>
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="BQ4" s="49">
         <v>123562</v>
       </c>
     </row>
-    <row r="5" ht="15.15" spans="1:69">
+    <row r="5" ht="15.75" spans="1:69">
       <c r="A5" s="7">
         <v>1</v>
       </c>
@@ -40473,16 +40563,16 @@
         <v>77</v>
       </c>
       <c r="F5" s="8">
-        <v>4</v>
-      </c>
-      <c r="G5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s" s="0">
         <v>92</v>
       </c>
       <c r="H5" s="8">
         <f t="shared" si="0"/>
-        <v>400</v>
-      </c>
-      <c r="I5" t="s">
+        <v>1200</v>
+      </c>
+      <c r="I5" t="s" s="0">
         <v>93</v>
       </c>
       <c r="J5" s="8">
@@ -40493,35 +40583,35 @@
       </c>
       <c r="L5" s="8">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="M5" s="8">
         <f>ROUND(L5*I5%,2)</f>
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="N5" s="8">
         <f t="shared" si="2"/>
-        <v>384</v>
+        <v>1152</v>
       </c>
       <c r="O5" s="8">
         <f>ROUND(N5*J5%,2)</f>
-        <v>34.56</v>
+        <v>103.68</v>
       </c>
       <c r="P5" s="8">
         <f t="shared" si="3"/>
-        <v>349.44</v>
+        <v>1048.32</v>
       </c>
       <c r="Q5" s="8">
         <f t="shared" si="4"/>
-        <v>20.97</v>
+        <v>62.9</v>
       </c>
       <c r="R5" s="8">
         <f>M5+O5+Q5</f>
-        <v>71.53</v>
+        <v>214.58</v>
       </c>
       <c r="S5" s="8">
         <f t="shared" ref="S4:S6" si="16">(H5-R5)</f>
-        <v>328.47</v>
+        <v>985.42</v>
       </c>
       <c r="T5" s="8">
         <v>88363222</v>
@@ -40530,26 +40620,26 @@
         <v>18</v>
       </c>
       <c r="V5" s="8">
-        <f>IF(OR(DGSUomWIPlSer!$C$2=1,DGSUomWIPlSer!$C$2=4),ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF(OR($C$2=1,$C$2=4),ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="W5" s="8">
-        <f>IF(DGSUomWIPlSer!$C$2=1,ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF($C$2=1,ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="X5" s="8">
-        <f>IF(DGSUomWIPlSer!$C$2=2,ROUND(((S5*U5)/100),2),0)</f>
+        <f>IF($C$2=2,ROUND(((S5*U5)/100),2),0)</f>
         <v>0</v>
       </c>
       <c r="Y5" s="8">
-        <f>IF(DGSUomWIPlSer!$C$2=4,ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF($C$2=4,ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="Z5" s="8">
         <v>0</v>
       </c>
       <c r="AA5" s="8">
-        <f>IF(DGSUomWIPlSer!$C3=3,0,(S5*Z5)/100)</f>
+        <f>IF($C3=3,0,(S5*Z5)/100)</f>
         <v>0</v>
       </c>
       <c r="AB5" s="8">
@@ -40557,35 +40647,35 @@
         <v>0</v>
       </c>
       <c r="AC5" s="8">
-        <f>IF(DGSUomWIPlSer!$V3=1,S5+AB5,S5)</f>
-        <v>328.47</v>
+        <f>IF($V3=1,S5+AB5,S5)</f>
+        <v>985.42</v>
       </c>
       <c r="AD5" s="26">
         <v>120</v>
       </c>
       <c r="AE5" s="26">
-        <f>IF(DGSUomWIPlSer!$P$2=1,(S5/DGSUomWIPlSer!$S$7)*DGSUomWIPlSer!$E$18,AD5/DGSUomWIPlSer!$AD$7*DGSUomWIPlSer!$E$18)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$18,AD5/$AD$7*$E$18)</f>
         <v>0</v>
       </c>
       <c r="AF5" s="26"/>
       <c r="AG5" s="26">
-        <f>IF(DGSUomWIPlSer!$P$2=1,(S5/DGSUomWIPlSer!$S$7)*DGSUomWIPlSer!$E$20,AD5/DGSUomWIPlSer!$AD$7*DGSUomWIPlSer!$E$20)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$20,AD5/$AD$7*$E$20)</f>
         <v>0</v>
       </c>
       <c r="AH5" s="26">
-        <f>IF(DGSUomWIPlSer!$P$2=1,(S5/DGSUomWIPlSer!$S$7)*DGSUomWIPlSer!$E$21,AD5/DGSUomWIPlSer!$AD$7*DGSUomWIPlSer!$E$21)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$21,AD5/$AD$7*$E$21)</f>
         <v>0</v>
       </c>
       <c r="AI5" s="26">
-        <f>S5*DGSUomWIPlSer!$M$2</f>
-        <v>27919.95</v>
+        <f>S5*$M$2</f>
+        <v>83760.7</v>
       </c>
       <c r="AJ5" s="26">
-        <f>IF(DGSUomWIPlSer!$C$2=3,0,AG5+AH5)</f>
+        <f>IF($C$2=3,0,AG5+AH5)</f>
         <v>0</v>
       </c>
       <c r="AK5" s="26">
-        <f>IF(DGSUomWIPlSer!$C$2=3,AE5+AG5+AH5,0)</f>
+        <f>IF($C$2=3,AE5+AG5+AH5,0)</f>
         <v>0</v>
       </c>
       <c r="AL5" s="34">
@@ -40593,11 +40683,11 @@
       </c>
       <c r="AM5" s="26">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AN5" s="26">
         <f t="shared" si="7"/>
-        <v>6979.9875</v>
+        <v>6980.05833</v>
       </c>
       <c r="AO5" s="26">
         <f t="shared" si="8"/>
@@ -40612,7 +40702,7 @@
       </c>
       <c r="AR5" s="26">
         <f t="shared" si="10"/>
-        <v>6979.9875</v>
+        <v>6980.05833</v>
       </c>
       <c r="AS5" s="38" t="s">
         <v>80</v>
@@ -40620,27 +40710,27 @@
       <c r="AT5" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AU5" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AV5" t="s" s="0">
         <v>95</v>
       </c>
       <c r="AW5" s="39">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AX5" s="42">
         <f t="shared" si="12"/>
-        <v>6979.9875</v>
+        <v>6980.05833</v>
       </c>
       <c r="AY5" s="39">
         <f t="shared" si="13"/>
-        <v>192</v>
-      </c>
-      <c r="AZ5" s="42">
-        <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),2)</f>
-        <v>2076.95</v>
+        <v>200</v>
+      </c>
+      <c r="AZ5" s="39">
+        <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),5)</f>
+        <v>2273.0731</v>
       </c>
       <c r="BA5" s="44"/>
       <c r="BB5" s="44" t="s">
@@ -40664,25 +40754,25 @@
       <c r="BL5" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BM5" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BN5" t="s" s="0">
         <v>97</v>
       </c>
       <c r="BO5" s="39">
         <f t="shared" si="14"/>
-        <v>206.79688</v>
+        <v>447.27885</v>
       </c>
       <c r="BP5" s="48">
         <f t="shared" si="15"/>
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="BQ5" s="49">
         <v>123562</v>
       </c>
     </row>
-    <row r="6" ht="15.15" spans="1:69">
+    <row r="6" ht="15.75" spans="1:69">
       <c r="A6" s="7">
         <v>1</v>
       </c>
@@ -40699,16 +40789,16 @@
         <v>77</v>
       </c>
       <c r="F6" s="8">
-        <v>20</v>
-      </c>
-      <c r="G6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H6" s="8">
         <f t="shared" si="0"/>
-        <v>1000</v>
-      </c>
-      <c r="I6" t="s">
+        <v>450</v>
+      </c>
+      <c r="I6" t="s" s="0">
         <v>101</v>
       </c>
       <c r="J6" s="8">
@@ -40719,35 +40809,35 @@
       </c>
       <c r="L6" s="8">
         <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="M6" s="8">
         <f>ROUND(L6*I6%,2)</f>
-        <v>30</v>
+        <v>13.5</v>
       </c>
       <c r="N6" s="8">
         <f t="shared" si="2"/>
-        <v>970</v>
+        <v>436.5</v>
       </c>
       <c r="O6" s="8">
         <f>ROUND(N6*J6%,2)</f>
-        <v>67.9</v>
+        <v>30.56</v>
       </c>
       <c r="P6" s="8">
         <f t="shared" si="3"/>
-        <v>902.1</v>
+        <v>405.94</v>
       </c>
       <c r="Q6" s="8">
         <f t="shared" si="4"/>
-        <v>36.08</v>
+        <v>16.24</v>
       </c>
       <c r="R6" s="8">
         <f>M6+O6+Q6</f>
-        <v>133.98</v>
+        <v>60.3</v>
       </c>
       <c r="S6" s="8">
         <f t="shared" si="16"/>
-        <v>866.02</v>
+        <v>389.7</v>
       </c>
       <c r="T6" s="8">
         <v>88363222</v>
@@ -40756,26 +40846,26 @@
         <v>18</v>
       </c>
       <c r="V6" s="8">
-        <f>IF(OR(DGSUomWIPlSer!$C$2=1,DGSUomWIPlSer!$C$2=4),ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF(OR($C$2=1,$C$2=4),ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="W6" s="8">
-        <f>IF(DGSUomWIPlSer!$C$2=1,ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF($C$2=1,ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="X6" s="8">
-        <f>IF(DGSUomWIPlSer!$C$2=2,ROUND(((S6*U6)/100),2),0)</f>
+        <f>IF($C$2=2,ROUND(((S6*U6)/100),2),0)</f>
         <v>0</v>
       </c>
       <c r="Y6" s="8">
-        <f>IF(DGSUomWIPlSer!$C$2=4,ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF($C$2=4,ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="Z6" s="8">
         <v>0</v>
       </c>
       <c r="AA6" s="8">
-        <f>IF(DGSUomWIPlSer!$C4=3,0,(S6*Z6)/100)</f>
+        <f>IF($C4=3,0,(S6*Z6)/100)</f>
         <v>0</v>
       </c>
       <c r="AB6" s="8">
@@ -40783,35 +40873,35 @@
         <v>0</v>
       </c>
       <c r="AC6" s="8">
-        <f>IF(DGSUomWIPlSer!$V4=1,S6+AB6,S6)</f>
-        <v>866.02</v>
+        <f>IF($V4=1,S6+AB6,S6)</f>
+        <v>389.7</v>
       </c>
       <c r="AD6" s="26">
         <v>120</v>
       </c>
       <c r="AE6" s="26">
-        <f>IF(DGSUomWIPlSer!$P$2=1,(S6/DGSUomWIPlSer!$S$7)*DGSUomWIPlSer!$E$18,AD6/DGSUomWIPlSer!$AD$7*DGSUomWIPlSer!$E$18)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$18,AD6/$AD$7*$E$18)</f>
         <v>0</v>
       </c>
       <c r="AF6" s="26"/>
       <c r="AG6" s="26">
-        <f>IF(DGSUomWIPlSer!$P$2=1,(S6/DGSUomWIPlSer!$S$7)*DGSUomWIPlSer!$E$20,AD6/DGSUomWIPlSer!$AD$7*DGSUomWIPlSer!$E$20)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$20,AD6/$AD$7*$E$20)</f>
         <v>0</v>
       </c>
       <c r="AH6" s="26">
-        <f>IF(DGSUomWIPlSer!$P$2=1,(S6/DGSUomWIPlSer!$S$7)*DGSUomWIPlSer!$E$21,AD6/DGSUomWIPlSer!$AD$7*DGSUomWIPlSer!$E$21)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$21,AD6/$AD$7*$E$21)</f>
         <v>0</v>
       </c>
       <c r="AI6" s="26">
-        <f>S6*DGSUomWIPlSer!$M$2</f>
-        <v>73611.7</v>
+        <f>S6*$M$2</f>
+        <v>33124.5</v>
       </c>
       <c r="AJ6" s="26">
-        <f>IF(DGSUomWIPlSer!$C$2=3,0,AG6+AH6)</f>
+        <f>IF($C$2=3,0,AG6+AH6)</f>
         <v>0</v>
       </c>
       <c r="AK6" s="26">
-        <f>IF(DGSUomWIPlSer!$C$2=3,AE6+AG6+AH6,0)</f>
+        <f>IF($C$2=3,AE6+AG6+AH6,0)</f>
         <v>0</v>
       </c>
       <c r="AL6" s="34">
@@ -40819,11 +40909,11 @@
       </c>
       <c r="AM6" s="26">
         <f t="shared" si="6"/>
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="AN6" s="26">
         <f t="shared" si="7"/>
-        <v>3680.585</v>
+        <v>3680.5</v>
       </c>
       <c r="AO6" s="26">
         <f t="shared" si="8"/>
@@ -40838,7 +40928,7 @@
       </c>
       <c r="AR6" s="26">
         <f t="shared" si="10"/>
-        <v>3680.585</v>
+        <v>3680.5</v>
       </c>
       <c r="AS6" s="38" t="s">
         <v>80</v>
@@ -40846,27 +40936,27 @@
       <c r="AT6" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AU6" t="s" s="0">
         <v>102</v>
       </c>
-      <c r="AV6" t="s">
+      <c r="AV6" t="s" s="0">
         <v>103</v>
       </c>
       <c r="AW6" s="39">
         <f t="shared" si="11"/>
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="AX6" s="39">
         <f t="shared" si="12"/>
-        <v>3680.585</v>
+        <v>3680.5</v>
       </c>
       <c r="AY6" s="39">
         <f t="shared" si="13"/>
-        <v>500</v>
+        <v>489</v>
       </c>
       <c r="AZ6" s="39">
-        <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),1)</f>
-        <v>1198.5</v>
+        <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),5)</f>
+        <v>1142.71268</v>
       </c>
       <c r="BA6" s="44"/>
       <c r="BB6" s="44" t="s">
@@ -40890,25 +40980,25 @@
       <c r="BL6" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="BM6" t="s">
+      <c r="BM6" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="BN6" t="s">
+      <c r="BN6" t="s" s="0">
         <v>105</v>
       </c>
       <c r="BO6" s="39">
         <f t="shared" si="14"/>
-        <v>115.5</v>
+        <v>75.32173</v>
       </c>
       <c r="BP6" s="48">
         <f t="shared" si="15"/>
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="BQ6" s="49">
         <v>123562</v>
       </c>
     </row>
-    <row r="7" ht="15.15" spans="1:69">
+    <row r="7" ht="15.75" spans="1:69">
       <c r="A7" s="9"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -40920,7 +41010,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="13">
         <f>SUM(H4:H4)</f>
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
@@ -40933,11 +41023,11 @@
       <c r="Q7" s="7"/>
       <c r="R7" s="27">
         <f t="shared" ref="R7:X7" si="17">SUM(R4:R4)</f>
-        <v>31.5</v>
+        <v>18.9</v>
       </c>
       <c r="S7" s="13">
         <f t="shared" si="17"/>
-        <v>218.5</v>
+        <v>131.1</v>
       </c>
       <c r="T7" s="27"/>
       <c r="U7" s="27"/>
@@ -40962,7 +41052,7 @@
       </c>
       <c r="AC7" s="32">
         <f t="shared" si="18"/>
-        <v>218.5</v>
+        <v>131.1</v>
       </c>
       <c r="AD7" s="33">
         <f t="shared" si="18"/>
@@ -40983,7 +41073,7 @@
       </c>
       <c r="AI7" s="33">
         <f t="shared" si="19"/>
-        <v>18572.5</v>
+        <v>11143.5</v>
       </c>
       <c r="AJ7" s="33">
         <f t="shared" si="19"/>
@@ -41026,7 +41116,7 @@
       <c r="BP7" s="40"/>
       <c r="BQ7" s="40"/>
     </row>
-    <row r="8" ht="15.15" spans="1:69">
+    <row r="8" ht="15.75" spans="1:69">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -41097,7 +41187,7 @@
       <c r="BP8" s="40"/>
       <c r="BQ8" s="40"/>
     </row>
-    <row r="9" ht="15.15" spans="1:69">
+    <row r="9" ht="15.75" spans="1:69">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -41110,7 +41200,7 @@
       <c r="H9" s="15"/>
       <c r="I9" s="19">
         <f>H7</f>
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="J9" s="19"/>
       <c r="K9" s="9"/>
@@ -41179,7 +41269,7 @@
       <c r="BP9" s="40"/>
       <c r="BQ9" s="40"/>
     </row>
-    <row r="10" ht="15.15" spans="1:69">
+    <row r="10" ht="15.75" spans="1:69">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -41192,7 +41282,7 @@
       <c r="H10" s="15"/>
       <c r="I10" s="19">
         <f>R7</f>
-        <v>31.5</v>
+        <v>18.9</v>
       </c>
       <c r="J10" s="19"/>
       <c r="K10" s="9"/>
@@ -41267,7 +41357,7 @@
       <c r="BP10" s="40"/>
       <c r="BQ10" s="40"/>
     </row>
-    <row r="11" ht="15.15" spans="1:69">
+    <row r="11" ht="15.75" spans="1:69">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -41280,7 +41370,7 @@
       <c r="H11" s="15"/>
       <c r="I11" s="19">
         <f>S7</f>
-        <v>218.5</v>
+        <v>131.1</v>
       </c>
       <c r="J11" s="19"/>
       <c r="K11" s="9"/>
@@ -41351,7 +41441,7 @@
       <c r="BP11" s="40"/>
       <c r="BQ11" s="40"/>
     </row>
-    <row r="12" ht="15.15" spans="1:69">
+    <row r="12" ht="15.75" spans="1:69">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -41435,7 +41525,7 @@
       <c r="BP12" s="40"/>
       <c r="BQ12" s="40"/>
     </row>
-    <row r="13" ht="15.15" spans="1:69">
+    <row r="13" ht="15.75" spans="1:69">
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -41448,7 +41538,7 @@
       <c r="H13" s="15"/>
       <c r="I13" s="24">
         <f>I11+I12</f>
-        <v>218.5</v>
+        <v>131.1</v>
       </c>
       <c r="J13" s="24"/>
       <c r="K13" s="9"/>

--- a/testdata/DirectGrn.xlsx
+++ b/testdata/DirectGrn.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21600" windowHeight="9600" tabRatio="703" firstSheet="1" activeTab="1"/>
+    <workbookView windowWidth="21600" windowHeight="9600" tabRatio="703" firstSheet="13" activeTab="17"/>
   </bookViews>
   <sheets>
     <sheet name="DGSUomWI" sheetId="6" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2784" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2794" uniqueCount="234">
   <si>
     <t>Purchase Order &amp; GRN</t>
   </si>
@@ -289,10 +289,10 @@
     <t>INS WH-1</t>
   </si>
   <si>
-    <t>375</t>
+    <t>687</t>
   </si>
   <si>
-    <t>3578.59301</t>
+    <t>4527.08809</t>
   </si>
   <si>
     <t>Receipt Qty &amp; Unit cost</t>
@@ -328,10 +328,10 @@
     <t>4</t>
   </si>
   <si>
-    <t>188</t>
+    <t>322</t>
   </si>
   <si>
-    <t>1972.62723</t>
+    <t>3701.11111</t>
   </si>
   <si>
     <t>82.12</t>
@@ -352,10 +352,10 @@
     <t>3</t>
   </si>
   <si>
-    <t>480</t>
+    <t>970</t>
   </si>
   <si>
-    <t>1095.12917</t>
+    <t>2195.50616</t>
   </si>
   <si>
     <t>43.3</t>
@@ -430,67 +430,85 @@
     <t>0</t>
   </si>
   <si>
-    <t>10586.325</t>
+    <t>10586.18333</t>
   </si>
   <si>
     <t>GWL_Item_WoQ_UD_Similar_02</t>
   </si>
   <si>
-    <t>6980.2</t>
+    <t>6980.10556</t>
   </si>
   <si>
     <t>GWL_Item_WoQ_UD_Similar_03</t>
   </si>
   <si>
-    <t>3680.5</t>
+    <t>3680.57083</t>
   </si>
   <si>
     <t>GWL_Item_Dissimilar_03</t>
   </si>
   <si>
-    <t>48.329</t>
+    <t>77.994</t>
   </si>
   <si>
-    <t>12278.62068</t>
+    <t>12377.30055</t>
   </si>
   <si>
     <t>GWL_Item_Dissimilar_04</t>
   </si>
   <si>
-    <t>22.661</t>
+    <t>36.327</t>
   </si>
   <si>
-    <t>7550.20941</t>
+    <t>9451.41481</t>
   </si>
   <si>
     <t>GWL_Item_Dissimilar_05</t>
   </si>
   <si>
-    <t>59.995</t>
+    <t>95.328</t>
   </si>
   <si>
-    <t>4373.41115</t>
+    <t>5108.78739</t>
   </si>
   <si>
     <t>GWL_Dissimilar_01</t>
   </si>
   <si>
-    <t>31758.975</t>
+    <t>31758.72</t>
   </si>
   <si>
     <t>GWL_Dissimilar_02</t>
   </si>
   <si>
-    <t>20940.6</t>
+    <t>20939.9625</t>
   </si>
   <si>
     <t>GWL_ITem_service_03</t>
   </si>
   <si>
+    <t>375</t>
+  </si>
+  <si>
+    <t>3578.59301</t>
+  </si>
+  <si>
     <t>GWL_Item_service_04</t>
   </si>
   <si>
+    <t>188</t>
+  </si>
+  <si>
+    <t>1972.62723</t>
+  </si>
+  <si>
     <t>GWL_Item_service_05</t>
+  </si>
+  <si>
+    <t>480</t>
+  </si>
+  <si>
+    <t>1095.12917</t>
   </si>
   <si>
     <t>GWL_Item_FP_service_01</t>
@@ -550,10 +568,10 @@
     <t>GWL_Item_Similar_Rc_01</t>
   </si>
   <si>
-    <t>155</t>
+    <t>186</t>
   </si>
   <si>
-    <t>800.03461</t>
+    <t>1144.62963</t>
   </si>
   <si>
     <t>GWL_Item_Similar_Rc_02</t>
@@ -562,10 +580,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>124</t>
-  </si>
-  <si>
-    <t>1545.84427</t>
+    <t>1513.71555</t>
   </si>
   <si>
     <t>GWL_Item_Similar_Rc_03</t>
@@ -574,10 +589,10 @@
     <t>7</t>
   </si>
   <si>
-    <t>320</t>
+    <t>380</t>
   </si>
   <si>
-    <t>2652.80851</t>
+    <t>4051.02893</t>
   </si>
   <si>
     <t>GWL_Item_FP_Rc_01</t>
@@ -589,37 +604,46 @@
     <t>GWL_Item_FP_Rc_02</t>
   </si>
   <si>
+    <t>6979.9875</t>
+  </si>
+  <si>
     <t>GWL_Item_FP_Rc_03</t>
+  </si>
+  <si>
+    <t>3680.585</t>
   </si>
   <si>
     <t>GWL_Item_Dissimilar_Rc_01</t>
   </si>
   <si>
-    <t>58.328</t>
+    <t>79.999</t>
   </si>
   <si>
-    <t>12031.21611</t>
+    <t>9936.85952</t>
   </si>
   <si>
     <t>GWL_Item_Dissimilar_Rc_02</t>
   </si>
   <si>
-    <t>59.327</t>
+    <t>79.997</t>
   </si>
   <si>
-    <t>7686.96602</t>
+    <t>5684.77537</t>
   </si>
   <si>
     <t>GWL_Item_Dissimilar_Rc_03</t>
   </si>
   <si>
-    <t>66.661</t>
+    <t>83.327</t>
   </si>
   <si>
-    <t>4494.63821</t>
+    <t>6015.31752</t>
   </si>
   <si>
     <t>GWL_Item_FP_Rc_Dissimilar_01</t>
+  </si>
+  <si>
+    <t>11143.5</t>
   </si>
   <si>
     <t>GWL_Item_FP_Rc_Dissimilar_02</t>
@@ -628,28 +652,31 @@
     <t>GWL_Item_FP_Rc_Dissimilar_03</t>
   </si>
   <si>
+    <t>11041.755</t>
+  </si>
+  <si>
     <t>GWL_Item_Similar_Pl_01</t>
   </si>
   <si>
-    <t>4047.7125</t>
+    <t>4921.42429</t>
   </si>
   <si>
     <t>GWL_Item_Similar_Pl_02</t>
   </si>
   <si>
-    <t>68</t>
+    <t>84</t>
   </si>
   <si>
-    <t>2516.73647</t>
+    <t>2153.36817</t>
   </si>
   <si>
     <t>GWL_Item_Similar_Pl_03</t>
   </si>
   <si>
-    <t>330</t>
+    <t>410</t>
   </si>
   <si>
-    <t>1365.91819</t>
+    <t>1894.95221</t>
   </si>
   <si>
     <t>GWL_Item_FP_Pl_Similar_01</t>
@@ -664,13 +691,40 @@
     <t>GWL_Item_Dissimilar_Pl_01</t>
   </si>
   <si>
+    <t>81.666</t>
+  </si>
+  <si>
+    <t>9420.67954</t>
+  </si>
+  <si>
+    <t>GWL_Item_Dissimilar_Pl_02</t>
+  </si>
+  <si>
+    <t>121.67</t>
+  </si>
+  <si>
+    <t>5177.38643</t>
+  </si>
+  <si>
+    <t>GWL_Item_Dissimilar_Pl_03</t>
+  </si>
+  <si>
+    <t>93.327</t>
+  </si>
+  <si>
+    <t>5702.29277</t>
+  </si>
+  <si>
+    <t>GWL_Item_FP_Pl_Dissimilar_01</t>
+  </si>
+  <si>
     <t>63.328</t>
   </si>
   <si>
     <t>11936.96801</t>
   </si>
   <si>
-    <t>GWL_Item_Dissimilar_Pl_02</t>
+    <t>GWL_Item_FP_Pl_Dissimilar_02</t>
   </si>
   <si>
     <t>100.999</t>
@@ -679,7 +733,7 @@
     <t>6939.4762</t>
   </si>
   <si>
-    <t>GWL_Item_Dissimilar_Pl_03</t>
+    <t>GWL_Item_FP_Pl_Dissimilar_03</t>
   </si>
   <si>
     <t>79.994</t>
@@ -688,67 +742,10 @@
     <t>4676.55914</t>
   </si>
   <si>
-    <t>GWL_Item_FP_Pl_Dissimilar_01</t>
+    <t>21812.7</t>
   </si>
   <si>
-    <t>GWL_Item_FP_Pl_Dissimilar_02</t>
-  </si>
-  <si>
-    <t>GWL_Item_FP_Pl_Dissimilar_03</t>
-  </si>
-  <si>
-    <t>662</t>
-  </si>
-  <si>
-    <t>3764.23791</t>
-  </si>
-  <si>
-    <t>274</t>
-  </si>
-  <si>
-    <t>2881.34244</t>
-  </si>
-  <si>
-    <t>730</t>
-  </si>
-  <si>
-    <t>1539.19605</t>
-  </si>
-  <si>
-    <t>667</t>
-  </si>
-  <si>
-    <t>3815.37799</t>
-  </si>
-  <si>
-    <t>278</t>
-  </si>
-  <si>
-    <t>2940.31881</t>
-  </si>
-  <si>
-    <t>750</t>
-  </si>
-  <si>
-    <t>1596.29749</t>
-  </si>
-  <si>
-    <t>672</t>
-  </si>
-  <si>
-    <t>3865.75706</t>
-  </si>
-  <si>
-    <t>282</t>
-  </si>
-  <si>
-    <t>2997.62209</t>
-  </si>
-  <si>
-    <t>770</t>
-  </si>
-  <si>
-    <t>1650.43262</t>
+    <t>11383.2</t>
   </si>
 </sst>
 </file>
@@ -1657,7 +1654,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="181" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1681,6 +1677,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="181" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="51">
@@ -2226,7 +2223,10 @@
     <col min="14" max="14" customWidth="true" width="13.847619047619"/>
     <col min="29" max="29" width="9.28571428571429"/>
     <col min="35" max="35" width="11.4285714285714"/>
-    <col min="52" max="52" width="13.2857142857143"/>
+    <col min="44" max="44" width="10.1428571428571"/>
+    <col min="48" max="48" width="11.7142857142857"/>
+    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
     <col min="64" max="64" customWidth="true" width="11.0"/>
     <col min="67" max="67" width="12.0"/>
   </cols>
@@ -2399,7 +2399,7 @@
       <c r="BP2" s="40"/>
       <c r="BQ2" s="40"/>
     </row>
-    <row r="3" ht="61.5" spans="1:69">
+    <row r="3" ht="46.5" spans="1:69">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
@@ -2763,7 +2763,7 @@
         <v>77</v>
       </c>
       <c r="AR4" s="26">
-        <f>ROUND(AN4+AO4+AP4,5)</f>
+        <f>AN4+AO4+AP4</f>
         <v>10586.24</v>
       </c>
       <c r="AS4" s="38" t="s">
@@ -2773,10 +2773,10 @@
         <v>77</v>
       </c>
       <c r="AU4" t="s" s="0">
-        <v>229</v>
+        <v>81</v>
       </c>
       <c r="AV4" t="s" s="0">
-        <v>230</v>
+        <v>82</v>
       </c>
       <c r="AW4" s="39">
         <f>AM4</f>
@@ -2792,28 +2792,28 @@
       </c>
       <c r="AZ4" s="39">
         <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),5)</f>
-        <v>3670.79889</v>
-      </c>
-      <c r="BA4" s="44"/>
-      <c r="BB4" s="44" t="s">
+        <v>3915.39135</v>
+      </c>
+      <c r="BA4" s="43"/>
+      <c r="BB4" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC4" s="45" t="s">
+      <c r="BC4" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD4" s="46" t="s">
+      <c r="BD4" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE4" s="46" t="s">
+      <c r="BE4" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF4" s="44"/>
-      <c r="BG4" s="44"/>
-      <c r="BH4" s="44"/>
+      <c r="BF4" s="43"/>
+      <c r="BG4" s="43"/>
+      <c r="BH4" s="43"/>
       <c r="BI4" s="39"/>
       <c r="BJ4" s="39"/>
       <c r="BK4" s="39"/>
-      <c r="BL4" s="47" t="s">
+      <c r="BL4" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM4" t="s" s="0">
@@ -2824,13 +2824,13 @@
       </c>
       <c r="BO4" s="39">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
-        <v>333.14817</v>
-      </c>
-      <c r="BP4" s="48">
+        <v>347.53596</v>
+      </c>
+      <c r="BP4" s="47">
         <f>ROUND(BN4+AW4,3)</f>
         <v>5</v>
       </c>
-      <c r="BQ4" s="49">
+      <c r="BQ4" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -2989,7 +2989,7 @@
         <v>77</v>
       </c>
       <c r="AR5" s="26">
-        <f>ROUND(AN5+AO5+AP5,5)</f>
+        <f>AN5+AO5+AP5</f>
         <v>6979.9875</v>
       </c>
       <c r="AS5" s="38" t="s">
@@ -2999,10 +2999,10 @@
         <v>77</v>
       </c>
       <c r="AU5" t="s" s="0">
-        <v>231</v>
+        <v>94</v>
       </c>
       <c r="AV5" t="s" s="0">
-        <v>232</v>
+        <v>95</v>
       </c>
       <c r="AW5" s="39">
         <f>AM5</f>
@@ -3018,28 +3018,28 @@
       </c>
       <c r="AZ5" s="39">
         <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),5)</f>
-        <v>2076.94724</v>
-      </c>
-      <c r="BA5" s="44"/>
-      <c r="BB5" s="44" t="s">
+        <v>3053.31951</v>
+      </c>
+      <c r="BA5" s="43"/>
+      <c r="BB5" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC5" s="45" t="s">
+      <c r="BC5" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD5" s="46" t="s">
+      <c r="BD5" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE5" s="46" t="s">
+      <c r="BE5" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF5" s="44"/>
-      <c r="BG5" s="44"/>
-      <c r="BH5" s="44"/>
+      <c r="BF5" s="43"/>
+      <c r="BG5" s="43"/>
+      <c r="BH5" s="43"/>
       <c r="BI5" s="39"/>
       <c r="BJ5" s="39"/>
       <c r="BK5" s="39"/>
-      <c r="BL5" s="47" t="s">
+      <c r="BL5" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM5" t="s" s="0">
@@ -3050,13 +3050,13 @@
       </c>
       <c r="BO5" s="39">
         <f>ROUND((((AW5*AZ5)+(BN5*BM5))/(AW5+BN5)),5)</f>
-        <v>206.7967</v>
-      </c>
-      <c r="BP5" s="48">
+        <v>267.81997</v>
+      </c>
+      <c r="BP5" s="47">
         <f>ROUND(BN5+AW5,3)</f>
         <v>4</v>
       </c>
-      <c r="BQ5" s="49">
+      <c r="BQ5" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -3215,7 +3215,7 @@
         <v>77</v>
       </c>
       <c r="AR6" s="26">
-        <f>ROUND(AN6+AO6+AP6,5)</f>
+        <f>AN6+AO6+AP6</f>
         <v>3680.585</v>
       </c>
       <c r="AS6" s="38" t="s">
@@ -3225,10 +3225,10 @@
         <v>77</v>
       </c>
       <c r="AU6" t="s" s="0">
-        <v>233</v>
+        <v>102</v>
       </c>
       <c r="AV6" t="s" s="0">
-        <v>234</v>
+        <v>103</v>
       </c>
       <c r="AW6" s="39">
         <f>AM6</f>
@@ -3244,28 +3244,28 @@
       </c>
       <c r="AZ6" s="39">
         <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),5)</f>
-        <v>1198.5474</v>
-      </c>
-      <c r="BA6" s="44"/>
-      <c r="BB6" s="44" t="s">
+        <v>1701.82888</v>
+      </c>
+      <c r="BA6" s="43"/>
+      <c r="BB6" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC6" s="45" t="s">
+      <c r="BC6" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD6" s="46" t="s">
+      <c r="BD6" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE6" s="46" t="s">
+      <c r="BE6" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF6" s="44"/>
-      <c r="BG6" s="44"/>
-      <c r="BH6" s="44"/>
+      <c r="BF6" s="43"/>
+      <c r="BG6" s="43"/>
+      <c r="BH6" s="43"/>
       <c r="BI6" s="39"/>
       <c r="BJ6" s="39"/>
       <c r="BK6" s="39"/>
-      <c r="BL6" s="47" t="s">
+      <c r="BL6" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM6" t="s" s="0">
@@ -3276,13 +3276,13 @@
       </c>
       <c r="BO6" s="39">
         <f>ROUND((((AW6*AZ6)+(BN6*BM6))/(AW6+BN6)),5)</f>
-        <v>115.50296</v>
-      </c>
-      <c r="BP6" s="48">
+        <v>146.95806</v>
+      </c>
+      <c r="BP6" s="47">
         <f>ROUND(BN6+AW6,3)</f>
         <v>20</v>
       </c>
-      <c r="BQ6" s="49">
+      <c r="BQ6" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -4841,11 +4841,11 @@
       <c r="A4" s="7">
         <v>1</v>
       </c>
-      <c r="B4" s="52" t="s">
-        <v>161</v>
-      </c>
-      <c r="C4" s="52" t="s">
-        <v>162</v>
+      <c r="B4" s="51" t="s">
+        <v>167</v>
+      </c>
+      <c r="C4" s="51" t="s">
+        <v>168</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>77</v>
@@ -4856,15 +4856,15 @@
       <c r="F4" s="8">
         <v>5</v>
       </c>
-      <c r="G4" s="0">
-        <v>150</v>
+      <c r="G4" t="s" s="0">
+        <v>78</v>
       </c>
       <c r="H4" s="8">
         <f t="shared" ref="H4:H6" si="0">F4*G4</f>
         <v>750</v>
       </c>
-      <c r="I4" s="0">
-        <v>5</v>
+      <c r="I4" t="s" s="0">
+        <v>79</v>
       </c>
       <c r="J4" s="8">
         <v>8</v>
@@ -5002,10 +5002,10 @@
         <v>77</v>
       </c>
       <c r="AU4" t="s" s="0">
-        <v>81</v>
+        <v>147</v>
       </c>
       <c r="AV4" t="s" s="0">
-        <v>82</v>
+        <v>148</v>
       </c>
       <c r="AW4" s="39">
         <f t="shared" ref="AW4:AW6" si="12">AM4</f>
@@ -5019,30 +5019,30 @@
         <f t="shared" ref="AY4:AY6" si="14">AU4+AW4</f>
         <v>380</v>
       </c>
-      <c r="AZ4" s="43">
+      <c r="AZ4" s="54">
         <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),3)</f>
         <v>3670.799</v>
       </c>
-      <c r="BA4" s="44"/>
-      <c r="BB4" s="44" t="s">
+      <c r="BA4" s="43"/>
+      <c r="BB4" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC4" s="45" t="s">
+      <c r="BC4" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD4" s="46" t="s">
+      <c r="BD4" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE4" s="46" t="s">
+      <c r="BE4" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF4" s="44"/>
-      <c r="BG4" s="44"/>
-      <c r="BH4" s="44"/>
+      <c r="BF4" s="43"/>
+      <c r="BG4" s="43"/>
+      <c r="BH4" s="43"/>
       <c r="BI4" s="39"/>
       <c r="BJ4" s="39"/>
       <c r="BK4" s="39"/>
-      <c r="BL4" s="47" t="s">
+      <c r="BL4" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM4" t="s" s="0">
@@ -5055,11 +5055,11 @@
         <f t="shared" ref="BO4:BO6" si="15">ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
         <v>333.14818</v>
       </c>
-      <c r="BP4" s="48">
+      <c r="BP4" s="47">
         <f t="shared" ref="BP4:BP6" si="16">ROUND(BN4+AW4,3)</f>
         <v>85</v>
       </c>
-      <c r="BQ4" s="49">
+      <c r="BQ4" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -5067,11 +5067,11 @@
       <c r="A5" s="7">
         <v>1</v>
       </c>
-      <c r="B5" s="52" t="s">
-        <v>163</v>
-      </c>
-      <c r="C5" s="52" t="s">
-        <v>164</v>
+      <c r="B5" s="51" t="s">
+        <v>169</v>
+      </c>
+      <c r="C5" s="51" t="s">
+        <v>170</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>77</v>
@@ -5228,10 +5228,10 @@
         <v>77</v>
       </c>
       <c r="AU5" t="s" s="0">
-        <v>94</v>
+        <v>150</v>
       </c>
       <c r="AV5" t="s" s="0">
-        <v>95</v>
+        <v>151</v>
       </c>
       <c r="AW5" s="39">
         <f t="shared" si="12"/>
@@ -5249,26 +5249,26 @@
         <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),2)</f>
         <v>2076.95</v>
       </c>
-      <c r="BA5" s="44"/>
-      <c r="BB5" s="44" t="s">
+      <c r="BA5" s="43"/>
+      <c r="BB5" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC5" s="45" t="s">
+      <c r="BC5" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD5" s="46" t="s">
+      <c r="BD5" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE5" s="46" t="s">
+      <c r="BE5" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF5" s="44"/>
-      <c r="BG5" s="44"/>
-      <c r="BH5" s="44"/>
+      <c r="BF5" s="43"/>
+      <c r="BG5" s="43"/>
+      <c r="BH5" s="43"/>
       <c r="BI5" s="39"/>
       <c r="BJ5" s="39"/>
       <c r="BK5" s="39"/>
-      <c r="BL5" s="47" t="s">
+      <c r="BL5" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM5" t="s" s="0">
@@ -5281,11 +5281,11 @@
         <f t="shared" si="15"/>
         <v>206.79688</v>
       </c>
-      <c r="BP5" s="48">
+      <c r="BP5" s="47">
         <f t="shared" si="16"/>
         <v>64</v>
       </c>
-      <c r="BQ5" s="49">
+      <c r="BQ5" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -5293,11 +5293,11 @@
       <c r="A6" s="7">
         <v>1</v>
       </c>
-      <c r="B6" s="53" t="s">
-        <v>165</v>
-      </c>
-      <c r="C6" s="54" t="s">
-        <v>166</v>
+      <c r="B6" s="52" t="s">
+        <v>171</v>
+      </c>
+      <c r="C6" s="53" t="s">
+        <v>172</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>77</v>
@@ -5454,10 +5454,10 @@
         <v>77</v>
       </c>
       <c r="AU6" t="s" s="0">
-        <v>102</v>
+        <v>153</v>
       </c>
       <c r="AV6" t="s" s="0">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="AW6" s="39">
         <f t="shared" si="12"/>
@@ -5475,26 +5475,26 @@
         <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),1)</f>
         <v>1198.5</v>
       </c>
-      <c r="BA6" s="44"/>
-      <c r="BB6" s="44" t="s">
+      <c r="BA6" s="43"/>
+      <c r="BB6" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC6" s="45" t="s">
+      <c r="BC6" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD6" s="46" t="s">
+      <c r="BD6" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE6" s="46" t="s">
+      <c r="BE6" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF6" s="44"/>
-      <c r="BG6" s="44"/>
-      <c r="BH6" s="44"/>
+      <c r="BF6" s="43"/>
+      <c r="BG6" s="43"/>
+      <c r="BH6" s="43"/>
       <c r="BI6" s="39"/>
       <c r="BJ6" s="39"/>
       <c r="BK6" s="39"/>
-      <c r="BL6" s="47" t="s">
+      <c r="BL6" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM6" t="s" s="0">
@@ -5507,11 +5507,11 @@
         <f t="shared" si="15"/>
         <v>115.5</v>
       </c>
-      <c r="BP6" s="48">
+      <c r="BP6" s="47">
         <f t="shared" si="16"/>
         <v>320</v>
       </c>
-      <c r="BQ6" s="49">
+      <c r="BQ6" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -7074,10 +7074,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>77</v>
@@ -7234,10 +7234,10 @@
         <v>77</v>
       </c>
       <c r="AU4" t="s" s="0">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AV4" t="s" s="0">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AW4" s="39">
         <f t="shared" ref="AW4:AW6" si="12">AM4</f>
@@ -7255,26 +7255,26 @@
         <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),5)</f>
         <v>851.84345</v>
       </c>
-      <c r="BA4" s="44"/>
-      <c r="BB4" s="44" t="s">
+      <c r="BA4" s="43"/>
+      <c r="BB4" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC4" s="45" t="s">
+      <c r="BC4" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD4" s="46" t="s">
+      <c r="BD4" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE4" s="46" t="s">
+      <c r="BE4" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF4" s="44"/>
-      <c r="BG4" s="44"/>
-      <c r="BH4" s="44"/>
+      <c r="BF4" s="43"/>
+      <c r="BG4" s="43"/>
+      <c r="BH4" s="43"/>
       <c r="BI4" s="39"/>
       <c r="BJ4" s="39"/>
       <c r="BK4" s="39"/>
-      <c r="BL4" s="47" t="s">
+      <c r="BL4" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM4" t="s" s="0">
@@ -7287,11 +7287,11 @@
         <f t="shared" ref="BO4:BO6" si="15">ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
         <v>150.8329</v>
       </c>
-      <c r="BP4" s="48">
+      <c r="BP4" s="47">
         <f t="shared" ref="BP4:BP6" si="16">ROUND(BN4+AW4,3)</f>
         <v>83</v>
       </c>
-      <c r="BQ4" s="49">
+      <c r="BQ4" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -7300,10 +7300,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>77</v>
@@ -7322,7 +7322,7 @@
         <v>600</v>
       </c>
       <c r="I5" t="s" s="0">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="J5" s="8">
         <v>9</v>
@@ -7460,10 +7460,10 @@
         <v>77</v>
       </c>
       <c r="AU5" t="s" s="0">
-        <v>172</v>
+        <v>78</v>
       </c>
       <c r="AV5" t="s" s="0">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="AW5" s="39">
         <f t="shared" si="12"/>
@@ -7481,26 +7481,26 @@
         <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),5)</f>
         <v>1789.94569</v>
       </c>
-      <c r="BA5" s="44"/>
-      <c r="BB5" s="44" t="s">
+      <c r="BA5" s="43"/>
+      <c r="BB5" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC5" s="45" t="s">
+      <c r="BC5" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD5" s="46" t="s">
+      <c r="BD5" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE5" s="46" t="s">
+      <c r="BE5" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF5" s="44"/>
-      <c r="BG5" s="44"/>
-      <c r="BH5" s="44"/>
+      <c r="BF5" s="43"/>
+      <c r="BG5" s="43"/>
+      <c r="BH5" s="43"/>
       <c r="BI5" s="39"/>
       <c r="BJ5" s="39"/>
       <c r="BK5" s="39"/>
-      <c r="BL5" s="47" t="s">
+      <c r="BL5" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM5" t="s" s="0">
@@ -7513,11 +7513,11 @@
         <f t="shared" si="15"/>
         <v>237.37688</v>
       </c>
-      <c r="BP5" s="48">
+      <c r="BP5" s="47">
         <f t="shared" si="16"/>
         <v>66</v>
       </c>
-      <c r="BQ5" s="49">
+      <c r="BQ5" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -7526,10 +7526,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>77</v>
@@ -7548,7 +7548,7 @@
         <v>1800</v>
       </c>
       <c r="I6" t="s" s="0">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="J6" s="8">
         <v>7</v>
@@ -7686,10 +7686,10 @@
         <v>77</v>
       </c>
       <c r="AU6" t="s" s="0">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="AV6" t="s" s="0">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="AW6" s="39">
         <f t="shared" si="12"/>
@@ -7707,26 +7707,26 @@
         <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),5)</f>
         <v>2939.56468</v>
       </c>
-      <c r="BA6" s="44"/>
-      <c r="BB6" s="44" t="s">
+      <c r="BA6" s="43"/>
+      <c r="BB6" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC6" s="45" t="s">
+      <c r="BC6" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD6" s="46" t="s">
+      <c r="BD6" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE6" s="46" t="s">
+      <c r="BE6" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF6" s="44"/>
-      <c r="BG6" s="44"/>
-      <c r="BH6" s="44"/>
+      <c r="BF6" s="43"/>
+      <c r="BG6" s="43"/>
+      <c r="BH6" s="43"/>
       <c r="BI6" s="39"/>
       <c r="BJ6" s="39"/>
       <c r="BK6" s="39"/>
-      <c r="BL6" s="47" t="s">
+      <c r="BL6" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM6" t="s" s="0">
@@ -7739,11 +7739,11 @@
         <f t="shared" si="15"/>
         <v>154.6948</v>
       </c>
-      <c r="BP6" s="48">
+      <c r="BP6" s="47">
         <f t="shared" si="16"/>
         <v>312</v>
       </c>
-      <c r="BQ6" s="49">
+      <c r="BQ6" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -8919,7 +8919,11 @@
     <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
     <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
     <col min="14" max="14" customWidth="true" width="13.847619047619"/>
+    <col min="29" max="29" width="9.57142857142857"/>
+    <col min="35" max="35" width="11.4285714285714"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
     <col min="64" max="64" customWidth="true" width="11.0"/>
+    <col min="67" max="67" width="12.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -9304,10 +9308,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>77</v>
@@ -9467,7 +9471,7 @@
         <v>127</v>
       </c>
       <c r="AV4" t="s" s="0">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="AW4" s="39">
         <f t="shared" ref="AW4:AW6" si="12">AM4</f>
@@ -9481,30 +9485,30 @@
         <f t="shared" ref="AY4:AY6" si="14">AU4+AW4</f>
         <v>160</v>
       </c>
-      <c r="AZ4" s="43">
-        <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),3)</f>
+      <c r="AZ4" s="39">
+        <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),5)</f>
         <v>3714.5</v>
       </c>
-      <c r="BA4" s="44"/>
-      <c r="BB4" s="44" t="s">
+      <c r="BA4" s="43"/>
+      <c r="BB4" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC4" s="45" t="s">
+      <c r="BC4" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD4" s="46" t="s">
+      <c r="BD4" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE4" s="46" t="s">
+      <c r="BE4" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF4" s="44"/>
-      <c r="BG4" s="44"/>
-      <c r="BH4" s="44"/>
+      <c r="BF4" s="43"/>
+      <c r="BG4" s="43"/>
+      <c r="BH4" s="43"/>
       <c r="BI4" s="39"/>
       <c r="BJ4" s="39"/>
       <c r="BK4" s="39"/>
-      <c r="BL4" s="47" t="s">
+      <c r="BL4" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM4" t="s" s="0">
@@ -9517,11 +9521,11 @@
         <f t="shared" ref="BO4:BO6" si="15">ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
         <v>335.71882</v>
       </c>
-      <c r="BP4" s="48">
+      <c r="BP4" s="47">
         <f t="shared" ref="BP4:BP6" si="16">ROUND(BN4+AW4,3)</f>
         <v>85</v>
       </c>
-      <c r="BQ4" s="49">
+      <c r="BQ4" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -9530,10 +9534,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>77</v>
@@ -9566,31 +9570,31 @@
       </c>
       <c r="M5" s="8">
         <f>ROUND(L5*I5%,2)</f>
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="N5" s="8">
         <f t="shared" si="2"/>
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="O5" s="8">
         <f>ROUND(N5*J5%,2)</f>
-        <v>33.84</v>
+        <v>34.56</v>
       </c>
       <c r="P5" s="8">
         <f t="shared" si="3"/>
-        <v>342.16</v>
+        <v>349.44</v>
       </c>
       <c r="Q5" s="8">
         <f t="shared" si="4"/>
-        <v>20.53</v>
+        <v>20.97</v>
       </c>
       <c r="R5" s="8">
         <f>M5+O5+Q5</f>
-        <v>78.37</v>
+        <v>71.53</v>
       </c>
       <c r="S5" s="8">
         <f t="shared" si="5"/>
-        <v>321.63</v>
+        <v>328.47</v>
       </c>
       <c r="T5" s="8">
         <v>88363222</v>
@@ -9599,26 +9603,26 @@
         <v>18</v>
       </c>
       <c r="V5" s="8">
-        <f>IF(OR(DGSUomWIWoQRcImp!$C$2=1,DGSUomWIWoQRcImp!$C$2=4),ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF(OR($C$2=1,$C$2=4),ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="W5" s="8">
-        <f>IF(DGSUomWIWoQRcImp!$C$2=1,ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF($C$2=1,ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="X5" s="8">
-        <f>IF(DGSUomWIWoQRcImp!$C$2=2,ROUND(((S5*U5)/100),2),0)</f>
+        <f>IF($C$2=2,ROUND(((S5*U5)/100),2),0)</f>
         <v>0</v>
       </c>
       <c r="Y5" s="8">
-        <f>IF(DGSUomWIWoQRcImp!$C$2=4,ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF($C$2=4,ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="Z5" s="8">
         <v>0</v>
       </c>
       <c r="AA5" s="8">
-        <f>IF(DGSUomWIWoQRcImp!$C3=3,0,(S5*Z5)/100)</f>
+        <f>IF($C3=3,0,(S5*Z5)/100)</f>
         <v>0</v>
       </c>
       <c r="AB5" s="8">
@@ -9626,35 +9630,35 @@
         <v>0</v>
       </c>
       <c r="AC5" s="8">
-        <f>IF(DGSUomWIWoQRcImp!$V3=1,S5+AB5,S5)</f>
-        <v>321.63</v>
+        <f>IF($V3=1,S5+AB5,S5)</f>
+        <v>328.47</v>
       </c>
       <c r="AD5" s="26">
         <v>120</v>
       </c>
       <c r="AE5" s="26">
-        <f>IF(DGSUomWIWoQRcImp!$P$2=1,(S5/DGSUomWIWoQRcImp!$S$7)*DGSUomWIWoQRcImp!$E$18,AD5/DGSUomWIWoQRcImp!$AD$7*DGSUomWIWoQRcImp!$E$18)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$18,AD5/$AD$7*$E$18)</f>
         <v>0</v>
       </c>
       <c r="AF5" s="26"/>
       <c r="AG5" s="26">
-        <f>IF(DGSUomWIWoQRcImp!$P$2=1,(S5/DGSUomWIWoQRcImp!$S$7)*DGSUomWIWoQRcImp!$E$20,AD5/DGSUomWIWoQRcImp!$AD$7*DGSUomWIWoQRcImp!$E$20)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$20,AD5/$AD$7*$E$20)</f>
         <v>0</v>
       </c>
       <c r="AH5" s="26">
-        <f>IF(DGSUomWIWoQRcImp!$P$2=1,(S5/DGSUomWIWoQRcImp!$S$7)*DGSUomWIWoQRcImp!$E$21,AD5/DGSUomWIWoQRcImp!$AD$7*DGSUomWIWoQRcImp!$E$21)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$21,AD5/$AD$7*$E$21)</f>
         <v>0</v>
       </c>
       <c r="AI5" s="26">
-        <f>S5*DGSUomWIWoQRcImp!$M$2</f>
-        <v>27338.55</v>
+        <f>S5*$M$2</f>
+        <v>27919.95</v>
       </c>
       <c r="AJ5" s="26">
-        <f>IF(DGSUomWIWoQRcImp!$C$2=3,0,AG5+AH5)</f>
+        <f>IF($C$2=3,0,AG5+AH5)</f>
         <v>0</v>
       </c>
       <c r="AK5" s="26">
-        <f>IF(DGSUomWIWoQRcImp!$C$2=3,AE5+AG5+AH5,0)</f>
+        <f>IF($C$2=3,AE5+AG5+AH5,0)</f>
         <v>0</v>
       </c>
       <c r="AL5" s="34">
@@ -9666,7 +9670,7 @@
       </c>
       <c r="AN5" s="26">
         <f t="shared" si="8"/>
-        <v>6834.6375</v>
+        <v>6979.9875</v>
       </c>
       <c r="AO5" s="26">
         <f t="shared" si="9"/>
@@ -9681,7 +9685,7 @@
       </c>
       <c r="AR5" s="26">
         <f t="shared" si="11"/>
-        <v>6834.6375</v>
+        <v>6979.9875</v>
       </c>
       <c r="AS5" s="38" t="s">
         <v>80</v>
@@ -9693,7 +9697,7 @@
         <v>127</v>
       </c>
       <c r="AV5" t="s" s="0">
-        <v>130</v>
+        <v>186</v>
       </c>
       <c r="AW5" s="39">
         <f t="shared" si="12"/>
@@ -9701,36 +9705,36 @@
       </c>
       <c r="AX5" s="42">
         <f t="shared" si="13"/>
-        <v>6834.6375</v>
+        <v>6979.9875</v>
       </c>
       <c r="AY5" s="39">
         <f t="shared" si="14"/>
         <v>128</v>
       </c>
-      <c r="AZ5" s="42">
-        <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),2)</f>
-        <v>6834.64</v>
-      </c>
-      <c r="BA5" s="44"/>
-      <c r="BB5" s="44" t="s">
+      <c r="AZ5" s="39">
+        <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),5)</f>
+        <v>6979.9875</v>
+      </c>
+      <c r="BA5" s="43"/>
+      <c r="BB5" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC5" s="45" t="s">
+      <c r="BC5" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD5" s="46" t="s">
+      <c r="BD5" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE5" s="46" t="s">
+      <c r="BE5" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF5" s="44"/>
-      <c r="BG5" s="44"/>
-      <c r="BH5" s="44"/>
+      <c r="BF5" s="43"/>
+      <c r="BG5" s="43"/>
+      <c r="BH5" s="43"/>
       <c r="BI5" s="39"/>
       <c r="BJ5" s="39"/>
       <c r="BK5" s="39"/>
-      <c r="BL5" s="47" t="s">
+      <c r="BL5" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM5" t="s" s="0">
@@ -9741,13 +9745,13 @@
       </c>
       <c r="BO5" s="39">
         <f t="shared" si="15"/>
-        <v>504.1525</v>
-      </c>
-      <c r="BP5" s="48">
+        <v>513.23672</v>
+      </c>
+      <c r="BP5" s="47">
         <f t="shared" si="16"/>
         <v>64</v>
       </c>
-      <c r="BQ5" s="49">
+      <c r="BQ5" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -9756,10 +9760,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>77</v>
@@ -9792,31 +9796,31 @@
       </c>
       <c r="M6" s="8">
         <f>ROUND(L6*I6%,2)</f>
-        <v>210</v>
+        <v>90</v>
       </c>
       <c r="N6" s="8">
         <f t="shared" si="2"/>
-        <v>2790</v>
+        <v>2910</v>
       </c>
       <c r="O6" s="8">
         <f>ROUND(N6*J6%,2)</f>
-        <v>195.3</v>
+        <v>203.7</v>
       </c>
       <c r="P6" s="8">
         <f t="shared" si="3"/>
-        <v>2594.7</v>
+        <v>2706.3</v>
       </c>
       <c r="Q6" s="8">
         <f t="shared" si="4"/>
-        <v>103.79</v>
+        <v>108.25</v>
       </c>
       <c r="R6" s="8">
         <f>M6+O6+Q6</f>
-        <v>509.09</v>
+        <v>401.95</v>
       </c>
       <c r="S6" s="8">
         <f t="shared" si="5"/>
-        <v>2490.91</v>
+        <v>2598.05</v>
       </c>
       <c r="T6" s="8">
         <v>88363222</v>
@@ -9825,26 +9829,26 @@
         <v>18</v>
       </c>
       <c r="V6" s="8">
-        <f>IF(OR(DGSUomWIWoQRcImp!$C$2=1,DGSUomWIWoQRcImp!$C$2=4),ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF(OR($C$2=1,$C$2=4),ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="W6" s="8">
-        <f>IF(DGSUomWIWoQRcImp!$C$2=1,ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF($C$2=1,ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="X6" s="8">
-        <f>IF(DGSUomWIWoQRcImp!$C$2=2,ROUND(((S6*U6)/100),2),0)</f>
+        <f>IF($C$2=2,ROUND(((S6*U6)/100),2),0)</f>
         <v>0</v>
       </c>
       <c r="Y6" s="8">
-        <f>IF(DGSUomWIWoQRcImp!$C$2=4,ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF($C$2=4,ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="Z6" s="8">
         <v>0</v>
       </c>
       <c r="AA6" s="8">
-        <f>IF(DGSUomWIWoQRcImp!$C4=3,0,(S6*Z6)/100)</f>
+        <f>IF($C4=3,0,(S6*Z6)/100)</f>
         <v>0</v>
       </c>
       <c r="AB6" s="8">
@@ -9852,35 +9856,35 @@
         <v>0</v>
       </c>
       <c r="AC6" s="8">
-        <f>IF(DGSUomWIWoQRcImp!$V4=1,S6+AB6,S6)</f>
-        <v>2490.91</v>
+        <f>IF($V4=1,S6+AB6,S6)</f>
+        <v>2598.05</v>
       </c>
       <c r="AD6" s="26">
         <v>120</v>
       </c>
       <c r="AE6" s="26">
-        <f>IF(DGSUomWIWoQRcImp!$P$2=1,(S6/DGSUomWIWoQRcImp!$S$7)*DGSUomWIWoQRcImp!$E$18,AD6/DGSUomWIWoQRcImp!$AD$7*DGSUomWIWoQRcImp!$E$18)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$18,AD6/$AD$7*$E$18)</f>
         <v>0</v>
       </c>
       <c r="AF6" s="26"/>
       <c r="AG6" s="26">
-        <f>IF(DGSUomWIWoQRcImp!$P$2=1,(S6/DGSUomWIWoQRcImp!$S$7)*DGSUomWIWoQRcImp!$E$20,AD6/DGSUomWIWoQRcImp!$AD$7*DGSUomWIWoQRcImp!$E$20)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$20,AD6/$AD$7*$E$20)</f>
         <v>0</v>
       </c>
       <c r="AH6" s="26">
-        <f>IF(DGSUomWIWoQRcImp!$P$2=1,(S6/DGSUomWIWoQRcImp!$S$7)*DGSUomWIWoQRcImp!$E$21,AD6/DGSUomWIWoQRcImp!$AD$7*DGSUomWIWoQRcImp!$E$21)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$21,AD6/$AD$7*$E$21)</f>
         <v>0</v>
       </c>
       <c r="AI6" s="26">
-        <f>S6*DGSUomWIWoQRcImp!$M$2</f>
-        <v>211727.35</v>
+        <f>S6*$M$2</f>
+        <v>220834.25</v>
       </c>
       <c r="AJ6" s="26">
-        <f>IF(DGSUomWIWoQRcImp!$C$2=3,0,AG6+AH6)</f>
+        <f>IF($C$2=3,0,AG6+AH6)</f>
         <v>0</v>
       </c>
       <c r="AK6" s="26">
-        <f>IF(DGSUomWIWoQRcImp!$C$2=3,AE6+AG6+AH6,0)</f>
+        <f>IF($C$2=3,AE6+AG6+AH6,0)</f>
         <v>0</v>
       </c>
       <c r="AL6" s="34">
@@ -9892,7 +9896,7 @@
       </c>
       <c r="AN6" s="26">
         <f t="shared" si="8"/>
-        <v>10586.3675</v>
+        <v>11041.7125</v>
       </c>
       <c r="AO6" s="26">
         <f t="shared" si="9"/>
@@ -9907,7 +9911,7 @@
       </c>
       <c r="AR6" s="26">
         <f t="shared" si="11"/>
-        <v>10586.3675</v>
+        <v>11041.7125</v>
       </c>
       <c r="AS6" s="38" t="s">
         <v>80</v>
@@ -9919,7 +9923,7 @@
         <v>127</v>
       </c>
       <c r="AV6" t="s" s="0">
-        <v>132</v>
+        <v>188</v>
       </c>
       <c r="AW6" s="39">
         <f t="shared" si="12"/>
@@ -9927,36 +9931,36 @@
       </c>
       <c r="AX6" s="39">
         <f t="shared" si="13"/>
-        <v>10586.3675</v>
+        <v>11041.7125</v>
       </c>
       <c r="AY6" s="39">
         <f t="shared" si="14"/>
         <v>340</v>
       </c>
       <c r="AZ6" s="39">
-        <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),1)</f>
-        <v>10586.4</v>
-      </c>
-      <c r="BA6" s="44"/>
-      <c r="BB6" s="44" t="s">
+        <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),5)</f>
+        <v>11041.7125</v>
+      </c>
+      <c r="BA6" s="43"/>
+      <c r="BB6" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC6" s="45" t="s">
+      <c r="BC6" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD6" s="46" t="s">
+      <c r="BD6" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE6" s="46" t="s">
+      <c r="BE6" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF6" s="44"/>
-      <c r="BG6" s="44"/>
-      <c r="BH6" s="44"/>
+      <c r="BF6" s="43"/>
+      <c r="BG6" s="43"/>
+      <c r="BH6" s="43"/>
       <c r="BI6" s="39"/>
       <c r="BJ6" s="39"/>
       <c r="BK6" s="39"/>
-      <c r="BL6" s="47" t="s">
+      <c r="BL6" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM6" t="s" s="0">
@@ -9967,13 +9971,13 @@
       </c>
       <c r="BO6" s="39">
         <f t="shared" si="15"/>
-        <v>702.24375</v>
-      </c>
-      <c r="BP6" s="48">
+        <v>730.70078</v>
+      </c>
+      <c r="BP6" s="47">
         <f t="shared" si="16"/>
         <v>320</v>
       </c>
-      <c r="BQ6" s="49">
+      <c r="BQ6" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -11537,10 +11541,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>77</v>
@@ -11697,10 +11701,10 @@
         <v>77</v>
       </c>
       <c r="AU4" t="s" s="0">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="AV4" t="s" s="0">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="AW4" s="39">
         <f t="shared" ref="AW4:AW6" si="12">AM4</f>
@@ -11718,26 +11722,26 @@
         <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),5)</f>
         <v>12363.72915</v>
       </c>
-      <c r="BA4" s="44"/>
-      <c r="BB4" s="44" t="s">
+      <c r="BA4" s="43"/>
+      <c r="BB4" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC4" s="45" t="s">
+      <c r="BC4" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD4" s="46" t="s">
+      <c r="BD4" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE4" s="46" t="s">
+      <c r="BE4" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF4" s="44"/>
-      <c r="BG4" s="44"/>
-      <c r="BH4" s="44"/>
+      <c r="BF4" s="43"/>
+      <c r="BG4" s="43"/>
+      <c r="BH4" s="43"/>
       <c r="BI4" s="39"/>
       <c r="BJ4" s="39"/>
       <c r="BK4" s="39"/>
-      <c r="BL4" s="47" t="s">
+      <c r="BL4" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM4" t="s" s="0">
@@ -11750,11 +11754,11 @@
         <f t="shared" ref="BO4:BO6" si="15">ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
         <v>275.64604</v>
       </c>
-      <c r="BP4" s="48">
+      <c r="BP4" s="47">
         <f t="shared" ref="BP4:BP6" si="16">ROUND(BN4+AW4,3)</f>
         <v>81</v>
       </c>
-      <c r="BQ4" s="49">
+      <c r="BQ4" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -11763,10 +11767,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>77</v>
@@ -11923,10 +11927,10 @@
         <v>77</v>
       </c>
       <c r="AU5" t="s" s="0">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="AV5" t="s" s="0">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="AW5" s="39">
         <f t="shared" si="12"/>
@@ -11944,26 +11948,26 @@
         <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),5)</f>
         <v>8524.09451</v>
       </c>
-      <c r="BA5" s="44"/>
-      <c r="BB5" s="44" t="s">
+      <c r="BA5" s="43"/>
+      <c r="BB5" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC5" s="45" t="s">
+      <c r="BC5" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD5" s="46" t="s">
+      <c r="BD5" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE5" s="46" t="s">
+      <c r="BE5" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF5" s="44"/>
-      <c r="BG5" s="44"/>
-      <c r="BH5" s="44"/>
+      <c r="BF5" s="43"/>
+      <c r="BG5" s="43"/>
+      <c r="BH5" s="43"/>
       <c r="BI5" s="39"/>
       <c r="BJ5" s="39"/>
       <c r="BK5" s="39"/>
-      <c r="BL5" s="47" t="s">
+      <c r="BL5" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM5" t="s" s="0">
@@ -11976,11 +11980,11 @@
         <f t="shared" si="15"/>
         <v>609.74341</v>
       </c>
-      <c r="BP5" s="48">
+      <c r="BP5" s="47">
         <f t="shared" si="16"/>
         <v>64</v>
       </c>
-      <c r="BQ5" s="49">
+      <c r="BQ5" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -11989,10 +11993,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>77</v>
@@ -12149,10 +12153,10 @@
         <v>77</v>
       </c>
       <c r="AU6" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="AV6" t="s" s="0">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="AW6" s="39">
         <f t="shared" si="12"/>
@@ -12170,26 +12174,26 @@
         <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),5)</f>
         <v>4776.58342</v>
       </c>
-      <c r="BA6" s="44"/>
-      <c r="BB6" s="44" t="s">
+      <c r="BA6" s="43"/>
+      <c r="BB6" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC6" s="45" t="s">
+      <c r="BC6" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD6" s="46" t="s">
+      <c r="BD6" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE6" s="46" t="s">
+      <c r="BE6" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF6" s="44"/>
-      <c r="BG6" s="44"/>
-      <c r="BH6" s="44"/>
+      <c r="BF6" s="43"/>
+      <c r="BG6" s="43"/>
+      <c r="BH6" s="43"/>
       <c r="BI6" s="39"/>
       <c r="BJ6" s="39"/>
       <c r="BK6" s="39"/>
-      <c r="BL6" s="47" t="s">
+      <c r="BL6" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM6" t="s" s="0">
@@ -12202,11 +12206,11 @@
         <f t="shared" si="15"/>
         <v>90.16419</v>
       </c>
-      <c r="BP6" s="48">
+      <c r="BP6" s="47">
         <f t="shared" si="16"/>
         <v>303</v>
       </c>
-      <c r="BQ6" s="49">
+      <c r="BQ6" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -13381,7 +13385,10 @@
     <col min="3" max="3" customWidth="true" width="30.0"/>
     <col min="13" max="13" customWidth="true" width="9.14285714285714"/>
     <col min="14" max="14" customWidth="true" width="13.847619047619"/>
+    <col min="35" max="35" width="11.4285714285714"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
     <col min="64" max="64" customWidth="true" width="11.0"/>
+    <col min="67" max="67" width="12.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -13766,10 +13773,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>77</v>
@@ -13780,15 +13787,15 @@
       <c r="F4" s="8">
         <v>5</v>
       </c>
-      <c r="G4" s="0">
-        <v>50</v>
+      <c r="G4" t="s" s="0">
+        <v>100</v>
       </c>
       <c r="H4" s="8">
         <f t="shared" ref="H4:H6" si="0">F4*G4</f>
         <v>250</v>
       </c>
-      <c r="I4" s="0">
-        <v>0</v>
+      <c r="I4" t="s" s="0">
+        <v>127</v>
       </c>
       <c r="J4" s="8">
         <v>8</v>
@@ -13926,10 +13933,10 @@
         <v>77</v>
       </c>
       <c r="AU4" t="s" s="0">
-        <v>183</v>
+        <v>127</v>
       </c>
       <c r="AV4" t="s" s="0">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="AW4" s="39">
         <f t="shared" ref="AW4:AW6" si="12">AM4</f>
@@ -13943,30 +13950,30 @@
         <f t="shared" ref="AY4:AY6" si="14">AU4+AW4</f>
         <v>59.9946666666667</v>
       </c>
-      <c r="AZ4" s="43">
-        <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),3)</f>
-        <v>12006.555</v>
-      </c>
-      <c r="BA4" s="44"/>
-      <c r="BB4" s="44" t="s">
+      <c r="AZ4" s="39">
+        <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),5)</f>
+        <v>12006.55514</v>
+      </c>
+      <c r="BA4" s="43"/>
+      <c r="BB4" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC4" s="45" t="s">
+      <c r="BC4" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD4" s="46" t="s">
+      <c r="BD4" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE4" s="46" t="s">
+      <c r="BE4" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF4" s="44"/>
-      <c r="BG4" s="44"/>
-      <c r="BH4" s="44"/>
+      <c r="BF4" s="43"/>
+      <c r="BG4" s="43"/>
+      <c r="BH4" s="43"/>
       <c r="BI4" s="39"/>
       <c r="BJ4" s="39"/>
       <c r="BK4" s="39"/>
-      <c r="BL4" s="47" t="s">
+      <c r="BL4" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM4" t="s" s="0">
@@ -13979,11 +13986,11 @@
         <f t="shared" ref="BO4:BO6" si="15">ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
         <v>367.035</v>
       </c>
-      <c r="BP4" s="48">
+      <c r="BP4" s="47">
         <f t="shared" ref="BP4:BP6" si="16">ROUND(BN4+AW4,3)</f>
         <v>81.667</v>
       </c>
-      <c r="BQ4" s="49">
+      <c r="BQ4" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -13992,10 +13999,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>77</v>
@@ -14061,26 +14068,26 @@
         <v>18</v>
       </c>
       <c r="V5" s="8">
-        <f>IF(OR(DGDUomWoQWIRcImp!$C$2=1,DGDUomWoQWIRcImp!$C$2=4),ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF(OR($C$2=1,$C$2=4),ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="W5" s="8">
-        <f>IF(DGDUomWoQWIRcImp!$C$2=1,ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF($C$2=1,ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="X5" s="8">
-        <f>IF(DGDUomWoQWIRcImp!$C$2=2,ROUND(((S5*U5)/100),2),0)</f>
+        <f>IF($C$2=2,ROUND(((S5*U5)/100),2),0)</f>
         <v>0</v>
       </c>
       <c r="Y5" s="8">
-        <f>IF(DGDUomWoQWIRcImp!$C$2=4,ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF($C$2=4,ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="Z5" s="8">
         <v>0</v>
       </c>
       <c r="AA5" s="8">
-        <f>IF(DGDUomWoQWIRcImp!$C3=3,0,(S5*Z5)/100)</f>
+        <f>IF($C3=3,0,(S5*Z5)/100)</f>
         <v>0</v>
       </c>
       <c r="AB5" s="8">
@@ -14088,35 +14095,35 @@
         <v>0</v>
       </c>
       <c r="AC5" s="8">
-        <f>IF(DGDUomWoQWIRcImp!$V3=1,S5+AB5,S5)</f>
+        <f>IF($V3=1,S5+AB5,S5)</f>
         <v>328.47</v>
       </c>
       <c r="AD5" s="26">
         <v>120</v>
       </c>
       <c r="AE5" s="26">
-        <f>IF(DGDUomWoQWIRcImp!$P$2=1,(S5/DGDUomWoQWIRcImp!$S$7)*DGDUomWoQWIRcImp!$E$18,AD5/DGDUomWoQWIRcImp!$AD$7*DGDUomWoQWIRcImp!$E$18)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$18,AD5/$AD$7*$E$18)</f>
         <v>0</v>
       </c>
       <c r="AF5" s="26"/>
       <c r="AG5" s="26">
-        <f>IF(DGDUomWoQWIRcImp!$P$2=1,(S5/DGDUomWoQWIRcImp!$S$7)*DGDUomWoQWIRcImp!$E$20,AD5/DGDUomWoQWIRcImp!$AD$7*DGDUomWoQWIRcImp!$E$20)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$20,AD5/$AD$7*$E$20)</f>
         <v>0</v>
       </c>
       <c r="AH5" s="26">
-        <f>IF(DGDUomWoQWIRcImp!$P$2=1,(S5/DGDUomWoQWIRcImp!$S$7)*DGDUomWoQWIRcImp!$E$21,AD5/DGDUomWoQWIRcImp!$AD$7*DGDUomWoQWIRcImp!$E$21)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$21,AD5/$AD$7*$E$21)</f>
         <v>0</v>
       </c>
       <c r="AI5" s="26">
-        <f>S5*DGDUomWoQWIRcImp!$M$2</f>
+        <f>S5*$M$2</f>
         <v>27919.95</v>
       </c>
       <c r="AJ5" s="26">
-        <f>IF(DGDUomWoQWIRcImp!$C$2=3,0,AG5+AH5)</f>
+        <f>IF($C$2=3,0,AG5+AH5)</f>
         <v>0</v>
       </c>
       <c r="AK5" s="26">
-        <f>IF(DGDUomWoQWIRcImp!$C$2=3,AE5+AG5+AH5,0)</f>
+        <f>IF($C$2=3,AE5+AG5+AH5,0)</f>
         <v>0</v>
       </c>
       <c r="AL5" s="34">
@@ -14152,10 +14159,10 @@
         <v>77</v>
       </c>
       <c r="AU5" t="s" s="0">
-        <v>186</v>
+        <v>127</v>
       </c>
       <c r="AV5" t="s" s="0">
-        <v>187</v>
+        <v>145</v>
       </c>
       <c r="AW5" s="39">
         <f t="shared" si="12"/>
@@ -14169,30 +14176,30 @@
         <f t="shared" si="14"/>
         <v>60.6603333333333</v>
       </c>
-      <c r="AZ5" s="42">
-        <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),2)</f>
-        <v>7978.27</v>
-      </c>
-      <c r="BA5" s="44"/>
-      <c r="BB5" s="44" t="s">
+      <c r="AZ5" s="39">
+        <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),5)</f>
+        <v>7978.27108</v>
+      </c>
+      <c r="BA5" s="43"/>
+      <c r="BB5" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC5" s="45" t="s">
+      <c r="BC5" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD5" s="46" t="s">
+      <c r="BD5" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE5" s="46" t="s">
+      <c r="BE5" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF5" s="44"/>
-      <c r="BG5" s="44"/>
-      <c r="BH5" s="44"/>
+      <c r="BF5" s="43"/>
+      <c r="BG5" s="43"/>
+      <c r="BH5" s="43"/>
       <c r="BI5" s="39"/>
       <c r="BJ5" s="39"/>
       <c r="BK5" s="39"/>
-      <c r="BL5" s="47" t="s">
+      <c r="BL5" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM5" t="s" s="0">
@@ -14203,13 +14210,13 @@
       </c>
       <c r="BO5" s="39">
         <f t="shared" si="15"/>
-        <v>253.77543</v>
-      </c>
-      <c r="BP5" s="48">
+        <v>253.77546</v>
+      </c>
+      <c r="BP5" s="47">
         <f t="shared" si="16"/>
         <v>61.333</v>
       </c>
-      <c r="BQ5" s="49">
+      <c r="BQ5" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -14218,10 +14225,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>77</v>
@@ -14287,26 +14294,26 @@
         <v>18</v>
       </c>
       <c r="V6" s="8">
-        <f>IF(OR(DGDUomWoQWIRcImp!$C$2=1,DGDUomWoQWIRcImp!$C$2=4),ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF(OR($C$2=1,$C$2=4),ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="W6" s="8">
-        <f>IF(DGDUomWoQWIRcImp!$C$2=1,ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF($C$2=1,ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="X6" s="8">
-        <f>IF(DGDUomWoQWIRcImp!$C$2=2,ROUND(((S6*U6)/100),2),0)</f>
+        <f>IF($C$2=2,ROUND(((S6*U6)/100),2),0)</f>
         <v>0</v>
       </c>
       <c r="Y6" s="8">
-        <f>IF(DGDUomWoQWIRcImp!$C$2=4,ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF($C$2=4,ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="Z6" s="8">
         <v>0</v>
       </c>
       <c r="AA6" s="8">
-        <f>IF(DGDUomWoQWIRcImp!$C4=3,0,(S6*Z6)/100)</f>
+        <f>IF($C4=3,0,(S6*Z6)/100)</f>
         <v>0</v>
       </c>
       <c r="AB6" s="8">
@@ -14314,35 +14321,35 @@
         <v>0</v>
       </c>
       <c r="AC6" s="8">
-        <f>IF(DGDUomWoQWIRcImp!$V4=1,S6+AB6,S6)</f>
+        <f>IF($V4=1,S6+AB6,S6)</f>
         <v>866.02</v>
       </c>
       <c r="AD6" s="26">
         <v>120</v>
       </c>
       <c r="AE6" s="26">
-        <f>IF(DGDUomWoQWIRcImp!$P$2=1,(S6/DGDUomWoQWIRcImp!$S$7)*DGDUomWoQWIRcImp!$E$18,AD6/DGDUomWoQWIRcImp!$AD$7*DGDUomWoQWIRcImp!$E$18)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$18,AD6/$AD$7*$E$18)</f>
         <v>0</v>
       </c>
       <c r="AF6" s="26"/>
       <c r="AG6" s="26">
-        <f>IF(DGDUomWoQWIRcImp!$P$2=1,(S6/DGDUomWoQWIRcImp!$S$7)*DGDUomWoQWIRcImp!$E$20,AD6/DGDUomWoQWIRcImp!$AD$7*DGDUomWoQWIRcImp!$E$20)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$20,AD6/$AD$7*$E$20)</f>
         <v>0</v>
       </c>
       <c r="AH6" s="26">
-        <f>IF(DGDUomWoQWIRcImp!$P$2=1,(S6/DGDUomWoQWIRcImp!$S$7)*DGDUomWoQWIRcImp!$E$21,AD6/DGDUomWoQWIRcImp!$AD$7*DGDUomWoQWIRcImp!$E$21)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$21,AD6/$AD$7*$E$21)</f>
         <v>0</v>
       </c>
       <c r="AI6" s="26">
-        <f>S6*DGDUomWoQWIRcImp!$M$2</f>
+        <f>S6*$M$2</f>
         <v>73611.7</v>
       </c>
       <c r="AJ6" s="26">
-        <f>IF(DGDUomWoQWIRcImp!$C$2=3,0,AG6+AH6)</f>
+        <f>IF($C$2=3,0,AG6+AH6)</f>
         <v>0</v>
       </c>
       <c r="AK6" s="26">
-        <f>IF(DGDUomWoQWIRcImp!$C$2=3,AE6+AG6+AH6,0)</f>
+        <f>IF($C$2=3,AE6+AG6+AH6,0)</f>
         <v>0</v>
       </c>
       <c r="AL6" s="34">
@@ -14378,10 +14385,10 @@
         <v>77</v>
       </c>
       <c r="AU6" t="s" s="0">
-        <v>189</v>
+        <v>127</v>
       </c>
       <c r="AV6" t="s" s="0">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="AW6" s="39">
         <f t="shared" si="12"/>
@@ -14396,29 +14403,29 @@
         <v>73.3276666666667</v>
       </c>
       <c r="AZ6" s="39">
-        <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),1)</f>
-        <v>5089.9</v>
-      </c>
-      <c r="BA6" s="44"/>
-      <c r="BB6" s="44" t="s">
+        <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),5)</f>
+        <v>5089.87664</v>
+      </c>
+      <c r="BA6" s="43"/>
+      <c r="BB6" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC6" s="45" t="s">
+      <c r="BC6" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD6" s="46" t="s">
+      <c r="BD6" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE6" s="46" t="s">
+      <c r="BE6" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF6" s="44"/>
-      <c r="BG6" s="44"/>
-      <c r="BH6" s="44"/>
+      <c r="BF6" s="43"/>
+      <c r="BG6" s="43"/>
+      <c r="BH6" s="43"/>
       <c r="BI6" s="39"/>
       <c r="BJ6" s="39"/>
       <c r="BK6" s="39"/>
-      <c r="BL6" s="47" t="s">
+      <c r="BL6" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM6" t="s" s="0">
@@ -14429,13 +14436,13 @@
       </c>
       <c r="BO6" s="39">
         <f t="shared" si="15"/>
-        <v>153.0087</v>
-      </c>
-      <c r="BP6" s="48">
+        <v>153.00819</v>
+      </c>
+      <c r="BP6" s="47">
         <f t="shared" si="16"/>
         <v>306.667</v>
       </c>
-      <c r="BQ6" s="49">
+      <c r="BQ6" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -15999,10 +16006,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>77</v>
@@ -16159,10 +16166,10 @@
         <v>77</v>
       </c>
       <c r="AU4" t="s" s="0">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AV4" t="s" s="0">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="AW4" s="39">
         <f t="shared" ref="AW4:AW6" si="12">AM4</f>
@@ -16180,26 +16187,26 @@
         <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),5)</f>
         <v>4284.04277</v>
       </c>
-      <c r="BA4" s="44"/>
-      <c r="BB4" s="44" t="s">
+      <c r="BA4" s="43"/>
+      <c r="BB4" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC4" s="45" t="s">
+      <c r="BC4" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD4" s="46" t="s">
+      <c r="BD4" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE4" s="46" t="s">
+      <c r="BE4" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF4" s="44"/>
-      <c r="BG4" s="44"/>
-      <c r="BH4" s="44"/>
+      <c r="BF4" s="43"/>
+      <c r="BG4" s="43"/>
+      <c r="BH4" s="43"/>
       <c r="BI4" s="39"/>
       <c r="BJ4" s="39"/>
       <c r="BK4" s="39"/>
-      <c r="BL4" s="47" t="s">
+      <c r="BL4" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM4" t="s" s="0">
@@ -16212,11 +16219,11 @@
         <f t="shared" ref="BO4:BO6" si="15">ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
         <v>274.88829</v>
       </c>
-      <c r="BP4" s="48">
+      <c r="BP4" s="47">
         <f t="shared" ref="BP4:BP6" si="16">ROUND(BN4+AW4,3)</f>
         <v>83</v>
       </c>
-      <c r="BQ4" s="49">
+      <c r="BQ4" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -16225,10 +16232,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>77</v>
@@ -16385,10 +16392,10 @@
         <v>77</v>
       </c>
       <c r="AU5" t="s" s="0">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="AV5" t="s" s="0">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="AW5" s="39">
         <f t="shared" si="12"/>
@@ -16406,26 +16413,26 @@
         <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),5)</f>
         <v>2878.62743</v>
       </c>
-      <c r="BA5" s="44"/>
-      <c r="BB5" s="44" t="s">
+      <c r="BA5" s="43"/>
+      <c r="BB5" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC5" s="45" t="s">
+      <c r="BC5" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD5" s="46" t="s">
+      <c r="BD5" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE5" s="46" t="s">
+      <c r="BE5" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF5" s="44"/>
-      <c r="BG5" s="44"/>
-      <c r="BH5" s="44"/>
+      <c r="BF5" s="43"/>
+      <c r="BG5" s="43"/>
+      <c r="BH5" s="43"/>
       <c r="BI5" s="39"/>
       <c r="BJ5" s="39"/>
       <c r="BK5" s="39"/>
-      <c r="BL5" s="47" t="s">
+      <c r="BL5" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM5" t="s" s="0">
@@ -16438,11 +16445,11 @@
         <f t="shared" si="15"/>
         <v>336.34795</v>
       </c>
-      <c r="BP5" s="48">
+      <c r="BP5" s="47">
         <f t="shared" si="16"/>
         <v>66</v>
       </c>
-      <c r="BQ5" s="49">
+      <c r="BQ5" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -16450,11 +16457,11 @@
       <c r="A6" s="7">
         <v>1</v>
       </c>
-      <c r="B6" s="50" t="s">
-        <v>199</v>
-      </c>
-      <c r="C6" s="51" t="s">
-        <v>199</v>
+      <c r="B6" s="49" t="s">
+        <v>208</v>
+      </c>
+      <c r="C6" s="50" t="s">
+        <v>208</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>77</v>
@@ -16611,10 +16618,10 @@
         <v>77</v>
       </c>
       <c r="AU6" t="s" s="0">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="AV6" t="s" s="0">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="AW6" s="39">
         <f t="shared" si="12"/>
@@ -16632,26 +16639,26 @@
         <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),5)</f>
         <v>1447.13407</v>
       </c>
-      <c r="BA6" s="44"/>
-      <c r="BB6" s="44" t="s">
+      <c r="BA6" s="43"/>
+      <c r="BB6" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC6" s="45" t="s">
+      <c r="BC6" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD6" s="46" t="s">
+      <c r="BD6" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE6" s="46" t="s">
+      <c r="BE6" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF6" s="44"/>
-      <c r="BG6" s="44"/>
-      <c r="BH6" s="44"/>
+      <c r="BF6" s="43"/>
+      <c r="BG6" s="43"/>
+      <c r="BH6" s="43"/>
       <c r="BI6" s="39"/>
       <c r="BJ6" s="39"/>
       <c r="BK6" s="39"/>
-      <c r="BL6" s="47" t="s">
+      <c r="BL6" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM6" t="s" s="0">
@@ -16664,11 +16671,11 @@
         <f t="shared" si="15"/>
         <v>97.29362</v>
       </c>
-      <c r="BP6" s="48">
+      <c r="BP6" s="47">
         <f t="shared" si="16"/>
         <v>312</v>
       </c>
-      <c r="BQ6" s="49">
+      <c r="BQ6" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -17843,7 +17850,10 @@
     <col min="3" max="3" customWidth="true" width="23.0"/>
     <col min="13" max="13" customWidth="true" width="9.14285714285714"/>
     <col min="14" max="14" customWidth="true" width="13.847619047619"/>
+    <col min="35" max="35" width="11.4285714285714"/>
+    <col min="52" max="52" width="13.1428571428571"/>
     <col min="64" max="64" customWidth="true" width="11.0"/>
+    <col min="67" max="67" width="12.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -18228,10 +18238,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>77</v>
@@ -18391,7 +18401,7 @@
         <v>127</v>
       </c>
       <c r="AV4" t="s" s="0">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="AW4" s="39">
         <f t="shared" ref="AW4:AW6" si="12">AM4</f>
@@ -18405,30 +18415,30 @@
         <f t="shared" ref="AY4:AY6" si="14">AU4+AW4</f>
         <v>85</v>
       </c>
-      <c r="AZ4" s="43">
-        <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),3)</f>
+      <c r="AZ4" s="39">
+        <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),5)</f>
         <v>3714.5</v>
       </c>
-      <c r="BA4" s="44"/>
-      <c r="BB4" s="44" t="s">
+      <c r="BA4" s="43"/>
+      <c r="BB4" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC4" s="45" t="s">
+      <c r="BC4" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD4" s="46" t="s">
+      <c r="BD4" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE4" s="46" t="s">
+      <c r="BE4" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF4" s="44"/>
-      <c r="BG4" s="44"/>
-      <c r="BH4" s="44"/>
+      <c r="BF4" s="43"/>
+      <c r="BG4" s="43"/>
+      <c r="BH4" s="43"/>
       <c r="BI4" s="39"/>
       <c r="BJ4" s="39"/>
       <c r="BK4" s="39"/>
-      <c r="BL4" s="47" t="s">
+      <c r="BL4" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM4" t="s" s="0">
@@ -18441,11 +18451,11 @@
         <f t="shared" ref="BO4:BO6" si="15">ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
         <v>335.71882</v>
       </c>
-      <c r="BP4" s="48">
+      <c r="BP4" s="47">
         <f t="shared" ref="BP4:BP6" si="16">ROUND(BN4+AW4,3)</f>
         <v>85</v>
       </c>
-      <c r="BQ4" s="49">
+      <c r="BQ4" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -18454,10 +18464,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>77</v>
@@ -18523,26 +18533,26 @@
         <v>18</v>
       </c>
       <c r="V5" s="8">
-        <f>IF(OR(DGSUomWIWoQPlImp!$C$2=1,DGSUomWIWoQPlImp!$C$2=4),ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF(OR($C$2=1,$C$2=4),ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="W5" s="8">
-        <f>IF(DGSUomWIWoQPlImp!$C$2=1,ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF($C$2=1,ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="X5" s="8">
-        <f>IF(DGSUomWIWoQPlImp!$C$2=2,ROUND(((S5*U5)/100),2),0)</f>
+        <f>IF($C$2=2,ROUND(((S5*U5)/100),2),0)</f>
         <v>0</v>
       </c>
       <c r="Y5" s="8">
-        <f>IF(DGSUomWIWoQPlImp!$C$2=4,ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF($C$2=4,ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="Z5" s="8">
         <v>0</v>
       </c>
       <c r="AA5" s="8">
-        <f>IF(DGSUomWIWoQPlImp!$C3=3,0,(S5*Z5)/100)</f>
+        <f>IF($C3=3,0,(S5*Z5)/100)</f>
         <v>0</v>
       </c>
       <c r="AB5" s="8">
@@ -18550,35 +18560,35 @@
         <v>0</v>
       </c>
       <c r="AC5" s="8">
-        <f>IF(DGSUomWIWoQPlImp!$V3=1,S5+AB5,S5)</f>
+        <f>IF($V3=1,S5+AB5,S5)</f>
         <v>328.47</v>
       </c>
       <c r="AD5" s="26">
         <v>120</v>
       </c>
       <c r="AE5" s="26">
-        <f>IF(DGSUomWIWoQPlImp!$P$2=1,(S5/DGSUomWIWoQPlImp!$S$7)*DGSUomWIWoQPlImp!$E$18,AD5/DGSUomWIWoQPlImp!$AD$7*DGSUomWIWoQPlImp!$E$18)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$18,AD5/$AD$7*$E$18)</f>
         <v>0</v>
       </c>
       <c r="AF5" s="26"/>
       <c r="AG5" s="26">
-        <f>IF(DGSUomWIWoQPlImp!$P$2=1,(S5/DGSUomWIWoQPlImp!$S$7)*DGSUomWIWoQPlImp!$E$20,AD5/DGSUomWIWoQPlImp!$AD$7*DGSUomWIWoQPlImp!$E$20)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$20,AD5/$AD$7*$E$20)</f>
         <v>0</v>
       </c>
       <c r="AH5" s="26">
-        <f>IF(DGSUomWIWoQPlImp!$P$2=1,(S5/DGSUomWIWoQPlImp!$S$7)*DGSUomWIWoQPlImp!$E$21,AD5/DGSUomWIWoQPlImp!$AD$7*DGSUomWIWoQPlImp!$E$21)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$21,AD5/$AD$7*$E$21)</f>
         <v>0</v>
       </c>
       <c r="AI5" s="26">
-        <f>S5*DGSUomWIWoQPlImp!$M$2</f>
+        <f>S5*$M$2</f>
         <v>27919.95</v>
       </c>
       <c r="AJ5" s="26">
-        <f>IF(DGSUomWIWoQPlImp!$C$2=3,0,AG5+AH5)</f>
+        <f>IF($C$2=3,0,AG5+AH5)</f>
         <v>0</v>
       </c>
       <c r="AK5" s="26">
-        <f>IF(DGSUomWIWoQPlImp!$C$2=3,AE5+AG5+AH5,0)</f>
+        <f>IF($C$2=3,AE5+AG5+AH5,0)</f>
         <v>0</v>
       </c>
       <c r="AL5" s="34">
@@ -18617,7 +18627,7 @@
         <v>127</v>
       </c>
       <c r="AV5" t="s" s="0">
-        <v>130</v>
+        <v>186</v>
       </c>
       <c r="AW5" s="39">
         <f t="shared" si="12"/>
@@ -18631,30 +18641,30 @@
         <f t="shared" si="14"/>
         <v>72</v>
       </c>
-      <c r="AZ5" s="42">
-        <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),2)</f>
-        <v>6979.99</v>
-      </c>
-      <c r="BA5" s="44"/>
-      <c r="BB5" s="44" t="s">
+      <c r="AZ5" s="39">
+        <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),5)</f>
+        <v>6979.9875</v>
+      </c>
+      <c r="BA5" s="43"/>
+      <c r="BB5" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC5" s="45" t="s">
+      <c r="BC5" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD5" s="46" t="s">
+      <c r="BD5" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE5" s="46" t="s">
+      <c r="BE5" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF5" s="44"/>
-      <c r="BG5" s="44"/>
-      <c r="BH5" s="44"/>
+      <c r="BF5" s="43"/>
+      <c r="BG5" s="43"/>
+      <c r="BH5" s="43"/>
       <c r="BI5" s="39"/>
       <c r="BJ5" s="39"/>
       <c r="BK5" s="39"/>
-      <c r="BL5" s="47" t="s">
+      <c r="BL5" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM5" t="s" s="0">
@@ -18665,13 +18675,13 @@
       </c>
       <c r="BO5" s="39">
         <f t="shared" si="15"/>
-        <v>513.23688</v>
-      </c>
-      <c r="BP5" s="48">
+        <v>513.23672</v>
+      </c>
+      <c r="BP5" s="47">
         <f t="shared" si="16"/>
         <v>64</v>
       </c>
-      <c r="BQ5" s="49">
+      <c r="BQ5" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -18680,10 +18690,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>77</v>
@@ -18749,26 +18759,26 @@
         <v>18</v>
       </c>
       <c r="V6" s="8">
-        <f>IF(OR(DGSUomWIWoQPlImp!$C$2=1,DGSUomWIWoQPlImp!$C$2=4),ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF(OR($C$2=1,$C$2=4),ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="W6" s="8">
-        <f>IF(DGSUomWIWoQPlImp!$C$2=1,ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF($C$2=1,ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="X6" s="8">
-        <f>IF(DGSUomWIWoQPlImp!$C$2=2,ROUND(((S6*U6)/100),2),0)</f>
+        <f>IF($C$2=2,ROUND(((S6*U6)/100),2),0)</f>
         <v>0</v>
       </c>
       <c r="Y6" s="8">
-        <f>IF(DGSUomWIWoQPlImp!$C$2=4,ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF($C$2=4,ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="Z6" s="8">
         <v>0</v>
       </c>
       <c r="AA6" s="8">
-        <f>IF(DGSUomWIWoQPlImp!$C4=3,0,(S6*Z6)/100)</f>
+        <f>IF($C4=3,0,(S6*Z6)/100)</f>
         <v>0</v>
       </c>
       <c r="AB6" s="8">
@@ -18776,35 +18786,35 @@
         <v>0</v>
       </c>
       <c r="AC6" s="8">
-        <f>IF(DGSUomWIWoQPlImp!$V4=1,S6+AB6,S6)</f>
+        <f>IF($V4=1,S6+AB6,S6)</f>
         <v>866.02</v>
       </c>
       <c r="AD6" s="26">
         <v>120</v>
       </c>
       <c r="AE6" s="26">
-        <f>IF(DGSUomWIWoQPlImp!$P$2=1,(S6/DGSUomWIWoQPlImp!$S$7)*DGSUomWIWoQPlImp!$E$18,AD6/DGSUomWIWoQPlImp!$AD$7*DGSUomWIWoQPlImp!$E$18)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$18,AD6/$AD$7*$E$18)</f>
         <v>0</v>
       </c>
       <c r="AF6" s="26"/>
       <c r="AG6" s="26">
-        <f>IF(DGSUomWIWoQPlImp!$P$2=1,(S6/DGSUomWIWoQPlImp!$S$7)*DGSUomWIWoQPlImp!$E$20,AD6/DGSUomWIWoQPlImp!$AD$7*DGSUomWIWoQPlImp!$E$20)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$20,AD6/$AD$7*$E$20)</f>
         <v>0</v>
       </c>
       <c r="AH6" s="26">
-        <f>IF(DGSUomWIWoQPlImp!$P$2=1,(S6/DGSUomWIWoQPlImp!$S$7)*DGSUomWIWoQPlImp!$E$21,AD6/DGSUomWIWoQPlImp!$AD$7*DGSUomWIWoQPlImp!$E$21)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$21,AD6/$AD$7*$E$21)</f>
         <v>0</v>
       </c>
       <c r="AI6" s="26">
-        <f>S6*DGSUomWIWoQPlImp!$M$2</f>
+        <f>S6*$M$2</f>
         <v>73611.7</v>
       </c>
       <c r="AJ6" s="26">
-        <f>IF(DGSUomWIWoQPlImp!$C$2=3,0,AG6+AH6)</f>
+        <f>IF($C$2=3,0,AG6+AH6)</f>
         <v>0</v>
       </c>
       <c r="AK6" s="26">
-        <f>IF(DGSUomWIWoQPlImp!$C$2=3,AE6+AG6+AH6,0)</f>
+        <f>IF($C$2=3,AE6+AG6+AH6,0)</f>
         <v>0</v>
       </c>
       <c r="AL6" s="34">
@@ -18843,7 +18853,7 @@
         <v>127</v>
       </c>
       <c r="AV6" t="s" s="0">
-        <v>132</v>
+        <v>188</v>
       </c>
       <c r="AW6" s="39">
         <f t="shared" si="12"/>
@@ -18858,29 +18868,29 @@
         <v>350</v>
       </c>
       <c r="AZ6" s="39">
-        <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),1)</f>
-        <v>3680.6</v>
-      </c>
-      <c r="BA6" s="44"/>
-      <c r="BB6" s="44" t="s">
+        <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),5)</f>
+        <v>3680.585</v>
+      </c>
+      <c r="BA6" s="43"/>
+      <c r="BB6" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC6" s="45" t="s">
+      <c r="BC6" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD6" s="46" t="s">
+      <c r="BD6" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE6" s="46" t="s">
+      <c r="BE6" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF6" s="44"/>
-      <c r="BG6" s="44"/>
-      <c r="BH6" s="44"/>
+      <c r="BF6" s="43"/>
+      <c r="BG6" s="43"/>
+      <c r="BH6" s="43"/>
       <c r="BI6" s="39"/>
       <c r="BJ6" s="39"/>
       <c r="BK6" s="39"/>
-      <c r="BL6" s="47" t="s">
+      <c r="BL6" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM6" t="s" s="0">
@@ -18891,13 +18901,13 @@
       </c>
       <c r="BO6" s="39">
         <f t="shared" si="15"/>
-        <v>270.63125</v>
-      </c>
-      <c r="BP6" s="48">
+        <v>270.63031</v>
+      </c>
+      <c r="BP6" s="47">
         <f t="shared" si="16"/>
         <v>320</v>
       </c>
-      <c r="BQ6" s="49">
+      <c r="BQ6" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -20461,10 +20471,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>77</v>
@@ -20621,10 +20631,10 @@
         <v>77</v>
       </c>
       <c r="AU4" t="s" s="0">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="AV4" t="s" s="0">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="AW4" s="39">
         <f t="shared" ref="AW4:AW6" si="12">AM4</f>
@@ -20642,26 +20652,26 @@
         <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),5)</f>
         <v>12245.10105</v>
       </c>
-      <c r="BA4" s="44"/>
-      <c r="BB4" s="44" t="s">
+      <c r="BA4" s="43"/>
+      <c r="BB4" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC4" s="45" t="s">
+      <c r="BC4" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD4" s="46" t="s">
+      <c r="BD4" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE4" s="46" t="s">
+      <c r="BE4" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF4" s="44"/>
-      <c r="BG4" s="44"/>
-      <c r="BH4" s="44"/>
+      <c r="BF4" s="43"/>
+      <c r="BG4" s="43"/>
+      <c r="BH4" s="43"/>
       <c r="BI4" s="39"/>
       <c r="BJ4" s="39"/>
       <c r="BK4" s="39"/>
-      <c r="BL4" s="47" t="s">
+      <c r="BL4" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM4" t="s" s="0">
@@ -20674,11 +20684,11 @@
         <f t="shared" ref="BO4:BO6" si="15">ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
         <v>274.18149</v>
       </c>
-      <c r="BP4" s="48">
+      <c r="BP4" s="47">
         <f t="shared" ref="BP4:BP6" si="16">ROUND(BN4+AW4,3)</f>
         <v>81</v>
       </c>
-      <c r="BQ4" s="49">
+      <c r="BQ4" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -20687,10 +20697,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>77</v>
@@ -20847,10 +20857,10 @@
         <v>77</v>
       </c>
       <c r="AU5" t="s" s="0">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="AV5" t="s" s="0">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="AW5" s="39">
         <f t="shared" si="12"/>
@@ -20868,26 +20878,26 @@
         <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),5)</f>
         <v>7343.35048</v>
       </c>
-      <c r="BA5" s="44"/>
-      <c r="BB5" s="44" t="s">
+      <c r="BA5" s="43"/>
+      <c r="BB5" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC5" s="45" t="s">
+      <c r="BC5" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD5" s="46" t="s">
+      <c r="BD5" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE5" s="46" t="s">
+      <c r="BE5" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF5" s="44"/>
-      <c r="BG5" s="44"/>
-      <c r="BH5" s="44"/>
+      <c r="BF5" s="43"/>
+      <c r="BG5" s="43"/>
+      <c r="BH5" s="43"/>
       <c r="BI5" s="39"/>
       <c r="BJ5" s="39"/>
       <c r="BK5" s="39"/>
-      <c r="BL5" s="47" t="s">
+      <c r="BL5" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM5" t="s" s="0">
@@ -20900,11 +20910,11 @@
         <f t="shared" si="15"/>
         <v>427.89288</v>
       </c>
-      <c r="BP5" s="48">
+      <c r="BP5" s="47">
         <f t="shared" si="16"/>
         <v>63</v>
       </c>
-      <c r="BQ5" s="49">
+      <c r="BQ5" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -20913,10 +20923,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>77</v>
@@ -21073,10 +21083,10 @@
         <v>77</v>
       </c>
       <c r="AU6" t="s" s="0">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="AV6" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="AW6" s="39">
         <f t="shared" si="12"/>
@@ -21094,26 +21104,26 @@
         <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),5)</f>
         <v>4979.68333</v>
       </c>
-      <c r="BA6" s="44"/>
-      <c r="BB6" s="44" t="s">
+      <c r="BA6" s="43"/>
+      <c r="BB6" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC6" s="45" t="s">
+      <c r="BC6" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD6" s="46" t="s">
+      <c r="BD6" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE6" s="46" t="s">
+      <c r="BE6" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF6" s="44"/>
-      <c r="BG6" s="44"/>
-      <c r="BH6" s="44"/>
+      <c r="BF6" s="43"/>
+      <c r="BG6" s="43"/>
+      <c r="BH6" s="43"/>
       <c r="BI6" s="39"/>
       <c r="BJ6" s="39"/>
       <c r="BK6" s="39"/>
-      <c r="BL6" s="47" t="s">
+      <c r="BL6" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM6" t="s" s="0">
@@ -21126,11 +21136,11 @@
         <f t="shared" si="15"/>
         <v>108.25241</v>
       </c>
-      <c r="BP6" s="48">
+      <c r="BP6" s="47">
         <f t="shared" si="16"/>
         <v>304</v>
       </c>
-      <c r="BQ6" s="49">
+      <c r="BQ6" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -22305,7 +22315,10 @@
     <col min="3" max="3" customWidth="true" width="29.447619047619"/>
     <col min="13" max="13" customWidth="true" width="9.14285714285714"/>
     <col min="14" max="14" customWidth="true" width="13.847619047619"/>
+    <col min="35" max="35" width="11.4285714285714"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
     <col min="64" max="64" customWidth="true" width="11.0"/>
+    <col min="67" max="67" width="12.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -22690,10 +22703,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>77</v>
@@ -22704,15 +22717,15 @@
       <c r="F4" s="8">
         <v>5</v>
       </c>
-      <c r="G4" s="0">
-        <v>50</v>
+      <c r="G4" t="s" s="0">
+        <v>100</v>
       </c>
       <c r="H4" s="8">
         <f t="shared" ref="H4:H6" si="0">F4*G4</f>
         <v>250</v>
       </c>
-      <c r="I4" s="0">
-        <v>0</v>
+      <c r="I4" t="s" s="0">
+        <v>127</v>
       </c>
       <c r="J4" s="8">
         <v>8</v>
@@ -22850,10 +22863,10 @@
         <v>77</v>
       </c>
       <c r="AU4" t="s" s="0">
-        <v>206</v>
+        <v>127</v>
       </c>
       <c r="AV4" t="s" s="0">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="AW4" s="39">
         <f t="shared" ref="AW4:AW6" si="12">AM4</f>
@@ -22867,30 +22880,30 @@
         <f t="shared" ref="AY4:AY6" si="14">AU4+AW4</f>
         <v>64.9946666666667</v>
       </c>
-      <c r="AZ4" s="43">
-        <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),3)</f>
-        <v>11916.621</v>
-      </c>
-      <c r="BA4" s="44"/>
-      <c r="BB4" s="44" t="s">
+      <c r="AZ4" s="39">
+        <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),5)</f>
+        <v>11916.62101</v>
+      </c>
+      <c r="BA4" s="43"/>
+      <c r="BB4" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC4" s="45" t="s">
+      <c r="BC4" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD4" s="46" t="s">
+      <c r="BD4" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE4" s="46" t="s">
+      <c r="BE4" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF4" s="44"/>
-      <c r="BG4" s="44"/>
-      <c r="BH4" s="44"/>
+      <c r="BF4" s="43"/>
+      <c r="BG4" s="43"/>
+      <c r="BH4" s="43"/>
       <c r="BI4" s="39"/>
       <c r="BJ4" s="39"/>
       <c r="BK4" s="39"/>
-      <c r="BL4" s="47" t="s">
+      <c r="BL4" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM4" t="s" s="0">
@@ -22903,11 +22916,11 @@
         <f t="shared" ref="BO4:BO6" si="15">ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
         <v>365.19961</v>
       </c>
-      <c r="BP4" s="48">
+      <c r="BP4" s="47">
         <f t="shared" ref="BP4:BP6" si="16">ROUND(BN4+AW4,3)</f>
         <v>81.667</v>
       </c>
-      <c r="BQ4" s="49">
+      <c r="BQ4" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -22916,10 +22929,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>77</v>
@@ -22938,7 +22951,7 @@
         <v>400</v>
       </c>
       <c r="I5" t="s" s="0">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="J5" s="8">
         <v>9</v>
@@ -22985,26 +22998,26 @@
         <v>18</v>
       </c>
       <c r="V5" s="8">
-        <f>IF(OR(DGDUomWoQWIPlImp!$C$2=1,DGDUomWoQWIPlImp!$C$2=4),ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF(OR($C$2=1,$C$2=4),ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="W5" s="8">
-        <f>IF(DGDUomWoQWIPlImp!$C$2=1,ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF($C$2=1,ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="X5" s="8">
-        <f>IF(DGDUomWoQWIPlImp!$C$2=2,ROUND(((S5*U5)/100),2),0)</f>
+        <f>IF($C$2=2,ROUND(((S5*U5)/100),2),0)</f>
         <v>0</v>
       </c>
       <c r="Y5" s="8">
-        <f>IF(DGDUomWoQWIPlImp!$C$2=4,ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF($C$2=4,ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="Z5" s="8">
         <v>0</v>
       </c>
       <c r="AA5" s="8">
-        <f>IF(DGDUomWoQWIPlImp!$C3=3,0,(S5*Z5)/100)</f>
+        <f>IF($C3=3,0,(S5*Z5)/100)</f>
         <v>0</v>
       </c>
       <c r="AB5" s="8">
@@ -23012,35 +23025,35 @@
         <v>0</v>
       </c>
       <c r="AC5" s="8">
-        <f>IF(DGDUomWoQWIPlImp!$V3=1,S5+AB5,S5)</f>
+        <f>IF($V3=1,S5+AB5,S5)</f>
         <v>328.47</v>
       </c>
       <c r="AD5" s="26">
         <v>120</v>
       </c>
       <c r="AE5" s="26">
-        <f>IF(DGDUomWoQWIPlImp!$P$2=1,(S5/DGDUomWoQWIPlImp!$S$7)*DGDUomWoQWIPlImp!$E$18,AD5/DGDUomWoQWIPlImp!$AD$7*DGDUomWoQWIPlImp!$E$18)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$18,AD5/$AD$7*$E$18)</f>
         <v>0</v>
       </c>
       <c r="AF5" s="26"/>
       <c r="AG5" s="26">
-        <f>IF(DGDUomWoQWIPlImp!$P$2=1,(S5/DGDUomWoQWIPlImp!$S$7)*DGDUomWoQWIPlImp!$E$20,AD5/DGDUomWoQWIPlImp!$AD$7*DGDUomWoQWIPlImp!$E$20)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$20,AD5/$AD$7*$E$20)</f>
         <v>0</v>
       </c>
       <c r="AH5" s="26">
-        <f>IF(DGDUomWoQWIPlImp!$P$2=1,(S5/DGDUomWoQWIPlImp!$S$7)*DGDUomWoQWIPlImp!$E$21,AD5/DGDUomWoQWIPlImp!$AD$7*DGDUomWoQWIPlImp!$E$21)</f>
+        <f>IF($P$2=1,(S5/$S$7)*$E$21,AD5/$AD$7*$E$21)</f>
         <v>0</v>
       </c>
       <c r="AI5" s="26">
-        <f>S5*DGDUomWoQWIPlImp!$M$2</f>
+        <f>S5*$M$2</f>
         <v>27919.95</v>
       </c>
       <c r="AJ5" s="26">
-        <f>IF(DGDUomWoQWIPlImp!$C$2=3,0,AG5+AH5)</f>
+        <f>IF($C$2=3,0,AG5+AH5)</f>
         <v>0</v>
       </c>
       <c r="AK5" s="26">
-        <f>IF(DGDUomWoQWIPlImp!$C$2=3,AE5+AG5+AH5,0)</f>
+        <f>IF($C$2=3,AE5+AG5+AH5,0)</f>
         <v>0</v>
       </c>
       <c r="AL5" s="34">
@@ -23076,10 +23089,10 @@
         <v>77</v>
       </c>
       <c r="AU5" t="s" s="0">
-        <v>209</v>
+        <v>127</v>
       </c>
       <c r="AV5" t="s" s="0">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="AW5" s="39">
         <f t="shared" si="12"/>
@@ -23093,30 +23106,30 @@
         <f t="shared" si="14"/>
         <v>102.332333333333</v>
       </c>
-      <c r="AZ5" s="42">
-        <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),2)</f>
-        <v>7121.89</v>
-      </c>
-      <c r="BA5" s="44"/>
-      <c r="BB5" s="44" t="s">
+      <c r="AZ5" s="39">
+        <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),5)</f>
+        <v>7121.89474</v>
+      </c>
+      <c r="BA5" s="43"/>
+      <c r="BB5" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC5" s="45" t="s">
+      <c r="BC5" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD5" s="46" t="s">
+      <c r="BD5" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE5" s="46" t="s">
+      <c r="BE5" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF5" s="44"/>
-      <c r="BG5" s="44"/>
-      <c r="BH5" s="44"/>
+      <c r="BF5" s="43"/>
+      <c r="BG5" s="43"/>
+      <c r="BH5" s="43"/>
       <c r="BI5" s="39"/>
       <c r="BJ5" s="39"/>
       <c r="BK5" s="39"/>
-      <c r="BL5" s="47" t="s">
+      <c r="BL5" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM5" t="s" s="0">
@@ -23127,13 +23140,13 @@
       </c>
       <c r="BO5" s="39">
         <f t="shared" si="15"/>
-        <v>235.15848</v>
-      </c>
-      <c r="BP5" s="48">
+        <v>235.15858</v>
+      </c>
+      <c r="BP5" s="47">
         <f t="shared" si="16"/>
         <v>61.333</v>
       </c>
-      <c r="BQ5" s="49">
+      <c r="BQ5" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -23142,10 +23155,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>77</v>
@@ -23164,7 +23177,7 @@
         <v>1000</v>
       </c>
       <c r="I6" t="s" s="0">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="J6" s="8">
         <v>7</v>
@@ -23211,26 +23224,26 @@
         <v>18</v>
       </c>
       <c r="V6" s="8">
-        <f>IF(OR(DGDUomWoQWIPlImp!$C$2=1,DGDUomWoQWIPlImp!$C$2=4),ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF(OR($C$2=1,$C$2=4),ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="W6" s="8">
-        <f>IF(DGDUomWoQWIPlImp!$C$2=1,ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF($C$2=1,ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="X6" s="8">
-        <f>IF(DGDUomWoQWIPlImp!$C$2=2,ROUND(((S6*U6)/100),2),0)</f>
+        <f>IF($C$2=2,ROUND(((S6*U6)/100),2),0)</f>
         <v>0</v>
       </c>
       <c r="Y6" s="8">
-        <f>IF(DGDUomWoQWIPlImp!$C$2=4,ROUND((((S6*U6)/100)/2),2),0)</f>
+        <f>IF($C$2=4,ROUND((((S6*U6)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="Z6" s="8">
         <v>0</v>
       </c>
       <c r="AA6" s="8">
-        <f>IF(DGDUomWoQWIPlImp!$C4=3,0,(S6*Z6)/100)</f>
+        <f>IF($C4=3,0,(S6*Z6)/100)</f>
         <v>0</v>
       </c>
       <c r="AB6" s="8">
@@ -23238,35 +23251,35 @@
         <v>0</v>
       </c>
       <c r="AC6" s="8">
-        <f>IF(DGDUomWoQWIPlImp!$V4=1,S6+AB6,S6)</f>
+        <f>IF($V4=1,S6+AB6,S6)</f>
         <v>866.02</v>
       </c>
       <c r="AD6" s="26">
         <v>120</v>
       </c>
       <c r="AE6" s="26">
-        <f>IF(DGDUomWoQWIPlImp!$P$2=1,(S6/DGDUomWoQWIPlImp!$S$7)*DGDUomWoQWIPlImp!$E$18,AD6/DGDUomWoQWIPlImp!$AD$7*DGDUomWoQWIPlImp!$E$18)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$18,AD6/$AD$7*$E$18)</f>
         <v>0</v>
       </c>
       <c r="AF6" s="26"/>
       <c r="AG6" s="26">
-        <f>IF(DGDUomWoQWIPlImp!$P$2=1,(S6/DGDUomWoQWIPlImp!$S$7)*DGDUomWoQWIPlImp!$E$20,AD6/DGDUomWoQWIPlImp!$AD$7*DGDUomWoQWIPlImp!$E$20)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$20,AD6/$AD$7*$E$20)</f>
         <v>0</v>
       </c>
       <c r="AH6" s="26">
-        <f>IF(DGDUomWoQWIPlImp!$P$2=1,(S6/DGDUomWoQWIPlImp!$S$7)*DGDUomWoQWIPlImp!$E$21,AD6/DGDUomWoQWIPlImp!$AD$7*DGDUomWoQWIPlImp!$E$21)</f>
+        <f>IF($P$2=1,(S6/$S$7)*$E$21,AD6/$AD$7*$E$21)</f>
         <v>0</v>
       </c>
       <c r="AI6" s="26">
-        <f>S6*DGDUomWoQWIPlImp!$M$2</f>
+        <f>S6*$M$2</f>
         <v>73611.7</v>
       </c>
       <c r="AJ6" s="26">
-        <f>IF(DGDUomWoQWIPlImp!$C$2=3,0,AG6+AH6)</f>
+        <f>IF($C$2=3,0,AG6+AH6)</f>
         <v>0</v>
       </c>
       <c r="AK6" s="26">
-        <f>IF(DGDUomWoQWIPlImp!$C$2=3,AE6+AG6+AH6,0)</f>
+        <f>IF($C$2=3,AE6+AG6+AH6,0)</f>
         <v>0</v>
       </c>
       <c r="AL6" s="34">
@@ -23302,10 +23315,10 @@
         <v>77</v>
       </c>
       <c r="AU6" t="s" s="0">
-        <v>212</v>
+        <v>127</v>
       </c>
       <c r="AV6" t="s" s="0">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="AW6" s="39">
         <f t="shared" si="12"/>
@@ -23320,29 +23333,29 @@
         <v>86.6606666666667</v>
       </c>
       <c r="AZ6" s="39">
-        <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),1)</f>
-        <v>5166.2</v>
-      </c>
-      <c r="BA6" s="44"/>
-      <c r="BB6" s="44" t="s">
+        <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),5)</f>
+        <v>5166.22349</v>
+      </c>
+      <c r="BA6" s="43"/>
+      <c r="BB6" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC6" s="45" t="s">
+      <c r="BC6" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD6" s="46" t="s">
+      <c r="BD6" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE6" s="46" t="s">
+      <c r="BE6" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF6" s="44"/>
-      <c r="BG6" s="44"/>
-      <c r="BH6" s="44"/>
+      <c r="BF6" s="43"/>
+      <c r="BG6" s="43"/>
+      <c r="BH6" s="43"/>
       <c r="BI6" s="39"/>
       <c r="BJ6" s="39"/>
       <c r="BK6" s="39"/>
-      <c r="BL6" s="47" t="s">
+      <c r="BL6" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM6" t="s" s="0">
@@ -23353,13 +23366,13 @@
       </c>
       <c r="BO6" s="39">
         <f t="shared" si="15"/>
-        <v>154.66739</v>
-      </c>
-      <c r="BP6" s="48">
+        <v>154.6679</v>
+      </c>
+      <c r="BP6" s="47">
         <f t="shared" si="16"/>
         <v>306.667</v>
       </c>
-      <c r="BQ6" s="49">
+      <c r="BQ6" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -25104,26 +25117,26 @@
         <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),5)</f>
         <v>10586.18333</v>
       </c>
-      <c r="BA4" s="44"/>
-      <c r="BB4" s="44" t="s">
+      <c r="BA4" s="43"/>
+      <c r="BB4" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC4" s="45" t="s">
+      <c r="BC4" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD4" s="46" t="s">
+      <c r="BD4" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE4" s="46" t="s">
+      <c r="BE4" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF4" s="44"/>
-      <c r="BG4" s="44"/>
-      <c r="BH4" s="44"/>
+      <c r="BF4" s="43"/>
+      <c r="BG4" s="43"/>
+      <c r="BH4" s="43"/>
       <c r="BI4" s="39"/>
       <c r="BJ4" s="39"/>
       <c r="BK4" s="39"/>
-      <c r="BL4" s="47" t="s">
+      <c r="BL4" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM4" t="s" s="0">
@@ -25136,11 +25149,11 @@
         <f t="shared" ref="BO4:BO6" si="15">ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
         <v>502.67651</v>
       </c>
-      <c r="BP4" s="48">
+      <c r="BP4" s="47">
         <f t="shared" ref="BP4:BP6" si="16">ROUND(BN4+AW4,3)</f>
         <v>83</v>
       </c>
-      <c r="BQ4" s="49">
+      <c r="BQ4" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -25330,26 +25343,26 @@
         <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),5)</f>
         <v>6980.10556</v>
       </c>
-      <c r="BA5" s="44"/>
-      <c r="BB5" s="44" t="s">
+      <c r="BA5" s="43"/>
+      <c r="BB5" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC5" s="45" t="s">
+      <c r="BC5" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD5" s="46" t="s">
+      <c r="BD5" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE5" s="46" t="s">
+      <c r="BE5" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF5" s="44"/>
-      <c r="BG5" s="44"/>
-      <c r="BH5" s="44"/>
+      <c r="BF5" s="43"/>
+      <c r="BG5" s="43"/>
+      <c r="BH5" s="43"/>
       <c r="BI5" s="39"/>
       <c r="BJ5" s="39"/>
       <c r="BK5" s="39"/>
-      <c r="BL5" s="47" t="s">
+      <c r="BL5" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM5" t="s" s="0">
@@ -25362,11 +25375,11 @@
         <f t="shared" si="15"/>
         <v>981.85725</v>
       </c>
-      <c r="BP5" s="48">
+      <c r="BP5" s="47">
         <f t="shared" si="16"/>
         <v>69</v>
       </c>
-      <c r="BQ5" s="49">
+      <c r="BQ5" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -25556,26 +25569,26 @@
         <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),5)</f>
         <v>3680.57083</v>
       </c>
-      <c r="BA6" s="44"/>
-      <c r="BB6" s="44" t="s">
+      <c r="BA6" s="43"/>
+      <c r="BB6" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC6" s="45" t="s">
+      <c r="BC6" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD6" s="46" t="s">
+      <c r="BD6" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE6" s="46" t="s">
+      <c r="BE6" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF6" s="44"/>
-      <c r="BG6" s="44"/>
-      <c r="BH6" s="44"/>
+      <c r="BF6" s="43"/>
+      <c r="BG6" s="43"/>
+      <c r="BH6" s="43"/>
       <c r="BI6" s="39"/>
       <c r="BJ6" s="39"/>
       <c r="BK6" s="39"/>
-      <c r="BL6" s="47" t="s">
+      <c r="BL6" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM6" t="s" s="0">
@@ -25588,11 +25601,11 @@
         <f t="shared" si="15"/>
         <v>183.19503</v>
       </c>
-      <c r="BP6" s="48">
+      <c r="BP6" s="47">
         <f t="shared" si="16"/>
         <v>312</v>
       </c>
-      <c r="BQ6" s="49">
+      <c r="BQ6" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -27337,26 +27350,26 @@
         <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),5)</f>
         <v>13767.68826</v>
       </c>
-      <c r="BA4" s="44"/>
-      <c r="BB4" s="44" t="s">
+      <c r="BA4" s="43"/>
+      <c r="BB4" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC4" s="45" t="s">
+      <c r="BC4" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD4" s="46" t="s">
+      <c r="BD4" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE4" s="46" t="s">
+      <c r="BE4" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF4" s="44"/>
-      <c r="BG4" s="44"/>
-      <c r="BH4" s="44"/>
+      <c r="BF4" s="43"/>
+      <c r="BG4" s="43"/>
+      <c r="BH4" s="43"/>
       <c r="BI4" s="39"/>
       <c r="BJ4" s="39"/>
       <c r="BK4" s="39"/>
-      <c r="BL4" s="47" t="s">
+      <c r="BL4" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM4" t="s" s="0">
@@ -27369,11 +27382,11 @@
         <f t="shared" ref="BO4:BO6" si="15">ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
         <v>774.21849</v>
       </c>
-      <c r="BP4" s="48">
+      <c r="BP4" s="47">
         <f t="shared" ref="BP4:BP6" si="16">ROUND(BN4+AW4,3)</f>
         <v>84</v>
       </c>
-      <c r="BQ4" s="49">
+      <c r="BQ4" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -27563,26 +27576,26 @@
         <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),5)</f>
         <v>8116.13607</v>
       </c>
-      <c r="BA5" s="44"/>
-      <c r="BB5" s="44" t="s">
+      <c r="BA5" s="43"/>
+      <c r="BB5" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC5" s="45" t="s">
+      <c r="BC5" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD5" s="46" t="s">
+      <c r="BD5" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE5" s="46" t="s">
+      <c r="BE5" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF5" s="44"/>
-      <c r="BG5" s="44"/>
-      <c r="BH5" s="44"/>
+      <c r="BF5" s="43"/>
+      <c r="BG5" s="43"/>
+      <c r="BH5" s="43"/>
       <c r="BI5" s="39"/>
       <c r="BJ5" s="39"/>
       <c r="BK5" s="39"/>
-      <c r="BL5" s="47" t="s">
+      <c r="BL5" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM5" t="s" s="0">
@@ -27595,11 +27608,11 @@
         <f t="shared" si="15"/>
         <v>213.82518</v>
       </c>
-      <c r="BP5" s="48">
+      <c r="BP5" s="47">
         <f t="shared" si="16"/>
         <v>61</v>
       </c>
-      <c r="BQ5" s="49">
+      <c r="BQ5" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -27789,26 +27802,26 @@
         <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),5)</f>
         <v>4690.96439</v>
       </c>
-      <c r="BA6" s="44"/>
-      <c r="BB6" s="44" t="s">
+      <c r="BA6" s="43"/>
+      <c r="BB6" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC6" s="45" t="s">
+      <c r="BC6" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD6" s="46" t="s">
+      <c r="BD6" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE6" s="46" t="s">
+      <c r="BE6" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF6" s="44"/>
-      <c r="BG6" s="44"/>
-      <c r="BH6" s="44"/>
+      <c r="BF6" s="43"/>
+      <c r="BG6" s="43"/>
+      <c r="BH6" s="43"/>
       <c r="BI6" s="39"/>
       <c r="BJ6" s="39"/>
       <c r="BK6" s="39"/>
-      <c r="BL6" s="47" t="s">
+      <c r="BL6" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM6" t="s" s="0">
@@ -27821,11 +27834,11 @@
         <f t="shared" si="15"/>
         <v>89.31648</v>
       </c>
-      <c r="BP6" s="48">
+      <c r="BP6" s="47">
         <f t="shared" si="16"/>
         <v>303</v>
       </c>
-      <c r="BQ6" s="49">
+      <c r="BQ6" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -29573,30 +29586,30 @@
         <f>AU4+AW4</f>
         <v>49.9956666666667</v>
       </c>
-      <c r="AZ4" s="43">
-        <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),3)</f>
-        <v>12928.014</v>
-      </c>
-      <c r="BA4" s="44"/>
-      <c r="BB4" s="44" t="s">
+      <c r="AZ4" s="39">
+        <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),5)</f>
+        <v>31758.72</v>
+      </c>
+      <c r="BA4" s="43"/>
+      <c r="BB4" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC4" s="45" t="s">
+      <c r="BC4" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD4" s="46" t="s">
+      <c r="BD4" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE4" s="46" t="s">
+      <c r="BE4" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF4" s="44"/>
-      <c r="BG4" s="44"/>
-      <c r="BH4" s="44"/>
+      <c r="BF4" s="43"/>
+      <c r="BG4" s="43"/>
+      <c r="BH4" s="43"/>
       <c r="BI4" s="39"/>
       <c r="BJ4" s="39"/>
       <c r="BK4" s="39"/>
-      <c r="BL4" s="47" t="s">
+      <c r="BL4" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM4" t="s" s="0">
@@ -29607,13 +29620,13 @@
       </c>
       <c r="BO4" s="39">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
-        <v>385.84029</v>
-      </c>
-      <c r="BP4" s="48">
+        <v>770.14041</v>
+      </c>
+      <c r="BP4" s="47">
         <f>ROUND(BN4+AW4,3)</f>
         <v>81.667</v>
       </c>
-      <c r="BQ4" s="49">
+      <c r="BQ4" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -29691,26 +29704,26 @@
         <v>18</v>
       </c>
       <c r="V5" s="8">
-        <f>IF(OR(DGDUomWoQWI!$C$2=1,DGDUomWoQWI!$C$2=4),ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF(OR($C$2=1,$C$2=4),ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="W5" s="8">
-        <f>IF(DGDUomWoQWI!$C$2=1,ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF($C$2=1,ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="X5" s="8">
-        <f>IF(DGDUomWoQWI!$C$2=2,ROUND(((S5*U5)/100),2),0)</f>
+        <f>IF($C$2=2,ROUND(((S5*U5)/100),2),0)</f>
         <v>0</v>
       </c>
       <c r="Y5" s="8">
-        <f>IF(DGDUomWoQWI!$C$2=4,ROUND((((S5*U5)/100)/2),2),0)</f>
+        <f>IF($C$2=4,ROUND((((S5*U5)/100)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="Z5" s="8">
         <v>0</v>
       </c>
       <c r="AA5" s="8">
-        <f>IF(DGDUomWoQWI!$C3=3,0,(S5*Z5)/100)</f>
+        <f>IF($C3=3,0,(S5*Z5)/100)</f>
         <v>0</v>
       </c>
       <c r="AB5" s="8">
@@ -29718,35 +29731,35 @@
         <v>0</v>
       </c>
       <c r="AC5" s="8">
-        <f>IF(DGDUomWoQWI!$V3=1,S5+AB5,S5)</f>
+        <f>IF($V3=1,S5+AB5,S5)</f>
         <v>328.47</v>
       </c>
       <c r="AD5" s="26">
         <v>120</v>
       </c>
       <c r="AE5" s="26">
-        <f>IF(DGDUomWoQWI!$P$2=1,(S5/DGDUomWoQWI!$S$6)*DGDUomWoQWI!$E$17,AD5/DGDUomWoQWI!$AD$6*DGDUomWoQWI!$E$17)</f>
+        <f>IF($P$2=1,(S5/$S$6)*$E$17,AD5/$AD$6*$E$17)</f>
         <v>0</v>
       </c>
       <c r="AF5" s="26"/>
       <c r="AG5" s="26">
-        <f>IF(DGDUomWoQWI!$P$2=1,(S5/DGDUomWoQWI!$S$6)*DGDUomWoQWI!$E$19,AD5/DGDUomWoQWI!$AD$6*DGDUomWoQWI!$E$19)</f>
+        <f>IF($P$2=1,(S5/$S$6)*$E$19,AD5/$AD$6*$E$19)</f>
         <v>0</v>
       </c>
       <c r="AH5" s="26">
-        <f>IF(DGDUomWoQWI!$P$2=1,(S5/DGDUomWoQWI!$S$6)*DGDUomWoQWI!$E$20,AD5/DGDUomWoQWI!$AD$6*DGDUomWoQWI!$E$20)</f>
+        <f>IF($P$2=1,(S5/$S$6)*$E$20,AD5/$AD$6*$E$20)</f>
         <v>0</v>
       </c>
       <c r="AI5" s="26">
-        <f>S5*DGDUomWoQWI!$M$2</f>
+        <f>S5*$M$2</f>
         <v>27919.95</v>
       </c>
       <c r="AJ5" s="26">
-        <f>IF(DGDUomWoQWI!$C$2=3,0,AG5+AH5)</f>
+        <f>IF($C$2=3,0,AG5+AH5)</f>
         <v>0</v>
       </c>
       <c r="AK5" s="26">
-        <f>IF(DGDUomWoQWI!$C$2=3,AE5+AG5+AH5,0)</f>
+        <f>IF($C$2=3,AE5+AG5+AH5,0)</f>
         <v>0</v>
       </c>
       <c r="AL5" s="34">
@@ -29799,30 +29812,30 @@
         <f>AU5+AW5</f>
         <v>23.9943333333333</v>
       </c>
-      <c r="AZ5" s="42">
-        <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),2)</f>
-        <v>8294.26</v>
-      </c>
-      <c r="BA5" s="44"/>
-      <c r="BB5" s="44" t="s">
+      <c r="AZ5" s="39">
+        <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),5)</f>
+        <v>20939.9625</v>
+      </c>
+      <c r="BA5" s="43"/>
+      <c r="BB5" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC5" s="45" t="s">
+      <c r="BC5" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD5" s="46" t="s">
+      <c r="BD5" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE5" s="46" t="s">
+      <c r="BE5" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF5" s="44"/>
-      <c r="BG5" s="44"/>
-      <c r="BH5" s="44"/>
+      <c r="BF5" s="43"/>
+      <c r="BG5" s="43"/>
+      <c r="BH5" s="43"/>
       <c r="BI5" s="39"/>
       <c r="BJ5" s="39"/>
       <c r="BK5" s="39"/>
-      <c r="BL5" s="47" t="s">
+      <c r="BL5" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM5" t="s" s="0">
@@ -29833,13 +29846,13 @@
       </c>
       <c r="BO5" s="39">
         <f>ROUND((((AW5*AZ5)+(BN5*BM5))/(AW5+BN5)),5)</f>
-        <v>260.64478</v>
-      </c>
-      <c r="BP5" s="48">
+        <v>535.55136</v>
+      </c>
+      <c r="BP5" s="47">
         <f>ROUND(BN5+AW5,3)</f>
         <v>61.333</v>
       </c>
-      <c r="BQ5" s="49">
+      <c r="BQ5" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -31562,10 +31575,10 @@
         <v>77</v>
       </c>
       <c r="AU4" t="s" s="0">
-        <v>81</v>
+        <v>147</v>
       </c>
       <c r="AV4" t="s" s="0">
-        <v>82</v>
+        <v>148</v>
       </c>
       <c r="AW4" s="39">
         <f t="shared" ref="AW4:AW6" si="12">AM4</f>
@@ -31583,26 +31596,26 @@
         <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),5)</f>
         <v>3634.20881</v>
       </c>
-      <c r="BA4" s="44"/>
-      <c r="BB4" s="44" t="s">
+      <c r="BA4" s="43"/>
+      <c r="BB4" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC4" s="45" t="s">
+      <c r="BC4" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD4" s="46" t="s">
+      <c r="BD4" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE4" s="46" t="s">
+      <c r="BE4" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF4" s="44"/>
-      <c r="BG4" s="44"/>
-      <c r="BH4" s="44"/>
+      <c r="BF4" s="43"/>
+      <c r="BG4" s="43"/>
+      <c r="BH4" s="43"/>
       <c r="BI4" s="39"/>
       <c r="BJ4" s="39"/>
       <c r="BK4" s="39"/>
-      <c r="BL4" s="47" t="s">
+      <c r="BL4" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM4" t="s" s="0">
@@ -31615,11 +31628,11 @@
         <f t="shared" ref="BO4:BO6" si="15">ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
         <v>251.40032</v>
       </c>
-      <c r="BP4" s="48">
+      <c r="BP4" s="47">
         <f t="shared" ref="BP4:BP6" si="16">ROUND(BN4+AW4,3)</f>
         <v>83</v>
       </c>
-      <c r="BQ4" s="49">
+      <c r="BQ4" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -31628,10 +31641,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>77</v>
@@ -31788,10 +31801,10 @@
         <v>77</v>
       </c>
       <c r="AU5" t="s" s="0">
-        <v>94</v>
+        <v>150</v>
       </c>
       <c r="AV5" t="s" s="0">
-        <v>95</v>
+        <v>151</v>
       </c>
       <c r="AW5" s="39">
         <f t="shared" si="12"/>
@@ -31809,26 +31822,26 @@
         <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),5)</f>
         <v>2127.49623</v>
       </c>
-      <c r="BA5" s="44"/>
-      <c r="BB5" s="44" t="s">
+      <c r="BA5" s="43"/>
+      <c r="BB5" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC5" s="45" t="s">
+      <c r="BC5" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD5" s="46" t="s">
+      <c r="BD5" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE5" s="46" t="s">
+      <c r="BE5" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF5" s="44"/>
-      <c r="BG5" s="44"/>
-      <c r="BH5" s="44"/>
+      <c r="BF5" s="43"/>
+      <c r="BG5" s="43"/>
+      <c r="BH5" s="43"/>
       <c r="BI5" s="39"/>
       <c r="BJ5" s="39"/>
       <c r="BK5" s="39"/>
-      <c r="BL5" s="47" t="s">
+      <c r="BL5" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM5" t="s" s="0">
@@ -31841,11 +31854,11 @@
         <f t="shared" si="15"/>
         <v>268.06329</v>
       </c>
-      <c r="BP5" s="48">
+      <c r="BP5" s="47">
         <f t="shared" si="16"/>
         <v>66</v>
       </c>
-      <c r="BQ5" s="49">
+      <c r="BQ5" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -31854,10 +31867,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>77</v>
@@ -32014,10 +32027,10 @@
         <v>77</v>
       </c>
       <c r="AU6" t="s" s="0">
-        <v>102</v>
+        <v>153</v>
       </c>
       <c r="AV6" t="s" s="0">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="AW6" s="39">
         <f t="shared" si="12"/>
@@ -32035,26 +32048,26 @@
         <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),5)</f>
         <v>1158.18872</v>
       </c>
-      <c r="BA6" s="44"/>
-      <c r="BB6" s="44" t="s">
+      <c r="BA6" s="43"/>
+      <c r="BB6" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC6" s="45" t="s">
+      <c r="BC6" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD6" s="46" t="s">
+      <c r="BD6" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE6" s="46" t="s">
+      <c r="BE6" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF6" s="44"/>
-      <c r="BG6" s="44"/>
-      <c r="BH6" s="44"/>
+      <c r="BF6" s="43"/>
+      <c r="BG6" s="43"/>
+      <c r="BH6" s="43"/>
       <c r="BI6" s="39"/>
       <c r="BJ6" s="39"/>
       <c r="BK6" s="39"/>
-      <c r="BL6" s="47" t="s">
+      <c r="BL6" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM6" t="s" s="0">
@@ -32067,11 +32080,11 @@
         <f t="shared" si="15"/>
         <v>86.18034</v>
       </c>
-      <c r="BP6" s="48">
+      <c r="BP6" s="47">
         <f t="shared" si="16"/>
         <v>312</v>
       </c>
-      <c r="BQ6" s="49">
+      <c r="BQ6" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -33630,11 +33643,11 @@
       <c r="A4" s="7">
         <v>1</v>
       </c>
-      <c r="B4" s="52" t="s">
-        <v>149</v>
-      </c>
-      <c r="C4" s="52" t="s">
-        <v>149</v>
+      <c r="B4" s="51" t="s">
+        <v>155</v>
+      </c>
+      <c r="C4" s="51" t="s">
+        <v>155</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>77</v>
@@ -33791,10 +33804,10 @@
         <v>77</v>
       </c>
       <c r="AU4" t="s" s="0">
-        <v>81</v>
+        <v>147</v>
       </c>
       <c r="AV4" t="s" s="0">
-        <v>82</v>
+        <v>148</v>
       </c>
       <c r="AW4" s="39">
         <f t="shared" ref="AW4:AW6" si="12">AM4</f>
@@ -33808,30 +33821,30 @@
         <f t="shared" ref="AY4:AY6" si="14">AU4+AW4</f>
         <v>380</v>
       </c>
-      <c r="AZ4" s="43">
+      <c r="AZ4" s="54">
         <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),3)</f>
         <v>3670.799</v>
       </c>
-      <c r="BA4" s="44"/>
-      <c r="BB4" s="44" t="s">
+      <c r="BA4" s="43"/>
+      <c r="BB4" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC4" s="45" t="s">
+      <c r="BC4" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD4" s="46" t="s">
+      <c r="BD4" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE4" s="46" t="s">
+      <c r="BE4" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF4" s="44"/>
-      <c r="BG4" s="44"/>
-      <c r="BH4" s="44"/>
+      <c r="BF4" s="43"/>
+      <c r="BG4" s="43"/>
+      <c r="BH4" s="43"/>
       <c r="BI4" s="39"/>
       <c r="BJ4" s="39"/>
       <c r="BK4" s="39"/>
-      <c r="BL4" s="47" t="s">
+      <c r="BL4" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM4" t="s" s="0">
@@ -33844,11 +33857,11 @@
         <f t="shared" ref="BO4:BO6" si="15">ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
         <v>333.14818</v>
       </c>
-      <c r="BP4" s="48">
+      <c r="BP4" s="47">
         <f t="shared" ref="BP4:BP6" si="16">ROUND(BN4+AW4,3)</f>
         <v>85</v>
       </c>
-      <c r="BQ4" s="49">
+      <c r="BQ4" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -33856,11 +33869,11 @@
       <c r="A5" s="7">
         <v>1</v>
       </c>
-      <c r="B5" s="52" t="s">
-        <v>150</v>
-      </c>
-      <c r="C5" s="53" t="s">
-        <v>150</v>
+      <c r="B5" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="C5" s="52" t="s">
+        <v>156</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>77</v>
@@ -34017,10 +34030,10 @@
         <v>77</v>
       </c>
       <c r="AU5" t="s" s="0">
-        <v>94</v>
+        <v>150</v>
       </c>
       <c r="AV5" t="s" s="0">
-        <v>95</v>
+        <v>151</v>
       </c>
       <c r="AW5" s="39">
         <f t="shared" si="12"/>
@@ -34038,26 +34051,26 @@
         <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),2)</f>
         <v>2076.95</v>
       </c>
-      <c r="BA5" s="44"/>
-      <c r="BB5" s="44" t="s">
+      <c r="BA5" s="43"/>
+      <c r="BB5" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC5" s="45" t="s">
+      <c r="BC5" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD5" s="46" t="s">
+      <c r="BD5" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE5" s="46" t="s">
+      <c r="BE5" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF5" s="44"/>
-      <c r="BG5" s="44"/>
-      <c r="BH5" s="44"/>
+      <c r="BF5" s="43"/>
+      <c r="BG5" s="43"/>
+      <c r="BH5" s="43"/>
       <c r="BI5" s="39"/>
       <c r="BJ5" s="39"/>
       <c r="BK5" s="39"/>
-      <c r="BL5" s="47" t="s">
+      <c r="BL5" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM5" t="s" s="0">
@@ -34070,11 +34083,11 @@
         <f t="shared" si="15"/>
         <v>206.79688</v>
       </c>
-      <c r="BP5" s="48">
+      <c r="BP5" s="47">
         <f t="shared" si="16"/>
         <v>64</v>
       </c>
-      <c r="BQ5" s="49">
+      <c r="BQ5" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -34082,11 +34095,11 @@
       <c r="A6" s="7">
         <v>1</v>
       </c>
-      <c r="B6" s="53" t="s">
-        <v>151</v>
-      </c>
-      <c r="C6" s="53" t="s">
-        <v>151</v>
+      <c r="B6" s="52" t="s">
+        <v>157</v>
+      </c>
+      <c r="C6" s="52" t="s">
+        <v>157</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>77</v>
@@ -34243,10 +34256,10 @@
         <v>77</v>
       </c>
       <c r="AU6" t="s" s="0">
-        <v>102</v>
+        <v>153</v>
       </c>
       <c r="AV6" t="s" s="0">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="AW6" s="39">
         <f t="shared" si="12"/>
@@ -34264,26 +34277,26 @@
         <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),1)</f>
         <v>1198.5</v>
       </c>
-      <c r="BA6" s="44"/>
-      <c r="BB6" s="44" t="s">
+      <c r="BA6" s="43"/>
+      <c r="BB6" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC6" s="45" t="s">
+      <c r="BC6" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD6" s="46" t="s">
+      <c r="BD6" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE6" s="46" t="s">
+      <c r="BE6" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF6" s="44"/>
-      <c r="BG6" s="44"/>
-      <c r="BH6" s="44"/>
+      <c r="BF6" s="43"/>
+      <c r="BG6" s="43"/>
+      <c r="BH6" s="43"/>
       <c r="BI6" s="39"/>
       <c r="BJ6" s="39"/>
       <c r="BK6" s="39"/>
-      <c r="BL6" s="47" t="s">
+      <c r="BL6" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM6" t="s" s="0">
@@ -34296,11 +34309,11 @@
         <f t="shared" si="15"/>
         <v>115.5</v>
       </c>
-      <c r="BP6" s="48">
+      <c r="BP6" s="47">
         <f t="shared" si="16"/>
         <v>320</v>
       </c>
-      <c r="BQ6" s="49">
+      <c r="BQ6" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -35859,11 +35872,11 @@
       <c r="A4" s="7">
         <v>1</v>
       </c>
-      <c r="B4" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="C4" s="52" t="s">
-        <v>152</v>
+      <c r="B4" s="51" t="s">
+        <v>158</v>
+      </c>
+      <c r="C4" s="51" t="s">
+        <v>158</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>77</v>
@@ -36020,10 +36033,10 @@
         <v>77</v>
       </c>
       <c r="AU4" t="s" s="0">
-        <v>81</v>
+        <v>147</v>
       </c>
       <c r="AV4" t="s" s="0">
-        <v>82</v>
+        <v>148</v>
       </c>
       <c r="AW4" s="39">
         <f t="shared" ref="AW4:AW6" si="12">AM4</f>
@@ -36037,30 +36050,30 @@
         <f t="shared" ref="AY4:AY6" si="14">AU4+AW4</f>
         <v>380</v>
       </c>
-      <c r="AZ4" s="43">
+      <c r="AZ4" s="54">
         <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),3)</f>
         <v>3580.381</v>
       </c>
-      <c r="BA4" s="44"/>
-      <c r="BB4" s="44" t="s">
+      <c r="BA4" s="43"/>
+      <c r="BB4" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC4" s="45" t="s">
+      <c r="BC4" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD4" s="46" t="s">
+      <c r="BD4" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE4" s="46" t="s">
+      <c r="BE4" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF4" s="44"/>
-      <c r="BG4" s="44"/>
-      <c r="BH4" s="44"/>
+      <c r="BF4" s="43"/>
+      <c r="BG4" s="43"/>
+      <c r="BH4" s="43"/>
       <c r="BI4" s="39"/>
       <c r="BJ4" s="39"/>
       <c r="BK4" s="39"/>
-      <c r="BL4" s="47" t="s">
+      <c r="BL4" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM4" t="s" s="0">
@@ -36073,11 +36086,11 @@
         <f t="shared" ref="BO4:BO6" si="15">ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
         <v>327.82947</v>
       </c>
-      <c r="BP4" s="48">
+      <c r="BP4" s="47">
         <f t="shared" ref="BP4:BP6" si="16">ROUND(BN4+AW4,3)</f>
         <v>85</v>
       </c>
-      <c r="BQ4" s="49">
+      <c r="BQ4" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -36085,11 +36098,11 @@
       <c r="A5" s="7">
         <v>1</v>
       </c>
-      <c r="B5" s="52" t="s">
-        <v>153</v>
-      </c>
-      <c r="C5" s="53" t="s">
-        <v>153</v>
+      <c r="B5" s="51" t="s">
+        <v>159</v>
+      </c>
+      <c r="C5" s="52" t="s">
+        <v>159</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>77</v>
@@ -36246,10 +36259,10 @@
         <v>77</v>
       </c>
       <c r="AU5" t="s" s="0">
-        <v>94</v>
+        <v>150</v>
       </c>
       <c r="AV5" t="s" s="0">
-        <v>95</v>
+        <v>151</v>
       </c>
       <c r="AW5" s="39">
         <f t="shared" si="12"/>
@@ -36267,26 +36280,26 @@
         <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),2)</f>
         <v>2076.95</v>
       </c>
-      <c r="BA5" s="44"/>
-      <c r="BB5" s="44" t="s">
+      <c r="BA5" s="43"/>
+      <c r="BB5" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC5" s="45" t="s">
+      <c r="BC5" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD5" s="46" t="s">
+      <c r="BD5" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE5" s="46" t="s">
+      <c r="BE5" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF5" s="44"/>
-      <c r="BG5" s="44"/>
-      <c r="BH5" s="44"/>
+      <c r="BF5" s="43"/>
+      <c r="BG5" s="43"/>
+      <c r="BH5" s="43"/>
       <c r="BI5" s="39"/>
       <c r="BJ5" s="39"/>
       <c r="BK5" s="39"/>
-      <c r="BL5" s="47" t="s">
+      <c r="BL5" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM5" t="s" s="0">
@@ -36299,11 +36312,11 @@
         <f t="shared" si="15"/>
         <v>206.79688</v>
       </c>
-      <c r="BP5" s="48">
+      <c r="BP5" s="47">
         <f t="shared" si="16"/>
         <v>64</v>
       </c>
-      <c r="BQ5" s="49">
+      <c r="BQ5" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -36311,11 +36324,11 @@
       <c r="A6" s="7">
         <v>1</v>
       </c>
-      <c r="B6" s="53" t="s">
-        <v>154</v>
-      </c>
-      <c r="C6" s="53" t="s">
-        <v>154</v>
+      <c r="B6" s="52" t="s">
+        <v>160</v>
+      </c>
+      <c r="C6" s="52" t="s">
+        <v>160</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>77</v>
@@ -36472,10 +36485,10 @@
         <v>77</v>
       </c>
       <c r="AU6" t="s" s="0">
-        <v>102</v>
+        <v>153</v>
       </c>
       <c r="AV6" t="s" s="0">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="AW6" s="39">
         <f t="shared" si="12"/>
@@ -36493,26 +36506,26 @@
         <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),1)</f>
         <v>1198.5</v>
       </c>
-      <c r="BA6" s="44"/>
-      <c r="BB6" s="44" t="s">
+      <c r="BA6" s="43"/>
+      <c r="BB6" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC6" s="45" t="s">
+      <c r="BC6" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD6" s="46" t="s">
+      <c r="BD6" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE6" s="46" t="s">
+      <c r="BE6" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF6" s="44"/>
-      <c r="BG6" s="44"/>
-      <c r="BH6" s="44"/>
+      <c r="BF6" s="43"/>
+      <c r="BG6" s="43"/>
+      <c r="BH6" s="43"/>
       <c r="BI6" s="39"/>
       <c r="BJ6" s="39"/>
       <c r="BK6" s="39"/>
-      <c r="BL6" s="47" t="s">
+      <c r="BL6" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM6" t="s" s="0">
@@ -36525,11 +36538,11 @@
         <f t="shared" si="15"/>
         <v>115.5</v>
       </c>
-      <c r="BP6" s="48">
+      <c r="BP6" s="47">
         <f t="shared" si="16"/>
         <v>320</v>
       </c>
-      <c r="BQ6" s="49">
+      <c r="BQ6" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -38093,10 +38106,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>77</v>
@@ -38253,10 +38266,10 @@
         <v>77</v>
       </c>
       <c r="AU4" t="s" s="0">
-        <v>81</v>
+        <v>147</v>
       </c>
       <c r="AV4" t="s" s="0">
-        <v>82</v>
+        <v>148</v>
       </c>
       <c r="AW4" s="39">
         <f t="shared" ref="AW4:AW6" si="12">AM4</f>
@@ -38274,26 +38287,26 @@
         <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),5)</f>
         <v>3634.20881</v>
       </c>
-      <c r="BA4" s="44"/>
-      <c r="BB4" s="44" t="s">
+      <c r="BA4" s="43"/>
+      <c r="BB4" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC4" s="45" t="s">
+      <c r="BC4" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD4" s="46" t="s">
+      <c r="BD4" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE4" s="46" t="s">
+      <c r="BE4" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF4" s="44"/>
-      <c r="BG4" s="44"/>
-      <c r="BH4" s="44"/>
+      <c r="BF4" s="43"/>
+      <c r="BG4" s="43"/>
+      <c r="BH4" s="43"/>
       <c r="BI4" s="39"/>
       <c r="BJ4" s="39"/>
       <c r="BK4" s="39"/>
-      <c r="BL4" s="47" t="s">
+      <c r="BL4" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM4" t="s" s="0">
@@ -38306,11 +38319,11 @@
         <f t="shared" ref="BO4:BO6" si="15">ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
         <v>251.40032</v>
       </c>
-      <c r="BP4" s="48">
+      <c r="BP4" s="47">
         <f t="shared" ref="BP4:BP6" si="16">ROUND(BN4+AW4,3)</f>
         <v>83</v>
       </c>
-      <c r="BQ4" s="49">
+      <c r="BQ4" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -38319,10 +38332,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>77</v>
@@ -38479,10 +38492,10 @@
         <v>77</v>
       </c>
       <c r="AU5" t="s" s="0">
-        <v>94</v>
+        <v>150</v>
       </c>
       <c r="AV5" t="s" s="0">
-        <v>95</v>
+        <v>151</v>
       </c>
       <c r="AW5" s="39">
         <f t="shared" si="12"/>
@@ -38500,26 +38513,26 @@
         <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),5)</f>
         <v>2127.49623</v>
       </c>
-      <c r="BA5" s="44"/>
-      <c r="BB5" s="44" t="s">
+      <c r="BA5" s="43"/>
+      <c r="BB5" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC5" s="45" t="s">
+      <c r="BC5" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD5" s="46" t="s">
+      <c r="BD5" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE5" s="46" t="s">
+      <c r="BE5" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF5" s="44"/>
-      <c r="BG5" s="44"/>
-      <c r="BH5" s="44"/>
+      <c r="BF5" s="43"/>
+      <c r="BG5" s="43"/>
+      <c r="BH5" s="43"/>
       <c r="BI5" s="39"/>
       <c r="BJ5" s="39"/>
       <c r="BK5" s="39"/>
-      <c r="BL5" s="47" t="s">
+      <c r="BL5" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM5" t="s" s="0">
@@ -38532,11 +38545,11 @@
         <f t="shared" si="15"/>
         <v>268.06329</v>
       </c>
-      <c r="BP5" s="48">
+      <c r="BP5" s="47">
         <f t="shared" si="16"/>
         <v>66</v>
       </c>
-      <c r="BQ5" s="49">
+      <c r="BQ5" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -38544,11 +38557,11 @@
       <c r="A6" s="7">
         <v>1</v>
       </c>
-      <c r="B6" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="C6" s="51" t="s">
-        <v>157</v>
+      <c r="B6" s="50" t="s">
+        <v>163</v>
+      </c>
+      <c r="C6" s="50" t="s">
+        <v>163</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>77</v>
@@ -38705,10 +38718,10 @@
         <v>77</v>
       </c>
       <c r="AU6" t="s" s="0">
-        <v>102</v>
+        <v>153</v>
       </c>
       <c r="AV6" t="s" s="0">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="AW6" s="39">
         <f t="shared" si="12"/>
@@ -38726,26 +38739,26 @@
         <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),5)</f>
         <v>1142.71268</v>
       </c>
-      <c r="BA6" s="44"/>
-      <c r="BB6" s="44" t="s">
+      <c r="BA6" s="43"/>
+      <c r="BB6" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC6" s="45" t="s">
+      <c r="BC6" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD6" s="46" t="s">
+      <c r="BD6" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE6" s="46" t="s">
+      <c r="BE6" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF6" s="44"/>
-      <c r="BG6" s="44"/>
-      <c r="BH6" s="44"/>
+      <c r="BF6" s="43"/>
+      <c r="BG6" s="43"/>
+      <c r="BH6" s="43"/>
       <c r="BI6" s="39"/>
       <c r="BJ6" s="39"/>
       <c r="BK6" s="39"/>
-      <c r="BL6" s="47" t="s">
+      <c r="BL6" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM6" t="s" s="0">
@@ -38758,11 +38771,11 @@
         <f t="shared" si="15"/>
         <v>75.32173</v>
       </c>
-      <c r="BP6" s="48">
+      <c r="BP6" s="47">
         <f t="shared" si="16"/>
         <v>309</v>
       </c>
-      <c r="BQ6" s="49">
+      <c r="BQ6" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -40325,10 +40338,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>77</v>
@@ -40485,10 +40498,10 @@
         <v>77</v>
       </c>
       <c r="AU4" t="s" s="0">
-        <v>81</v>
+        <v>147</v>
       </c>
       <c r="AV4" t="s" s="0">
-        <v>82</v>
+        <v>148</v>
       </c>
       <c r="AW4" s="39">
         <f t="shared" ref="AW4:AW6" si="11">AM4</f>
@@ -40506,26 +40519,26 @@
         <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),5)</f>
         <v>3579.67164</v>
       </c>
-      <c r="BA4" s="44"/>
-      <c r="BB4" s="44" t="s">
+      <c r="BA4" s="43"/>
+      <c r="BB4" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC4" s="45" t="s">
+      <c r="BC4" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD4" s="46" t="s">
+      <c r="BD4" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE4" s="46" t="s">
+      <c r="BE4" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF4" s="44"/>
-      <c r="BG4" s="44"/>
-      <c r="BH4" s="44"/>
+      <c r="BF4" s="43"/>
+      <c r="BG4" s="43"/>
+      <c r="BH4" s="43"/>
       <c r="BI4" s="39"/>
       <c r="BJ4" s="39"/>
       <c r="BK4" s="39"/>
-      <c r="BL4" s="47" t="s">
+      <c r="BL4" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM4" t="s" s="0">
@@ -40538,11 +40551,11 @@
         <f t="shared" ref="BO4:BO6" si="14">ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
         <v>249.4291</v>
       </c>
-      <c r="BP4" s="48">
+      <c r="BP4" s="47">
         <f t="shared" ref="BP4:BP6" si="15">ROUND(BN4+AW4,3)</f>
         <v>83</v>
       </c>
-      <c r="BQ4" s="49">
+      <c r="BQ4" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -40551,10 +40564,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>77</v>
@@ -40711,10 +40724,10 @@
         <v>77</v>
       </c>
       <c r="AU5" t="s" s="0">
-        <v>94</v>
+        <v>150</v>
       </c>
       <c r="AV5" t="s" s="0">
-        <v>95</v>
+        <v>151</v>
       </c>
       <c r="AW5" s="39">
         <f t="shared" si="11"/>
@@ -40732,26 +40745,26 @@
         <f>ROUND(((AU5*AV5)+(AW5*AX5))/(AU5+AW5),5)</f>
         <v>2273.0731</v>
       </c>
-      <c r="BA5" s="44"/>
-      <c r="BB5" s="44" t="s">
+      <c r="BA5" s="43"/>
+      <c r="BB5" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC5" s="45" t="s">
+      <c r="BC5" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD5" s="46" t="s">
+      <c r="BD5" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE5" s="46" t="s">
+      <c r="BE5" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF5" s="44"/>
-      <c r="BG5" s="44"/>
-      <c r="BH5" s="44"/>
+      <c r="BF5" s="43"/>
+      <c r="BG5" s="43"/>
+      <c r="BH5" s="43"/>
       <c r="BI5" s="39"/>
       <c r="BJ5" s="39"/>
       <c r="BK5" s="39"/>
-      <c r="BL5" s="47" t="s">
+      <c r="BL5" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM5" t="s" s="0">
@@ -40764,11 +40777,11 @@
         <f t="shared" si="14"/>
         <v>447.27885</v>
       </c>
-      <c r="BP5" s="48">
+      <c r="BP5" s="47">
         <f t="shared" si="15"/>
         <v>72</v>
       </c>
-      <c r="BQ5" s="49">
+      <c r="BQ5" s="48">
         <v>123562</v>
       </c>
     </row>
@@ -40776,11 +40789,11 @@
       <c r="A6" s="7">
         <v>1</v>
       </c>
-      <c r="B6" s="50" t="s">
-        <v>160</v>
-      </c>
-      <c r="C6" s="51" t="s">
-        <v>160</v>
+      <c r="B6" s="49" t="s">
+        <v>166</v>
+      </c>
+      <c r="C6" s="50" t="s">
+        <v>166</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>77</v>
@@ -40937,10 +40950,10 @@
         <v>77</v>
       </c>
       <c r="AU6" t="s" s="0">
-        <v>102</v>
+        <v>153</v>
       </c>
       <c r="AV6" t="s" s="0">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="AW6" s="39">
         <f t="shared" si="11"/>
@@ -40958,26 +40971,26 @@
         <f>ROUND(((AU6*AV6)+(AW6*AX6))/(AU6+AW6),5)</f>
         <v>1142.71268</v>
       </c>
-      <c r="BA6" s="44"/>
-      <c r="BB6" s="44" t="s">
+      <c r="BA6" s="43"/>
+      <c r="BB6" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BC6" s="45" t="s">
+      <c r="BC6" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="BD6" s="46" t="s">
+      <c r="BD6" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="BE6" s="46" t="s">
+      <c r="BE6" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="BF6" s="44"/>
-      <c r="BG6" s="44"/>
-      <c r="BH6" s="44"/>
+      <c r="BF6" s="43"/>
+      <c r="BG6" s="43"/>
+      <c r="BH6" s="43"/>
       <c r="BI6" s="39"/>
       <c r="BJ6" s="39"/>
       <c r="BK6" s="39"/>
-      <c r="BL6" s="47" t="s">
+      <c r="BL6" s="46" t="s">
         <v>87</v>
       </c>
       <c r="BM6" t="s" s="0">
@@ -40990,11 +41003,11 @@
         <f t="shared" si="14"/>
         <v>75.32173</v>
       </c>
-      <c r="BP6" s="48">
+      <c r="BP6" s="47">
         <f t="shared" si="15"/>
         <v>309</v>
       </c>
-      <c r="BQ6" s="49">
+      <c r="BQ6" s="48">
         <v>123562</v>
       </c>
     </row>

--- a/testdata/DirectGrn.xlsx
+++ b/testdata/DirectGrn.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2772" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2854" uniqueCount="264">
   <si>
     <t>Purchase Order &amp; GRN</t>
   </si>
@@ -289,10 +289,10 @@
     <t>INS WH-1</t>
   </si>
   <si>
-    <t>1432</t>
+    <t>1492</t>
   </si>
   <si>
-    <t>5315.99665</t>
+    <t>5277.91012</t>
   </si>
   <si>
     <t>Receipt Qty &amp; Unit cost</t>
@@ -328,10 +328,10 @@
     <t>4</t>
   </si>
   <si>
-    <t>426</t>
+    <t>454</t>
   </si>
   <si>
-    <t>6694.90186</t>
+    <t>6732.74603</t>
   </si>
   <si>
     <t>82.12</t>
@@ -352,10 +352,10 @@
     <t>3</t>
   </si>
   <si>
-    <t>1392</t>
+    <t>1512</t>
   </si>
   <si>
-    <t>3604.92118</t>
+    <t>3626.96254</t>
   </si>
   <si>
     <t>43.3</t>
@@ -727,13 +727,115 @@
     <t>GWL_Item_FP_Pl_Dissimilar_01</t>
   </si>
   <si>
+    <t>12978.9</t>
+  </si>
+  <si>
     <t>GWL_Item_FP_Pl_Dissimilar_02</t>
+  </si>
+  <si>
+    <t>25405.38</t>
   </si>
   <si>
     <t>GWL_Item_FP_Pl_Dissimilar_03</t>
   </si>
   <si>
-    <t>129.9</t>
+    <t>13258.08</t>
+  </si>
+  <si>
+    <t>205.323</t>
+  </si>
+  <si>
+    <t>14164.93776</t>
+  </si>
+  <si>
+    <t>383.326</t>
+  </si>
+  <si>
+    <t>10044.56288</t>
+  </si>
+  <si>
+    <t>375.327</t>
+  </si>
+  <si>
+    <t>9091.00385</t>
+  </si>
+  <si>
+    <t>14250.20994</t>
+  </si>
+  <si>
+    <t>386.326</t>
+  </si>
+  <si>
+    <t>10129.17345</t>
+  </si>
+  <si>
+    <t>379.327</t>
+  </si>
+  <si>
+    <t>9111.57406</t>
+  </si>
+  <si>
+    <t>14335.06883</t>
+  </si>
+  <si>
+    <t>10212.48006</t>
+  </si>
+  <si>
+    <t>9131.71497</t>
+  </si>
+  <si>
+    <t>206.323</t>
+  </si>
+  <si>
+    <t>14419.51643</t>
+  </si>
+  <si>
+    <t>389.326</t>
+  </si>
+  <si>
+    <t>10295.14474</t>
+  </si>
+  <si>
+    <t>383.327</t>
+  </si>
+  <si>
+    <t>9151.64571</t>
+  </si>
+  <si>
+    <t>207.323</t>
+  </si>
+  <si>
+    <t>14503.14938</t>
+  </si>
+  <si>
+    <t>392.326</t>
+  </si>
+  <si>
+    <t>10376.5452</t>
+  </si>
+  <si>
+    <t>387.327</t>
+  </si>
+  <si>
+    <t>9171.16479</t>
+  </si>
+  <si>
+    <t>235.654</t>
+  </si>
+  <si>
+    <t>12986.52483</t>
+  </si>
+  <si>
+    <t>381.652</t>
+  </si>
+  <si>
+    <t>12015.33048</t>
+  </si>
+  <si>
+    <t>281.327</t>
+  </si>
+  <si>
+    <t>9420.99171</t>
   </si>
 </sst>
 </file>
@@ -1556,7 +1658,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2205,18 +2307,18 @@
   <dimension ref="A1:BQ20"/>
   <sheetFormatPr defaultColWidth="8.84761904761905" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="13" max="13" width="9.14285714285714" customWidth="1"/>
-    <col min="14" max="14" width="13.847619047619" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="28.0"/>
+    <col min="3" max="3" customWidth="true" width="23.0"/>
+    <col min="13" max="13" customWidth="true" width="9.14285714285714"/>
+    <col min="14" max="14" customWidth="true" width="13.847619047619"/>
     <col min="29" max="29" width="9.28571428571429"/>
     <col min="35" max="35" width="11.4285714285714"/>
     <col min="44" max="44" width="10.1428571428571"/>
     <col min="48" max="48" width="11.7142857142857"/>
-    <col min="50" max="50" width="16.7142857142857" customWidth="1"/>
-    <col min="52" max="52" width="19.4285714285714" customWidth="1"/>
-    <col min="64" max="64" width="11" customWidth="1"/>
-    <col min="67" max="67" width="12"/>
+    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="64" max="64" customWidth="true" width="11.0"/>
+    <col min="67" max="67" width="12.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -2615,14 +2717,14 @@
       <c r="F4" s="20">
         <v>5</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" t="s" s="0">
         <v>78</v>
       </c>
       <c r="H4" s="20">
         <f>F4*G4</f>
         <v>750</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" t="s" s="0">
         <v>79</v>
       </c>
       <c r="J4" s="20">
@@ -2760,10 +2862,10 @@
       <c r="AT4" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AU4" t="s" s="0">
         <v>81</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AV4" t="s" s="0">
         <v>82</v>
       </c>
       <c r="AW4" s="25">
@@ -2804,10 +2906,10 @@
       <c r="BL4" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>89</v>
       </c>
       <c r="BO4" s="25">
@@ -2841,14 +2943,14 @@
       <c r="F5" s="20">
         <v>4</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" t="s" s="0">
         <v>92</v>
       </c>
       <c r="H5" s="20">
         <f>F5*G5</f>
         <v>400</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" t="s" s="0">
         <v>93</v>
       </c>
       <c r="J5" s="20">
@@ -2986,10 +3088,10 @@
       <c r="AT5" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AU5" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AV5" t="s" s="0">
         <v>95</v>
       </c>
       <c r="AW5" s="25">
@@ -3030,10 +3132,10 @@
       <c r="BL5" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BM5" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BN5" t="s" s="0">
         <v>97</v>
       </c>
       <c r="BO5" s="25">
@@ -3067,14 +3169,14 @@
       <c r="F6" s="20">
         <v>20</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H6" s="20">
         <f>F6*G6</f>
         <v>1000</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" t="s" s="0">
         <v>101</v>
       </c>
       <c r="J6" s="20">
@@ -3212,10 +3314,10 @@
       <c r="AT6" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AU6" t="s" s="0">
         <v>102</v>
       </c>
-      <c r="AV6" t="s">
+      <c r="AV6" t="s" s="0">
         <v>103</v>
       </c>
       <c r="AW6" s="25">
@@ -3256,10 +3358,10 @@
       <c r="BL6" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM6" t="s">
+      <c r="BM6" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="BN6" t="s">
+      <c r="BN6" t="s" s="0">
         <v>105</v>
       </c>
       <c r="BO6" s="25">
@@ -4441,11 +4543,11 @@
   <dimension ref="A1:BQ20"/>
   <sheetFormatPr defaultColWidth="8.84761904761905" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="27.1428571428571" customWidth="1"/>
-    <col min="13" max="13" width="9.14285714285714" customWidth="1"/>
-    <col min="14" max="14" width="13.847619047619" customWidth="1"/>
-    <col min="64" max="64" width="11" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="28.0"/>
+    <col min="3" max="3" customWidth="true" width="27.1428571428571"/>
+    <col min="13" max="13" customWidth="true" width="9.14285714285714"/>
+    <col min="14" max="14" customWidth="true" width="13.847619047619"/>
+    <col min="64" max="64" customWidth="true" width="11.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -4844,14 +4946,14 @@
       <c r="F4" s="20">
         <v>5</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" t="s" s="0">
         <v>78</v>
       </c>
       <c r="H4" s="20">
         <f t="shared" ref="H4:H6" si="0">F4*G4</f>
         <v>750</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" t="s" s="0">
         <v>79</v>
       </c>
       <c r="J4" s="20">
@@ -4989,10 +5091,10 @@
       <c r="AT4" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AU4" t="s" s="0">
         <v>147</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AV4" t="s" s="0">
         <v>148</v>
       </c>
       <c r="AW4" s="25">
@@ -5033,10 +5135,10 @@
       <c r="BL4" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>89</v>
       </c>
       <c r="BO4" s="25">
@@ -5070,14 +5172,14 @@
       <c r="F5" s="20">
         <v>4</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" t="s" s="0">
         <v>92</v>
       </c>
       <c r="H5" s="20">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" t="s" s="0">
         <v>93</v>
       </c>
       <c r="J5" s="20">
@@ -5215,10 +5317,10 @@
       <c r="AT5" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AU5" t="s" s="0">
         <v>150</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AV5" t="s" s="0">
         <v>151</v>
       </c>
       <c r="AW5" s="25">
@@ -5259,10 +5361,10 @@
       <c r="BL5" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BM5" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BN5" t="s" s="0">
         <v>97</v>
       </c>
       <c r="BO5" s="25">
@@ -5296,14 +5398,14 @@
       <c r="F6" s="20">
         <v>20</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H6" s="20">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" t="s" s="0">
         <v>101</v>
       </c>
       <c r="J6" s="20">
@@ -5441,10 +5543,10 @@
       <c r="AT6" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AU6" t="s" s="0">
         <v>153</v>
       </c>
-      <c r="AV6" t="s">
+      <c r="AV6" t="s" s="0">
         <v>154</v>
       </c>
       <c r="AW6" s="25">
@@ -5485,10 +5587,10 @@
       <c r="BL6" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM6" t="s">
+      <c r="BM6" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="BN6" t="s">
+      <c r="BN6" t="s" s="0">
         <v>105</v>
       </c>
       <c r="BO6" s="25">
@@ -6670,14 +6772,14 @@
   <dimension ref="A1:BQ20"/>
   <sheetFormatPr defaultColWidth="8.84761904761905" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="13" max="13" width="9.14285714285714" customWidth="1"/>
-    <col min="14" max="14" width="13.847619047619" customWidth="1"/>
-    <col min="35" max="35" width="14.7142857142857" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="28.0"/>
+    <col min="3" max="3" customWidth="true" width="23.0"/>
+    <col min="13" max="13" customWidth="true" width="9.14285714285714"/>
+    <col min="14" max="14" customWidth="true" width="13.847619047619"/>
+    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
     <col min="52" max="52" width="13.2857142857143"/>
-    <col min="64" max="64" width="11" customWidth="1"/>
-    <col min="67" max="67" width="12"/>
+    <col min="64" max="64" customWidth="true" width="11.0"/>
+    <col min="67" max="67" width="12.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -7076,14 +7178,14 @@
       <c r="F4" s="20">
         <v>3</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H4" s="20">
         <f t="shared" ref="H4:H6" si="0">F4*G4</f>
         <v>150</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" t="s" s="0">
         <v>79</v>
       </c>
       <c r="J4" s="20">
@@ -7221,10 +7323,10 @@
       <c r="AT4" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AU4" t="s" s="0">
         <v>174</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AV4" t="s" s="0">
         <v>175</v>
       </c>
       <c r="AW4" s="25">
@@ -7265,10 +7367,10 @@
       <c r="BL4" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>89</v>
       </c>
       <c r="BO4" s="25">
@@ -7302,14 +7404,14 @@
       <c r="F5" s="20">
         <v>6</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" t="s" s="0">
         <v>92</v>
       </c>
       <c r="H5" s="20">
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" t="s" s="0">
         <v>177</v>
       </c>
       <c r="J5" s="20">
@@ -7447,10 +7549,10 @@
       <c r="AT5" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AU5" t="s" s="0">
         <v>178</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AV5" t="s" s="0">
         <v>179</v>
       </c>
       <c r="AW5" s="25">
@@ -7491,10 +7593,10 @@
       <c r="BL5" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BM5" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BN5" t="s" s="0">
         <v>97</v>
       </c>
       <c r="BO5" s="25">
@@ -7528,14 +7630,14 @@
       <c r="F6" s="20">
         <v>12</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" t="s" s="0">
         <v>78</v>
       </c>
       <c r="H6" s="20">
         <f t="shared" si="0"/>
         <v>1800</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" t="s" s="0">
         <v>181</v>
       </c>
       <c r="J6" s="20">
@@ -7673,10 +7775,10 @@
       <c r="AT6" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AU6" t="s" s="0">
         <v>182</v>
       </c>
-      <c r="AV6" t="s">
+      <c r="AV6" t="s" s="0">
         <v>183</v>
       </c>
       <c r="AW6" s="25">
@@ -7717,10 +7819,10 @@
       <c r="BL6" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM6" t="s">
+      <c r="BM6" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="BN6" t="s">
+      <c r="BN6" t="s" s="0">
         <v>105</v>
       </c>
       <c r="BO6" s="25">
@@ -8902,16 +9004,16 @@
   <dimension ref="A1:BQ20"/>
   <sheetFormatPr defaultColWidth="8.84761904761905" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="12" max="12" width="14.2857142857143" customWidth="1"/>
-    <col min="13" max="13" width="9.42857142857143" customWidth="1"/>
-    <col min="14" max="14" width="13.847619047619" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="28.0"/>
+    <col min="3" max="3" customWidth="true" width="23.0"/>
+    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
+    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
+    <col min="14" max="14" customWidth="true" width="13.847619047619"/>
     <col min="29" max="29" width="9.57142857142857"/>
     <col min="35" max="35" width="11.4285714285714"/>
-    <col min="52" max="52" width="19.4285714285714" customWidth="1"/>
-    <col min="64" max="64" width="11" customWidth="1"/>
-    <col min="67" max="67" width="12"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="64" max="64" customWidth="true" width="11.0"/>
+    <col min="67" max="67" width="12.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -9310,14 +9412,14 @@
       <c r="F4" s="20">
         <v>5</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H4" s="20">
         <f t="shared" ref="H4:H6" si="0">F4*G4</f>
         <v>250</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J4" s="20">
@@ -9455,10 +9557,10 @@
       <c r="AT4" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AU4" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AV4" t="s" s="0">
         <v>88</v>
       </c>
       <c r="AW4" s="25">
@@ -9499,10 +9601,10 @@
       <c r="BL4" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>89</v>
       </c>
       <c r="BO4" s="25">
@@ -9536,14 +9638,14 @@
       <c r="F5" s="20">
         <v>4</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" t="s" s="0">
         <v>92</v>
       </c>
       <c r="H5" s="20">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" t="s" s="0">
         <v>93</v>
       </c>
       <c r="J5" s="20">
@@ -9681,10 +9783,10 @@
       <c r="AT5" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AU5" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AV5" t="s" s="0">
         <v>96</v>
       </c>
       <c r="AW5" s="25">
@@ -9725,10 +9827,10 @@
       <c r="BL5" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BM5" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BN5" t="s" s="0">
         <v>97</v>
       </c>
       <c r="BO5" s="25">
@@ -9762,14 +9864,14 @@
       <c r="F6" s="20">
         <v>20</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H6" s="20">
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" t="s" s="0">
         <v>101</v>
       </c>
       <c r="J6" s="20">
@@ -9907,10 +10009,10 @@
       <c r="AT6" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AU6" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="AV6" t="s">
+      <c r="AV6" t="s" s="0">
         <v>104</v>
       </c>
       <c r="AW6" s="25">
@@ -9951,10 +10053,10 @@
       <c r="BL6" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM6" t="s">
+      <c r="BM6" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="BN6" t="s">
+      <c r="BN6" t="s" s="0">
         <v>105</v>
       </c>
       <c r="BO6" s="25">
@@ -11136,15 +11238,15 @@
   <dimension ref="A1:BQ20"/>
   <sheetFormatPr defaultColWidth="8.84761904761905" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="13" max="13" width="9.14285714285714" customWidth="1"/>
-    <col min="14" max="14" width="13.847619047619" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="28.0"/>
+    <col min="3" max="3" customWidth="true" width="23.0"/>
+    <col min="13" max="13" customWidth="true" width="9.14285714285714"/>
+    <col min="14" max="14" customWidth="true" width="13.847619047619"/>
     <col min="29" max="29" width="9.28571428571429"/>
     <col min="35" max="35" width="11.4285714285714"/>
-    <col min="52" max="52" width="19.4285714285714" customWidth="1"/>
-    <col min="64" max="64" width="11" customWidth="1"/>
-    <col min="67" max="67" width="12"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="64" max="64" customWidth="true" width="11.0"/>
+    <col min="67" max="67" width="12.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -11543,14 +11645,14 @@
       <c r="F4" s="20">
         <v>3</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" t="s" s="0">
         <v>78</v>
       </c>
       <c r="H4" s="20">
         <f t="shared" ref="H4:H6" si="0">F4*G4</f>
         <v>450</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" t="s" s="0">
         <v>79</v>
       </c>
       <c r="J4" s="20">
@@ -11688,11 +11790,11 @@
       <c r="AT4" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU4" t="s">
-        <v>188</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>189</v>
+      <c r="AU4" t="s" s="0">
+        <v>258</v>
+      </c>
+      <c r="AV4" t="s" s="0">
+        <v>259</v>
       </c>
       <c r="AW4" s="25">
         <f t="shared" ref="AW4:AW6" si="12">AM4</f>
@@ -11732,10 +11834,10 @@
       <c r="BL4" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>89</v>
       </c>
       <c r="BO4" s="25">
@@ -11769,14 +11871,14 @@
       <c r="F5" s="20">
         <v>12</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" t="s" s="0">
         <v>92</v>
       </c>
       <c r="H5" s="20">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" t="s" s="0">
         <v>93</v>
       </c>
       <c r="J5" s="20">
@@ -11914,11 +12016,11 @@
       <c r="AT5" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU5" t="s">
-        <v>191</v>
-      </c>
-      <c r="AV5" t="s">
-        <v>192</v>
+      <c r="AU5" t="s" s="0">
+        <v>260</v>
+      </c>
+      <c r="AV5" t="s" s="0">
+        <v>261</v>
       </c>
       <c r="AW5" s="25">
         <f t="shared" si="12"/>
@@ -11958,10 +12060,10 @@
       <c r="BL5" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BM5" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BN5" t="s" s="0">
         <v>97</v>
       </c>
       <c r="BO5" s="25">
@@ -11995,14 +12097,14 @@
       <c r="F6" s="20">
         <v>9</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H6" s="20">
         <f t="shared" si="0"/>
         <v>450</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" t="s" s="0">
         <v>101</v>
       </c>
       <c r="J6" s="20">
@@ -12140,11 +12242,11 @@
       <c r="AT6" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU6" t="s">
-        <v>194</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>195</v>
+      <c r="AU6" t="s" s="0">
+        <v>262</v>
+      </c>
+      <c r="AV6" t="s" s="0">
+        <v>263</v>
       </c>
       <c r="AW6" s="25">
         <f t="shared" si="12"/>
@@ -12184,10 +12286,10 @@
       <c r="BL6" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM6" t="s">
+      <c r="BM6" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="BN6" t="s">
+      <c r="BN6" t="s" s="0">
         <v>105</v>
       </c>
       <c r="BO6" s="25">
@@ -13369,14 +13471,14 @@
   <dimension ref="A1:BQ20"/>
   <sheetFormatPr defaultColWidth="8.84761904761905" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="13" max="13" width="9.14285714285714" customWidth="1"/>
-    <col min="14" max="14" width="13.847619047619" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="28.0"/>
+    <col min="3" max="3" customWidth="true" width="30.0"/>
+    <col min="13" max="13" customWidth="true" width="9.14285714285714"/>
+    <col min="14" max="14" customWidth="true" width="13.847619047619"/>
     <col min="35" max="35" width="11.4285714285714"/>
-    <col min="52" max="52" width="19.4285714285714" customWidth="1"/>
-    <col min="64" max="64" width="11" customWidth="1"/>
-    <col min="67" max="67" width="12"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="64" max="64" customWidth="true" width="11.0"/>
+    <col min="67" max="67" width="12.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -13775,14 +13877,14 @@
       <c r="F4" s="20">
         <v>5</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H4" s="20">
         <f t="shared" ref="H4:H6" si="0">F4*G4</f>
         <v>250</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J4" s="20">
@@ -13920,10 +14022,10 @@
       <c r="AT4" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AU4" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AV4" t="s" s="0">
         <v>197</v>
       </c>
       <c r="AW4" s="25">
@@ -13964,10 +14066,10 @@
       <c r="BL4" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>89</v>
       </c>
       <c r="BO4" s="25">
@@ -14001,14 +14103,14 @@
       <c r="F5" s="20">
         <v>4</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" t="s" s="0">
         <v>92</v>
       </c>
       <c r="H5" s="20">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" t="s" s="0">
         <v>93</v>
       </c>
       <c r="J5" s="20">
@@ -14146,10 +14248,10 @@
       <c r="AT5" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AU5" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AV5" t="s" s="0">
         <v>199</v>
       </c>
       <c r="AW5" s="25">
@@ -14190,10 +14292,10 @@
       <c r="BL5" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BM5" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BN5" t="s" s="0">
         <v>97</v>
       </c>
       <c r="BO5" s="25">
@@ -14227,14 +14329,14 @@
       <c r="F6" s="20">
         <v>20</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H6" s="20">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" t="s" s="0">
         <v>101</v>
       </c>
       <c r="J6" s="20">
@@ -14372,10 +14474,10 @@
       <c r="AT6" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AU6" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="AV6" t="s">
+      <c r="AV6" t="s" s="0">
         <v>201</v>
       </c>
       <c r="AW6" s="25">
@@ -14416,10 +14518,10 @@
       <c r="BL6" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM6" t="s">
+      <c r="BM6" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="BN6" t="s">
+      <c r="BN6" t="s" s="0">
         <v>105</v>
       </c>
       <c r="BO6" s="25">
@@ -15601,15 +15703,15 @@
   <dimension ref="A1:BQ20"/>
   <sheetFormatPr defaultColWidth="8.84761904761905" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="13" max="13" width="9.14285714285714" customWidth="1"/>
-    <col min="14" max="14" width="13.847619047619" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="28.0"/>
+    <col min="3" max="3" customWidth="true" width="23.0"/>
+    <col min="13" max="13" customWidth="true" width="9.14285714285714"/>
+    <col min="14" max="14" customWidth="true" width="13.847619047619"/>
     <col min="29" max="29" width="9.28571428571429"/>
     <col min="35" max="35" width="11.4285714285714"/>
     <col min="52" max="52" width="13.2857142857143"/>
-    <col min="64" max="64" width="11" customWidth="1"/>
-    <col min="67" max="67" width="12"/>
+    <col min="64" max="64" customWidth="true" width="11.0"/>
+    <col min="67" max="67" width="12.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -16008,14 +16110,14 @@
       <c r="F4" s="20">
         <v>3</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" t="s" s="0">
         <v>78</v>
       </c>
       <c r="H4" s="20">
         <f t="shared" ref="H4:H6" si="0">F4*G4</f>
         <v>450</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" t="s" s="0">
         <v>79</v>
       </c>
       <c r="J4" s="20">
@@ -16153,10 +16255,10 @@
       <c r="AT4" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AU4" t="s" s="0">
         <v>203</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AV4" t="s" s="0">
         <v>204</v>
       </c>
       <c r="AW4" s="25">
@@ -16197,10 +16299,10 @@
       <c r="BL4" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>89</v>
       </c>
       <c r="BO4" s="25">
@@ -16234,14 +16336,14 @@
       <c r="F5" s="20">
         <v>6</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" t="s" s="0">
         <v>92</v>
       </c>
       <c r="H5" s="20">
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" t="s" s="0">
         <v>93</v>
       </c>
       <c r="J5" s="20">
@@ -16379,10 +16481,10 @@
       <c r="AT5" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AU5" t="s" s="0">
         <v>206</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AV5" t="s" s="0">
         <v>207</v>
       </c>
       <c r="AW5" s="25">
@@ -16423,10 +16525,10 @@
       <c r="BL5" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BM5" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BN5" t="s" s="0">
         <v>97</v>
       </c>
       <c r="BO5" s="25">
@@ -16460,14 +16562,14 @@
       <c r="F6" s="20">
         <v>12</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H6" s="20">
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" t="s" s="0">
         <v>101</v>
       </c>
       <c r="J6" s="20">
@@ -16605,10 +16707,10 @@
       <c r="AT6" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AU6" t="s" s="0">
         <v>209</v>
       </c>
-      <c r="AV6" t="s">
+      <c r="AV6" t="s" s="0">
         <v>210</v>
       </c>
       <c r="AW6" s="25">
@@ -16649,10 +16751,10 @@
       <c r="BL6" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM6" t="s">
+      <c r="BM6" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="BN6" t="s">
+      <c r="BN6" t="s" s="0">
         <v>105</v>
       </c>
       <c r="BO6" s="25">
@@ -17834,14 +17936,14 @@
   <dimension ref="A1:BQ20"/>
   <sheetFormatPr defaultColWidth="8.84761904761905" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="13" max="13" width="9.14285714285714" customWidth="1"/>
-    <col min="14" max="14" width="13.847619047619" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="28.0"/>
+    <col min="3" max="3" customWidth="true" width="23.0"/>
+    <col min="13" max="13" customWidth="true" width="9.14285714285714"/>
+    <col min="14" max="14" customWidth="true" width="13.847619047619"/>
     <col min="35" max="35" width="11.4285714285714"/>
     <col min="52" max="52" width="13.1428571428571"/>
-    <col min="64" max="64" width="11" customWidth="1"/>
-    <col min="67" max="67" width="12"/>
+    <col min="64" max="64" customWidth="true" width="11.0"/>
+    <col min="67" max="67" width="12.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -18240,14 +18342,14 @@
       <c r="F4" s="20">
         <v>5</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H4" s="20">
         <f t="shared" ref="H4:H6" si="0">F4*G4</f>
         <v>250</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J4" s="20">
@@ -18385,10 +18487,10 @@
       <c r="AT4" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AU4" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AV4" t="s" s="0">
         <v>212</v>
       </c>
       <c r="AW4" s="25">
@@ -18429,10 +18531,10 @@
       <c r="BL4" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>89</v>
       </c>
       <c r="BO4" s="25">
@@ -18466,14 +18568,14 @@
       <c r="F5" s="20">
         <v>4</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" t="s" s="0">
         <v>92</v>
       </c>
       <c r="H5" s="20">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" t="s" s="0">
         <v>93</v>
       </c>
       <c r="J5" s="20">
@@ -18611,10 +18713,10 @@
       <c r="AT5" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AU5" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AV5" t="s" s="0">
         <v>214</v>
       </c>
       <c r="AW5" s="25">
@@ -18655,10 +18757,10 @@
       <c r="BL5" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BM5" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BN5" t="s" s="0">
         <v>97</v>
       </c>
       <c r="BO5" s="25">
@@ -18692,14 +18794,14 @@
       <c r="F6" s="20">
         <v>20</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H6" s="20">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" t="s" s="0">
         <v>101</v>
       </c>
       <c r="J6" s="20">
@@ -18837,10 +18939,10 @@
       <c r="AT6" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AU6" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="AV6" t="s">
+      <c r="AV6" t="s" s="0">
         <v>216</v>
       </c>
       <c r="AW6" s="25">
@@ -18881,10 +18983,10 @@
       <c r="BL6" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM6" t="s">
+      <c r="BM6" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="BN6" t="s">
+      <c r="BN6" t="s" s="0">
         <v>105</v>
       </c>
       <c r="BO6" s="25">
@@ -20066,15 +20168,15 @@
   <dimension ref="A1:BQ20"/>
   <sheetFormatPr defaultColWidth="8.84761904761905" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="13" max="13" width="9.14285714285714" customWidth="1"/>
-    <col min="14" max="14" width="13.847619047619" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="28.0"/>
+    <col min="3" max="3" customWidth="true" width="23.0"/>
+    <col min="13" max="13" customWidth="true" width="9.14285714285714"/>
+    <col min="14" max="14" customWidth="true" width="13.847619047619"/>
     <col min="29" max="29" width="9.28571428571429"/>
     <col min="35" max="35" width="11.4285714285714"/>
-    <col min="52" max="52" width="19.4285714285714" customWidth="1"/>
-    <col min="64" max="64" width="11" customWidth="1"/>
-    <col min="67" max="67" width="12"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="64" max="64" customWidth="true" width="11.0"/>
+    <col min="67" max="67" width="12.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -20473,14 +20575,14 @@
       <c r="F4" s="20">
         <v>3</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" t="s" s="0">
         <v>78</v>
       </c>
       <c r="H4" s="20">
         <f t="shared" ref="H4:H6" si="0">F4*G4</f>
         <v>450</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" t="s" s="0">
         <v>79</v>
       </c>
       <c r="J4" s="20">
@@ -20618,11 +20720,11 @@
       <c r="AT4" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU4" t="s">
-        <v>218</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>219</v>
+      <c r="AU4" t="s" s="0">
+        <v>252</v>
+      </c>
+      <c r="AV4" t="s" s="0">
+        <v>253</v>
       </c>
       <c r="AW4" s="25">
         <f t="shared" ref="AW4:AW6" si="12">AM4</f>
@@ -20662,10 +20764,10 @@
       <c r="BL4" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>89</v>
       </c>
       <c r="BO4" s="25">
@@ -20699,14 +20801,14 @@
       <c r="F5" s="20">
         <v>9</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" t="s" s="0">
         <v>92</v>
       </c>
       <c r="H5" s="20">
         <f t="shared" si="0"/>
         <v>900</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" t="s" s="0">
         <v>93</v>
       </c>
       <c r="J5" s="20">
@@ -20844,11 +20946,11 @@
       <c r="AT5" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU5" t="s">
-        <v>221</v>
-      </c>
-      <c r="AV5" t="s">
-        <v>222</v>
+      <c r="AU5" t="s" s="0">
+        <v>254</v>
+      </c>
+      <c r="AV5" t="s" s="0">
+        <v>255</v>
       </c>
       <c r="AW5" s="25">
         <f t="shared" si="12"/>
@@ -20888,10 +20990,10 @@
       <c r="BL5" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BM5" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BN5" t="s" s="0">
         <v>97</v>
       </c>
       <c r="BO5" s="25">
@@ -20925,14 +21027,14 @@
       <c r="F6" s="20">
         <v>12</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H6" s="20">
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" t="s" s="0">
         <v>101</v>
       </c>
       <c r="J6" s="20">
@@ -21070,11 +21172,11 @@
       <c r="AT6" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU6" t="s">
-        <v>224</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>225</v>
+      <c r="AU6" t="s" s="0">
+        <v>256</v>
+      </c>
+      <c r="AV6" t="s" s="0">
+        <v>257</v>
       </c>
       <c r="AW6" s="25">
         <f t="shared" si="12"/>
@@ -21114,10 +21216,10 @@
       <c r="BL6" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM6" t="s">
+      <c r="BM6" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="BN6" t="s">
+      <c r="BN6" t="s" s="0">
         <v>105</v>
       </c>
       <c r="BO6" s="25">
@@ -22299,15 +22401,15 @@
   <dimension ref="A1:BQ20"/>
   <sheetFormatPr defaultColWidth="8.84761904761905" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="29.447619047619" customWidth="1"/>
-    <col min="13" max="13" width="9.14285714285714" customWidth="1"/>
-    <col min="14" max="14" width="13.847619047619" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="28.0"/>
+    <col min="3" max="3" customWidth="true" width="29.447619047619"/>
+    <col min="13" max="13" customWidth="true" width="9.14285714285714"/>
+    <col min="14" max="14" customWidth="true" width="13.847619047619"/>
     <col min="35" max="35" width="11.4285714285714"/>
-    <col min="50" max="50" width="16.7142857142857" customWidth="1"/>
-    <col min="52" max="52" width="19.4285714285714" customWidth="1"/>
-    <col min="64" max="64" width="11" customWidth="1"/>
-    <col min="67" max="67" width="12"/>
+    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="64" max="64" customWidth="true" width="11.0"/>
+    <col min="67" max="67" width="12.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -22687,7 +22789,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="19">
         <v>1</v>
       </c>
@@ -22706,14 +22808,14 @@
       <c r="F4" s="20">
         <v>9</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H4" s="20">
         <f t="shared" ref="H4:H6" si="0">F4*G4</f>
         <v>450</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J4" s="20">
@@ -22851,11 +22953,11 @@
       <c r="AT4" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AU4" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="AV4" t="s">
-        <v>143</v>
+      <c r="AV4" t="s" s="0">
+        <v>227</v>
       </c>
       <c r="AW4" s="25">
         <f t="shared" ref="AW4:AW6" si="12">AM4</f>
@@ -22895,10 +22997,10 @@
       <c r="BL4" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>89</v>
       </c>
       <c r="BO4" s="25">
@@ -22913,15 +23015,15 @@
         <v>123562</v>
       </c>
     </row>
-    <row r="5" spans="1:69">
+    <row r="5" ht="15.75" spans="1:69">
       <c r="A5" s="19">
         <v>1</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>77</v>
@@ -22932,14 +23034,14 @@
       <c r="F5" s="20">
         <v>12</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" t="s" s="0">
         <v>92</v>
       </c>
       <c r="H5" s="20">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J5" s="20">
@@ -23077,11 +23179,11 @@
       <c r="AT5" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AU5" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="AV5" t="s">
-        <v>145</v>
+      <c r="AV5" t="s" s="0">
+        <v>229</v>
       </c>
       <c r="AW5" s="25">
         <f t="shared" si="12"/>
@@ -23121,10 +23223,10 @@
       <c r="BL5" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BM5" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BN5" t="s" s="0">
         <v>97</v>
       </c>
       <c r="BO5" s="25">
@@ -23139,15 +23241,15 @@
         <v>123562</v>
       </c>
     </row>
-    <row r="6" spans="1:69">
+    <row r="6" ht="15.75" spans="1:69">
       <c r="A6" s="19">
         <v>1</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>77</v>
@@ -23158,14 +23260,14 @@
       <c r="F6" s="20">
         <v>15</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H6" s="20">
         <f t="shared" si="0"/>
         <v>750</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J6" s="20">
@@ -23303,11 +23405,11 @@
       <c r="AT6" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AU6" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="AV6" t="s">
-        <v>229</v>
+      <c r="AV6" t="s" s="0">
+        <v>231</v>
       </c>
       <c r="AW6" s="25">
         <f t="shared" si="12"/>
@@ -23347,10 +23449,10 @@
       <c r="BL6" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM6" t="s">
+      <c r="BM6" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="BN6" t="s">
+      <c r="BN6" t="s" s="0">
         <v>105</v>
       </c>
       <c r="BO6" s="25">
@@ -24532,15 +24634,15 @@
   <dimension ref="A1:BQ20"/>
   <sheetFormatPr defaultColWidth="8.84761904761905" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="3" width="32.1428571428571" customWidth="1"/>
-    <col min="13" max="13" width="9.14285714285714" customWidth="1"/>
-    <col min="14" max="14" width="13.847619047619" customWidth="1"/>
+    <col min="2" max="3" customWidth="true" width="32.1428571428571"/>
+    <col min="13" max="13" customWidth="true" width="9.14285714285714"/>
+    <col min="14" max="14" customWidth="true" width="13.847619047619"/>
     <col min="29" max="29" width="9.28571428571429"/>
-    <col min="35" max="35" width="14.7142857142857" customWidth="1"/>
-    <col min="51" max="51" width="14.5714285714286" customWidth="1"/>
-    <col min="52" max="52" width="19.4285714285714" customWidth="1"/>
-    <col min="64" max="64" width="11" customWidth="1"/>
-    <col min="67" max="67" width="12"/>
+    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
+    <col min="51" max="51" customWidth="true" width="14.5714285714286"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="64" max="64" customWidth="true" width="11.0"/>
+    <col min="67" max="67" width="12.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -24939,14 +25041,14 @@
       <c r="F4" s="20">
         <v>3</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" t="s" s="0">
         <v>78</v>
       </c>
       <c r="H4" s="20">
         <f t="shared" ref="H4:H6" si="0">F4*G4</f>
         <v>450</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" t="s" s="0">
         <v>79</v>
       </c>
       <c r="J4" s="20">
@@ -25084,10 +25186,10 @@
       <c r="AT4" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AU4" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AV4" t="s" s="0">
         <v>128</v>
       </c>
       <c r="AW4" s="25">
@@ -25128,10 +25230,10 @@
       <c r="BL4" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>89</v>
       </c>
       <c r="BO4" s="25">
@@ -25165,14 +25267,14 @@
       <c r="F5" s="20">
         <v>9</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" t="s" s="0">
         <v>92</v>
       </c>
       <c r="H5" s="20">
         <f t="shared" si="0"/>
         <v>900</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" t="s" s="0">
         <v>93</v>
       </c>
       <c r="J5" s="20">
@@ -25310,10 +25412,10 @@
       <c r="AT5" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AU5" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AV5" t="s" s="0">
         <v>130</v>
       </c>
       <c r="AW5" s="25">
@@ -25354,10 +25456,10 @@
       <c r="BL5" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BM5" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BN5" t="s" s="0">
         <v>97</v>
       </c>
       <c r="BO5" s="25">
@@ -25391,14 +25493,14 @@
       <c r="F6" s="20">
         <v>12</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H6" s="20">
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" t="s" s="0">
         <v>101</v>
       </c>
       <c r="J6" s="20">
@@ -25536,10 +25638,10 @@
       <c r="AT6" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AU6" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="AV6" t="s">
+      <c r="AV6" t="s" s="0">
         <v>132</v>
       </c>
       <c r="AW6" s="25">
@@ -25580,10 +25682,10 @@
       <c r="BL6" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM6" t="s">
+      <c r="BM6" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="BN6" t="s">
+      <c r="BN6" t="s" s="0">
         <v>105</v>
       </c>
       <c r="BO6" s="25">
@@ -26765,15 +26867,15 @@
   <dimension ref="A1:BQ20"/>
   <sheetFormatPr defaultColWidth="8.84761904761905" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="13" max="13" width="9.14285714285714" customWidth="1"/>
-    <col min="14" max="14" width="13.847619047619" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="28.0"/>
+    <col min="3" max="3" customWidth="true" width="23.0"/>
+    <col min="13" max="13" customWidth="true" width="9.14285714285714"/>
+    <col min="14" max="14" customWidth="true" width="13.847619047619"/>
     <col min="29" max="29" width="10.5714285714286"/>
     <col min="35" max="35" width="12.8571428571429"/>
-    <col min="52" max="52" width="19.4285714285714" customWidth="1"/>
-    <col min="64" max="64" width="11" customWidth="1"/>
-    <col min="67" max="67" width="12"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="64" max="64" customWidth="true" width="11.0"/>
+    <col min="67" max="67" width="12.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -27172,14 +27274,14 @@
       <c r="F4" s="20">
         <v>12</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" t="s" s="0">
         <v>78</v>
       </c>
       <c r="H4" s="20">
         <f t="shared" ref="H4:H6" si="0">F4*G4</f>
         <v>1800</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" t="s" s="0">
         <v>79</v>
       </c>
       <c r="J4" s="20">
@@ -27317,10 +27419,10 @@
       <c r="AT4" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AU4" t="s" s="0">
         <v>134</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AV4" t="s" s="0">
         <v>135</v>
       </c>
       <c r="AW4" s="25">
@@ -27361,10 +27463,10 @@
       <c r="BL4" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>89</v>
       </c>
       <c r="BO4" s="25">
@@ -27398,14 +27500,14 @@
       <c r="F5" s="20">
         <v>3</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" t="s" s="0">
         <v>92</v>
       </c>
       <c r="H5" s="20">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" t="s" s="0">
         <v>93</v>
       </c>
       <c r="J5" s="20">
@@ -27543,10 +27645,10 @@
       <c r="AT5" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AU5" t="s" s="0">
         <v>137</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AV5" t="s" s="0">
         <v>138</v>
       </c>
       <c r="AW5" s="25">
@@ -27587,10 +27689,10 @@
       <c r="BL5" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BM5" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BN5" t="s" s="0">
         <v>97</v>
       </c>
       <c r="BO5" s="25">
@@ -27624,14 +27726,14 @@
       <c r="F6" s="20">
         <v>9</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H6" s="20">
         <f t="shared" si="0"/>
         <v>450</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" t="s" s="0">
         <v>101</v>
       </c>
       <c r="J6" s="20">
@@ -27769,10 +27871,10 @@
       <c r="AT6" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AU6" t="s" s="0">
         <v>140</v>
       </c>
-      <c r="AV6" t="s">
+      <c r="AV6" t="s" s="0">
         <v>141</v>
       </c>
       <c r="AW6" s="25">
@@ -27813,10 +27915,10 @@
       <c r="BL6" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM6" t="s">
+      <c r="BM6" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="BN6" t="s">
+      <c r="BN6" t="s" s="0">
         <v>105</v>
       </c>
       <c r="BO6" s="25">
@@ -28998,10 +29100,10 @@
   <dimension ref="A1:BQ19"/>
   <sheetFormatPr defaultColWidth="8.84761904761905" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="13" max="13" width="9.14285714285714" customWidth="1"/>
-    <col min="14" max="14" width="13.847619047619" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="28.0"/>
+    <col min="3" max="3" customWidth="true" width="23.0"/>
+    <col min="13" max="13" customWidth="true" width="9.14285714285714"/>
+    <col min="14" max="14" customWidth="true" width="13.847619047619"/>
     <col min="18" max="19" width="9.28571428571429"/>
     <col min="20" max="20" width="10.7142857142857"/>
     <col min="29" max="29" width="9.28571428571429"/>
@@ -29011,9 +29113,9 @@
     <col min="49" max="49" width="14.5714285714286"/>
     <col min="50" max="50" width="10.1428571428571"/>
     <col min="51" max="51" width="14.5714285714286"/>
-    <col min="52" max="52" width="19.4285714285714" customWidth="1"/>
-    <col min="64" max="64" width="11" customWidth="1"/>
-    <col min="67" max="67" width="12"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="64" max="64" customWidth="true" width="11.0"/>
+    <col min="67" max="67" width="12.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -29412,14 +29514,14 @@
       <c r="F4" s="20">
         <v>9</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" t="s" s="0">
         <v>78</v>
       </c>
       <c r="H4" s="20">
         <f>F4*G4</f>
         <v>1350</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" t="s" s="0">
         <v>79</v>
       </c>
       <c r="J4" s="20">
@@ -29456,7 +29558,7 @@
         <f>ROUND(M4+O4+Q4,3)</f>
         <v>229.1</v>
       </c>
-      <c r="S4" s="21">
+      <c r="S4" s="20">
         <f>(H4-R4)</f>
         <v>1120.9</v>
       </c>
@@ -29557,10 +29659,10 @@
       <c r="AT4" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AU4" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AV4" t="s" s="0">
         <v>143</v>
       </c>
       <c r="AW4" s="25">
@@ -29601,10 +29703,10 @@
       <c r="BL4" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>89</v>
       </c>
       <c r="BO4" s="25">
@@ -29638,14 +29740,14 @@
       <c r="F5" s="20">
         <v>12</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" t="s" s="0">
         <v>92</v>
       </c>
       <c r="H5" s="20">
         <f>F5*G5</f>
         <v>1200</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" t="s" s="0">
         <v>93</v>
       </c>
       <c r="J5" s="20">
@@ -29783,10 +29885,10 @@
       <c r="AT5" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AU5" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AV5" t="s" s="0">
         <v>145</v>
       </c>
       <c r="AW5" s="25">
@@ -29827,10 +29929,10 @@
       <c r="BL5" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BM5" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BN5" t="s" s="0">
         <v>97</v>
       </c>
       <c r="BO5" s="25">
@@ -31011,15 +31113,15 @@
   <dimension ref="A1:BQ20"/>
   <sheetFormatPr defaultColWidth="8.84761904761905" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="13" max="13" width="9.14285714285714" customWidth="1"/>
-    <col min="14" max="14" width="13.847619047619" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="28.0"/>
+    <col min="3" max="3" customWidth="true" width="23.0"/>
+    <col min="13" max="13" customWidth="true" width="9.14285714285714"/>
+    <col min="14" max="14" customWidth="true" width="13.847619047619"/>
     <col min="29" max="29" width="9.28571428571429"/>
     <col min="35" max="35" width="11.4285714285714"/>
     <col min="52" max="52" width="13.2857142857143"/>
-    <col min="64" max="64" width="11" customWidth="1"/>
-    <col min="67" max="67" width="12"/>
+    <col min="64" max="64" customWidth="true" width="11.0"/>
+    <col min="67" max="67" width="12.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -31418,14 +31520,14 @@
       <c r="F4" s="20">
         <v>3</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" t="s" s="0">
         <v>78</v>
       </c>
       <c r="H4" s="20">
         <f t="shared" ref="H4:H6" si="0">F4*G4</f>
         <v>450</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" t="s" s="0">
         <v>79</v>
       </c>
       <c r="J4" s="20">
@@ -31563,10 +31665,10 @@
       <c r="AT4" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AU4" t="s" s="0">
         <v>147</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AV4" t="s" s="0">
         <v>148</v>
       </c>
       <c r="AW4" s="25">
@@ -31607,10 +31709,10 @@
       <c r="BL4" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>89</v>
       </c>
       <c r="BO4" s="25">
@@ -31644,14 +31746,14 @@
       <c r="F5" s="20">
         <v>6</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" t="s" s="0">
         <v>92</v>
       </c>
       <c r="H5" s="20">
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" t="s" s="0">
         <v>93</v>
       </c>
       <c r="J5" s="20">
@@ -31789,10 +31891,10 @@
       <c r="AT5" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AU5" t="s" s="0">
         <v>150</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AV5" t="s" s="0">
         <v>151</v>
       </c>
       <c r="AW5" s="25">
@@ -31833,10 +31935,10 @@
       <c r="BL5" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BM5" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BN5" t="s" s="0">
         <v>97</v>
       </c>
       <c r="BO5" s="25">
@@ -31870,14 +31972,14 @@
       <c r="F6" s="20">
         <v>12</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H6" s="20">
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" t="s" s="0">
         <v>101</v>
       </c>
       <c r="J6" s="20">
@@ -32015,10 +32117,10 @@
       <c r="AT6" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AU6" t="s" s="0">
         <v>153</v>
       </c>
-      <c r="AV6" t="s">
+      <c r="AV6" t="s" s="0">
         <v>154</v>
       </c>
       <c r="AW6" s="25">
@@ -32059,10 +32161,10 @@
       <c r="BL6" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM6" t="s">
+      <c r="BM6" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="BN6" t="s">
+      <c r="BN6" t="s" s="0">
         <v>105</v>
       </c>
       <c r="BO6" s="25">
@@ -33244,11 +33346,11 @@
   <dimension ref="A1:BQ20"/>
   <sheetFormatPr defaultColWidth="8.84761904761905" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="13" max="13" width="9.14285714285714" customWidth="1"/>
-    <col min="14" max="14" width="13.847619047619" customWidth="1"/>
-    <col min="64" max="64" width="11" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="28.0"/>
+    <col min="3" max="3" customWidth="true" width="23.0"/>
+    <col min="13" max="13" customWidth="true" width="9.14285714285714"/>
+    <col min="14" max="14" customWidth="true" width="13.847619047619"/>
+    <col min="64" max="64" customWidth="true" width="11.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -33647,14 +33749,14 @@
       <c r="F4" s="20">
         <v>5</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" t="s" s="0">
         <v>78</v>
       </c>
       <c r="H4" s="20">
         <f t="shared" ref="H4:H6" si="0">F4*G4</f>
         <v>750</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" t="s" s="0">
         <v>79</v>
       </c>
       <c r="J4" s="20">
@@ -33792,10 +33894,10 @@
       <c r="AT4" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AU4" t="s" s="0">
         <v>147</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AV4" t="s" s="0">
         <v>148</v>
       </c>
       <c r="AW4" s="25">
@@ -33836,10 +33938,10 @@
       <c r="BL4" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>89</v>
       </c>
       <c r="BO4" s="25">
@@ -33873,14 +33975,14 @@
       <c r="F5" s="20">
         <v>4</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" t="s" s="0">
         <v>92</v>
       </c>
       <c r="H5" s="20">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" t="s" s="0">
         <v>93</v>
       </c>
       <c r="J5" s="20">
@@ -34018,10 +34120,10 @@
       <c r="AT5" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AU5" t="s" s="0">
         <v>150</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AV5" t="s" s="0">
         <v>151</v>
       </c>
       <c r="AW5" s="25">
@@ -34062,10 +34164,10 @@
       <c r="BL5" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BM5" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BN5" t="s" s="0">
         <v>97</v>
       </c>
       <c r="BO5" s="25">
@@ -34099,14 +34201,14 @@
       <c r="F6" s="20">
         <v>20</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H6" s="20">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" t="s" s="0">
         <v>101</v>
       </c>
       <c r="J6" s="20">
@@ -34244,10 +34346,10 @@
       <c r="AT6" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AU6" t="s" s="0">
         <v>153</v>
       </c>
-      <c r="AV6" t="s">
+      <c r="AV6" t="s" s="0">
         <v>154</v>
       </c>
       <c r="AW6" s="25">
@@ -34288,10 +34390,10 @@
       <c r="BL6" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM6" t="s">
+      <c r="BM6" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="BN6" t="s">
+      <c r="BN6" t="s" s="0">
         <v>105</v>
       </c>
       <c r="BO6" s="25">
@@ -35473,11 +35575,11 @@
   <dimension ref="A1:BQ20"/>
   <sheetFormatPr defaultColWidth="8.84761904761905" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="29.1428571428571" customWidth="1"/>
-    <col min="13" max="13" width="9.14285714285714" customWidth="1"/>
-    <col min="14" max="14" width="13.847619047619" customWidth="1"/>
-    <col min="64" max="64" width="11" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="28.0"/>
+    <col min="3" max="3" customWidth="true" width="29.1428571428571"/>
+    <col min="13" max="13" customWidth="true" width="9.14285714285714"/>
+    <col min="14" max="14" customWidth="true" width="13.847619047619"/>
+    <col min="64" max="64" customWidth="true" width="11.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -35876,14 +35978,14 @@
       <c r="F4" s="20">
         <v>5</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H4" s="20">
         <f t="shared" ref="H4:H6" si="0">F4*G4</f>
         <v>250</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J4" s="20">
@@ -36021,10 +36123,10 @@
       <c r="AT4" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AU4" t="s" s="0">
         <v>147</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AV4" t="s" s="0">
         <v>148</v>
       </c>
       <c r="AW4" s="25">
@@ -36065,10 +36167,10 @@
       <c r="BL4" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>89</v>
       </c>
       <c r="BO4" s="25">
@@ -36102,14 +36204,14 @@
       <c r="F5" s="20">
         <v>4</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" t="s" s="0">
         <v>92</v>
       </c>
       <c r="H5" s="20">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" t="s" s="0">
         <v>93</v>
       </c>
       <c r="J5" s="20">
@@ -36247,10 +36349,10 @@
       <c r="AT5" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AU5" t="s" s="0">
         <v>150</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AV5" t="s" s="0">
         <v>151</v>
       </c>
       <c r="AW5" s="25">
@@ -36291,10 +36393,10 @@
       <c r="BL5" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BM5" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BN5" t="s" s="0">
         <v>97</v>
       </c>
       <c r="BO5" s="25">
@@ -36328,14 +36430,14 @@
       <c r="F6" s="20">
         <v>20</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H6" s="20">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" t="s" s="0">
         <v>101</v>
       </c>
       <c r="J6" s="20">
@@ -36473,10 +36575,10 @@
       <c r="AT6" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AU6" t="s" s="0">
         <v>153</v>
       </c>
-      <c r="AV6" t="s">
+      <c r="AV6" t="s" s="0">
         <v>154</v>
       </c>
       <c r="AW6" s="25">
@@ -36517,10 +36619,10 @@
       <c r="BL6" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM6" t="s">
+      <c r="BM6" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="BN6" t="s">
+      <c r="BN6" t="s" s="0">
         <v>105</v>
       </c>
       <c r="BO6" s="25">
@@ -37702,15 +37804,15 @@
   <dimension ref="A1:BQ20"/>
   <sheetFormatPr defaultColWidth="8.84761904761905" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="13" max="13" width="9.14285714285714" customWidth="1"/>
-    <col min="14" max="14" width="13.847619047619" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="28.0"/>
+    <col min="3" max="3" customWidth="true" width="23.0"/>
+    <col min="13" max="13" customWidth="true" width="9.14285714285714"/>
+    <col min="14" max="14" customWidth="true" width="13.847619047619"/>
     <col min="29" max="29" width="9.28571428571429"/>
     <col min="35" max="35" width="11.4285714285714"/>
     <col min="52" max="52" width="13.2857142857143"/>
-    <col min="64" max="64" width="11" customWidth="1"/>
-    <col min="67" max="67" width="12"/>
+    <col min="64" max="64" customWidth="true" width="11.0"/>
+    <col min="67" max="67" width="12.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -38109,14 +38211,14 @@
       <c r="F4" s="20">
         <v>3</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" t="s" s="0">
         <v>78</v>
       </c>
       <c r="H4" s="20">
         <f t="shared" ref="H4:H6" si="0">F4*G4</f>
         <v>450</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" t="s" s="0">
         <v>79</v>
       </c>
       <c r="J4" s="20">
@@ -38254,10 +38356,10 @@
       <c r="AT4" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AU4" t="s" s="0">
         <v>147</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AV4" t="s" s="0">
         <v>148</v>
       </c>
       <c r="AW4" s="25">
@@ -38298,10 +38400,10 @@
       <c r="BL4" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>89</v>
       </c>
       <c r="BO4" s="25">
@@ -38335,14 +38437,14 @@
       <c r="F5" s="20">
         <v>6</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" t="s" s="0">
         <v>92</v>
       </c>
       <c r="H5" s="20">
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" t="s" s="0">
         <v>93</v>
       </c>
       <c r="J5" s="20">
@@ -38480,10 +38582,10 @@
       <c r="AT5" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AU5" t="s" s="0">
         <v>150</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AV5" t="s" s="0">
         <v>151</v>
       </c>
       <c r="AW5" s="25">
@@ -38524,10 +38626,10 @@
       <c r="BL5" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BM5" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BN5" t="s" s="0">
         <v>97</v>
       </c>
       <c r="BO5" s="25">
@@ -38561,14 +38663,14 @@
       <c r="F6" s="20">
         <v>9</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H6" s="20">
         <f t="shared" si="0"/>
         <v>450</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" t="s" s="0">
         <v>101</v>
       </c>
       <c r="J6" s="20">
@@ -38706,10 +38808,10 @@
       <c r="AT6" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AU6" t="s" s="0">
         <v>153</v>
       </c>
-      <c r="AV6" t="s">
+      <c r="AV6" t="s" s="0">
         <v>154</v>
       </c>
       <c r="AW6" s="25">
@@ -38750,10 +38852,10 @@
       <c r="BL6" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM6" t="s">
+      <c r="BM6" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="BN6" t="s">
+      <c r="BN6" t="s" s="0">
         <v>105</v>
       </c>
       <c r="BO6" s="25">
@@ -39935,14 +40037,14 @@
   <dimension ref="A1:BQ20"/>
   <sheetFormatPr defaultColWidth="8.84761904761905" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="13" max="13" width="9.14285714285714" customWidth="1"/>
-    <col min="14" max="14" width="13.847619047619" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="28.0"/>
+    <col min="3" max="3" customWidth="true" width="23.0"/>
+    <col min="13" max="13" customWidth="true" width="9.14285714285714"/>
+    <col min="14" max="14" customWidth="true" width="13.847619047619"/>
     <col min="35" max="35" width="11.4285714285714"/>
     <col min="52" max="52" width="13.2857142857143"/>
-    <col min="64" max="64" width="11" customWidth="1"/>
-    <col min="67" max="67" width="12"/>
+    <col min="64" max="64" customWidth="true" width="11.0"/>
+    <col min="67" max="67" width="12.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -40341,14 +40443,14 @@
       <c r="F4" s="20">
         <v>3</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H4" s="20">
         <f t="shared" ref="H4:H6" si="0">F4*G4</f>
         <v>150</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J4" s="20">
@@ -40486,10 +40588,10 @@
       <c r="AT4" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AU4" t="s" s="0">
         <v>147</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AV4" t="s" s="0">
         <v>148</v>
       </c>
       <c r="AW4" s="25">
@@ -40530,10 +40632,10 @@
       <c r="BL4" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>89</v>
       </c>
       <c r="BO4" s="25">
@@ -40567,14 +40669,14 @@
       <c r="F5" s="20">
         <v>12</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" t="s" s="0">
         <v>92</v>
       </c>
       <c r="H5" s="20">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" t="s" s="0">
         <v>93</v>
       </c>
       <c r="J5" s="20">
@@ -40712,10 +40814,10 @@
       <c r="AT5" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AU5" t="s" s="0">
         <v>150</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AV5" t="s" s="0">
         <v>151</v>
       </c>
       <c r="AW5" s="25">
@@ -40756,10 +40858,10 @@
       <c r="BL5" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BM5" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BN5" t="s" s="0">
         <v>97</v>
       </c>
       <c r="BO5" s="25">
@@ -40793,14 +40895,14 @@
       <c r="F6" s="20">
         <v>9</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" t="s" s="0">
         <v>100</v>
       </c>
       <c r="H6" s="20">
         <f t="shared" si="0"/>
         <v>450</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" t="s" s="0">
         <v>101</v>
       </c>
       <c r="J6" s="20">
@@ -40938,10 +41040,10 @@
       <c r="AT6" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AU6" t="s" s="0">
         <v>153</v>
       </c>
-      <c r="AV6" t="s">
+      <c r="AV6" t="s" s="0">
         <v>154</v>
       </c>
       <c r="AW6" s="25">
@@ -40982,10 +41084,10 @@
       <c r="BL6" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="BM6" t="s">
+      <c r="BM6" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="BN6" t="s">
+      <c r="BN6" t="s" s="0">
         <v>105</v>
       </c>
       <c r="BO6" s="25">
